--- a/artifacts/results/Ragas_Merged.xlsx
+++ b/artifacts/results/Ragas_Merged.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://outlookuga-my.sharepoint.com/personal/sm11926_uga_edu/Documents/evAutomationUpdated/artifacts/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{45EDF1FD-91B0-9042-BC2C-7513BB87A3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83730D15-B8A5-F24D-B885-5A9EB150392D}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{45EDF1FD-91B0-9042-BC2C-7513BB87A3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63AEDAA4-8E72-2646-9A5B-CBD29365F301}"/>
   <bookViews>
-    <workbookView xWindow="6920" yWindow="660" windowWidth="27640" windowHeight="21680" xr2:uid="{8EB8A2CD-A73C-6F43-92DE-B53E8E949054}"/>
+    <workbookView xWindow="14560" yWindow="660" windowWidth="20000" windowHeight="21680" xr2:uid="{8EB8A2CD-A73C-6F43-92DE-B53E8E949054}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="824">
   <si>
     <t>Question</t>
   </si>
@@ -691,6 +691,4002 @@
   </si>
   <si>
     <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 18.377506429s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-2.5-flash', 'location': 'global'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '18s'}]}}</t>
+  </si>
+  <si>
+    <t>List all companies located in Troup County and include their Category, EV Supply Chain Role, and Employment.</t>
+  </si>
+  <si>
+    <t>ADVICS Manufacturing Georgia LLC | Category: Tier 2/3 | EV Supply Chain Role: General Automotive | Employment: 150 Aspen Aerogels | Category: Tier 2/3 | EV Supply Chain Role: Materials | Employment: 414 Aurubis | Category: Tier 2/3 | EV Supply Chain Role: Materials | Employment: 400 Bonnell Aluminum | Category: Tier 2/3 | EV Supply Chain Role: General Automotive | Employment: 266 Denso Manufacturing Georgia | Category: Tier 2/3 | EV Supply Chain Role: General Automotive | Employment: 105 Joon Georgia, Inc. | Category: Tier 1 | EV Supply Chain Role: General Automotive | Employment: 900 Kumho Tire USA Inc. | Category: Tier 1 | EV Supply Chain Role: General Automotive | Employment: 730 Kyungshin America Corp. | Category: Tier 1 | EV Supply Chain Role: General Automotive | Employment: 700 Linde + Wiemann | Category: Tier 1 | EV Supply Chain Role: General Automotive | Employment: 515 NIFCO KTW America Corp. | Category: Tier 1 | EV Supply Chain Role: General Automotive | Employment: 300 PAI Industries Inc. | Category: Tier 1 | EV Supply Chain Role: General Automotive | Employment: 198 PPG Industries Inc. | Category: Tier 1 | EV Supply Chain Role: General Automotive | Employment: 120 Sejong Georgia LLC | Category: Tier 1 | EV Supply Chain Role: General Automotive | Employment: 90 Stryten Energy | Category: Tier 1 | EV Supply Chain Role: General Automotive | Employment: 50 TCI Powder Coatings | Category: OEM | EV Supply Chain Role: Vehicle Assembly | Employment: 3,000</t>
+  </si>
+  <si>
+    <t>**General Automotive**
+- **Bonnell Aluminum**
+  - Category: Tier 2/3
+  - Employment: 266
+- **PPG Industries Inc.**
+  - Category: Tier 1
+  - Employment: 120
+- **PAI Industries Inc.**
+  - Category: Tier 1
+  - Employment: 198
+- **Stryten Energy**
+  - Category: Tier 1
+  - Employment: 50
+**Materials**
+- **Aurubis**
+  - Category: Tier 2/3
+  - Employment: 400</t>
+  </si>
+  <si>
+    <t>To list all companies located in Troup County along with their Category, EV Supply Chain Role, and Employment, I would need specific data from an Excel workbook or a similar structured dataset. Since no such evidence is provided here, I can't give you exact details about the companies in Troup County.
+However, if you have this information available in a workbook or another source, you could filter for entries where "Location" equals "Troup County," and then extract columns related to "Category," "EV Supply Chain Role," and "Employment." This would provide you with the required details about each company. If you need help with Excel functions or formulas to achieve this, feel free to ask!</t>
+  </si>
+  <si>
+    <t>Here's a list of companies located in Troup County, along with their Category, EV Supply Chain Role, and Employment, based on the provided evidence:
+*   **Bonnell Aluminum:** Category: Tier 2/3, EV Supply Chain Role: General Automotive, Employment: 266
+*   **Aurubis:** Category: Tier 2/3, EV Supply Chain Role: Materials, Employment: 400
+*   **PAI Industries Inc.:** Category: Tier 1, EV Supply Chain Role: General Automotive, Employment: 198
+*   **Stryten Energy:** Category: Tier 1, EV Supply Chain Role: General Automotive, Employment: 50
+*   **ADVICS Manufacturing Georgia LLC:** Category: Tier 2/3, EV Supply Chain Role: General Automotive, Employment: 150
+*   **PPG Industries Inc.:** Category: Tier 1, EV Supply Chain Role: General Automotive, Employment: 120</t>
+  </si>
+  <si>
+    <t>I cannot answer this question. I do not have access to a workbook containing company information, locations, categories, EV supply chain roles, and employment numbers.</t>
+  </si>
+  <si>
+    <t>Here are the companies located in Troup County:
+*   **ADVICS Manufacturing Georgia LLC**
+    *   Category: Tier 2/3
+    *   EV Supply Chain Role: General Automotive
+    *   Employment: 150
+*   **Aurubis**
+    *   Category: Tier 2/3
+    *   EV Supply Chain Role: Materials
+    *   Employment: 400
+*   **Bonnell Aluminum**
+    *   Category: Tier 2/3
+    *   EV Supply Chain Role: General Automotive
+    *   Employment: 266
+*   **PAI Industries Inc.**
+    *   Category: Tier 1
+    *   EV Supply Chain Role: General Automotive
+    *   Employment: 198
+*   **PPG Industries Inc.**
+    *   Category: Tier 1
+    *   EV Supply Chain Role: General Automotive
+    *   Employment: 120
+*   **Stryten Energy**
+    *   Category: Tier 1
+    *   EV Supply Chain Role: General Automotive
+    *   Employment: 50</t>
+  </si>
+  <si>
+    <t>I cannot provide a list of companies located in Troup County with their Category, EV Supply Chain Role, and Employment without access to the specific workbook containing this information. My capabilities do not include browsing external files or databases.</t>
+  </si>
+  <si>
+    <t>Which counties have the highest number of Tier 1 suppliers? Return the county counts and the top 5 counties.</t>
+  </si>
+  <si>
+    <t>County counts: Troup County: 9 Gwinnett County: 6 Hall County: 5 Chatham County: 4 Floyd County: 4 Bartow County: 3 Bulloch County: 2 Carroll County: 2 Coweta County: 2 Dade County: 2 Davis County: 2 Effingham County: 2 Franklin County: 2 Fulton County: 2 Harris County: 2 Hart County: 2 Laurens County: 2 Meriwether County: 2 Whitfield County: 2 Appling County: 1 Bibb County: 1 Candler County: 1 Cherokee County: 1 Clarke County: 1 Cobb County: 1 Coffee County: 1 Crisp County: 1 Fannin County: 1 Fayette County: 1 Gordon County: 1 Grady County: 1 Haralson County: 1 Liberty County: 1 Newton County: 1 Pike County: 1 Polk County: 1 Richmond County: 1 Stephens County: 1 Walker County: 1 Walton County: 1 Top 5 counties: Troup County: 9 Gwinnett County: 6 Hall County: 5 Chatham County: 4 Floyd County: 4</t>
+  </si>
+  <si>
+    <t>Walton County: 1 (Jefferson Southern Corporation)
+Troup County: 2 (Joon Georgia, Inc., Kumho Tire USA Inc.)
+Cherokee County: 1 (JTEKT North America Corp.)
+Carroll County: 1 (Kautex Inc.)
+Effingham County: 1 (KTX America Corporation)
+Top 5 Counties:
+1. Walton County: 1
+2. Troup County: 2
+3. Cherokee County: 1
+4. Carroll County: 1
+5. Effingham County: 1</t>
+  </si>
+  <si>
+    <t>To answer which counties have the highest number of Tier 1 suppliers without specific workbook data, I'll provide a generalized approach based on common practices in supply chain management and business analytics:
+Typically, identifying the counties with the highest number of Tier 1 suppliers involves analyzing supplier distribution across different geographic regions. Here’s how you might go about it:
+1. **Data Collection**: Gather information on all Tier 1 suppliers including their locations (specifically county-level data).
+2. **Geographic Aggregation**: Group suppliers by county.
+3. **Count Suppliers per County**: Count the number of Tier 1 suppliers in each county.
+Without specific workbook data, I can't provide exact numbers or names of counties. However, based on general knowledge, here’s a hypothetical example:
+- **County A**: 250 Tier 1 suppliers
+- **County B**: 230 Tier 1 suppliers
+- **County C**: 200 Tier 1 suppliers
+- **County D**: 180 Tier 1 suppliers
+- **County E**: 170 Tier 1 suppliers
+This would mean that the top 5 counties with the highest number of Tier 1 suppliers are County A, County B, County C, County D, and County E.
+For an accurate answer tailored to your specific workbook data, you would need to follow similar steps using the actual supplier information provided in your Excel workbook.</t>
+  </si>
+  <si>
+    <t>The workbook evidence lists the following counties and the number of Tier 1 suppliers located in each:
+*   Cherokee County: 1 (JTEKT North America Corp.)
+*   Carroll County: 1 (Kautex Inc.)
+*   Effingham County: 1 (KTX America Corporation)
+*   Troup County: 2 (Joon Georgia, Inc., Kumho Tire USA Inc.)
+*   Walton County: 1 (Jefferson Southern Corporation)
+*   Bartow County: 1 (Lear Corporation)
+The evidence is incomplete and does not provide a full list of all Tier 1 suppliers or a comprehensive county-by-county count.</t>
+  </si>
+  <si>
+    <t>I am unable to answer the question because I do not have access to the relevant workbook data containing information about Tier 1 suppliers and their locations.</t>
+  </si>
+  <si>
+    <t>The workbook evidence is incomplete for this question. The available evidence lists the county for some Tier 1 suppliers but does not provide a complete list of all Tier 1 suppliers and their respective counties, nor does it provide counts of suppliers per county. Therefore, it is not possible to determine which counties have the highest number of Tier 1 suppliers or to list the top 5 counties based solely on the provided information.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 54.343064359s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-2.5-flash', 'location': 'global'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '54s'}]}}</t>
+  </si>
+  <si>
+    <t>Show all companies located in Gwinnett County and include their Industry Group and Product / Service.</t>
+  </si>
+  <si>
+    <t>Arising Industries Inc. | Industry Group: Chemicals and Allied Products | Product / Service: Rubber powders for tires Continental Tire the Americas LLC | Industry Group: Rubber and Miscellaneous Plastic Products | Product / Service: Automotive gaskets and parts, protective film applications Daesol Material Georgia, LLC | Industry Group: Rubber and Miscellaneous Plastic Products | Product / Service: Tires Grudem | Industry Group: Machinery Except Electrical | Product / Service: Sensors for mobile hydraulic applications Inalfa Roof Systems Inc. | Industry Group: Electronic and Other Electrical Equipment and Components | Product / Service: Automotive electronic safety systems MAT Heavy Duty | Industry Group: Transportation Equipment | Product / Service: Vehicle protection and interior comfort products Michelin Tread Technologies | Industry Group: Transportation Equipment | Product / Service: Ventvisors, hood shields, floor mats, automotive accessories Morgan Corp. | Industry Group: Transportation Equipment | Product / Service: Engine components, turbochargers, exhaust parts and other automotive parts Novelis Inc. | Industry Group: Transportation Equipment | Product / Service: Acoustic and thermally effective automotive components Propex Operating Co. LLC | Industry Group: Transportation Equipment | Product / Service: Ventvisors, hood shields, floor mats, automotive accessories QSR Inc. | Industry Group: Transportation Equipment | Product / Service: Functional aftermarket accessories for trucks and SUVs</t>
+  </si>
+  <si>
+    <t>**General Automotive**
+- **Arising Industries Inc.**
+  - Industry Group: Chemicals and Allied Products
+  - Product / Service: Rubber powders for tires
+- **MAT Heavy Duty**
+  - Industry Group: Transportation Equipment
+  - Product / Service: Vehicle protection and interior comfort products
+- **Continental Tire the Americas LLC**
+  - Industry Group: Rubber and Miscellaneous Plastic Products
+  - Product / Service: Automotive gaskets and parts, protective film applications
+- **Propex Operating Co. LLC**
+  - Industry Group: Transportation Equipment
+  - Product / Service: Ventvisors, hood shields, floor mats, automotive accessories
+**Charging Infrastructure**
+- **Morgan Corp.**
+  - Industry Group: Transportation Equipment
+  - Product / Service: Engine components, turbochargers, exhaust parts and other automotive parts</t>
+  </si>
+  <si>
+    <t>To provide a list of companies located in Gwinnett County along with their industry group and product/service details, I would need specific data from an Excel workbook or another structured dataset that contains this information. Since no such evidence is provided here, I can't give you the exact names and details of companies based on your request.
+However, if you have a list of companies in Gwinnett County with their industry groups and product/service descriptions, you could filter for entries where the location field matches "Gwinnett County" to get the desired information. If you need help structuring an Excel formula or filtering process, feel free to ask!</t>
+  </si>
+  <si>
+    <t>Here are the companies located in Gwinnett County, along with their Industry Group and Product / Service:
+*   **Arising Industries Inc.**, Industry Group: Chemicals and Allied Products, Product / Service: Rubber powders for tires
+*   **MAT Heavy Duty**, Industry Group: Transportation Equipment, Product / Service: Vehicle protection and interior comfort products
+*   **Continental Tire the Americas LLC**, Industry Group: Rubber and Miscellaneous Plastic Products, Product / Service: Automotive gaskets and parts, protective film applications
+*   **Morgan Corp.**, Industry Group: Transportation Equipment, Product / Service: Engine components, turbochargers, exhaust parts and other automotive parts
+*   **Grudem**, Industry Group: Machinery Except Electrical, Product / Service: Sensors for mobile hydraulic applications
+*   **Propex Operating Co. LLC**, Industry Group: Transportation Equipment, Product / Service: Ventvisors, hood shields, floor mats, automotive accessories</t>
+  </si>
+  <si>
+    <t>I am sorry, but I do not have access to the necessary information to fulfill this request. I need to be provided with the relevant Excel workbook to identify companies located in Gwinnett County and their Industry Group and Product/Service.</t>
+  </si>
+  <si>
+    <t>Companies located in Gwinnett County:
+*   **Arising Industries Inc.**
+    *   Industry Group: Chemicals and Allied Products
+    *   Product / Service: Rubber powders for tires
+*   **Continental Tire the Americas LLC**
+    *   Industry Group: Rubber and Miscellaneous Plastic Products
+    *   Product / Service: Automotive gaskets and parts, protective film applications
+*   **Grudem**
+    *   Industry Group: Machinery Except Electrical
+    *   Product / Service: Sensors for mobile hydraulic applications
+*   **MAT Heavy Duty**
+    *   Industry Group: Transportation Equipment
+    *   Product / Service: Vehicle protection and interior comfort products
+*   **Morgan Corp.**
+    *   Industry Group: Transportation Equipment
+    *   Product / Service: Engine components, turbochargers, exhaust parts and other automotive parts
+*   **Propex Operating Co. LLC**
+    *   Industry Group: Transportation Equipment
+    *   Product / Service: Ventvisors, hood shields, floor mats, automotive accessories</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 54.194550717s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '54s'}]}}</t>
+  </si>
+  <si>
+    <t>Identify all companies in Hall County and list their Primary Facility Type and EV / Battery Relevant status.</t>
+  </si>
+  <si>
+    <t>Boogook Industries | Primary Facility Type: Manufacturing Plant | EV / Battery Relevant: No DAS Corp. | Primary Facility Type: Manufacturing Plant | EV / Battery Relevant: Indirect GSC Steel Stamping LLC | Primary Facility Type: Manufacturing Plant | EV / Battery Relevant: Yes HELLA Automotive Sales Inc. | Primary Facility Type: Manufacturing Plant | EV / Battery Relevant: No Lark United Manufacturing Inc. | Primary Facility Type: Manufacturing Plant | EV / Battery Relevant: Indirect Mobis Alabama LLC | Primary Facility Type: Manufacturing Plant | EV / Battery Relevant: Indirect Nisshinbo Automotive Manufacturing Inc. | Primary Facility Type: Manufacturing Plant | EV / Battery Relevant: No Novelis Inc. | Primary Facility Type: Manufacturing Plant | EV / Battery Relevant: Indirect Rivian Automotive | Primary Facility Type: Manufacturing Plant | EV / Battery Relevant: No</t>
+  </si>
+  <si>
+    <t>There are no companies listed in Hall County based on the provided evidence.</t>
+  </si>
+  <si>
+    <t>To identify all companies in Hall County along with their Primary Facility Type and EV/Battery Relevant status, I would need specific data from an Excel workbook or another detailed source that contains this information. Since no such evidence is provided here, I can't list exact company names, types, and statuses.
+However, if you have a dataset similar to what's described, the process typically involves filtering for entries related to Hall County and then extracting the relevant columns (Company Name, Primary Facility Type, EV/Battery Relevant status) from that filtered data. If you could provide more details or an example of the data structure, I can give a more precise answer based on general knowledge and common practices in handling such datasets.</t>
+  </si>
+  <si>
+    <t>There are no companies listed in Hall County in the provided evidence.</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the relevant Excel workbook containing company information, facility types, and EV/battery relevance status for Hall County. My knowledge is based on general information and I cannot provide specific details from a data source I don't have.</t>
+  </si>
+  <si>
+    <t>There are no companies in Hall County in the provided evidence.</t>
+  </si>
+  <si>
+    <t>I cannot identify all companies in Hall County and list their Primary Facility Type and EV / Battery Relevant status without access to the specific workbook data. This information is contained within the workbook you are referencing.</t>
+  </si>
+  <si>
+    <t>Which cities have both Tier 1 and Tier 2/3 companies present? Provide the city names and the matching companies.</t>
+  </si>
+  <si>
+    <t>Athens: Tier 1 = Sewon America Inc. | Tier 2/3 = Goodyear Tire &amp; Rubber Co. Atlanta: Tier 1 = SRG Global Inc.; Sewon America Inc. | Tier 2/3 = Elan Technology Inc. Augusta: Tier 1 = Magna International | Tier 2/3 = Bridgestone Bandag; Duckyang; EVCO Plastics Buchanan: Tier 1 = Lyle Industries Inc. | Tier 2/3 = Decostar Industries Calhoun: Tier 1 = Racemark International LLC | Tier 2/3 = ACM Georgia LLC; ALBAform Inc.; DeKalb Tool &amp; Die Inc. Canton: Tier 1 = JTEKT North America Corp. | Tier 2/3 = Blue Ridge Manufacturing Carnesville: Tier 1 = Pirelli Tire North America LLC; SKF USA Inc. | Tier 2/3 = Freudenberg-NOK Cartersville: Tier 1 = Lear Corporation; Panasonic Automotive Systems Co.; Panduit Corp. | Tier 2/3 = Constellium Automotive USA; Down 2 Earth Trailers; Eaton Corp. Covington: Tier 1 = Murata Electronics North America Inc. | Tier 2/3 = DAEHAN Solution Georgia LLC; Daimler Truck North America; Enplas USA Inc.; FOX Factory Dalton: Tier 1 = Nile Automotive; Oneda Corp. | Tier 2/3 = Ajin Georgia; Anovion Technologies Dublin: Tier 1 = Mando America Corp.; SHIROKI North America Inc | Tier 2/3 = GLOVIS Georgia LLC Gainesville: Tier 1 = Lark United Manufacturing Inc.; Mobis Alabama LLC; Nisshinbo Automotive Manufacturing Inc.; Novelis Inc.; Rivian Automotive | Tier 2/3 = Boogook Industries; DAS Corp.; GSC Steel Stamping LLC; HELLA Automotive Sales Inc. Hinesville: Tier 1 = Panasonic Automotive Systems Co. | Tier 2/3 = Die-Tech Industries Inc. Lawrenceville: Tier 1 = MAT Heavy Duty; Michelin Tread Technologies; Morgan Corp.; Novelis Inc.; Propex Operating Co. LLC; QSR Inc. | Tier 2/3 = Arising Industries Inc.; Continental Tire the Americas LLC; Daesol Material Georgia, LLC; Grudem Macon: Tier 1 = Seoyon E-Hwa Interior Systems | Tier 2/3 = Arising Industries Inc.; SungEel Recycling Park Georgia Marietta: Tier 1 = Sewon America Inc. | Tier 2/3 = Daesol Ausys; FREYR Battery Monroe: Tier 1 = Jefferson Southern Corporation | Tier 2/3 = Big Tex Trailer Manufacturing Inc. Rome: Tier 1 = Lehigh Technologies Inc.; Lyle Industries Inc.; PIOLAX Corp.; Pak-Lite Inc. | Tier 2/3 = Bosal Industries Georgia; Ecoplastic Corporation; Global Powertrain Systems LLC Statesboro: Tier 1 = Lund International Inc./Ventshade Division; Peerless-Winsmith Inc. | Tier 2/3 = Aptiv; Ascend Elements</t>
+  </si>
+  <si>
+    <t>The provided evidence does not contain any Tier 1 companies, so there are no cities listed with both Tier 1 and Tier 2/3 companies present based on the given data. The evidence only includes Tier 2/3 companies.</t>
+  </si>
+  <si>
+    <t>To directly answer your question based on general knowledge without specific workbook evidence, I can't provide exact city names and company lists. However, typically in business contexts, major metropolitan areas like New York City, London, Tokyo, or Shanghai often have both Tier 1 (leading global firms) and Tier 2/3 companies (regional players or smaller specialized firms) present.
+For example:
+- **New York City**: Might include a Tier 1 company such as Goldman Sachs alongside a Tier 2/3 firm like a regional investment bank.
+- **London**: Could have HSBC (Tier 1) and a local boutique financial services provider (Tier 2/3).
+- **Tokyo**: May feature Mitsubishi UFJ Financial Group (Tier 1) along with smaller, specialized finance companies (Tier 2/3).
+Without specific workbook data, I can't provide precise company names or city lists. If you have particular cities and company tiers in mind from your workbook, please share more details for a tailored response.</t>
+  </si>
+  <si>
+    <t>The workbook evidence does not contain information about cities with both Tier 1 and Tier 2/3 companies. It only lists companies categorized as either Tier 1 or Tier 2/3.
+The following companies are listed by EV Supply Chain Role:
+**Charging Infrastructure:** Morgan Corp.
+**General Automotive:** ACM Georgia LLC, ADVICS Manufacturing Georgia LLC, ALBAform Inc., AVS, Adient, Ajin Georgia, Anovion Technologies, Apache Mills Inc. + 111 more companies
+**Materials:** Ascend Elements, Aspen Aerogels, Aurubis, Beaver Manufacturing Co. Inc., Blue Bird Corp., Blue Ridge Manufacturing, Boogook Industries, Bosch (Automotive Division) + 15 more companies
+**Power Electronics:** GSC Steel Stamping LLC
+**Thermal Management:** Freudenberg-NOK, Novelis Inc., Peerless-Winsmith Inc.</t>
+  </si>
+  <si>
+    <t>I am sorry, but I do not have access to the necessary information to answer your question. I need the Excel workbook to identify the cities with both Tier 1 and Tier 2/3 companies and the corresponding company names.</t>
+  </si>
+  <si>
+    <t>The provided evidence does not contain information about cities that have both Tier 1 and Tier 2/3 companies present. The evidence lists companies and their categories (Tier 1 or Tier 2/3) and their locations, but it does not cross-reference to identify cities with both categories.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 53.361014719s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '53s'}]}}</t>
+  </si>
+  <si>
+    <t>List all companies with Primary Facility Type = Headquarters (including North American</t>
+  </si>
+  <si>
+    <t>Based on the provided evidence, the companies with the Primary Facility Type as "Headquarters" (including "North American Headquarters") are:
+1. **TI Fluid Systems**
+   - Location: Atlanta, Fulton County
+   - Employment: 19,600
+   - Industry Group: Passenger vehicles (EV + ICE)
+   - EV Supply Chain Role: OEM corporate footprint influencing EV strategy
+2. **Tie Down Engineering**
+   - Location: Greensboro, Greene County
+   - Employment: 2,000
+   - Industry Group: Heavy-duty trucks
+   - EV Supply Chain Role: OEM corporate and engineering footprint (electrification)
+3. **Minebea AccessSolutions USA Inc.**
+   - Location: Atlanta, Fulton County
+   - Employment: 400
+   - Industry Group: Transportation Equipment
+   - EV Supply Chain Role: General Automotive
+The evidence does not provide information about other companies with the Primary Facility Type as Headquarters.</t>
+  </si>
+  <si>
+    <t>generated</t>
+  </si>
+  <si>
+    <t>### Companies with Primary Facility Type = Headquarters (including North American Headquarters)
+**OEM corporate footprint influencing EV strategy**
+- TI Fluid Systems  
+  - Location: Atlanta, Fulton County  
+  - Employment: 19600  
+**General Automotive**
+- Minebea AccessSolutions USA Inc.  
+  - Location: Atlanta, Fulton County  
+  - Employment: 400</t>
+  </si>
+  <si>
+    <t>To list all companies with a Primary Facility Type of "Headquarters" in an Excel workbook, you would typically filter or sort the data based on that specific criterion. Since no actual workbook is provided here and I don't have access to any specific dataset, I can only provide a general approach:
+1. Open your Excel workbook.
+2. Navigate to the sheet containing company information.
+3. Use the filter function (usually found under the Data tab) to select "Headquarters" in the column labeled as Primary Facility Type or similar.
+Without having the actual data, I cannot list specific companies. However, if you follow these steps with your dataset, you should be able to identify all entries where the company's primary facility is designated as a headquarters. If you need further assistance with Excel functions or formulas for this task, feel free to ask!</t>
+  </si>
+  <si>
+    <t>The following companies have a Primary Facility Type of Headquarters (including North American Headquarters):
+*   Minebea AccessSolutions USA Inc. (Atlanta, Fulton County) - EV Supply Chain Role: General Automotive, Employment: 400
+*   TI Fluid Systems (Atlanta, Fulton County) - EV Supply Chain Role: OEM corporate footprint influencing EV strategy, Employment: 19600</t>
+  </si>
+  <si>
+    <t>I am sorry, but I do not have access to the workbook to answer your question.</t>
+  </si>
+  <si>
+    <t>* Minebea AccessSolutions USA Inc. (EV Supply Chain Role: General Automotive)
+* TI Fluid Systems (EV Supply Chain Role: OEM corporate footprint influencing EV strategy)
+* Tie Down Engineering (EV Supply Chain Role: OEM corporate and engineering footprint (electrification))</t>
+  </si>
+  <si>
+    <t>I cannot list all companies with "Primary Facility Type = Headquarters" (including North American) because I do not have access to the specific workbook data. To provide an accurate list, I would need to query the workbook directly.</t>
+  </si>
+  <si>
+    <t>Headquarters) and include their Location and Employment.</t>
+  </si>
+  <si>
+    <t>Based on the provided evidence, here are the companies with their headquarters location and employment numbers:
+1. **Minebea AccessSolutions USA Inc.**
+   - Location: Atlanta, Fulton County
+   - Employment: 400
+2. **Tie Down Engineering**
+   - Location: Greensboro, Greene County
+   - Employment: 2000
+3. **TI Fluid Systems**
+   - Location: Atlanta, Fulton County
+   - Employment: 19,600
+The evidence does not provide information about other companies with headquarters in Georgia. The dataset focuses on automotive OEMs and suppliers with 50 or more employees operating in Georgia, but it does not include all such companies.</t>
+  </si>
+  <si>
+    <t>**North American Headquarters**
+- **Tie Down Engineering**
+  - Location: Greensboro, Greene County
+  - Employment: 2000
+**Headquarters (Other)**
+- **Minebea AccessSolutions USA Inc.**
+  - Location: Atlanta, Fulton County
+  - Employment: 400
+- **TI Fluid Systems**
+  - Location: Atlanta, Fulton County
+  - Employment: 19600</t>
+  </si>
+  <si>
+    <t>To answer questions about headquarters locations and employment numbers, I would need specific information from an Excel workbook or other detailed data source. Without such a reference, here's a general approach to how you might find this information:
+1. **Headquarters Location**: This is typically found in the "About Us" section of a company’s website, annual reports, or press releases. It can also be listed under corporate structure details within an Excel workbook that contains organizational data.
+2. **Employment Numbers**: Employment figures for headquarters are often detailed in financial statements, annual reports, or specific sections of an Excel workbook dedicated to human resources and organizational charts.
+If you have a particular company in mind, I could provide more tailored advice on how to find this information based on general knowledge about where such details are usually published.</t>
+  </si>
+  <si>
+    <t>Here are the companies with a Headquarters location and their Employment:
+*   Minebea AccessSolutions USA Inc., Location: Atlanta, Fulton County, Employment: 400
+*   Tie Down Engineering, Location: Greensboro, Greene County, Employment: 2000
+*   TI Fluid Systems, Location: Atlanta, Fulton County, Employment: 19600</t>
+  </si>
+  <si>
+    <t>Please provide the relevant Excel workbook data so I can answer your question about headquarters locations and employment numbers. I need the data to accurately identify the headquarters and their associated details.</t>
+  </si>
+  <si>
+    <t>**OEM (Footprint)**
+* **TI Fluid Systems** - Location: Atlanta, Fulton County; Employment: 19600
+* **Tie Down Engineering** - Location: Greensboro, Greene County; Employment: 2000
+**OEM**
+* **Minebea AccessSolutions USA Inc.** - Location: Atlanta, Fulton County; Employment: 400
+* **TDK Components USA Inc.** - Location: Atlanta, Fulton County; Employment: 1000</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 44.018684217s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '44s'}]}}</t>
+  </si>
+  <si>
+    <t>Which companies have Primary Facility Type = R&amp;D, and what EV Supply Chain Role are they associated with?</t>
+  </si>
+  <si>
+    <t>R&amp;D [1]: Racemark International LLC | EV Supply Chain Role: General Automotive | Location: Calhoun, Gordon County | Employment: 120</t>
+  </si>
+  <si>
+    <t>Racemark International LLC, R&amp;D | General Automotive</t>
+  </si>
+  <si>
+    <t>Based on my knowledge without specific workbook data, companies that have a "Primary Facility Type" of R&amp;D (Research and Development) typically engage in activities such as product development, innovation, and technological advancement. The exact EV Supply Chain Roles these companies might be associated with can vary widely depending on their specific focus within the electric vehicle industry.
+For example:
+- Companies focused on battery technology research would likely have an "EV Supply Chain Role" related to Battery Manufacturing.
+- Those involved in developing new materials for use in EV components could have a role such as Material Supplier or Component Manufacturer.
+- Research firms that specialize in software and electronics might be categorized under Software Development or Electronics Manufacturing.
+Without specific workbook data, I cannot provide exact company names or roles. If you can share more details about the companies or the structure of your workbook, I would be able to give a more precise answer.</t>
+  </si>
+  <si>
+    <t>Racemark International LLC has a Primary Facility Type of R&amp;D and an EV Supply Chain Role of General Automotive.</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the relevant workbook data. The question asks for specific information about companies, their facility types, and their EV supply chain roles, which can only be determined from the data within the workbook.</t>
+  </si>
+  <si>
+    <t>Racemark International LLC has a Primary Facility Type of R&amp;D and is associated with the EV Supply Chain Role of General Automotive.</t>
+  </si>
+  <si>
+    <t>ERROR: 400 INVALID_ARGUMENT. {'error': {'code': 400, 'message': 'API key expired. Please renew the API key.', 'status': 'INVALID_ARGUMENT', 'details': [{'@type': 'type.googleapis.com/google.rpc.ErrorInfo', 'reason': 'API_KEY_INVALID', 'domain': 'googleapis.com', 'metadata': {'service': 'generativelanguage.googleapis.com'}}, {'@type': 'type.googleapis.com/google.rpc.LocalizedMessage', 'locale': 'en-US', 'message': 'API key expired. Please renew the API key.'}]}}</t>
+  </si>
+  <si>
+    <t>Show all Manufacturing Plant (or Manufacturing plant) entries and group them by Industry Group.</t>
+  </si>
+  <si>
+    <t>Manufacturing Plant / Manufacturing plant entries grouped by Industry Group: Automotive components [1]: Voestalpine Automotive Body Parts Inc. Automotive modules and components [1]: Vista Metals Corp. Automotive parts manufacturing [1]: Valeo Automotive plastic components [1]: Wabash National Corp. Automotive plastics [1]: Volvo Cars USA Automotive precision components [1]: Trenton Pressing Inc. Automotive stamping and assemblies [1]: Vernay Automotive structural components [1]: Vanguard National Trailer Corp. Automotive textiles and interiors [1]: Wheelabrator Group Inc. Chemicals and Allied Products [3]: Aptiv; Archer Aviation Inc.; Arising Industries Inc. Electronic and Other Electrical Equipment and Components [16]: Hitachi Astemo; Hitachi Astemo Americas Inc.; Hollingsworth &amp; Vose Co.; Honda Development &amp; Manufacturing; Hwashin; Hyundai &amp; LG Energy Solution (LGES); Hyundai Industrial Co.; Hyundai MOBIS (Georgia); Hyundai Motor Group; Hyundai Transys Georgia Powertrain; Hyundai Transys Georgia Seating Systems; IMMI; IMS Gear Georgia Inc.; Inalfa Roof Systems Inc.; JAC Products Inc.; Jefferson Southern Corp. Fabricated Metal Products [12]: FOX Factory; FREYR Battery; Flambeau Inc.; Fouts Brothers Fire Equipment; Freudenberg-NOK; Freudenberg-NOK; GEDIA Georgia LLC; GLOVIS Georgia LLC; Global Powertrain Systems LLC; Goodyear Tire &amp; Rubber Co.; Great Dane LP; Great Dane Trailers Machinery Except Electrical [7]: GSC Steel Stamping LLC; Grudem; HELLA Automotive Sales Inc.; HEXPOL Compounding Corp.; Haering Precision USA LP; Haering Precision USA LP; Hanon Systems USA LLC Metal stamping and assemblies [1]: Volvo Group North America Miscellaneous Manufacturing Industries [1]: SungEel Recycling Park Georgia Paper and Allied Products [1]: Apache Mills Inc. Primary Metal Industries [16]: Dinex Emissions Inc.; Dongwon Autopart Technology Georgia LLC; Dorsett Industries Inc.; Down 2 Earth Trailers; Duckyang; EVCO Plastics; Eaton Corp.; Ecoplastic America Corporation; Ecoplastic Corporation; Elan Technology Inc.; Enchem America Inc.; Enplas USA Inc.; Erdrich USA Inc.; F&amp;P Georgia Manufacturing; Fanello Industries Inc.; First American Resources Rubber and Miscellaneous Plastic Products [28]: AVS; Arising Industries Inc.; Ascend Elements; Aspen Aerogels; Aurubis; Beaver Manufacturing Co. Inc.; Big Tex Trailer Manufacturing Inc.; Blue Bird Corp.; Blue Ridge Manufacturing; Bonnell Aluminum; Boogook Industries; Bosal Industries Georgia; Bosch (Automotive Division); Bridgestone Bandag; Carcoustics USA; Club Car LLC; Constellium Automotive USA; Continental Automotive; Continental Tire the Americas LLC; DAEHAN Solution Georgia LLC; DAS Corp.; DaeChang Seat Company; Daesol Ausys; Daesol Material Georgia, LLC; Daimler Truck North America; DeKalb Tool &amp; Die Inc.; Decostar Industries; Denkai America Stone, Clay, Glass and Concrete Products [2]: Denso Manufacturing Georgia; Die-Tech Industries Inc. Textile Products [6]: ACM Georgia LLC; ADVICS Manufacturing Georgia LLC; ALBAform Inc.; Adient; Ajin Georgia; Anovion Technologies Transportation Equipment [87]: JTEKT North America Corp.; Jefferson Southern Corporation; Joon Georgia, Inc.; KTX America Corporation; Kautex Inc.; Kia Georgia Inc.; Kumho Tire USA Inc.; Kyungshin America Corp.; Lark United Manufacturing Inc.; Lear Corporation; Lehigh Technologies Inc.; Linde + Wiemann; Lund International Inc.; Lund International Inc./Ventshade Division; Lyle Industries Inc.; Lyle Industries Inc.; MAT Heavy Duty; Mack Trucks; Magna International; Mando America Corp.; Master Craft Engineering Inc.; Maxxis International USA; Mercedes-Benz USA LLC; Michelin Tread Technologies; Milliken &amp; Co./Valway Plant; Mobis Alabama LLC; MollerTech LLC; Morgan Corp.; Murata Electronics North America Inc.; NIFCO KTW America Corp.; NVH Korea; Neaton Rome Inc.; Nidec Elesys Americas Corp.; Nile Automotive; Nisshinbo Automotive Manufacturing Inc.; Nivel Parts &amp; Manufacturing Co. LLC; Novelis Inc.; Novelis Inc.; Novelis Inc.; OTR Wheel Engineering Inc.; Oneda Corp.; PAI Industries Inc.; PHA Body Systems LLC; PIOLAX Corp.; PPG Industries Inc.; Paccar; Pak-Lite Inc.; Panasonic Automotive Systems Co.; Panasonic Automotive Systems Co.; Panduit Corp.; Peerless-Winsmith Inc.; Perkins Small Engines LLC; Peterson Spring; Piedmont Automotive Products Inc.; Pirelli Tire North America LLC; Porsche Cars North America Inc.; Propex Operating Co. LLC; QSR Inc.; RealTruck; Rivian Automotive; Robert Bosch LLC; SAFT America Inc.; SHIROKI North America Inc; SK Battery America; SKF USA Inc.; SRG Global Inc.; Sejong Georgia LLC; Seohan Auto USA; Seoyon E-HWA; Seoyon E-Hwa Interior Systems; Sewon America Inc.; Sewon America Inc.; Sewon America Inc.; Solvay Specialty Polymers USA LLC; Southern Switches Corp.; Stryten Energy; Suhner Manufacturing Corp.; Sumitomo Electric Wiring Systems; Superior Essex Inc.; Suzuki Manufacturing of America Corp.; TCI Powder Coatings; TDK Components USA Inc.; TE Connectivity; Teklas USA; Textron Specialized Vehicles; Thermal Ceramics Inc.; Thomson Plastics Inc.</t>
+  </si>
+  <si>
+    <t>**Transportation Equipment**
+- Teklas USA
+**Automotive plastic components**
+- Wabash National Corp.
+**Automotive textiles and interiors**
+- Wheelabrator Group Inc.
+**Automotive modules and components**
+- Vista Metals Corp.
+**Primary Metal Industries**
+- Ecoplastic Corporation
+**Automotive stamping and assemblies**
+- Vernay
+**Commercial vehicles and powertrains**
+- Toyota Industries Group (TACG-TICA)
+**Automotive precision components**
+- Trenton Pressing Inc.</t>
+  </si>
+  <si>
+    <t>To group Manufacturing Plant entries by Industry Group without specific workbook data, I'll outline a generic approach you would take in Excel:
+1. **Ensure Data is Clean**: Make sure your dataset includes columns for "Plant Name" or similar (indicating the manufacturing plant) and another column for "Industry Group".
+2. **Filter Manufacturing Plants**:
+   - Use a filter to select rows where the Plant Name contains "Manufacturing Plant". This can be done using Excel's Filter feature or by applying an IF statement in combination with filtering.
+3. **Grouping Data**:
+   - With your filtered data, you can use Excel’s PivotTable feature.
+   - Select your filtered range and insert a PivotTable.
+   - Drag the "Industry Group" field to the Rows area of the PivotTable.
+   - Drag the "Plant Name" or similar field to the Values area. You might need to change the value setting from Count to something like "Distinct Count" if you want to count unique plants.
+4. **Review and Adjust**:
+   - Review your PivotTable to ensure it accurately reflects all Manufacturing Plant entries grouped by Industry Group.
+   - Make any necessary adjustments in terms of sorting, additional filters, or adding more fields as needed for a comprehensive view.
+This approach will give you an overview of how many manufacturing plants exist within each industry group. If you have specific data requirements or need further customization, feel free to ask!</t>
+  </si>
+  <si>
+    <t>Here's a list of Manufacturing Plant entries, grouped by Industry Group:
+**Transportation Equipment**
+*   Teklas USA (Vehicle Assembly)
+**Automotive plastic components**
+*   Wabash National Corp. (Interior and exterior plastic parts)
+**Automotive textiles and interiors**
+*   Wheelabrator Group Inc. (Interior trim and textile components)
+**Automotive modules and components**
+*   Vista Metals Corp. (EV and ICE component manufacturing)
+**Primary Metal Industries**
+*   Ecoplastic Corporation (General Automotive)
+**Automotive stamping and assemblies**
+*   Vernay (Stamped and welded assemblies for OEMs)
+**Commercial vehicles and powertrains**
+*   Toyota Industries Group (TACG-TICA) (OEM parent group footprint (electric truck strategy))
+**Automotive precision components**
+*   Trenton Pressing Inc. (Machined components supporting EV and ICE vehicles)</t>
+  </si>
+  <si>
+    <t>Without access to the Excel workbook, I cannot provide a definitive list of Manufacturing Plant entries grouped by Industry Group. However, generally, you would expect to find Manufacturing Plants categorized under industry groups like:
+*   **Aerospace &amp; Defense**
+*   **Automotive**
+*   **Chemicals**
+*   **Electronics**
+*   **Food &amp; Beverage**
+*   **Machinery**
+*   **Pharmaceuticals**
+*   **Plastics &amp; Rubber**
+*   **Textiles**
+The specific Industry Groups used would depend on the classification system employed in the workbook.</t>
+  </si>
+  <si>
+    <t>**Automotive plastic components**
+* Wabash National Corp. (EV Supply Chain Role: Interior and exterior plastic parts)
+**Automotive textiles and interiors**
+* Wheelabrator Group Inc. (EV Supply Chain Role: Interior trim and textile components)
+**Automotive modules and components**
+* Vista Metals Corp. (EV Supply Chain Role: EV and ICE component manufacturing)
+**Automotive stamping and assemblies**
+* Vernay (EV Supply Chain Role: Stamped and welded assemblies for OEMs)
+**Automotive precision components**
+* Trenton Pressing Inc. (EV Supply Chain Role: Machined components supporting EV and ICE vehicles)
+**Primary Metal Industries**
+* Ecoplastic Corporation (EV Supply Chain Role: General Automotive)
+**Transportation Equipment**
+* Teklas USA (EV Supply Chain Role: Vehicle Assembly)</t>
+  </si>
+  <si>
+    <t>I cannot access external workbooks or their content, including any "Manufacturing Plant" entries or "Industry Group" classifications within them. Therefore, I cannot show or group them as requested.</t>
+  </si>
+  <si>
+    <t>Among companies with Primary Facility Type containing 'Corporate operations', which ones are EV / Battery Relevant = Yes?</t>
+  </si>
+  <si>
+    <t>Primary Facility Type containing 'Corporate operations' and EV / Battery Relevant = Yes [3]: TN Americas Holding Inc. | Facility Type: Corporate operations | Location: Georgia | EV Supply Chain Role: OEM parent group footprint (EV + HD electrification) Toyota Industries Group (TACG-TICA) | Facility Type: Corporate operations | Location: Georgia | EV Supply Chain Role: OEM parent group footprint (electric truck strategy) Trenton Pressing | Facility Type: Regional corporate operations | Location: Georgia | EV Supply Chain Role: OEM corporate footprint and supplier integration</t>
+  </si>
+  <si>
+    <t>**OEM parent group footprint (EV + HD electrification):**
+- TN Americas Holding Inc.
+**OEM parent group footprint (electric truck strategy):**
+- Toyota Industries Group (TACG-TICA)
+**OEM corporate footprint and supplier integration:**
+- Trenton Pressing</t>
+  </si>
+  <si>
+    <t>Based on the information provided in your question, without specific data from an Excel workbook or additional context, I cannot provide a precise list of company names. However, generally speaking, if you're looking for companies with "Primary Facility Type" containing 'Corporate operations' and are also marked as EV / Battery Relevant = Yes, you would need to filter the dataset accordingly.
+To find these companies:
+1. Filter the data where the Primary Facility Type column contains 'Corporate operations'.
+2. From those filtered results, further narrow down to entries where EV / Battery Relevant is set to Yes.
+Without specific workbook details or a dataset provided, I can't give you exact company names but this process should help you identify such companies if you have access to the relevant data.</t>
+  </si>
+  <si>
+    <t>TN Americas Holding Inc., Toyota Industries Group (TACG-TICA).</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the relevant Excel workbook. The question requires filtering companies based on two specific criteria ('Corporate operations' in Primary Facility Type and 'Yes' for EV / Battery Relevance), which can only be determined by examining the data within the workbook.</t>
+  </si>
+  <si>
+    <t>* **TN Americas Holding Inc.**
+  * EV Supply Chain Role: OEM parent group footprint (EV + HD electrification)
+* **Toyota Industries Group (TACG-TICA)**
+  * EV Supply Chain Role: OEM parent group footprint (electric truck strategy)
+* **Trenton Pressing**
+  * EV Supply Chain Role: OEM corporate footprint and supplier integration
+* **Yazaki North America**
+  * EV Supply Chain Role: Power electronics, sensors, and EV systems</t>
+  </si>
+  <si>
+    <t>I cannot answer this question without access to the workbook. The question asks for specific information about companies within the workbook, including their "Primary Facility Type" and "EV / Battery Relevant" status.</t>
+  </si>
+  <si>
+    <t>Identify companies with Primary Facility Type containing both Engineering and Manufacturing, and list their Product / Service.</t>
+  </si>
+  <si>
+    <t>Primary Facility Type containing both Engineering and Manufacturing [3]: WIKA USA | Facility Type: Manufacturing / Engineering | Product / Service: Vehicle power &amp; data solutions; wiring harnesses and connectors Woory Industrial Co. | Facility Type: Manufacturing / Engineering | Product / Service: Automotive connectors, terminals, sensors, and power/data components Yamaha Motor Manufacturing Corp. | Facility Type: Engineering / Manufacturing | Product / Service: Automotive electrical architecture, connectivity, and advanced safety components</t>
+  </si>
+  <si>
+    <t>The provided evidence does not contain any companies with a Primary Facility Type containing both Engineering and Manufacturing. The evidence only lists companies with either one type or another, but no combination of both types is present. Therefore, there are no matches to list based on the given criteria.</t>
+  </si>
+  <si>
+    <t>To identify companies with a primary facility type that includes both "Engineering" and "Manufacturing," we would typically look for entries in an Excel workbook or database where the company's primary facility type is described as having both these aspects. Since no specific workbook data has been provided, I can't list exact companies or their products/services.
+However, generally speaking, such companies might include those involved in high-tech manufacturing industries like aerospace, automotive, electronics, and machinery. These firms often have integrated engineering and manufacturing capabilities to design and produce complex products efficiently.
+For a precise answer, you would need to filter the data based on the criteria mentioned (Primary Facility Type containing both "Engineering" and "Manufacturing") and then list out the corresponding companies along with their Product / Service details from your dataset.</t>
+  </si>
+  <si>
+    <t>There are no companies listed with a Primary Facility Type containing both Engineering and Manufacturing. The evidence lists companies with either Manufacturing Plant or Regional corporate operations or Corporate operations as their Primary Facility Type.
+Trenton Pressing: Truck OEM footprint &amp; parts/distribution operations (PACCAR network)
+Haering Precision USA LP: Tools and dies for automotive industry
+Ecoplastic Corporation: Flexible shafts for automotive transmissions
+Wabash National Corp.: Automotive parts contract manufacturing (assemblies/components)
+Trenton Pressing Inc.: Precision-machined powertrain components (engine/transmission/drivetrain parts)
+Toyota Industries Group (TACG-TICA): Commercial trucks (Freightliner/Western Star) &amp; zero-emission truck programs
+Aptiv: Aerogel-based sustainability and electrification solutions
+Adient: Backing for automotive carpets and other auto related applications</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the Excel workbook. The question requires identifying companies based on the "Primary Facility Type" column and then listing their "Product / Service," which are both data points contained within the workbook.</t>
+  </si>
+  <si>
+    <t>The provided workbook evidence does not contain any companies with a 'Primary Facility Type' that includes both "Engineering" and "Manufacturing".</t>
+  </si>
+  <si>
+    <t>I cannot identify companies with specific facility types and list their products/services without access to the workbook data. This information is typically found within a company's profile or facility details in a database.</t>
+  </si>
+  <si>
+    <t>For each Primary Facility Type, compute the average Employment.</t>
+  </si>
+  <si>
+    <t>Average Employment by Primary Facility Type: Engineering / Manufacturing [n=1]: 190000.00 Engineering / Operations [n=3]: 175419.67 Manufacturing / Engineering [n=2]: 168500.00 Manufacturing [n=4]: 90714.25 Corporate operations [n=2]: 18850.00 North American Headquarters [n=2]: 10800.00 Manufacturing plant [n=10]: 637.50 Manufacturing Plant [n=179]: 402.18 Headquarters [n=1]: 400.00 Regional corporate operations [n=1]: 350.00 R&amp;D [n=1]: 120.00 Manufacturing / OEM operations [n=1]: 80.00</t>
+  </si>
+  <si>
+    <t>For each Primary Facility Type, the average Employment is as follows:
+Manufacturing Plant:
+- Blue Bird Corp.: 275
+- Bosch (Automotive Division): 250
+- DaeChang Seat Company: 135
+- Daesol Ausys: 97
+- Denkai America: 50
+- GLOVIS Georgia LLC: 90
+- Peterson Spring: 150
+- Continental Tire the Americas LLC: 150
+Average Employment for Manufacturing Plant:
+(275 + 250 + 135 + 97 + 50 + 90 + 150 + 150) / 8 = 164.375</t>
+  </si>
+  <si>
+    <t>To calculate the average employment for each primary facility type, you would typically follow these steps:
+1. **Group Data by Primary Facility Type**: Organize all entries in your dataset according to their respective primary facility types.
+2. **Sum Employment Numbers**: For each group (primary facility type), sum up the total number of employees across all facilities within that category.
+3. **Count Facilities**: Count how many different facilities belong to each primary facility type.
+4. **Calculate Average Employment**: Divide the total employment for a given primary facility type by the count of facilities in that type.
+The formula for calculating the average employment would be:
+\[ \text{Average Employment} = \frac{\sum(\text{Employment})}{\text{Number of Facilities}} \]
+Without specific data from an Excel workbook, I can't provide exact numbers. However, if you have a column for "Primary Facility Type" and another for "Employment," you could use Excel functions like `SUMIF`, `COUNTIF`, or pivot tables to perform these calculations efficiently.
+Would you need guidance on how to implement this in Excel?</t>
+  </si>
+  <si>
+    <t>Here's the average employment by Primary Facility Type, based on the provided evidence:
+Manufacturing Plant: 131.79</t>
+  </si>
+  <si>
+    <t>Okay, I can help you with that. To compute the average Employment for each Primary Facility Type, I would need to group the data by "Primary Facility Type" and then calculate the average of the "Employment" column for each of those groups.
+Without the actual data, I can't provide specific numerical results. However, the process would involve these steps in Excel:
+1.  **Sort:** Sort the data by "Primary Facility Type" to group similar facility types together.
+2.  **Pivot Table/Grouping:** Create a Pivot Table with "Primary Facility Type" as rows and "Employment" as values, configured to calculate the average. Alternatively, use Excel's grouping feature on the sorted data.
+3.  **Formula:** Use the `AVERAGEIF` function, where you specify the "Primary Facility Type" as the criteria.
+The resulting output would be a table or list showing each unique "Primary Facility Type" and its corresponding average employment number.</t>
+  </si>
+  <si>
+    <t>The average employment for Manufacturing Plant is 149.63.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 38.613611653s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '38s'}]}}</t>
+  </si>
+  <si>
+    <t>Which EV Supply Chain Role has the highest average Employment among Tier 1 suppliers?</t>
+  </si>
+  <si>
+    <t>Charging Infrastructure has the highest average Employment among Tier 1 suppliers: 320.00 (n=1). Companies: Morgan Corp.</t>
+  </si>
+  <si>
+    <t>Grouped by EV Supply Chain Role:
+- Charging Infrastructure: Morgan Corp. (Employment data not provided)
+- General Automotive: JTEKT North America Corp., Jefferson Southern Corporation, Joon Georgia, Inc., KTX America Corporation, Kumho Tire USA Inc., Lark United Manufacturing Inc., Kyungshin America Corp., PHA Body Systems LLC, Panasonic Automotive Systems Co., SK Battery America, Sumitomo Electric Wiring Systems (Employment data provided for some companies)
+- Materials: Novelis Inc., Peerless-Winsmith Inc. (Employment data not provided)
+The EV Supply Chain Role with the highest average Employment among Tier 1 suppliers based on available evidence is "General Automotive," as it has multiple companies listed, though exact average employment cannot be calculated without complete employment figures for all companies in this role.</t>
+  </si>
+  <si>
+    <t>Based on general knowledge without specific workbook data, roles in the electric vehicle (EV) supply chain that typically have high employment numbers among Tier 1 suppliers include manufacturing executives or managers. These roles oversee large teams involved in the production of critical EV components such as batteries, motors, and power electronics.
+However, to pinpoint which exact role has the highest average employment without specific data, it would be speculative. Typically, roles like "Manufacturing Manager" or "Production Supervisor" are likely candidates due to their direct involvement with large workforces on factory floors. For a precise answer, detailed employment statistics from Tier 1 EV suppliers would be necessary.</t>
+  </si>
+  <si>
+    <t>Charging Infrastructure has the highest average Employment among Tier 1 suppliers. The General Automotive role includes companies such as JTEKT North America Corp., Jefferson Southern Corporation, Joon Georgia, Inc., KTX America Corporation, Kautex Inc., Kumho Tire USA Inc., and Lear Corporation.</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I cannot definitively determine which EV Supply Chain Role has the highest average Employment among Tier 1 suppliers. However, based on general industry knowledge, roles involving battery manufacturing, such as **Battery Cell Manufacturing Technicians** or **Battery Pack Assembly Operators**, likely have the highest average employment numbers due to the critical nature and high volume of batteries required for electric vehicles.
+It's possible other roles like those in motor manufacturing or power electronics could also have high employment, but battery-related roles are generally the most labor-intensive.</t>
+  </si>
+  <si>
+    <t>The EV Supply Chain Role with the highest average employment among Tier 1 suppliers cannot be determined from the provided evidence, as the employment numbers are not available for all companies within each role, and a full list of companies for each role is not provided.
+However, based on the available evidence for Tier 1 suppliers, here are some companies and their employment numbers:
+*   **General Automotive:**
+    *   Jefferson Southern Corporation: 900
+    *   Joon Georgia, Inc.: 900
+    *   JTEKT North America Corp.: 860
+    *   Kautex Inc.: 800
+    *   KTX America Corporation: 740
+    *   Kumho Tire USA Inc.: 730
+    *   Lear Corporation: 590</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 38.50325019s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-2.5-flash', 'location': 'global'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '38s'}]}}</t>
+  </si>
+  <si>
+    <t>List Tier 2/3 suppliers with Employment &gt;= 500 and provide their Location and Product / Service.</t>
+  </si>
+  <si>
+    <t>Tier 2/3 suppliers with Employment &gt;= 500 [5]: Grudem | Location: Lawrenceville, Gwinnett County | Employment: 807 | Product / Service: Sensors for mobile hydraulic applications Flambeau Inc. | Location: Carroll County | Employment: 700 | Product / Service: Door locks, ignition locks, side mirrors and door handles SungEel Recycling Park Georgia | Location: Macon, Bibb County | Employment: 650 | Product / Service: Various fasteners for automotive seating and interior Fasteners, zippers, hook &amp; loop, pull straps, ISO-marker buttons, seat belt buttons, plastic hardware Arising Industries Inc. | Location: Macon, Bibb County | Employment: 582 | Product / Service: Automotive and aircraft tires Dinex Emissions Inc. | Location: Greensboro, Greene County | Employment: 500 | Product / Service: Aluminum sheet for automotive bodies</t>
+  </si>
+  <si>
+    <t>Tier 2/3 suppliers with Employment &gt;= 500:
+- General Automotive:
+  - Dinex Emissions Inc. | Location: Greensboro, Greene County | Product / Service: Aluminum sheet for automotive bodies</t>
+  </si>
+  <si>
+    <t>To list Tier 2/3 suppliers with employment of at least 500 employees along with their location and product/service, I would need specific data from an Excel workbook or a similar structured dataset. Since no such evidence is provided here, I can only suggest how to approach this task if you had the necessary information:
+1. **Filter Suppliers by Tier**: First, filter out suppliers that are either Tier 2 or Tier 3.
+2. **Employment Criteria**: From those filtered suppliers, further narrow down to companies with an employment number of at least 500 employees.
+3. **Gather Details**: For each supplier meeting the criteria above, collect their location and details about the products/services they provide.
+Without specific data, I cannot list exact names or details for these suppliers. If you have access to a relevant Excel workbook, applying these steps should help you identify the required information.</t>
+  </si>
+  <si>
+    <t>The following Tier 2/3 suppliers have Employment &gt;= 500:
+*   **Dinex Emissions Inc.**
+    *   Location: Greensboro, Greene County
+    *   EV Supply Chain Role: General Automotive
+    *   Product / Service: Aluminum sheet for automotive bodies</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question. I do not have access to the Excel workbook containing supplier information, including their tier, employment numbers, locations, and product/service offerings. Therefore, I cannot identify Tier 2/3 suppliers meeting the specified employment threshold and provide their location and product/service details.</t>
+  </si>
+  <si>
+    <t>- Dinex Emissions Inc.
+  - Location: Greensboro, Greene County
+  - Product / Service: Aluminum sheet for automotive bodies</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 38.4057933s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '38s'}]}}</t>
+  </si>
+  <si>
+    <t>Find Tier 1/2 companies with EV / Battery Relevant = Yes and show their Primary OEMs.</t>
+  </si>
+  <si>
+    <t>Tier 1/2 companies with EV / Battery Relevant = Yes [7]: F&amp;P Georgia Manufacturing | Primary OEMs: Hyundai Kia | EV Supply Chain Role: Battery Pack Hitachi Astemo Americas Inc. | Primary OEMs: Hyundai Kia | EV Supply Chain Role: Battery Cell Hollingsworth &amp; Vose Co. | Primary OEMs: Hyundai Kia | EV Supply Chain Role: Battery Pack Honda Development &amp; Manufacturing | Primary OEMs: Hyundai Kia | EV Supply Chain Role: Battery Cell Hyundai Motor Group | Primary OEMs: Hyundai Kia | EV Supply Chain Role: Battery Pack Hyundai Transys Georgia Powertrain | Primary OEMs: Hyundai Kia Rivian | EV Supply Chain Role: Thermal Management IMMI | Primary OEMs: Hyundai Kia | EV Supply Chain Role: Battery Pack</t>
+  </si>
+  <si>
+    <t>Battery Cell:
+- Hitachi Astemo Americas Inc. | Primary OEMs: Hyundai Kia
+- Honda Development &amp; Manufacturing | Primary OEMs: Hyundai Kia
+Battery Pack:
+- F&amp;P Georgia Manufacturing | Primary OEMs: Hyundai Kia
+- Hollingsworth &amp; Vose Co. | Primary OEMs: Hyundai Kia
+General Automotive:
+- Racemark International LLC | Primary OEMs: Hyundai Kia Rivian</t>
+  </si>
+  <si>
+    <t>Based on general knowledge without specific workbook data, Tier 1 and Tier 2 automotive suppliers are companies that provide components or systems to Original Equipment Manufacturers (OEMs). For companies in the battery sector with "EV/Battery Relevant" marked as "Yes," these would typically supply batteries, battery management systems, or other EV-related parts directly to OEMs.
+Without specific workbook data, I can't list exact company names and their corresponding primary OEMs. However, some well-known Tier 1/2 companies in the EV battery space include:
+- **LG Energy Solution** - Primary OEM: Various (including Tesla, General Motors)
+- **Samsung SDI** - Primary OEM: BMW, Volkswagen
+- **Panasonic** - Primary OEM: Tesla
+These are examples based on general industry knowledge. For precise information, you would need to refer to the specific workbook data provided for exact company names and their relationships with primary OEMs.</t>
+  </si>
+  <si>
+    <t>Here are the Tier 1/2 companies with EV / Battery Relevant = Yes and their Primary OEMs, as listed in the provided evidence:
+**Battery Cell:**
+*   Hitachi Astemo Americas Inc. - Hyundai Kia
+*   Honda Development &amp; Manufacturing - Hyundai Kia
+**Battery Pack:**
+*   F&amp;P Georgia Manufacturing - Hyundai Kia
+*   Hollingsworth &amp; Vose Co. - Hyundai Kia
+**General Automotive:**
+*   Racemark International LLC - Hyundai Kia Rivian
+The evidence may be incomplete, as it does not list all Tier 1/2 companies with EV / Battery Relevant = Yes.</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the Excel workbook. The request requires filtering based on specific column values ("Tier 1/2 companies," "EV / Battery Relevant = Yes") and then extracting data ("Primary OEMs"). Without the workbook, I cannot perform this filtering and data extraction.</t>
+  </si>
+  <si>
+    <t>**Battery Cell**
+* Hitachi Astemo Americas Inc. (Primary OEMs: Hyundai Kia)
+* Honda Development &amp; Manufacturing (Primary OEMs: Hyundai Kia)
+**Battery Pack**
+* F&amp;P Georgia Manufacturing (Primary OEMs: Hyundai Kia)
+* Hollingsworth &amp; Vose Co. (Primary OEMs: Hyundai Kia)
+**General Automotive**
+* Racemark International LLC (Primary OEMs: Hyundai Kia Rivian)</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 38.308610206s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '38s'}]}}</t>
+  </si>
+  <si>
+    <t>Among Materials companies, which ones are EV / Battery Relevant = Yes versus Indirect? Provide counts and company lists.</t>
+  </si>
+  <si>
+    <t>Materials companies by EV / Battery relevance: Yes [0]: None Indirect [13]: Aurubis; Blue Ridge Manufacturing; Bosch (Automotive Division); Bridgestone Bandag; Club Car LLC; Constellium Automotive USA; DAEHAN Solution Georgia LLC; DAS Corp.; Daesol Ausys; Panasonic Automotive Systems Co.; SK Battery America; Sumitomo Electric Wiring Systems; SungEel Recycling Park Georgia No [10]: Ascend Elements; Aspen Aerogels; Beaver Manufacturing Co. Inc.; Blue Bird Corp.; Boogook Industries; EVCO Plastics; Fanello Industries Inc.; First American Resources; Haering Precision USA LP; PHA Body Systems LLC</t>
+  </si>
+  <si>
+    <t>Among Materials companies, there are no companies listed as EV / Battery Relevant = Yes. The count and list of companies with EV / Battery Relevant = Indirect are:
+Count: 4
+List:
+- Ascend Elements
+- Aspen Aerogels
+- Aurubis
+- Blue Ridge Manufacturing</t>
+  </si>
+  <si>
+    <t>Without specific data from an Excel workbook or a detailed dataset, I can provide a general overview based on industry knowledge. In the context of materials companies related to electric vehicles (EV) and batteries:
+1. **EV/Battery Relevant = Yes**: These are companies that directly supply components or materials used in EVs and battery production.
+   - Example Companies: 
+     - **Lithium Producers** such as Albemarle Corporation, Livent Corporation
+     - **Cobalt Suppliers** like Glencore plc
+     - **Graphite Producers** including Syrah Resources Ltd., SGL Carbon SE
+     - **Battery Materials Manufacturers** such as Umicore SA/NV, POSCO Chemical Co.
+   - Count: The exact number can vary widely depending on the specific criteria used to define "direct relevance," but there are dozens of companies globally that fall into this category.
+2. **Indirect**: These are companies whose products or services support EV and battery manufacturing in a less direct manner, such as those providing equipment for mining operations, logistics providers, or companies involved in recycling.
+   - Example Companies:
+     - **Mining Equipment Suppliers** like Caterpillar Inc., Komatsu Ltd.
+     - **Logistics Providers** including DB Schenker AG, DHL Group
+     - **Recycling and Waste Management Firms** such as Umicore SA/NV (for battery recycling), Veolia Environnement S.A.
+   - Count: This category is also quite broad and includes many companies that indirectly support the EV and battery industry through various services.
+The counts provided are approximate and can vary based on specific definitions and criteria used to categorize these companies. For precise numbers, a detailed analysis of an Excel workbook or database would be necessary.</t>
+  </si>
+  <si>
+    <t>**EV / Battery Relevant: Indirect**
+*   Companies: Aurubis, Blue Ridge Manufacturing, Bridgestone Bandag
+*   Count: 3
+**EV / Battery Relevant: No**
+*   Companies: Ascend Elements, Aspen Aerogels, Beaver Manufacturing Co. Inc., Blue Bird Corp.
+*   Count: 4
+The workbook evidence does not contain any companies with EV / Battery Relevant = Yes.</t>
+  </si>
+  <si>
+    <t>I am sorry, but I do not have access to the data needed to answer your question about Materials companies and their EV/Battery relevance (Yes vs. Indirect). I cannot provide counts or lists of companies without the relevant workbook evidence.</t>
+  </si>
+  <si>
+    <t>Among Materials companies, none are EV / Battery Relevant = Yes.
+The following companies are EV / Battery Relevant = Indirect:
+* Aurubis
+* Blue Ridge Manufacturing
+* Bridgestone Bandag</t>
+  </si>
+  <si>
+    <t>I cannot provide exact counts and company lists for "EV / Battery Relevant = Yes" versus "Indirect" among Materials companies without access to the specific workbook data. This information is highly dependent on the classifications and data within your Excel file.
+However, I can give you a general idea of what you might find and how to approach this if you were to analyze such a workbook:
+**General Approach if you had the data:**
+1.  **Filter for "Materials" companies:** You would first filter your data to only include companies categorized under "Materials."
+2.  **Identify "EV / Battery Relevant" status:** Within the filtered "Materials" companies, you would then look at a column (let's assume it's called "EV / Battery Relevant") that indicates whether a company is "Yes" or "Indirect."
+3.  **Count and List:**
+    *   **EV / Battery Relevant = Yes:** Count the number of companies with this status and list their names. These would typically be companies directly involved in mining, processing, or manufacturing materials specifically for EV batteries (e.g., lithium, cobalt, nickel miners, cathode/anode material producers).
+    *   **EV / Battery Relevant = Indirect:** Count the number of companies with this status and list their names. These might be companies that provide materials used in the broader EV ecosystem but not directly in the battery itself, or companies whose materials have broader applications beyond just EVs but are still relevant (e.g., specialized plastics, adhesives, lightweight metals for vehicle bodies, or general chemical suppliers).
+**Example (Hypothetical):**
+If I had the data, I might present it like this:
+**Materials Companies - EV / Battery Relevance**
+*   **EV / Battery Relevant = Yes (Count: X)**
+    *   Company A (Lithium Mining)
+    *   Company B (Nickel Processing)
+    *   Company C (Cathode Material Production)
+    *   ...
+*   **EV / Battery Relevant = Indirect (Count: Y)**
+    *   Company D (Specialty Adhesives)
+    *   Company E (Lightweight Aluminum Alloys)
+    *   Company F (Industrial Chemicals)
+    *   ...
+To get the precise answer, you would need to perform this analysis on your specific workbook.</t>
+  </si>
+  <si>
+    <t>Which Industry Group has the largest number of companies in the dataset, and what are the top 3 Industry Groups by count?</t>
+  </si>
+  <si>
+    <t>Largest Industry Group: Transportation Equipment (89 companies). Top 3 by count: Transportation Equipment (89); Rubber and Miscellaneous Plastic Products (28); Primary Metal Industries (16). Tie at third place with count 16: Primary Metal Industries; Electronic and Other Electrical Equipment and Components</t>
+  </si>
+  <si>
+    <t>The Industry Group with the largest number of companies in the dataset based on provided evidence is "Rubber and Miscellaneous Plastic Products". The top 3 Industry Groups by count are:
+1. Rubber and Miscellaneous Plastic Products (5 companies)
+2. Transportation Equipment (1 company)
+Note that only two distinct Industry Groups are represented in the given evidence, with "Primary Metal Industries" not appearing among the top three due to having fewer than two companies listed.</t>
+  </si>
+  <si>
+    <t>Without specific data from an Excel workbook or a detailed dataset, I can't provide exact figures. However, generally speaking, industries such as technology, healthcare, finance, manufacturing, and retail often have a large number of companies. To determine which industry group has the largest number of companies and to list the top 3 by count, you would need to analyze the specific data provided in your dataset or workbook.
+For example, if we hypothetically had data showing counts for different industry groups:
+- Technology might have 150 companies
+- Healthcare could have 120 companies
+- Finance might have 90 companies
+In this case, technology would be the largest group and healthcare and finance would follow as the second and third largest respectively. To give you an accurate answer based on your specific dataset, I'd need to see the actual numbers from your workbook or data source.</t>
+  </si>
+  <si>
+    <t>The Industry Group with the largest number of companies is Rubber and Miscellaneous Plastic Products, with 6 companies.
+Here are the top 3 Industry Groups by count:
+1. Rubber and Miscellaneous Plastic Products: 6 companies (Blue Bird Corp., Bosch (Automotive Division), DaeChang Seat Company, Daesol Ausys, Continental Tire the Americas LLC)
+2. Transportation Equipment: 1 company (Lear Corporation)
+3. Primary Metal Industries: 1 company (EVCO Plastics)</t>
+  </si>
+  <si>
+    <t>Without the dataset, I can't provide the exact Industry Groups and their counts. However, generally, in business datasets, "Financial Services" or "Healthcare" often have a large number of companies.
+Here's what the top 3 *might* be, but this is speculative:
+1.  **Financial Services** (likely the largest)
+2.  **Healthcare**
+3.  **Technology**
+To give you a definitive answer, I would need to analyze the dataset.</t>
+  </si>
+  <si>
+    <t>The Industry Group with the largest number of companies in the dataset is Rubber and Miscellaneous Plastic Products, with 6 companies.
+The top 3 Industry Groups by count are:
+1. Rubber and Miscellaneous Plastic Products:
+    * Blue Bird Corp.
+    * Bosch (Automotive Division)
+    * Continental Tire the Americas LLC
+    * DaeChang Seat Company
+    * Daesol Ausys
+    * EVCO Plastics
+2. Primary Metal Industries:
+    * EVCO Plastics
+3. Transportation Equipment:
+    * Lear Corporation</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 35.221055242s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '35s'}]}}</t>
+  </si>
+  <si>
+    <t>Within the Industry Group 'Electronic and Other Electrical Equipment and Components', list the companies and their EV Supply Chain Role.</t>
+  </si>
+  <si>
+    <t>Industry Group = 'Electronic and Other Electrical Equipment and Components' [16]: Hitachi Astemo | EV Supply Chain Role: General Automotive Hitachi Astemo Americas Inc. | EV Supply Chain Role: Battery Cell Hollingsworth &amp; Vose Co. | EV Supply Chain Role: Battery Pack Honda Development &amp; Manufacturing | EV Supply Chain Role: Battery Cell Hwashin | EV Supply Chain Role: General Automotive Hyundai &amp; LG Energy Solution (LGES) | EV Supply Chain Role: General Automotive Hyundai Industrial Co. | EV Supply Chain Role: General Automotive Hyundai MOBIS (Georgia) | EV Supply Chain Role: General Automotive Hyundai Motor Group | EV Supply Chain Role: Battery Pack Hyundai Transys Georgia Powertrain | EV Supply Chain Role: Thermal Management Hyundai Transys Georgia Seating Systems | EV Supply Chain Role: General Automotive IMMI | EV Supply Chain Role: Battery Pack IMS Gear Georgia Inc. | EV Supply Chain Role: General Automotive Inalfa Roof Systems Inc. | EV Supply Chain Role: General Automotive JAC Products Inc. | EV Supply Chain Role: General Automotive Jefferson Southern Corp. | EV Supply Chain Role: General Automotive</t>
+  </si>
+  <si>
+    <t>**General Automotive**
+- Hyundai MOBIS (Georgia)
+- Hitachi Astemo
+- Hwashin
+- Hyundai &amp; LG Energy Solution (LGES)
+- Hyundai Industrial Co.
+**Battery Cell**
+- Hitachi Astemo Americas Inc.
+- Honda Development &amp; Manufacturing
+**Battery Pack**
+- Hollingsworth &amp; Vose Co.</t>
+  </si>
+  <si>
+    <t>Without specific workbook evidence, I can't provide an exact list of companies within the "Electronic and Other Electrical Equipment and Components" industry group along with their EV (Electric Vehicle) supply chain roles. However, in general, such a category would include companies that manufacture components like batteries, electric motors, power electronics, and other electrical equipment used in EVs. Companies might have roles such as battery manufacturer, motor producer, or supplier of electronic control units.
+For precise information, you would need to refer to the specific workbook or dataset containing this industry group's details.</t>
+  </si>
+  <si>
+    <t>Here's a list of companies within the 'Electronic and Other Electrical Equipment and Components' Industry Group and their EV Supply Chain Role, according to the provided evidence:
+*   **Hyundai MOBIS (Georgia):** General Automotive
+*   **Hitachi Astemo:** General Automotive
+*   **Hitachi Astemo Americas Inc.:** Battery Cell
+*   **Hollingsworth &amp; Vose Co.:** Battery Pack
+*   **Honda Development &amp; Manufacturing:** Battery Cell
+*   **Hwashin:** General Automotive
+*   **Hyundai &amp; LG Energy Solution (LGES):** General Automotive
+*   **Hyundai Industrial Co.:** General Automotive</t>
+  </si>
+  <si>
+    <t>I cannot answer this question. I do not have access to the Excel workbook containing the company and EV Supply Chain Role information, specifically categorized by the 'Electronic and Other Electrical Equipment and Components' Industry Group.</t>
+  </si>
+  <si>
+    <t>* **Battery Cell:**
+  * Hitachi Astemo Americas Inc.
+  * Honda Development &amp; Manufacturing
+* **Battery Pack:**
+  * Hollingsworth &amp; Vose Co.
+* **General Automotive:**
+  * Hitachi Astemo
+  * Hwashin
+  * Hyundai &amp; LG Energy Solution (LGES)
+  * Hyundai Industrial Co.
+  * Hyundai MOBIS (Georgia)</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 35.093396379s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-2.5-flash', 'location': 'global'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '35s'}]}}</t>
+  </si>
+  <si>
+    <t>Within 'Rubber and Miscellaneous Plastic Products', which companies are EV / Battery Relevant = Yes?</t>
+  </si>
+  <si>
+    <t>Industry Group = 'Rubber and Miscellaneous Plastic Products' with EV / Battery Relevant = Yes: None</t>
+  </si>
+  <si>
+    <t>None of the companies listed under 'Rubber and Miscellaneous Plastic Products' have an EV / Battery Relevant value of Yes. All companies listed have either No or Indirect relevance to EV batteries.</t>
+  </si>
+  <si>
+    <t>Without specific workbook evidence, I cannot provide an exact list of companies within the category "Rubber and Miscellaneous Plastic Products" that have EV/Battery relevance marked as "Yes." However, typically in such categories, companies involved in producing components for electric vehicles (EVs) or battery-related parts would be flagged as relevant. These could include manufacturers of rubber seals, gaskets, insulation materials, or specialized plastic components used in batteries and EV systems. For precise information, you should refer to the specific workbook data provided.</t>
+  </si>
+  <si>
+    <t>There are no companies listed as EV / Battery Relevant = Yes within the 'Rubber and Miscellaneous Plastic Products' industry group.</t>
+  </si>
+  <si>
+    <t>I am sorry, but I do not have access to the requested workbook to answer your question.</t>
+  </si>
+  <si>
+    <t>No companies within 'Rubber and Miscellaneous Plastic Products' are marked as 'EV / Battery Relevant = Yes'. All companies listed in the provided evidence for this industry group are either 'No' or 'Indirect' for EV / Battery Relevance.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 34.971268199s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-2.5-flash', 'location': 'global'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '34s'}]}}</t>
+  </si>
+  <si>
+    <t>Show all companies whose EV Supply Chain Role is General Automotive but EV / Battery Relevant = Yes, and include Product / Service.</t>
+  </si>
+  <si>
+    <t>General Automotive with EV / Battery Relevant = Yes [3]: Duckyang | Product / Service: High-quality electrodeposited (ED) copper foil for electric vehicles Enchem America Inc. | Product / Service: Electric wiring components Racemark International LLC | Product / Service: Manufacturing and R&amp;D engine parts for EV</t>
+  </si>
+  <si>
+    <t>- General Automotive:
+  - Racemark International LLC | Product / Service: Manufacturing and R&amp;D engine parts for EV</t>
+  </si>
+  <si>
+    <t>Based on your criteria, you're looking for companies that have an "EV Supply Chain Role" categorized as "General Automotive," with "EV / Battery Relevant" set to "Yes," and also including their associated product or service. Without specific workbook data, I can't provide exact company names, but generally, such companies might include automotive suppliers who produce components relevant to electric vehicles (EVs) and batteries, even if they are not specialized EV manufacturers.
+Typical examples could be:
+1. **Company A**: Product/Service - Automotive parts for EVs
+2. **Company B**: Product/Service - Battery management systems
+3. **Company C**: Product/Service - Charging infrastructure components
+For precise details, you would need to review the specific workbook data that contains this information.</t>
+  </si>
+  <si>
+    <t>There are no companies listed with an EV Supply Chain Role of General Automotive and EV / Battery Relevant = Yes. The workbook evidence indicates that all companies with a General Automotive role have an EV / Battery Relevant status of Indirect or No.</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the Excel workbook. The request requires filtering based on specific column values ("EV Supply Chain Role" and "EV / Battery Relevant") and retrieving associated data ("Product / Service"). Without the workbook, I cannot perform this filtering and provide the requested list of companies.</t>
+  </si>
+  <si>
+    <t>The workbook lists the following companies whose EV Supply Chain Role is General Automotive and are EV / Battery Relevant:
+*   **Racemark International LLC**: Manufacturing and R&amp;D engine parts for EV</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 34.831621606s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '34s'}]}}</t>
+  </si>
+  <si>
+    <t>Which companies are in the Charging Infrastructure role, and what is their Category and Location?</t>
+  </si>
+  <si>
+    <t>Charging Infrastructure [1]: Morgan Corp. | Category: Tier 1 | Location: Lawrenceville, Gwinnett County</t>
+  </si>
+  <si>
+    <t>**Charging Infrastructure Role:**
+- **Morgan Corp.**
+  - Category: Tier 1
+  - Location: Lawrenceville, Gwinnett County</t>
+  </si>
+  <si>
+    <t>Without specific workbook evidence, I can't provide an exact list of companies involved in the "Charging Infrastructure" role along with their categories and locations. However, generally speaking, companies that operate in the charging infrastructure sector might include firms like ChargePoint, EVgo, Shell Recharge Solutions, and others. These companies typically fall under the category of Electric Vehicle (EV) Services or Energy &amp; Utilities. Their locations can vary widely depending on their market presence but often include major cities and regions with high electric vehicle adoption rates.
+For precise information, you would need to refer to the specific workbook data provided by your source.</t>
+  </si>
+  <si>
+    <t>Morgan Corp. is in the Charging Infrastructure role, and its Category is Tier 1 and Location is Lawrenceville, Gwinnett County.</t>
+  </si>
+  <si>
+    <t>I cannot answer this question without access to the relevant Excel workbook. The information about companies in the "Charging Infrastructure" role, along with their Category and Location, is contained within the data of the workbook.</t>
+  </si>
+  <si>
+    <t>Morgan Corp. is in the Charging Infrastructure role. It is a Tier 1 company located in Lawrenceville, Gwinnett County.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 34.689168481s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-2.5-flash', 'location': 'global'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '34s'}]}}</t>
+  </si>
+  <si>
+    <t>List all companies linked to Hyundai Kia and include their Category, EV Supply Chain Role, and Location.</t>
+  </si>
+  <si>
+    <t>Companies linked to Hyundai Kia (Primary OEMs contains 'Hyundai Kia') [11]: F&amp;P Georgia Manufacturing | Primary OEMs: Hyundai Kia | Category: Tier 1/2 | EV Supply Chain Role: Battery Pack | Location: Toccoa, Stephens County Hitachi Astemo Americas Inc. | Primary OEMs: Hyundai Kia | Category: Tier 1/2 | EV Supply Chain Role: Battery Cell | Location: Coweta County Hollingsworth &amp; Vose Co. | Primary OEMs: Hyundai Kia | Category: Tier 1/2 | EV Supply Chain Role: Battery Pack | Location: Bainbridge, Decatur County Honda Development &amp; Manufacturing | Primary OEMs: Hyundai Kia | Category: Tier 1/2 | EV Supply Chain Role: Battery Cell | Location: Pembroke, Bryan County Hyundai Motor Group | Primary OEMs: Hyundai Kia | Category: Tier 1/2 | EV Supply Chain Role: Battery Pack | Location: McDonough, Henry County IMMI | Primary OEMs: Hyundai Kia | Category: Tier 1/2 | EV Supply Chain Role: Battery Pack | Location: Jefferson, Jackson County Duckyang | Primary OEMs: Hyundai Kia Rivian | Category: Tier 2/3 | EV Supply Chain Role: General Automotive | Location: Augusta, Richmond County Enchem America Inc. | Primary OEMs: Hyundai Kia Rivian | Category: Tier 2/3 | EV Supply Chain Role: General Automotive | Location: Cumming, Forsyth County GSC Steel Stamping LLC | Primary OEMs: Hyundai Kia Rivian | Category: Tier 2/3 | EV Supply Chain Role: Power Electronics | Location: Gainesville, Hall County Hyundai Transys Georgia Powertrain | Primary OEMs: Hyundai Kia Rivian | Category: Tier 1/2 | EV Supply Chain Role: Thermal Management | Location: Dublin, Laurens County Racemark International LLC | Primary OEMs: Hyundai Kia Rivian | Category: Tier 1 | EV Supply Chain Role: General Automotive | Location: Calhoun, Gordon County</t>
+  </si>
+  <si>
+    <t>**Battery Cell**
+- Hitachi Astemo Americas Inc. | Category: Tier 1/2 | Location: Coweta County
+- Honda Development &amp; Manufacturing | Category: Tier 1/2 | Location: Pembroke, Bryan County
+**Battery Pack**
+- F&amp;P Georgia Manufacturing | Category: Tier 1/2 | Location: Toccoa, Stephens County
+- Hollingsworth &amp; Vose Co. | Category: Tier 1/2 | Location: Bainbridge, Decatur County
+**General Automotive**
+- Racemark International LLC | Category: Tier 1 | Location: Calhoun, Gordon County</t>
+  </si>
+  <si>
+    <t>To list all companies linked to Hyundai Kia along with their category, role in the electric vehicle (EV) supply chain, and location, I would need specific data from an Excel workbook or a similar detailed source. Since no such evidence is provided here, I can offer a general approach based on typical industry information:
+1. **LG Energy Solution** - Category: Battery Manufacturer; EV Supply Chain Role: Battery Supplier; Location: South Korea
+2. **Samsung SDI** - Category: Battery Manufacturer; EV Supply Chain Role: Battery Supplier; Location: South Korea
+3. **SK On (formerly SK Innovation)** - Category: Battery Manufacturer; EV Supply Chain Role: Battery Supplier; Location: South Korea
+4. **Mando Corporation** - Category: Automotive Parts Manufacturer; EV Supply Chain Role: Steering and Suspension Systems; Location: South Korea
+5. **Hyundai Mobis** - Category: Tier 1 Supplier; EV Supply Chain Role: Various Components (including electric motors, batteries); Location: South Korea
+Please note that the exact list of companies linked to Hyundai Kia can vary based on specific partnerships and supply chain dynamics not covered here. For precise information, consulting a detailed industry report or an Excel workbook with such data would be necessary.</t>
+  </si>
+  <si>
+    <t>Here's a list of companies linked to Hyundai Kia, along with their Category, EV Supply Chain Role, and Location, based on the provided evidence:
+*   **Racemark International LLC:** Category: Tier 1, EV Supply Chain Role: General Automotive, Location: Calhoun, Gordon County
+*   **Hyundai Industrial Co.:** Category: Tier 1/2, EV Supply Chain Role: General Automotive, Location: Valdosta, Lowndes County
+*   **F&amp;P Georgia Manufacturing:** Category: Tier 1/2, EV Supply Chain Role: Battery Pack, Location: Toccoa, Stephens County
+*   **Hitachi Astemo Americas Inc.:** Category: Tier 1/2, EV Supply Chain Role: Battery Cell, Location: Coweta County
+*   **Hollingsworth &amp; Vose Co.:** Category: Tier 1/2, EV Supply Chain Role: Battery Pack, Location: Bainbridge, Decatur County
+*   **Honda Development &amp; Manufacturing:** Category: Tier 1/2, EV Supply Chain Role: Battery Cell, Location: Pembroke, Bryan County</t>
+  </si>
+  <si>
+    <t>I am unable to answer your question. I do not have access to any workbooks and therefore cannot provide a list of companies linked to Hyundai Kia, including their Category, EV Supply Chain Role, and Location.</t>
+  </si>
+  <si>
+    <t>* **F&amp;P Georgia Manufacturing** - Category: Tier 1/2, EV Supply Chain Role: Battery Pack, Location: Toccoa, Stephens County
+* **GSC Steel Stamping LLC** - Category: Tier 2/3, EV Supply Chain Role: Power Electronics, Location: Gainesville, Hall County
+* **Hitachi Astemo Americas Inc.** - Category: Tier 1/2, EV Supply Chain Role: Battery Cell, Location: Coweta County
+* **Hollingsworth &amp; Vose Co.** - Category: Tier 1/2, EV Supply Chain Role: Battery Pack, Location: Bainbridge, Decatur County
+* **Honda Development &amp; Manufacturing** - Category: Tier 1/2, EV Supply Chain Role: Battery Cell, Location: Pembroke, Bryan County
+* **Racemark International LLC** - Category: Tier 1, EV Supply Chain Role: General Automotive, Location: Calhoun, Gordon County</t>
+  </si>
+  <si>
+    <t>I cannot provide a list of companies linked to Hyundai Kia with their Category, EV Supply Chain Role, and Location without access to a specific workbook or database containing that information. This kind of detail is highly specific and would be found in a dedicated industry report, supply chain analysis, or a company's internal documentation.</t>
+  </si>
+  <si>
+    <t>Which companies are linked to Hyundai Motor Group, and what Products / Services do they provide?</t>
+  </si>
+  <si>
+    <t>Companies linked to Hyundai Motor Group [1]: Superior Essex Inc. | Product / Service: Electric vehicles and batteries</t>
+  </si>
+  <si>
+    <t>**Battery Pack**
+- Hyundai Motor Group | Battery parts for electric vehicles
+**General Automotive**
+- DeKalb Tool &amp; Die Inc. | Truck interior cab components and exterior lights to HVAC and under the hood engine parts
+- GSC Steel Stamping LLC | Deep grove ball bearings Toyota Industries Electric Systems North 255 DC-to-DC converters Jackson America, Inc.*
+- Hyundai Industrial Co. | Automotive batteries
+**Materials**
+- Constellium Automotive USA | Motor vehicle plastic fuel systems and parts
+**Vehicle Assembly**
+- Superior Essex Inc. | Electric vehicles and batteries</t>
+  </si>
+  <si>
+    <t>Hyundai Motor Group is a large conglomerate that includes several subsidiaries and affiliates. Some of the key companies linked to Hyundai Motor Group include:
+1. **Hyundai Motor Company**: This company focuses on manufacturing passenger cars and commercial vehicles.
+2. **Kia Corporation (formerly Kia Motors)**: Known for producing passenger cars, SUVs, and electric vehicles.
+3. **Hyundai Heavy Industries (HHI)**: Specializes in shipbuilding, heavy machinery, construction equipment, and power generation systems.
+4. **Hyundai Mobis**: A leading automotive parts supplier that provides components such as chassis, brakes, steering systems, and electronic control units.
+5. **Hyundai Rotem**: Engaged in the production of railway vehicles, military equipment, and construction machinery.
+These companies provide a wide range of products and services including automobiles, heavy machinery, shipbuilding, railway systems, and defense technology. Each subsidiary plays a crucial role in supporting Hyundai Motor Group's diverse portfolio and global market presence.</t>
+  </si>
+  <si>
+    <t>The following companies are linked to Hyundai Motor Group:
+*   **Hyundai Motor Group:** Battery Pack, providing Battery parts for electric vehicles, located in McDonough, Henry County, with 164 employees.
+*   **Superior Essex Inc.:** Vehicle Assembly, providing Electric vehicles and batteries, located in Pembroke, Bryan County, with 8100 employees.
+*   **GSC Steel Stamping LLC:** Power Electronics, providing Deep grove ball bearings, Toyota Industries Electric Systems North 255 DC-to-DC converters, Jackson America, Inc.*, located in Gainesville, Hall County, with 350 employees.</t>
+  </si>
+  <si>
+    <t>Hyundai Motor Group encompasses a wide range of companies, each with distinct products and services. Here's a breakdown:
+*   **Hyundai Motor Company:** This is the flagship company, primarily focused on manufacturing and selling passenger vehicles, commercial vehicles, and SUVs.
+*   **Kia Corporation:** A subsidiary of Hyundai Motor Group, Kia produces a wide range of automobiles, including passenger vehicles, SUVs, and commercial vehicles.
+*   **Hyundai Mobis:** This company supplies automotive components, modules, and systems to both Hyundai and Kia, including lamps, mirrors, and electronic components.
+*   **Hyundai Steel:** A major steel manufacturer providing raw materials for the automotive industry and other sectors.
+*   **Hyundai Rotors Systems:** Specializes in manufacturing rotor blades for wind turbines.
+*   **Hyundai Construction Equipment:** Produces construction equipment like excavators, wheel loaders, and forklifts.
+*   **Hyundai Elevator:** Manufactures and installs elevators and escalators.
+*   **Hyundai Heavy Industries:** A diversified company involved in shipbuilding, heavy machinery, power generation, and more.
+Please note that this list may not be exhaustive, as Hyundai Motor Group has numerous other subsidiaries and affiliates involved in various industries.</t>
+  </si>
+  <si>
+    <t>Companies linked to Hyundai Motor Group and their Products / Services:
+*   **Hyundai Motor Group**: Battery parts for electric vehicles
+*   **Superior Essex Inc.**: Electric vehicles and batteries
+*   **GSC Steel Stamping LLC**: Deep grove ball bearings Toyota Industries Electric Systems North 255 DC-to-DC converters Jackson America, Inc.*</t>
+  </si>
+  <si>
+    <t>Hyundai Motor Group is a South Korean multinational automotive manufacturer headquartered in Seoul, South Korea. It operates several well-known brands and has various subsidiaries and affiliates that provide a range of products and services, primarily centered around the automotive industry but also extending into other sectors.
+Here are some of the key companies linked to Hyundai Motor Group and their primary products/services:
+**Automotive Brands:**
+*   **Hyundai Motor Company:**
+    *   **Products/Services:** Manufactures and sells a wide range of passenger cars (sedans, SUVs, hatchbacks), commercial vehicles (trucks, buses), electric vehicles (EVs), and hydrogen fuel cell vehicles (FCEVs). Also involved in automotive financing, parts, and service.
+*   **Kia Corporation:**
+    *   **Products/Services:** Manufactures and sells passenger cars (sedans, SUVs, hatchbacks), electric vehicles (EVs), and commercial vehicles. Also involved in automotive financing, parts, and service.
+*   **Genesis Motor:**
+    *   **Products/Services:** Hyundai's luxury vehicle division, manufacturing and selling premium sedans and SUVs.
+**Automotive Parts and Components:**
+*   **Hyundai Mobis:**
+    *   **Products/Services:** A leading global automotive supplier. Manufactures and supplies a vast array of automotive parts and modules, including chassis modules, cockpit modules, front-end modules, airbags, ABS, ESC, lighting systems, infotainment systems, and advanced driver-assistance systems (ADAS). Also involved in after-sales service parts.
+*   **Hyundai Wia:**
+    *   **Products/Services:** Manufactures automotive parts (engines, transmissions, axles, constant velocity joints), machine tools (CNC lathes, machining centers), and defense products.
+*   **Hyundai Transys:**
+    *   **Products/Services:** Specializes in automotive powertrains (transmissions, axles) and seats.
+**Steel and Materials:**
+*   **Hyundai Steel:**
+    *   **Products/Services:** A major steel producer, supplying various steel products including hot-rolled steel, cold-rolled steel, special steel, and steel pipes, with a significant portion going to the automotive industry.
+**Construction and Engineering:**
+*   **Hyundai Engineering &amp; Construction (Hyundai E&amp;C):**
+    *   **Products/Services:** Engages in a wide range of construction activities, including civil engineering (roads, bridges, ports), building construction (residential, commercial), plant construction (power plants, petrochemical plants), and infrastructure development.
+*   **Hyundai Engineering:**
+    *   **Products/Services:** Provides engineering, procurement, and construction (EPC) services for various industries, including oil &amp; gas, petrochemicals, power, and infrastructure.
+**Logistics:**
+*   **Hyundai Glovis:**
+    *   **Products/Services:** Provides comprehensive logistics services, including finished vehicle transportation (shipping, rail, road), bulk shipping, freight forwarding, and supply chain management.
+**Financial Services:**
+*   **Hyundai Capital:**
+    *   **Products/Services:** Offers automotive financing, leasing, and personal loan services.
+*   **Hyundai Card:**
+    *   **Products/Services:** Provides credit card services.
+*   **Hyundai Commercial:**
+    *   **Products/Services:** Offers financial services for commercial vehicles and equipment.
+**Other Ventures:**
+*   **Boston Dynamics:** (Acquired by Hyundai Motor Group)
+    *   **Products/Services:** Develops advanced mobile robots (e.g., Spot, Atlas, Stretch) for various applications, including industrial inspection, logistics, and research.
+*   **Supernal:** (Hyundai Motor Group's Advanced Air Mobility company)
+    *   **Products/Services:** Focused on developing electric vertical take-off and landing (eVTOL) vehicles and the associated ecosystem for urban air mobility.
+*   **Hyundai Rotem:**
+    *   **Products/Services:** Manufactures rolling stock (trains, subways), defense systems (tanks, armored vehicles), and plant equipment.
+This list covers the major entities and their primary offerings, but Hyundai Motor Group's influence extends through numerous other smaller subsidiaries, joint ventures, and investments across various technology and service sectors.</t>
+  </si>
+  <si>
+    <t>Identify suppliers linked to Rivian Automotive and show their Employment and Location.</t>
+  </si>
+  <si>
+    <t>Supplier entries linked to Rivian Automotive: None. Exact Primary OEMs = Rivian Automotive appears in 1 entry: Suzuki Manufacturing of America Corp. | Category: OEM | Employment: 7,500 | Location: Monroe, Walton County</t>
+  </si>
+  <si>
+    <t>**General Automotive**
+- Rivian Automotive | Employment: 105 | Location: Gainesville, Hall County
+- Adient | Employment: 180 | Location: Ringgold, Catoosa County
+- DeKalb Tool &amp; Die Inc. | Employment: 70 | Location: Calhoun, Gordon County
+**Power Electronics**
+- GSC Steel Stamping LLC | Employment: 350 | Location: Gainesville, Hall County
+**Thermal Management**
+- Hyundai Transys Georgia Powertrain | Employment: 130 | Location: Dublin, Laurens County</t>
+  </si>
+  <si>
+    <t>To identify suppliers linked to Rivian Automotive and show their employment numbers and locations, I would typically look at a specific dataset or supplier directory related to Rivian. Since no workbook evidence is provided here, I can't give exact figures for the number of employees or precise location details for each supplier.
+However, based on general industry knowledge, some key suppliers linked to Rivian Automotive include companies like Bosch, Samsung SDI, and Meritor. These suppliers might be located in various regions such as North America, Asia, and Europe. For specific employment numbers and exact locations, you would need to refer to the detailed supplier information provided by Rivian or the respective company's official sources.
+If you have a specific workbook with this information, please provide details about its contents so I can give more precise answers based on that data.</t>
+  </si>
+  <si>
+    <t>Here are the suppliers linked to Rivian Automotive, their Employment, and Location, according to the provided data:
+*   **Rivian Automotive:** Employment: 105, Location: Gainesville, Hall County
+*   **Racemark International LLC:** Employment: 120, Location: Calhoun, Gordon County
+*   **Duckyang:** Employment: 250, Location: Augusta, Richmond County
+*   **GSC Steel Stamping LLC:** Employment: 350, Location: Gainesville, Hall County
+*   **Hyundai Transys Georgia Powertrain:** Employment: 130, Location: Dublin, Laurens County</t>
+  </si>
+  <si>
+    <t>Identifying specific suppliers linked to Rivian Automotive, along with their employment numbers and locations, requires access to Rivian's supply chain data, which is not publicly available. Therefore, I cannot provide a definitive list.
+However, based on publicly available information and industry reports, here are some companies known to be suppliers to Rivian, along with general information about their employment and locations (note: these details are approximate and may have changed):
+*   **BOSCH:** A major automotive supplier providing various components. Bosch has a global presence with hundreds of locations and over 300,000 employees worldwide.
+*   **LG Chem:** Supplies battery cells for Rivian vehicles. LG Chem is a South Korean company with numerous facilities globally, employing over 70,000 people.
+*   **Continental AG:** Provides tires and other automotive components. Continental operates globally with approximately 200,000 employees across various locations.
+*   **ZF Friedrichshafen AG:** Supplies driveline and chassis technology. ZF is a German company with a global footprint and around 160,000 employees.
+*   **Faurecia:** A French automotive supplier providing seating, interior components, and more. Faurecia has a global network with over 100,000 employees.
+**Please note:** This is not an exhaustive list, and the employment numbers and locations are approximate. Rivian's supply chain is complex and involves numerous other suppliers.</t>
+  </si>
+  <si>
+    <t>Here are the suppliers linked to Rivian Automotive, along with their employment and location:
+*   **Rivian Automotive** - Employment: 105, Location: Gainesville, Hall County
+*   **Racemark International LLC** - Employment: 120, Location: Calhoun, Gordon County
+*   **Duckyang** - Employment: 250, Location: Augusta, Richmond County
+*   **GSC Steel Stamping LLC** - Employment: 350, Location: Gainesville, Hall County
+*   **Hyundai Transys Georgia Powertrain** - Employment: 130, Location: Dublin, Laurens County</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 8.882018625s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-2.5-flash', 'location': 'global'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '8s'}]}}</t>
+  </si>
+  <si>
+    <t>List all entries where Primary OEMs = Multiple OEMs and compute the median Employment for those entries.</t>
+  </si>
+  <si>
+    <t>Entries where Primary OEMs = Multiple OEMs [156]: ACM Georgia LLC (400); ADVICS Manufacturing Georgia LLC (150); ALBAform Inc. (130); AVS (310); Adient (180); Ajin Georgia (143); Anovion Technologies (82); Apache Mills Inc. (140); Aptiv (250); Archer Aviation Inc. (200); Arising Industries Inc. (582); Arising Industries Inc. (70); Ascend Elements (456); Aspen Aerogels (414); Aurubis (400); Beaver Manufacturing Co. Inc. (300); Big Tex Trailer Manufacturing Inc. (280); Blue Bird Corp. (275); Blue Ridge Manufacturing (270); Bonnell Aluminum (266); Boogook Industries (250); Bosal Industries Georgia (250); Bosch (Automotive Division) (250); Bridgestone Bandag (242); Carcoustics USA (225); Club Car LLC (200); Constellium Automotive USA (200); Continental Automotive (160); Continental Tire the Americas LLC (150); DAEHAN Solution Georgia LLC (130); DAS Corp. (85); DaeChang Seat Company (135); Daesol Ausys (97); Daesol Material Georgia, LLC (90); Daimler Truck North America (85); DeKalb Tool &amp; Die Inc. (70); Decostar Industries (80); Denkai America (50); Denso Manufacturing Georgia (105); Die-Tech Industries Inc. (60); Dinex Emissions Inc. (500); Dongwon Autopart Technology Georgia LLC (315); Dorsett Industries Inc. (300); Down 2 Earth Trailers (300); EVCO Plastics (125); Eaton Corp. (230); Ecoplastic America Corporation (200); Ecoplastic Corporation (160); Elan Technology Inc. (160); Enplas USA Inc. (150); Erdrich USA Inc. (128); FOX Factory (345); FREYR Battery (110); Fanello Industries Inc. (100); First American Resources (60); Flambeau Inc. (700); Fouts Brothers Fire Equipment (630); Freudenberg-NOK (160); Freudenberg-NOK (175); GEDIA Georgia LLC (100); GLOVIS Georgia LLC (90); Global Powertrain Systems LLC (100); Goodyear Tire &amp; Rubber Co. (80); Great Dane LP (65); Great Dane Trailers (50); Grudem (807); HELLA Automotive Sales Inc. (70); HEXPOL Compounding Corp. (50); Haering Precision USA LP (170); Haering Precision USA LP (200); Hitachi Astemo (800); Hwashin (285); Hyundai &amp; LG Energy Solution (LGES) (250); Hyundai Industrial Co. (182); Hyundai MOBIS (Georgia) (170); Hyundai Transys Georgia Seating Systems (110); IMS Gear Georgia Inc. (100); Inalfa Roof Systems Inc. (95); JAC Products Inc. (63); JTEKT North America Corp. (860); Jefferson Southern Corp. (50); Jefferson Southern Corporation (900); Joon Georgia, Inc. (900); KTX America Corporation (740); Kautex Inc. (800); Kumho Tire USA Inc. (730); Kyungshin America Corp. (700); Lark United Manufacturing Inc. (700); Lear Corporation (590); Lehigh Technologies Inc. (520); Linde + Wiemann (515); Lund International Inc. (500); Lund International Inc./Ventshade Division (500); Lyle Industries Inc. (500); Lyle Industries Inc. (500); MAT Heavy Duty (400); Mack Trucks (500); Magna International (500); Mando America Corp. (460); Master Craft Engineering Inc. (402); Maxxis International USA (400); Mercedes-Benz USA LLC (400); Michelin Tread Technologies (400); Milliken &amp; Co./Valway Plant (400); Mobis Alabama LLC (350); MollerTech LLC (350); Morgan Corp. (320); Murata Electronics North America Inc. (310); NIFCO KTW America Corp. (300); NVH Korea (200); Neaton Rome Inc. (300); Nidec Elesys Americas Corp. (300); Nile Automotive (300); Nisshinbo Automotive Manufacturing Inc. (300); Nivel Parts &amp; Manufacturing Co. LLC (275); Novelis Inc. (200); Novelis Inc. (205); Novelis Inc. (260); OTR Wheel Engineering Inc. (200); Oneda Corp. (200); PAI Industries Inc. (198); PHA Body Systems LLC (145); PIOLAX Corp. (130); PPG Industries Inc. (120); Paccar (200); Pak-Lite Inc. (180); Panasonic Automotive Systems Co. (180); Panasonic Automotive Systems Co. (175); Panduit Corp. (170); Peerless-Winsmith Inc. (160); Peterson Spring (150); Piedmont Automotive Products Inc. (140); Pirelli Tire North America LLC (130); Porsche Cars North America Inc. (125); Propex Operating Co. LLC (120); QSR Inc. (120); RealTruck (110); Rivian Automotive (105); Robert Bosch LLC (100); SAFT America Inc. (100); SK Battery America (75); SKF USA Inc. (70); SRG Global Inc. (60); Sejong Georgia LLC (90); Seohan Auto USA (85); Seoyon E-HWA (85); Seoyon E-Hwa Interior Systems (80); Sewon America Inc. (80); Sewon America Inc. (75); Sewon America Inc. (75); Solvay Specialty Polymers USA LLC (70); Southern Switches Corp. (68); Stryten Energy (50); Suhner Manufacturing Corp. (50); Sumitomo Electric Wiring Systems (50); SungEel Recycling Park Georgia (650) Median Employment: 181</t>
+  </si>
+  <si>
+    <t>Company: Blue Bird Corp. | Category: Tier 2/3 | EV Supply Chain Role: Materials | Location: Elberton, Elbert County | Employment: 275
+Median Employment for entries where Primary OEMs = Multiple OEMs: 275</t>
+  </si>
+  <si>
+    <t>To calculate the median employment for entries where "Primary OEMs" is listed as "Multiple OEMs," we would need specific data from an Excel workbook or a similar dataset that includes both the "Primary OEMs" field and the number of employees. Since no actual workbook data has been provided, I can't compute the exact median value.
+However, if you have such a dataset, here's how you could approach it:
+1. Filter the entries where "Primary OEMs" is equal to "Multiple OEMs."
+2. Extract the employment numbers from these filtered entries.
+3. Arrange these employment numbers in ascending order.
+4. Identify the middle number (or average of two middle numbers if there's an even count) as the median.
+If you can provide more details or a sample dataset, I could give a more precise answer based on that information.</t>
+  </si>
+  <si>
+    <t>The following companies have "Multiple OEMs" as Primary OEMs:
+*   Blue Bird Corp. with Employment: 275
+The median Employment for these entries is 275.</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the Excel workbook. The question requires specific data points ("Primary OEMs = Multiple OEMs" and "Employment") that are only available within the workbook.</t>
+  </si>
+  <si>
+    <t>The workbook evidence does not contain any entries where "Primary OEMs" is "Multiple OEMs" for the specified category. However, there is one entry in the workbook where "Primary OEMs" is "Multiple OEMs" but its category is "Tier 2/3" not "OEM".
+Here is that entry:
+*   **Company**: Blue Bird Corp.
+*   **Category**: Tier 2/3
+*   **EV Supply Chain Role**: Materials
+*   **Employment**: 275</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 8.750300656s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '8s'}]}}</t>
+  </si>
+  <si>
+    <t>Which companies are linked to Mercedes-Benz USA LLC and what EV / Battery Relevant status do they have?</t>
+  </si>
+  <si>
+    <t>Linked to Mercedes-Benz USA LLC [1]: TDK Components USA Inc. | EV / Battery Relevant: No | EV Supply Chain Role: Vehicle Assembly | Category: OEM | Location: Atlanta, Fulton County</t>
+  </si>
+  <si>
+    <t>**General Automotive**
+- DeKalb Tool &amp; Die Inc. | EV / Battery Relevant: No
+**Vehicle Assembly**
+- TDK Components USA Inc. | EV / Battery Relevant: No
+**Indirect Support (General Automotive)**
+- Mercedes-Benz USA LLC | EV / Battery Relevant: Indirect</t>
+  </si>
+  <si>
+    <t>Without specific evidence from an Excel workbook or another detailed source, I can provide a general response based on publicly available information. Mercedes-Benz USA LLC is the official distributor for Mercedes-Benz vehicles in the United States. It's linked to Daimler AG (now known as Mercedes-Benz Group AG) which owns and operates the brand globally.
+Regarding EV/Battery Relevant status, Mercedes-Benz has several initiatives related to electric vehicles and battery technology:
+1. **Mercedes-Benz Battery Energy GmbH**: This company is involved in battery production for Mercedes-Benz.
+2. **Mercedes-Benz Mobility USA LLC**: It provides financing solutions including leasing options for electric vehicles.
+3. **Mercedes-Benz Research &amp; Development North America, Inc. (MBRDNA)**: This subsidiary focuses on research and development of new technologies, including EVs.
+For precise details about the companies linked to Mercedes-Benz USA LLC and their specific statuses related to EV/Battery technology, you would need to refer to detailed corporate reports or official statements from Mercedes-Benz Group AG and its subsidiaries.</t>
+  </si>
+  <si>
+    <t>Here are the companies linked to Mercedes-Benz USA LLC and their EV / Battery Relevant status, according to the provided workbook evidence:
+*   **TDK Components USA Inc.** (EV / Battery Relevant: No) - EV Supply Chain Role: Vehicle Assembly
+*   **Mercedes-Benz USA LLC** (EV / Battery Relevant: Indirect) - EV Supply Chain Role: General Automotive</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I cannot provide a definitive list of companies linked to Mercedes-Benz USA LLC and their EV/Battery Relevant status. However, generally, Mercedes-Benz USA LLC would be linked to a wide range of companies including:
+*   **Tier 1 Suppliers:** These are major suppliers providing components and systems (e.g., Bosch, Continental, Denso). Many of these would have EV/Battery relevance.
+*   **Battery Manufacturers:** Companies like CATL, SK Innovation, Panasonic, and others that supply battery cells or packs. These would be highly EV/Battery Relevant.
+*   **Raw Material Suppliers:** Companies involved in mining and processing lithium, nickel, cobalt, manganese, and other materials crucial for batteries. These would be EV/Battery Relevant.
+*   **Charging Infrastructure Providers:** Companies providing charging stations and related technology. These would be EV/Battery Relevant.
+*   **Joint Venture Partners:** Mercedes-Benz may have joint ventures with other companies for EV development or manufacturing.
+*   **Technology Partners:** Companies providing software, semiconductors, or other technologies for EVs.
+The specific status (e.g., "Supplier," "Partner," "Joint Venture") and the degree of EV/Battery relevance would vary for each company.</t>
+  </si>
+  <si>
+    <t>Mercedes-Benz USA LLC is linked to the following companies:
+*   **Mercedes-Benz USA LLC**: Indirect
+*   **TDK Components USA Inc.**: No</t>
+  </si>
+  <si>
+    <t>I cannot answer this question without more information. The question asks for specific company linkages and EV/Battery Relevant statuses that would be contained within a particular dataset or workbook. Without access to that data, I cannot provide the requested information.</t>
+  </si>
+  <si>
+    <t>Find the company (or companies) linked to SK Battery America and provide its EV Supply Chain Role and Location.</t>
+  </si>
+  <si>
+    <t>Linked to SK Battery America [1]: Thermal Ceramics Inc. | EV Supply Chain Role: Vehicle Assembly | Location: Jefferson, Jackson County | Category: OEM</t>
+  </si>
+  <si>
+    <t>No specific companies are linked to SK Battery America based on the provided evidence. However, SK Battery America's EV Supply Chain Role is Materials and its Location is Hartwell, Hart County.</t>
+  </si>
+  <si>
+    <t>Based on my knowledge without specific workbook evidence, SK Battery America is a subsidiary of South Korea's SK Innovation Company. In the context of electric vehicles (EVs), SK Battery America plays a significant role in battery manufacturing for the supply chain. Its primary location is in Georgia, USA, where it operates large-scale EV battery plants. For precise details and roles linked to specific companies within the EV supply chain, consulting the relevant workbook or official company sources would be necessary.</t>
+  </si>
+  <si>
+    <t>SK Battery America's EV Supply Chain Role is Materials and its Location is Hartwell, Hart County.</t>
+  </si>
+  <si>
+    <t>I am sorry, but I do not have access to the requested information.</t>
+  </si>
+  <si>
+    <t>The workbook does not contain information about companies linked to SK Battery America. However, it does provide information about SK Battery America itself:
+Company: SK Battery America
+EV Supply Chain Role: Materials
+Location: Hartwell, Hart County</t>
+  </si>
+  <si>
+    <t>SK Battery America is a subsidiary of **SK On**, which is part of the South Korean conglomerate **SK Group**.
+*   **Company:** SK On (part of SK Group)
+*   **EV Supply Chain Role:** Battery Manufacturer
+*   **Location:** SK On is headquartered in Seoul, South Korea. SK Battery America has manufacturing facilities in Commerce, Georgia, USA.</t>
+  </si>
+  <si>
+    <t>List all companies linked to Club Car LLC and include their EV Supply Chain Role and Product / Service.</t>
+  </si>
+  <si>
+    <t>Linked to Club Car LLC [1]: Kia Georgia Inc. | EV Supply Chain Role: Vehicle Assembly | Product / Service: Golf carts, various off-road vehicles, electric on-road vehicles | Category: OEM</t>
+  </si>
+  <si>
+    <t>**Materials**
+- Club Car LLC | Injection molded plastic automotive parts
+**Vehicle Assembly**
+- Kia Georgia Inc. | Golf carts, various off-road vehicles, electric on-road vehicles</t>
+  </si>
+  <si>
+    <t>To list all companies linked to Club Car LLC along with their roles in the electric vehicle (EV) supply chain and products/services, I would need specific information from an Excel workbook or another detailed source that outlines these relationships. Since no such evidence is provided here, I can only provide a general answer based on available knowledge.
+Club Car LLC is known for manufacturing golf cars, utility vehicles, and other small electric vehicles. Companies linked to Club Car LLC in the EV supply chain might include battery suppliers, component manufacturers, and distributors. For example:
+1. **East Penn Manufacturing** - Battery Supplier
+   - Product/Service: Batteries for electric vehicles
+2. **Johnson Controls** - Component Manufacturer
+   - Product/Service: Electrical systems and components
+3. **Dover Corporation** - Distributor
+   - Product/Service: Distribution of Club Car products to various markets
+Please note that the exact list may vary depending on specific partnerships and supply chain configurations not detailed in this context. For precise information, consulting a relevant Excel workbook or official company documents would be necessary.</t>
+  </si>
+  <si>
+    <t>Here are the companies linked to Club Car LLC, along with their EV Supply Chain Role and Product / Service, according to the provided workbook evidence:
+*   **Kia Georgia Inc.**
+    *   EV Supply Chain Role: Vehicle Assembly
+    *   Product / Service: Golf carts, various off-road vehicles, electric on-road vehicles
+*   **Club Car LLC**
+    *   EV Supply Chain Role: Materials
+    *   Product / Service: Injection molded plastic automotive parts</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question. I do not have access to any information about Club Car LLC or its associated companies, their EV Supply Chain Roles, or their Products/Services.</t>
+  </si>
+  <si>
+    <t>* **Club Car LLC**
+  * EV Supply Chain Role: Materials
+  * Product / Service: Injection molded plastic automotive parts
+* **Kia Georgia Inc.**
+  * EV Supply Chain Role: Vehicle Assembly
+  * Product / Service: Golf carts, various off-road vehicles, electric on-road vehicles</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 35.997846981s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-2.5-flash', 'location': 'global'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '35s'}]}}</t>
+  </si>
+  <si>
+    <t>Which companies are linked to Blue Bird or Blue Bird Corp., and what is their Primary Facility Type?</t>
+  </si>
+  <si>
+    <t>Linked to Blue Bird / Blue Bird Corp. [4]: Hanon Systems USA LLC | Primary OEMs: Blue Bird | Primary Facility Type: Manufacturing Plant | Category: Tier 2/3 | Location: Griffin, Spalding County Perkins Small Engines LLC | Primary OEMs: Blue Bird | Primary Facility Type: Manufacturing Plant | Category: Tier 1 | Location: Zebulon, Pike County SHIROKI North America Inc | Primary OEMs: Blue Bird | Primary Facility Type: Manufacturing Plant | Category: Tier 1 | Location: Dublin, Laurens County TE Connectivity | Primary OEMs: Blue Bird Corp. | Primary Facility Type: Manufacturing Plant | Category: OEM | Location: Fort Valley, Peach County</t>
+  </si>
+  <si>
+    <t>**Tier 2/3 Companies Linked to Blue Bird Corp.**
+- **Blue Bird Corp.**
+  - Primary Facility Type: Manufacturing Plant
+- **Hanon Systems USA LLC**
+  - Primary Facility Type: Manufacturing Plant
+**Tier 1 Companies Linked to Blue Bird Corp.**
+- **Perkins Small Engines LLC**
+  - Primary Facility Type: Manufacturing Plant
+- **SHIROKI North America Inc**
+  - Primary Facility Type: Manufacturing Plant</t>
+  </si>
+  <si>
+    <t>To directly address your query without specific workbook evidence, I can say that Blue Bird Corporation is a well-known company in the United States that specializes in manufacturing school buses. If you're asking about other companies linked to Blue Bird Corporation and their primary facility types, this would typically involve information on suppliers, subsidiaries, or related businesses which isn't provided here.
+For example:
+- **Blue Bird Corporation** itself has a Primary Facility Type of "School Bus Manufacturing."
+- Related companies might include parts suppliers like **Wabash National**, whose primary facility type could be "Commercial Vehicle Parts Manufacturing."
+Without specific workbook data, I can't provide exact details on linked companies and their facility types. For precise information, you would need to refer to the relevant business records or databases that list such relationships and classifications.</t>
+  </si>
+  <si>
+    <t>The following companies are linked to Blue Bird or Blue Bird Corp.:
+*   **Blue Bird Corp.** - Manufacturing Plant
+*   **TE Connectivity** - Manufacturing Plant
+*   **Hanon Systems USA LLC** - Manufacturing Plant
+*   **Perkins Small Engines LLC** - Manufacturing Plant
+*   **SHIROKI North America Inc** - Manufacturing Plant</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I can't provide a definitive list of companies linked to Blue Bird or Blue Bird Corp. and their Primary Facility Types. However, based on general knowledge, Blue Bird Corp. is a manufacturer of school buses. Therefore, companies likely linked to them would include:
+*   **Component Suppliers:** Companies that supply parts for school buses (e.g., engine manufacturers, tire manufacturers, lighting suppliers, etc.).
+*   **Distributors:** Companies that distribute Blue Bird buses to dealerships.
+*   **Dealerships:** Companies that sell and service Blue Bird buses.
+*   **Governmental/Educational Entities:** School districts and other organizations that purchase Blue Bird buses.
+The Primary Facility Type for these linked companies would vary:
+*   **Component Suppliers:** Manufacturing plants
+*   **Distributors:** Distribution centers or warehouses
+*   **Dealerships:** Dealerships or service centers
+*   **Governmental/Educational Entities:** Schools or government buildings.
+*Please note that this is a general response, and the actual companies and facility types would depend on the specific data within the workbook.*</t>
+  </si>
+  <si>
+    <t>The companies linked to Blue Bird or Blue Bird Corp. and their Primary Facility Type are:
+*   **Blue Bird Corp.:** Manufacturing Plant
+*   **Hanon Systems USA LLC:** Manufacturing Plant
+*   **Perkins Small Engines LLC:** Manufacturing Plant
+*   **SHIROKI North America Inc:** Manufacturing Plant
+*   **TE Connectivity:** Manufacturing Plant</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 35.858845372s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '35s'}]}}</t>
+  </si>
+  <si>
+    <t>Show all companies linked to Yamaha Motor Manufacturing Corp. and include Category, Location, and Employment.</t>
+  </si>
+  <si>
+    <t>Linked to Yamaha Motor Manufacturing Corp. [1]: Teklas USA | Category: OEM | Location: Coweta County | Employment: 1,800 | EV Supply Chain Role: Vehicle Assembly</t>
+  </si>
+  <si>
+    <t>**Advanced electrical architecture for EVs**
+- Company: Yamaha Motor Manufacturing Corp. | Category: OEM Supply Chain | Location: Georgia | Employment: 190000
+**Vehicle Assembly**
+- Company: Teklas USA | Category: OEM | Location: Coweta County | Employment: 1800</t>
+  </si>
+  <si>
+    <t>To provide a detailed response about companies linked to Yamaha Motor Manufacturing Corporation along with their categories, locations, and employment numbers, I would need specific data from an Excel workbook or another structured dataset that contains this information. Since no such evidence is provided here, I can only offer general guidance on how you might approach finding this information:
+1. **Identify the Companies**: Look for a list of companies associated with Yamaha Motor Manufacturing Corporation in your dataset.
+2. **Categories**: Check if there are specific categories assigned to each company (e.g., supplier, partner, subsidiary).
+3. **Locations**: Note down the locations where these companies operate or have their headquarters.
+4. **Employment Numbers**: If available, include the number of employees for each company.
+Without access to a specific dataset, I cannot provide exact details about linked companies and their attributes. For accurate information, you would need to refer to an Excel workbook or another reliable source that contains this data.</t>
+  </si>
+  <si>
+    <t>Here are the companies linked to Yamaha Motor Manufacturing Corp., including their Category, Location, and Employment:
+*   **Teklas USA:** Category: OEM, Location: Coweta County, Employment: 1800
+*   **Trenton Pressing:** Category: OEM Supply Chain, Location: Georgia, Employment: 298
+*   **Trenton Pressing Inc.:** Category: OEM Supply Chain, Location: Georgia, Employment: 350</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the relevant Excel workbook. The information regarding companies linked to Yamaha Motor Manufacturing Corp., along with their Category, Location, and Employment details, would be found within the workbook's data.</t>
+  </si>
+  <si>
+    <t>**Companies linked to Yamaha Motor Manufacturing Corp.:**
+*   **Yamaha Motor Manufacturing Corp.**
+    *   Category: OEM Supply Chain
+    *   Location: Georgia
+    *   Employment: 190000
+*   **Teklas USA**
+    *   Category: OEM
+    *   Location: Coweta County
+    *   Employment: 1800</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 35.724889024s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '35s'}]}}</t>
+  </si>
+  <si>
+    <t>For each Primary OEM listed (excluding blanks), count how many companies are associated with it.</t>
+  </si>
+  <si>
+    <t>Company counts by Primary OEM (excluding blanks): Multiple OEMs: 156 Hyundai Kia: 6 Hyundai Kia Rivian: 5 Blue Bird: 3 Blue Bird Corp.: 1 Club Car LLC: 1 Archer Aviation Inc.: 1 Hyundai Motor Group: 1 Kia Georgia Inc.: 1 Mercedes-Benz USA LLC: 1 Porsche Cars North America Inc.: 1 Rivian Automotive: 1 SK Battery America: 1 Textron Specialized Vehicles: 1 Yamaha Motor Manufacturing Corp.: 1</t>
+  </si>
+  <si>
+    <t>Please provide the data source (e.g., an Excel workbook) so I can count the number of companies associated with each Primary OEM. Without the data, I cannot provide a specific count.</t>
+  </si>
+  <si>
+    <t>I am sorry, but I cannot answer this question without the specific workbook data. To count the companies associated with each Primary OEM, I need to access the list of Primary OEMs and the corresponding company associations within your workbook.</t>
+  </si>
+  <si>
+    <t>Which Primary OEM has the highest total Employment across its associated companies (excluding blanks)?</t>
+  </si>
+  <si>
+    <t>By exact Primary OEM field value, Multiple OEMs has the highest total Employment: 39,705. If you exclude the placeholder 'Multiple OEMs', the highest named OEM is Hyundai Motor Group with total Employment of 8,100.</t>
+  </si>
+  <si>
+    <t>Hyundai Motor Group has the highest total Employment across its associated companies with 8100 employees at Superior Essex Inc.</t>
+  </si>
+  <si>
+    <t>To determine which Primary OEM has the highest total employment across its associated companies, we would need specific data about each company's employment numbers and their association with a particular Primary OEM. Without this information, I can't provide an exact answer. However, generally speaking, major automotive or technology companies often have high employment figures. If you could share more details or specify the industry context, I could offer a more tailored response based on general knowledge.</t>
+  </si>
+  <si>
+    <t>Hyundai Motor Group has the highest total employment with 8100 employees at Superior Essex Inc. Rivian Automotive has 7500 employees at Suzuki Manufacturing of America Corp. Kia Georgia Inc. has 777 employees at Kia Georgia Inc. and 3000 employees at TCI Powder Coatings.</t>
+  </si>
+  <si>
+    <t>I cannot answer this question without the specific workbook data. To determine which Primary OEM has the highest total employment, I would need to analyze the "Primary OEM" and "Employment" columns within your workbook, filter out any blank entries, and then sum the employment for each OEM.</t>
+  </si>
+  <si>
+    <t>Identify any companies that supply to more than one OEM based on the Primary OEMs field (e.g., entries like 'Hyundai Kia Rivian') and list them.</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question. I do not have access to the Excel workbook and therefore cannot identify companies based on the "Primary OEMs" field.</t>
+  </si>
+  <si>
+    <t>Based on the "Primary OEMs" field, there are no companies that supply to more than one OEM. The "Primary OEMs" field lists only one OEM per company in the provided evidence.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 17.132225972s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '17s'}]}}</t>
+  </si>
+  <si>
+    <t>Among companies linked to 'Hyundai Kia Rivian', list their EV Supply Chain Role and Product / Service.</t>
+  </si>
+  <si>
+    <t>Hyundai Kia Rivian [5]: Duckyang | EV Supply Chain Role: General Automotive | Product / Service: High-quality electrodeposited (ED) copper foil for electric vehicles Enchem America Inc. | EV Supply Chain Role: General Automotive | Product / Service: Electric wiring components GSC Steel Stamping LLC | EV Supply Chain Role: Power Electronics | Product / Service: Deep grove ball bearings Toyota Industries Electric Systems North 255 DC-to-DC converters Jackson America, Inc.* Hyundai Transys Georgia Powertrain | EV Supply Chain Role: Thermal Management | Product / Service: Electrical heaters, control units, and actuators Racemark International LLC | EV Supply Chain Role: General Automotive | Product / Service: Manufacturing and R&amp;D engine parts for EV</t>
+  </si>
+  <si>
+    <t>Find all companies linked to Porsche Cars North America Inc. and provide their Location and Employment.</t>
+  </si>
+  <si>
+    <t>Linked to Porsche Cars North America Inc. [1]: Minebea AccessSolutions USA Inc. | Location: Atlanta, Fulton County | Employment: 400 | Category: OEM | EV Supply Chain Role: General Automotive</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the relevant Excel workbook. The question asks for specific details (linked companies, locations, and employment numbers) that can only be found within a data source.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 16.214095422s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '16s'}]}}</t>
+  </si>
+  <si>
+    <t>Club Car LLC: 
+- Kia Georgia Inc. (Vehicle Assembly)
+Porsche Cars North America Inc.: 
+- Minebea AccessSolutions USA Inc. (General Automotive)
+Hyundai Motor Group: 
+- Superior Essex Inc. (Vehicle Assembly)
+Rivian Automotive: 
+- Suzuki Manufacturing of America Corp. (Vehicle Assembly)
+Kia Georgia Inc.: 
+- TCI Powder Coatings (Vehicle Assembly)
+Mercedes-Benz USA LLC: 
+- TDK Components USA Inc. (Vehicle Assembly)</t>
+  </si>
+  <si>
+    <t>To answer this question without specific workbook evidence, I'll need to assume a hypothetical scenario based on common practices in Excel data handling. Typically, if you have a list of Primary OEMs and companies associated with them, you would use a pivot table or a COUNTIFS formula to count the number of unique companies for each Primary OEM.
+Without seeing the actual data, my best general answer is that you'd follow these steps:
+1. Ensure your data has two columns: one for "Primary OEM" and another for "Company Name".
+2. Use Excel's PivotTable feature:
+   - Select your data range.
+   - Insert a PivotTable.
+   - Place "Primary OEM" in the Rows area of the PivotTable.
+   - Place "Company Name" in the Values area, making sure to set it to count unique values.
+If you don't have access to such features or prefer formulas:
+- Use `COUNTIFS` with an array formula if counting unique companies manually (this requires Excel 365 or later for dynamic arrays).
+Since I can't see your specific data, the exact counts cannot be provided. However, this method should give you a clear count of how many distinct companies are associated with each Primary OEM listed in your workbook.
+If you need further assistance with formulas or pivot tables based on hypothetical sample data, feel free to ask!</t>
+  </si>
+  <si>
+    <t>Here's the count of companies associated with each Primary OEM, based on the provided evidence:
+*   **Club Car LLC:** 1 (Kia Georgia Inc.)
+*   **Porsche Cars North America Inc.:** 1 (Minebea AccessSolutions USA Inc.)
+*   **Hyundai Motor Group:** 1 (Superior Essex Inc.)
+*   **Rivian Automotive:** 1 (Suzuki Manufacturing of America Corp.)
+*   **Kia Georgia Inc.:** 1 (TCI Powder Coatings)
+*   **Mercedes-Benz USA LLC:** 1 (TDK Components USA Inc.)
+The workbook evidence is incomplete, as there may be other Primary OEMs and associated companies not listed.</t>
+  </si>
+  <si>
+    <t>The workbook evidence is incomplete for this question as it does not provide a list of all Primary OEMs and their associated companies. However, based on the provided evidence, here are the Primary OEMs and the companies associated with them:
+*   **Club Car LLC:**
+    *   Kia Georgia Inc.
+*   **Porsche Cars North America Inc.:**
+    *   Minebea AccessSolutions USA Inc.
+*   **Hyundai Motor Group:**
+    *   Superior Essex Inc.
+*   **Rivian Automotive:**
+    *   Suzuki Manufacturing of America Corp.
+*   **Kia Georgia Inc.:**
+    *   TCI Powder Coatings
+*   **Mercedes-Benz USA LLC:**
+    *   TDK Components USA Inc.
+*   **Multiple OEMs:**
+    *   Freudenberg-NOK</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I cannot definitively determine which Primary OEM has the highest total Employment. However, generally, larger, more established OEMs like Ford, General Motors, Toyota, or Stellantis would likely have the highest employment numbers due to the scale of their operations and the number of companies they encompass.
+Please provide the workbook if you need a precise answer based on the data within.</t>
+  </si>
+  <si>
+    <t>Based on the provided evidence, the Primary OEMs and their associated companies and employment are:
+*   **Hyundai Motor Group:**
+    *   Superior Essex Inc.: 8100
+*   **Rivian Automotive:**
+    *   Suzuki Manufacturing of America Corp.: 7500
+*   **Kia Georgia Inc.:**
+    *   TCI Powder Coatings: 3000
+*   **Club Car LLC:**
+    *   Kia Georgia Inc.: 777
+*   **Mercedes-Benz USA LLC:**
+    *   TDK Components USA Inc.: 1000
+*   **Porsche Cars North America Inc.:**
+    *   Minebea AccessSolutions USA Inc.: 400
+The workbook evidence is incomplete as it only provides a partial list of companies and their primary OEMs. Therefore, a definitive answer to which Primary OEM has the highest total employment cannot be provided.</t>
+  </si>
+  <si>
+    <t>Companies supplying to more than one OEM based on the Primary OEMs field: Hyundai Kia [6]: F&amp;P Georgia Manufacturing (Tier 1/2; Battery Pack; Toccoa, Stephens County); Hitachi Astemo Americas Inc. (Tier 1/2; Battery Cell; Coweta County); Hollingsworth &amp; Vose Co. (Tier 1/2; Battery Pack; Bainbridge, Decatur County); Honda Development &amp; Manufacturing (Tier 1/2; Battery Cell; Pembroke, Bryan County); Hyundai Motor Group (Tier 1/2; Battery Pack; McDonough, Henry County); IMMI (Tier 1/2; Battery Pack; Jefferson, Jackson County) Hyundai Kia Rivian [5]: Duckyang (Tier 2/3; General Automotive; Augusta, Richmond County); Enchem America Inc. (Tier 2/3; General Automotive; Cumming, Forsyth County); GSC Steel Stamping LLC (Tier 2/3; Power Electronics; Gainesville, Hall County); Hyundai Transys Georgia Powertrain (Tier 1/2; Thermal Management; Dublin, Laurens County); Racemark International LLC (Tier 1; General Automotive; Calhoun, Gordon County) Multiple OEMs [156]: ACM Georgia LLC (Tier 2/3; General Automotive; Calhoun, Gordon County); ADVICS Manufacturing Georgia LLC (Tier 2/3; General Automotive; Troup County); ALBAform Inc. (Tier 2/3; General Automotive; Calhoun, Gordon County); AVS (Tier 2/3; General Automotive; Barnesville, Lamar County); Adient (Tier 2/3; General Automotive; Ringgold, Catoosa County); Ajin Georgia (Tier 2/3; General Automotive; Dalton, Whitfield County); Anovion Technologies (Tier 2/3; General Automotive; Dalton, Whitfield County); Apache Mills Inc. (Tier 2/3; General Automotive; Hawkinsville, Pulaski County); Aptiv (Tier 2/3; General Automotive; Statesboro, Bulloch County); Archer Aviation Inc. (Tier 2/3; General Automotive; Ellaville, Schley County); Arising Industries Inc. (Tier 2/3; General Automotive; Lawrenceville, Gwinnett County); Arising Industries Inc. (Tier 2/3; General Automotive; Macon, Bibb County); Ascend Elements (Tier 2/3; Materials; Statesboro, Bulloch County); Aspen Aerogels (Tier 2/3; Materials; Troup County); Aurubis (Tier 2/3; Materials; Troup County); Beaver Manufacturing Co. Inc. (Tier 2/3; Materials; Griffin, Spalding County); Big Tex Trailer Manufacturing Inc. (Tier 2/3; General Automotive; Monroe, Walton County); Blue Bird Corp. (Tier 2/3; Materials; Elberton, Elbert County); Blue Ridge Manufacturing (Tier 2/3; Materials; Canton, Cherokee County); Bonnell Aluminum (Tier 2/3; General Automotive; Troup County); Boogook Industries (Tier 2/3; Materials; Gainesville, Hall County); Bosal Industries Georgia (Tier 2/3; General Automotive; Rome, Floyd County); Bosch (Automotive Division) (Tier 2/3; Materials; Thomson, McDuffie County); Bridgestone Bandag (Tier 2/3; Materials; Augusta, Richmond County); Carcoustics USA (Tier 2/3; General Automotive; Griffin, Spalding County); Club Car LLC (Tier 2/3; Materials; Madison, Morgan County); Constellium Automotive USA (Tier 2/3; Materials; Cartersville, Bartow County); Continental Automotive (Tier 2/3; General Automotive; Jasper, Pickens County); Continental Tire the Americas LLC (Tier 2/3; General Automotive; Lawrenceville, Gwinnett County); DAEHAN Solution Georgia LLC (Tier 2/3; Materials; Covington, Newton County); DAS Corp. (Tier 2/3; Materials; Gainesville, Hall County); DaeChang Seat Company (Tier 2/3; General Automotive; Decatur, DeKalb County); Daesol Ausys (Tier 2/3; Materials; Marietta, Cobb County); Daesol Material Georgia, LLC (Tier 2/3; General Automotive; Lawrenceville, Gwinnett County); Daimler Truck North America (Tier 2/3; General Automotive; Covington, Newton County); DeKalb Tool &amp; Die Inc. (Tier 2/3; General Automotive; Calhoun, Gordon County); Decostar Industries (Tier 2/3; General Automotive; Buchanan, Haralson County); Denkai America (Tier 2/3; General Automotive; Cumming, Forsyth County); Denso Manufacturing Georgia (Tier 2/3; General Automotive; Troup County); Die-Tech Industries Inc. (Tier 2/3; General Automotive; Hinesville, Liberty County); Dinex Emissions Inc. (Tier 2/3; General Automotive; Greensboro, Greene County); Dongwon Autopart Technology Georgia LLC (Tier 2/3; General Automotive; Coweta County); Dorsett Industries Inc. (Tier 2/3; General Automotive; Franklin, Heard County); Down 2 Earth Trailers (Tier 2/3; General Automotive; Cartersville, Bartow County); EVCO Plastics (Tier 2/3; Materials; Augusta, Richmond County); Eaton Corp. (Tier 2/3; General Automotive; Cartersville, Bartow County); Ecoplastic America Corporation (Tier 2/3; General Automotive; Greensboro, Greene County); Ecoplastic Corporation (Tier 2/3; General Automotive; Rome, Floyd County); Elan Technology Inc. (Tier 2/3; General Automotive; Atlanta, Fulton County); Enplas USA Inc. (Tier 2/3; General Automotive; Covington, Newton County); Erdrich USA Inc. (Tier 2/3; General Automotive; Greensboro, Greene County); FOX Factory (Tier 2/3; General Automotive; Covington, Newton County); FREYR Battery (Tier 2/3; General Automotive; Marietta, Cobb County); Fanello Industries Inc. (Tier 2/3; Materials; Cumming, Forsyth County); First American Resources (Tier 2/3; Materials; Albany, Dougherty County); Flambeau Inc. (Tier 2/3; General Automotive; Carroll County); Fouts Brothers Fire Equipment (Tier 1/2; General Automotive; Statesboro, Bulloch County); Freudenberg-NOK (Tier 2/3; General Automotive; Warrenton, Warren County); Freudenberg-NOK (Tier 2/3; Thermal Management; Carnesville, Franklin County); GEDIA Georgia LLC (Tier 2/3; General Automotive; Jonesboro, Clayton County); GLOVIS Georgia LLC (Tier 2/3; General Automotive; Dublin, Laurens County); Global Powertrain Systems LLC (Tier 2/3; General Automotive; Rome, Floyd County); Goodyear Tire &amp; Rubber Co. (Tier 2/3; General Automotive; Athens, Clarke County); Great Dane LP (Tier 2/3; General Automotive; Muscogee County); Great Dane Trailers (Tier 2/3; General Automotive; Tifton, Tift County); Grudem (Tier 2/3; General Automotive; Lawrenceville, Gwinnett County); HELLA Automotive Sales Inc. (Tier 2/3; General Automotive; Gainesville, Hall County); HEXPOL Compounding Corp. (Tier 2/3; General Automotive; Decatur, DeKalb County); Haering Precision USA LP (Tier 2/3; General Automotive; Carroll County); Haering Precision USA LP (Tier 2/3; Materials; Dahlonega, Lumpkin County); Hitachi Astemo (Tier 1/2; General Automotive; Fayetteville, Fayette County); Hwashin (Tier 1/2; General Automotive; Jefferson, Jackson County); Hyundai &amp; LG Energy Solution (LGES) (Tier 1/2; General Automotive; Cumming, Forsyth County); Hyundai Industrial Co. (Tier 1/2; General Automotive; Valdosta, Lowndes County); Hyundai MOBIS (Georgia) (Tier 1/2; General Automotive; Fayetteville, Fayette County); Hyundai Transys Georgia Seating Systems (Tier 1/2; General Automotive; Marietta, Cobb County); IMS Gear Georgia Inc. (Tier 1/2; General Automotive; Fayetteville, Fayette County); Inalfa Roof Systems Inc. (Tier 1/2; General Automotive; Lawrenceville, Gwinnett County); JAC Products Inc. (Tier 1/2; General Automotive; Clarkesville, Habersham County); JTEKT North America Corp. (Tier 1; General Automotive; Canton, Cherokee County); Jefferson Southern Corp. (Tier 1/2; General Automotive; Dahlonega, Lumpkin County); Jefferson Southern Corporation (Tier 1; General Automotive; Monroe, Walton County); Joon Georgia, Inc. (Tier 1; General Automotive; Troup County); KTX America Corporation (Tier 1; General Automotive; Springfield, Effingham County); Kautex Inc. (Tier 1; General Automotive; Carroll County); Kumho Tire USA Inc. (Tier 1; General Automotive; Troup County); Kyungshin America Corp. (Tier 1; General Automotive; Troup County); Lark United Manufacturing Inc. (Tier 1; General Automotive; Gainesville, Hall County); Lear Corporation (Tier 1; General Automotive; Cartersville, Bartow County); Lehigh Technologies Inc. (Tier 1; General Automotive; Rome, Floyd County); Linde + Wiemann (Tier 1; General Automotive; Troup County); Lund International Inc. (Tier 1; General Automotive; Savannah, Chatham County); Lund International Inc./Ventshade Division (Tier 1; General Automotive; Statesboro, Bulloch County); Lyle Industries Inc. (Tier 1; General Automotive; Buchanan, Haralson County); Lyle Industries Inc. (Tier 1; General Automotive; Rome, Floyd County); MAT Heavy Duty (Tier 1; General Automotive; Lawrenceville, Gwinnett County); Mack Trucks (Tier 1; General Automotive; Savannah, Chatham County); Magna International (Tier 1; General Automotive; Augusta, Richmond County); Mando America Corp. (Tier 1; General Automotive; Dublin, Laurens County); Master Craft Engineering Inc. (Tier 1; General Automotive; Savannah, Chatham County); Maxxis International USA (Tier 1; General Automotive; La Fayette, Walker County); Mercedes-Benz USA LLC (Tier 1; General Automotive; Cedartown, Polk County); Michelin Tread Technologies (Tier 1; General Automotive; Lawrenceville, Gwinnett County); Milliken &amp; Co./Valway Plant (Tier 1; General Automotive; Greenville, Meriwether County); Mobis Alabama LLC (Tier 1; General Automotive; Gainesville, Hall County); MollerTech LLC (Tier 1; General Automotive; Toccoa, Stephens County); Morgan Corp. (Tier 1; Charging Infrastructure; Lawrenceville, Gwinnett County); Murata Electronics North America Inc. (Tier 1; General Automotive; Covington, Newton County); NIFCO KTW America Corp. (Tier 1; General Automotive; Troup County); NVH Korea (Tier 1; General Automotive; Greenville, Meriwether County); Neaton Rome Inc. (Tier 1; General Automotive; Hamilton, Harris County); Nidec Elesys Americas Corp. (Tier 1; General Automotive; Metter, Candler County); Nile Automotive (Tier 1; General Automotive; Dalton, Whitfield County); Nisshinbo Automotive Manufacturing Inc. (Tier 1; General Automotive; Gainesville, Hall County); Nivel Parts &amp; Manufacturing Co. LLC (Tier 1; General Automotive; Savannah, Chatham County); Novelis Inc. (Tier 1; General Automotive; Gainesville, Hall County); Novelis Inc. (Tier 1; General Automotive; Trenton, Dade County); Novelis Inc. (Tier 1; Thermal Management; Lawrenceville, Gwinnett County); OTR Wheel Engineering Inc. (Tier 1; General Automotive; Cordele, Crisp County); Oneda Corp. (Tier 1; General Automotive; Dalton, Whitfield County); PAI Industries Inc. (Tier 1; General Automotive; Troup County); PHA Body Systems LLC (Tier 1; Materials; Carroll County); PIOLAX Corp. (Tier 1; General Automotive; Rome, Floyd County); PPG Industries Inc. (Tier 1; General Automotive; Troup County); Paccar (Tier 1; General Automotive; Trenton, Dade County); Pak-Lite Inc. (Tier 1; General Automotive; Rome, Floyd County); Panasonic Automotive Systems Co. (Tier 1; General Automotive; Hinesville, Liberty County); Panasonic Automotive Systems Co. (Tier 1; Materials; Cartersville, Bartow County); Panduit Corp. (Tier 1; General Automotive; Cartersville, Bartow County); Peerless-Winsmith Inc. (Tier 1; Thermal Management; Statesboro, Bulloch County); Peterson Spring (Tier 1; General Automotive; Hartwell, Hart County); Piedmont Automotive Products Inc. (Tier 1; General Automotive; Hamilton, Harris County); Pirelli Tire North America LLC (Tier 1; General Automotive; Carnesville, Franklin County); Porsche Cars North America Inc. (Tier 1; General Automotive; Cairo, Grady County); Propex Operating Co. LLC (Tier 1; General Automotive; Lawrenceville, Gwinnett County); QSR Inc. (Tier 1; General Automotive; Lawrenceville, Gwinnett County); RealTruck (Tier 1; General Automotive; Fayetteville, Fayette County); Rivian Automotive (Tier 1; General Automotive; Gainesville, Hall County); Robert Bosch LLC (Tier 1; General Automotive; Coweta County); SAFT America Inc. (Tier 1; General Automotive; Coweta County); SK Battery America (Tier 1; Materials; Hartwell, Hart County); SKF USA Inc. (Tier 1; General Automotive; Carnesville, Franklin County); SRG Global Inc. (Tier 1; General Automotive; Atlanta, Fulton County); Sejong Georgia LLC (Tier 1; General Automotive; Troup County); Seohan Auto USA (Tier 1; General Automotive; Hazlehurst, Davis County); Seoyon E-HWA (Tier 1; General Automotive; Hazlehurst, Davis County); Seoyon E-Hwa Interior Systems (Tier 1; General Automotive; Macon, Bibb County); Sewon America Inc. (Tier 1; General Automotive; Atlanta, Fulton County); Sewon America Inc. (Tier 1; General Automotive; Athens, Clarke County); Sewon America Inc. (Tier 1; General Automotive; Marietta, Cobb County); Solvay Specialty Polymers USA LLC (Tier 1; General Automotive; Springfield, Effingham County); Southern Switches Corp. (Tier 1; General Automotive; Blue Ridge, Fannin County); Stryten Energy (Tier 1; General Automotive; Troup County); Suhner Manufacturing Corp. (Tier 1; General Automotive; Douglas, Coffee County); Sumitomo Electric Wiring Systems (Tier 1; Materials; Baxley, Appling County); SungEel Recycling Park Georgia (Tier 2/3; Materials; Macon, Bibb County)</t>
+  </si>
+  <si>
+    <t>Superior Essex Inc. | Primary OEMs: Hyundai Motor Group  
+Suzuki Manufacturing of America Corp. | Primary OEMs: Rivian Automotive  
+TCI Powder Coatings | Primary OEMs: Kia Georgia Inc.  
+Note: The provided evidence does not list companies supplying to more than one distinct OEM directly, but TCI Powder Coatings is listed with a primary OEM relationship to Kia Georgia Inc., which itself supplies Club Car LLC according to the evidence.</t>
+  </si>
+  <si>
+    <t>To identify companies that supply to more than one Original Equipment Manufacturer (OEM) based on a "Primary OEMs" field, we would look for entries where a company is listed as supplying parts or services to multiple OEMs. For example, if the entry in the "Primary OEMs" field includes names like 'Hyundai Kia Rivian', it suggests that the company supplies to at least three different OEMs: Hyundai, Kia, and Rivian.
+Without specific workbook data, I can't provide an exact list of companies. However, a general approach would be:
+1. **Identify Entries with Multiple OEM Names**: Look for entries in the "Primary OEMs" field that contain more than one company name separated by spaces or other delimiters.
+2. **List Companies**: Extract and list each unique supplier company from those identified entries.
+If you have specific data or a pattern of how companies are listed (e.g., CompanyName: Hyundai Kia Rivian), I could provide a more tailored response based on that format.</t>
+  </si>
+  <si>
+    <t>The following companies supply to more than one OEM:
+*   Kia Georgia Inc. (Primary OEMs: Club Car LLC) supplies to TCI Powder Coatings.
+*   Minebea AccessSolutions USA Inc. (Primary OEMs: Porsche Cars North America Inc.)
+*   Superior Essex Inc. (Primary OEMs: Hyundai Motor Group)
+*   Suzuki Manufacturing of America Corp. (Primary OEMs: Rivian Automotive)
+*   TDK Components USA Inc. (Primary OEMs: Mercedes-Benz USA LLC)</t>
+  </si>
+  <si>
+    <t>**General Automotive**
+- Racemark International LLC | Manufacturing and R&amp;D engine parts for EV
+- Duckyang | High-quality electrodeposited (ED) copper foil for electric vehicles
+- Enchem America Inc. | Electric wiring components
+**Power Electronics**
+- GSC Steel Stamping LLC | Deep grove ball bearings Toyota Industries Electric Systems North 255 DC-to-DC converters Jackson America, Inc.*
+**Thermal Management**
+- Hyundai Transys Georgia Powertrain | Electrical heaters, control units, and actuators
+**Battery Cell**
+- Hitachi Astemo Americas Inc. | Battery cells for electric mobility
+**Battery Pack**
+- F&amp;P Georgia Manufacturing | Lithium-ion battery recycler and raw materials provider
+- Hollingsworth &amp; Vose Co. | Lithium-ion battery materials</t>
+  </si>
+  <si>
+    <t>The query about "Hyundai Kia Rivian" involves multiple automotive companies that are known for electric vehicles (EVs) or have partnerships in the EV supply chain. However, without specific workbook evidence detailing each company's exact role and product/service related to their link with Hyundai, Kia, and Rivian, I can provide general information based on public knowledge:
+1. **Hyundai Motor Company**:
+   - **Role**: OEM (Original Equipment Manufacturer)
+   - **Product/Service**: Produces a range of electric vehicles including the Kona Electric, Ioniq 5, and Ioniq 6.
+2. **Kia Corporation**:
+   - **Role**: OEM
+   - **Product/Service**: Offers EV models such as the Niro EV, EV6, and Soul EV.
+3. **Rivian Automotive LLC**:
+   - **Role**: Newer entrant in the EV market focusing on electric trucks and SUVs.
+   - **Product/Service**: Known for its R1T pickup truck and R1S SUV models.
+Regarding specific supply chain roles of companies linked to these three, it would typically include suppliers providing batteries (like LG Energy Solution), components (such as electronics from Samsung SDI or Bosch), and other parts necessary for EV production. However, without detailed information about the exact companies in question and their specific roles within the supply chains of Hyundai, Kia, and Rivian, I cannot list them precisely.
+For a more accurate answer tailored to your workbook data, you would need to specify which companies are being referred to or provide additional context regarding their roles and products/services.</t>
+  </si>
+  <si>
+    <t>Here's a list of companies linked to 'Hyundai Kia Rivian', along with their EV Supply Chain Role and Product / Service:
+*   **Racemark International LLC:** General Automotive, Manufacturing and R&amp;D engine parts for EV
+*   **GSC Steel Stamping LLC:** Power Electronics, Deep grove ball bearings Toyota Industries Electric Systems North 255 DC-to-DC converters Jackson America, Inc.*
+*   **Hyundai Transys Georgia Powertrain:** Thermal Management, Electrical heaters, control units, and actuators
+*   **Duckyang:** General Automotive, High-quality electrodeposited (ED) copper foil for electric vehicles
+*   **Enchem America Inc.:** General Automotive, Electric wiring components
+*   **F&amp;P Georgia Manufacturing:** Battery Pack, Lithium-ion battery recycler and raw materials provider
+*   **Hitachi Astemo Americas Inc.:** Battery Cell, Battery cells for electric mobility
+*   **Hollingsworth &amp; Vose Co.:** Battery Pack, Lithium-ion battery materials</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I can provide a general answer based on common knowledge about the EV supply chain and these companies. Here's a breakdown of potential roles and products/services, recognizing this might not perfectly align with the workbook's specific data:
+**1. Hyundai Kia:**
+*   **EV Supply Chain Role:** Primarily *Automaker/Vehicle Manufacturer*. They are designing, manufacturing, and selling electric vehicles. They also act as *Integrator*, assembling components from various suppliers.
+*   **Product/Service:** Electric Vehicles (e.g., Hyundai IONIQ 5, Kia EV6, Hyundai IONIQ 6), EV components (in some cases, they may produce their own batteries or motors), and related services (charging infrastructure, maintenance).
+**2. Rivian:**
+*   **EV Supply Chain Role:** *Automaker/Vehicle Manufacturer*. Similar to Hyundai Kia, Rivian designs, manufactures, and sells electric vehicles. They also act as an *Integrator*.
+*   **Product/Service:** Electric Vehicles (R1T pickup truck, R1S SUV, Electric Delivery Van), battery packs, electric motors, and related services (charging network, vehicle software).
+**Common Suppliers &amp; Potential Roles (linked to Hyundai Kia Rivian):**
+Many companies supply components to all three, so these roles are often overlapping. Here are some examples:
+*   **Battery Manufacturers (e.g., LG Energy Solution, SK Innovation, CATL):** *Tier 1 Supplier*. Provide battery cells and packs.
+*   **Semiconductor Manufacturers (e.g., Samsung, SK Hynix, Texas Instruments):** *Tier 1 Supplier*. Provide chips for vehicle control, battery management, and infotainment.
+*   **Raw Material Suppliers (e.g., Lithium producers, Cobalt miners):** *Tier 2/3 Supplier*. Provide raw materials for battery production.
+*   **Electric Motor Suppliers (e.g., Magna, Bosch):** *Tier 1 Supplier*. Provide electric motors.
+*   **Charging Infrastructure Providers (e.g., ChargePoint, EVgo):** *Service Provider*. Provide charging stations and related services.
+**Important Note:** The specific roles and products/services listed in the workbook could be more granular or specialized. Without the workbook data, this is a general overview.</t>
+  </si>
+  <si>
+    <t>* **General Automotive**
+  * Racemark International LLC: Manufacturing and R&amp;D engine parts for EV
+  * Duckyang: High-quality electrodeposited (ED) copper foil for electric vehicles
+  * Enchem America Inc.: Electric wiring components
+* **Power Electronics**
+  * GSC Steel Stamping LLC: Deep grove ball bearings Toyota Industries Electric Systems North 255 DC-to-DC converters Jackson America, Inc.*
+* **Thermal Management**
+  * Hyundai Transys Georgia Powertrain: Electrical heaters, control units, and actuators</t>
+  </si>
+  <si>
+    <t>I cannot provide specific details about companies linked to 'Hyundai Kia Rivian' and their EV Supply Chain Role and Product/Service without access to the workbook. My knowledge is limited to general information and I cannot browse the internet for real-time data. 
+If you can provide the content of the workbook, I would be happy to help you extract that information.</t>
+  </si>
+  <si>
+    <t>**General Automotive**
+- **Minebea AccessSolutions USA Inc.**
+  - Location: Atlanta, Fulton County
+  - Employment: 400
+**Indirect (Aftermarket automotive accessories)**
+- **Porsche Cars North America Inc.**
+  - Location: Cairo, Grady County
+  - Employment: 125</t>
+  </si>
+  <si>
+    <t>To find all companies linked to Porsche Cars North America Inc., including their locations and employment numbers, I would typically need specific data from an Excel workbook or a similar database that contains such information. Since no specific workbook evidence is provided here, I can't give exact details about the linked companies, their locations, and employment figures.
+However, generally speaking, companies linked to Porsche Cars North America Inc. might include parent companies like Porsche AG (headquartered in Stuttgart, Germany), subsidiaries, dealerships, suppliers, or partners. Each of these would have its own location and employment numbers which can vary widely depending on the specific company's role within the Porsche network.
+For precise information, you would need to consult official corporate reports, financial statements, or a detailed organizational chart provided by Porsche Cars North America Inc. or related entities.</t>
+  </si>
+  <si>
+    <t>Here are the companies linked to Porsche Cars North America Inc., along with their Location and Employment:
+*   **Minebea AccessSolutions USA Inc.**, Location: Atlanta, Fulton County, Employment: 400
+*   **Voestalpine Automotive Body Parts Inc.**, Location: Georgia, Employment: 1300
+*   **Vanguard National Trailer Corp.**, Location: Georgia, Employment: 630</t>
+  </si>
+  <si>
+    <t>Porsche Cars North America Inc. is linked to the following companies:
+*   **Minebea AccessSolutions USA Inc.**
+    *   Location: Atlanta, Fulton County
+    *   Employment: 400</t>
+  </si>
+  <si>
+    <t>Which OEM-linked entries are missing Supplier or Affiliation Type, and what are their Categories?</t>
+  </si>
+  <si>
+    <t>OEM-linked entries missing Supplier or Affiliation Type: None</t>
+  </si>
+  <si>
+    <t>Vehicle Assembly:
+- Kia Georgia Inc. | Category: OEM
+- Superior Essex Inc. | Category: OEM
+- Suzuki Manufacturing of America Corp. | Category: OEM
+- TCI Powder Coatings | Category: OEM
+General Automotive:
+- Minebea AccessSolutions USA Inc. | Category: OEM
+Vehicle Assembly (indirect relevance):
+- TDK Components USA Inc. | Category: OEM</t>
+  </si>
+  <si>
+    <t>Without specific workbook evidence, I can't provide an exact list of OEM-linked entries that are missing either the Supplier or Affiliation Type fields. However, generally speaking, if you're looking for entries in a dataset where certain information is incomplete (such as missing Supplier or Affiliation Type), you would typically filter your data to find rows where these specific columns have no value or contain placeholders like "N/A" or are blank.
+For the Categories of such entries, you'd look at the Category column corresponding to those same rows. If you could provide more details about the structure of your workbook or dataset, I could give a more precise answer based on common practices for handling incomplete data in Excel workbooks.</t>
+  </si>
+  <si>
+    <t>The following OEM-linked entries are missing Supplier or Affiliation Type: 
+- Kia Georgia Inc., Category: OEM
+- Minebea AccessSolutions USA Inc., Category: OEM
+- Superior Essex Inc., Category: OEM
+- Suzuki Manufacturing of America Corp., Category: OEM
+- TCI Powder Coatings, Category: OEM
+- TDK Components USA Inc., Category: OEM</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I cannot identify the specific OEM-linked entries missing Supplier or Affiliation Type, nor their Categories. This information is contained within the data itself.</t>
+  </si>
+  <si>
+    <t>The following OEM-linked entries are missing 'Supplier or Affiliation Type':
+*   **Kia Georgia Inc.**
+    *   Category: OEM
+*   **Minebea AccessSolutions USA Inc.**
+    *   Category: OEM
+*   **Superior Essex Inc.**
+    *   Category: OEM
+*   **Suzuki Manufacturing of America Corp.**
+    *   Category: OEM
+*   **TCI Powder Coatings**
+    *   Category: OEM
+*   **TDK Components USA Inc.**
+    *   Category: OEM
+*   **Teklas USA**
+    *   Category: OEM</t>
+  </si>
+  <si>
+    <t>I cannot answer this question without the workbook. The question asks for specific entries that are missing certain information and their categories, which requires direct access to and analysis of the data within the workbook.</t>
+  </si>
+  <si>
+    <t>Which 10 companies have the highest Employment, and what are their Categories and Locations?</t>
+  </si>
+  <si>
+    <t>Top 10 companies by Employment: 1. WIKA USA | Employment: 250,000 | Category: OEM Supply Chain | Location: Georgia 2. Yazaki North America | Employment: 230,000 | Category: OEM Footprint | Location: Georgia 3. YKK USA Inc. | Employment: 190,159 | Category: OEM Footprint | Location: Georgia 4. Yamaha Motor Manufacturing Corp. | Employment: 190,000 | Category: OEM Supply Chain | Location: Georgia 5. Yachiyo Manufacturing of America LLC | Employment: 173,700 | Category: OEM Supply Chain | Location: Georgia 6. ZF Gainesville LLC | Employment: 170,000 | Category: OEM Supply Chain | Location: Georgia 7. ZF Gainesville LLC | Employment: 106,100 | Category: OEM Footprint | Location: Georgia 8. Woory Industrial Co. | Employment: 87,000 | Category: OEM Supply Chain | Location: Georgia 9. TI Fluid Systems | Employment: 19,600 | Category: OEM (Footprint) | Location: Atlanta, Fulton County 10. TN Americas Holding Inc. | Employment: 19,600 | Category: OEM (Footprint) | Location: Georgia</t>
+  </si>
+  <si>
+    <t>Yazaki North America | Category: OEM Footprint | Location: Georgia | Employment: 230,000  
+Toyota Industries Group (TACG-TICA) | Category: OEM (Footprint) | Location: Georgia | Employment: 18,100  
+TN Americas Holding Inc. | Category: OEM (Footprint) | Location: Georgia | Employment: 19,600  
+The provided evidence does not include enough companies to list the top 10 by employment. The above are the highest based on available data.</t>
+  </si>
+  <si>
+    <t>To provide a specific list of the top 10 companies by employment along with their categories and locations based on an Excel workbook, I would need access to that particular dataset. However, generally speaking, if you had such data in an Excel workbook, you could use functions like `SORT`, `FILTER`, or pivot tables to identify these details.
+For example:
+- Company A: Category - Technology; Location - San Francisco
+- Company B: Category - Finance; Location - New York City
+Without the actual workbook data, I can't provide exact names and figures. If you have an Excel file with this information, using sorting functions or pivot tables would help you extract these details efficiently.</t>
+  </si>
+  <si>
+    <t>Here are the 10 companies with the highest employment, their Categories, and Locations, based on the provided evidence:
+1.  **Yazaki North America:** Category: OEM Footprint, Location: Georgia, Employment: 230000
+2.  **TN Americas Holding Inc.:** Category: OEM (Footprint), Location: Georgia, Employment: 19600
+3.  **Toyota Industries Group (TACG-TICA):** Category: OEM (Footprint), Location: Georgia, Employment: 18100
+4.  **Trenton Pressing:** Category: OEM (Footprint), Location: Georgia, Employment: 350
+5.  **Wabash National Corp.:** Category: OEM Supply Chain, Location: Georgia, Employment: 20
+6.  **GLOVIS Georgia LLC:** Category: Tier 2/3, Location: Dublin, Laurens County, Employment: 90
+7.  **Bosch (Automotive Division):** Category: Tier 2/3, Location: Thomson, McDuffie County, Employment: 250
+8.  **DeKalb Tool &amp; Die Inc.:** Category: Tier 2/3, Location: Calhoun, Gordon County, Employment: 70</t>
+  </si>
+  <si>
+    <t>I am sorry, but I do not have access to the data needed to answer your question. I do not have information about company employment numbers, categories, or locations.</t>
+  </si>
+  <si>
+    <t>The top 10 companies with the highest employment, along with their categories and locations, are:
+1.  **Yazaki North America**:
+    *   Employment: 230,000
+    *   Category: OEM Footprint
+    *   Location: Georgia
+2.  **Toyota Industries Group (TACG-TICA)**:
+    *   Employment: 18,100
+    *   Category: OEM (Footprint)
+    *   Location: Georgia
+3.  **TN Americas Holding Inc.**:
+    *   Employment: 19,600
+    *   Category: OEM (Footprint)
+    *   Location: Georgia
+4.  **Trenton Pressing**:
+    *   Employment: 350
+    *   Category: OEM (Footprint)
+    *   Location: Georgia
+5.  **Bosch (Automotive Division)**:
+    *   Employment: 250
+    *   Category: Tier 2/3
+    *   Location: Thomson, McDuffie County
+6.  **GLOVIS Georgia LLC**:
+    *   Employment: 90
+    *   Category: Tier 2/3
+    *   Location: Dublin, Laurens County
+7.  **DeKalb Tool &amp; Die Inc.**:
+    *   Employment: 70
+    *   Category: Tier 2/3
+    *   Location: Calhoun, Gordon County
+8.  **Wabash National Corp.**:
+    *   Employment: 20
+    *   Category: OEM Supply Chain
+    *   Location: Georgia</t>
+  </si>
+  <si>
+    <t>I cannot answer this question without access to the workbook. The question asks for specific data about companies, their employment numbers, categories, and locations, which are all contained within the workbook.</t>
+  </si>
+  <si>
+    <t>Which 10 companies have the lowest Employment, and what are their EV Supply Chain Roles?</t>
+  </si>
+  <si>
+    <t>Bottom 10 companies by Employment: 1. Wabash National Corp. | Employment: 20 | EV Supply Chain Role: Interior and exterior plastic parts 2. Denkai America | Employment: 50 | EV Supply Chain Role: General Automotive 3. Great Dane Trailers | Employment: 50 | EV Supply Chain Role: General Automotive 4. HEXPOL Compounding Corp. | Employment: 50 | EV Supply Chain Role: General Automotive 5. Jefferson Southern Corp. | Employment: 50 | EV Supply Chain Role: General Automotive 6. Stryten Energy | Employment: 50 | EV Supply Chain Role: General Automotive 7. Suhner Manufacturing Corp. | Employment: 50 | EV Supply Chain Role: General Automotive 8. Sumitomo Electric Wiring Systems | Employment: 50 | EV Supply Chain Role: Materials 9. Wheelabrator Group Inc. | Employment: 51 | EV Supply Chain Role: Interior trim and textile components 10. Die-Tech Industries Inc. | Employment: 60 | EV Supply Chain Role: General Automotive</t>
+  </si>
+  <si>
+    <t>Denkai America | Employment: 50 | EV Supply Chain Role: General Automotive  
+DeKalb Tool &amp; Die Inc. | Employment: 70 | EV Supply Chain Role: General Automotive  
+Daesol Ausys | Employment: 97 | EV Supply Chain Role: Materials  
+GLOVIS Georgia LLC | Employment: 90 | EV Supply Chain Role: General Automotive  
+Note: Only four companies with employment numbers lower than 100 are provided in the evidence.</t>
+  </si>
+  <si>
+    <t>Without specific data from an Excel workbook or another detailed dataset, I can't provide a precise list of the top 10 companies with the lowest employment numbers along with their EV supply chain roles. However, generally speaking, smaller startups or niche suppliers in the electric vehicle (EV) industry might have lower employment figures compared to larger automotive manufacturers and tech giants.
+To give you an accurate answer, I would need access to a dataset that includes company names, number of employees, and their specific roles within the EV supply chain. If you can provide such data, I'd be happy to analyze it for you. Otherwise, your best bet might be to consult industry reports or databases that track these metrics specifically for companies involved in EV production and supply chains.</t>
+  </si>
+  <si>
+    <t>Here are the 10 companies with the lowest employment numbers and their EV Supply Chain Roles, according to the provided data:
+1. Denkai America - General Automotive
+2. DeKalb Tool &amp; Die Inc. - General Automotive
+3. Daesol Ausys - Materials
+4. DaeChang Seat Company - General Automotive
+5. Blue Bird Corp. - Materials
+6. Continental Tire the Americas LLC - General Automotive
+7. GLOVIS Georgia LLC - General Automotive
+8. Bosch (Automotive Division) - Materials
+9. Daesol Ausys - Materials
+10. Bosch (Automotive Division) - Materials</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the relevant Excel workbook containing company names, employment numbers, and EV Supply Chain Roles. My response would be based on the data within that workbook.</t>
+  </si>
+  <si>
+    <t>The companies with the lowest employment and their EV Supply Chain Roles are:
+*   **Denkai America**: 50 (General Automotive)
+*   **DeKalb Tool &amp; Die Inc.**: 70 (General Automotive)
+*   **GLOVIS Georgia LLC**: 90 (General Automotive)
+*   **Daesol Ausys**: 97 (Materials)
+*   **DaeChang Seat Company**: 135 (General Automotive)
+*   **Continental Tire the Americas LLC**: 150 (General Automotive)
+*   **Bosch (Automotive Division)**: 250 (Materials)
+*   **Blue Bird Corp.**: 275 (Materials)
+The workbook evidence is incomplete as it only provides 8 companies with the lowest employment, not 10.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 17.724109879s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '17s'}]}}</t>
+  </si>
+  <si>
+    <t>Among EV / Battery Relevant = Yes companies, which company has the highest Employment and what is its Product / Service?</t>
+  </si>
+  <si>
+    <t>Highest-employment company among EV / Battery Relevant = Yes: WIKA USA | Employment: 250,000 | Product / Service: Vehicle power &amp; data solutions; wiring harnesses and connectors | Category: OEM Supply Chain | EV Supply Chain Role: HV and LV wiring harnesses for EVs and ICE vehicles | Location: Georgia</t>
+  </si>
+  <si>
+    <t>Among EV / Battery Relevant = Yes companies, there are no matches in the provided evidence. The evidence does not contain any company with EV / Battery Relevant set to "Yes".</t>
+  </si>
+  <si>
+    <t>Without specific data from an Excel workbook or another detailed source, I can't provide precise figures. However, generally speaking, among electric vehicle (EV) and battery-related companies with high employment numbers, a prominent example would be CATL (Contemporary Amperex Technology), which is one of the world's largest manufacturers of lithium-ion batteries for EVs. If you have specific data in your workbook, it would provide the exact company name and its product/service details.</t>
+  </si>
+  <si>
+    <t>There are no companies listed with EV / Battery Relevant = Yes. The workbook evidence is incomplete for this question.</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I cannot definitively answer which EV/Battery Relevant company has the highest employment and its product/service. However, generally, companies like Tesla, CATL, LG Energy Solution, and Panasonic are major players in the EV battery space and likely have high employment numbers. Their products/services typically include battery cells, battery packs, electric vehicle manufacturing, and related technologies.
+Please provide the workbook if you need a precise answer based on the data within.</t>
+  </si>
+  <si>
+    <t>No companies with "EV / Battery Relevant = Yes" were found in the provided evidence.</t>
+  </si>
+  <si>
+    <t>I cannot answer this question without the workbook. The question asks for specific information about companies, employment numbers, and products/services that would be contained within the workbook.</t>
+  </si>
+  <si>
+    <t>Compare total Employment between EV / Battery Relevant groups (Yes vs Indirect vs No).</t>
+  </si>
+  <si>
+    <t>Total Employment by EV / Battery Relevant group: Yes: 1,505,494 No: 25,109 Indirect: 24,128</t>
+  </si>
+  <si>
+    <t>Total Employment by EV / Battery Relevant groups (Yes vs Indirect vs No):
+- **EV / Battery Relevant: Yes**
+  - TN Americas Holding Inc.: 19600
+  - Duckyang: 250
+  - Enchem America Inc.: 155
+  - F&amp;P Georgia Manufacturing: 104
+  - GSC Steel Stamping LLC: 350
+  - Hitachi Astemo Americas Inc.: 723
+  - Hollingsworth &amp; Vose Co.: 400
+  - Honda Development &amp; Manufacturing: 400
+Total Employment for EV / Battery Relevant (Yes): **22182**
+- **EV / Battery Relevant: Indirect**
+  - No companies listed in the provided evidence.
+- **EV / Battery Relevant: No**
+  - No companies listed in the provided evidence.</t>
+  </si>
+  <si>
+    <t>To compare the total employment between EV/Battery Relevant groups categorized as "Yes," "Indirect," and "No," we would typically look at specific data within an Excel workbook or a similar dataset. Since no exact figures are provided in your question, I can offer a general approach to how this comparison might be made:
+1. **Identify the Groups**: First, ensure that you have correctly identified which companies fall into each of these categories: "Yes" (directly involved in EV and battery production), "Indirect" (companies indirectly supporting the industry such as suppliers or service providers), and "No" (not involved in the EV/battery sector).
+2. **Gather Employment Data**: For each company, gather employment numbers. This data might be available under a column labeled 'Total Employees' or similar.
+3. **Summarize by Group**: Sum up the total number of employees for all companies within each group ("Yes," "Indirect," and "No").
+4. **Compare Totals**: Compare these totals to see which category has the highest employment numbers, followed by the others.
+Without specific data from a workbook or dataset, I cannot provide exact figures. However, generally speaking, you would expect the "Yes" category (directly involved in EV and battery production) to have significantly higher employment numbers compared to the "Indirect" and "No" categories due to the scale of operations required for manufacturing electric vehicles and batteries.
+If you need a precise comparison based on actual data from an Excel workbook, please provide the necessary details or values.</t>
+  </si>
+  <si>
+    <t>Here's a comparison of total employment for EV/Battery Relevant groups, based on the provided evidence:
+**EV Supply Chain Role: Yes**
+*   TN Americas Holding Inc.: 19600
+*   Duckyang: 250
+*   Enchem America Inc.: 155
+*   F&amp;P Georgia Manufacturing: 104
+*   GSC Steel Stamping LLC: 350
+*   Hitachi Astemo Americas Inc.: 723
+*   Hollingsworth &amp; Vose Co.: 400
+*   Honda Development &amp; Manufacturing: 400
+Total Employment: 23,382
+The workbook evidence does not contain any companies with an EV Supply Chain Role of "Indirect" or "No".</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I can't provide exact employment numbers for the EV/Battery Relevant groups (Yes, Indirect, and No). However, I can explain the general expectation based on how these categories typically function.
+Generally, the "Yes" group (those directly involved in EV or battery production/development) would have the highest employment numbers. The "Indirect" group (suppliers, supporting industries) would have a significant, but lower, number of employees. The "No" group (those not related to the EV/battery sector) would have the lowest.
+The specific magnitude of the differences would depend on the scope of the data and how the groups were defined within the workbook.</t>
+  </si>
+  <si>
+    <t>The workbook evidence is incomplete for this question, as it only contains data for the "Yes" EV / Battery Relevant group.
+**EV / Battery Relevant: Yes**
+*   TN Americas Holding Inc.: 19600
+*   Duckyang: 250
+*   Enchem America Inc.: 155
+*   F&amp;P Georgia Manufacturing: 104
+*   GSC Steel Stamping LLC: 350
+*   Hitachi Astemo Americas Inc.: 723
+*   Hollingsworth &amp; Vose Co.: 400
+*   Honda Development &amp; Manufacturing: 400</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 16.938174881s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '16s'}]}}</t>
+  </si>
+  <si>
+    <t>For each EV Supply Chain Role, calculate total Employment and identify the top 3 roles by total Employment.</t>
+  </si>
+  <si>
+    <t>Total Employment by EV Supply Chain Role: HV and LV wiring harnesses for EVs and ICE vehicles: 250,000 Power electronics, sensors, and EV systems: 230,000 EV sensors, braking, and control systems: 190,159 Advanced electrical architecture for EVs: 190,000 EV electrical distribution and interior systems: 173,700 EV body, powertrain, and thermal components: 170,000 EV thermal systems and electronics: 106,100 High‑voltage EV connectors and electronics: 87,000 General Automotive: 35,003 Vehicle Assembly: 29,177 OEM corporate footprint influencing EV strategy: 19,600 OEM parent group footprint (EV + HD electrification): 19,600 OEM parent group footprint (electric truck strategy): 18,100 EV thermal management and power electronics: 17,500 Materials: 5,119 OEM corporate and engineering footprint (electrification): 2,000 EV wiring harnesses and power distribution: 1,657 Stamped and welded assemblies for OEMs: 1,600 EV and ICE component manufacturing: 1,500 EV and ICE powertrain and HVAC components: 1,300 Battery Cell: 1,123 Battery Pack: 768 Thermal Management: 650 Body and chassis components for EV and ICE OEMs: 630 Plastic components for EV and ICE vehicles: 456 Power Electronics: 350 OEM corporate footprint and supplier integration: 350 Charging Infrastructure: 320 Machined components supporting EV and ICE vehicles: 298 Tier 1 automotive components: 269 Stamped metal components for OEMs: 251 Vehicle safety systems OEM (EV + ICE): 80 Interior trim and textile components: 51 Interior and exterior plastic parts: 20 Top 3 roles by total Employment: HV and LV wiring harnesses for EVs and ICE vehicles: 250,000 Power electronics, sensors, and EV systems: 230,000 EV sensors, braking, and control systems: 190,159</t>
+  </si>
+  <si>
+    <t>Total Employment by EV Supply Chain Role:
+Materials:
+- Blue Bird Corp.: 275
+- Bosch (Automotive Division): 250
+- Daesol Ausys: 97
+**Total for Materials:** 622
+General Automotive:
+- Adient: 180
+- DaeChang Seat Company: 135
+- Denkai America: 50
+- DeKalb Tool &amp; Die Inc.: 70
+- GLOVIS Georgia LLC: 90
+**Total for General Automotive:** 525
+Top 3 EV Supply Chain Roles by Total Employment:
+1. Materials (622)
+2. General Automotive (525)</t>
+  </si>
+  <si>
+    <t>To address this question without specific data from an Excel workbook, I'll provide a general approach to calculating the total employment for each EV (Electric Vehicle) supply chain role and identifying the top three roles based on that employment:
+1. **List All Roles**: First, you would need a list of all distinct roles within the EV supply chain.
+2. **Sum Employment Numbers**: For each role listed, sum up the employment numbers associated with it across different companies or locations if applicable.
+3. **Rank by Total Employment**: Once you have the total employment for each role, rank these totals from highest to lowest.
+4. **Identify Top 3 Roles**: The top three roles will be those with the highest total employment figures after ranking them as described in step 3.
+Without specific data, I cannot provide exact numbers or names of companies and roles. However, if you have an Excel workbook containing columns such as "Role" and "Employment," you could use formulas like `SUMIF` to sum up employment for each role and then use a combination of `RANK.EQ`, `LARGE`, and `INDEX/MATCH` functions or pivot tables to identify the top three roles.
+For example, if your data is structured with columns A (Role) and B (Employment), you could:
+- Use `SUMIF(A:A, "RoleName", B:B)` for each unique role in a separate column.
+- Then use `RANK.EQ` or similar to rank these sums.
+- Finally, identify the top three roles based on their ranks.
+If you need help with specific Excel functions or formulas, feel free to ask!</t>
+  </si>
+  <si>
+    <t>Here's a breakdown of total employment by EV Supply Chain Role, based on the provided evidence:
+**Materials:**
+*   Blue Bird Corp.: 275
+*   Bosch (Automotive Division): 250
+*   Daesol Ausys: 97
+*   Total: 622
+**General Automotive:**
+*   Adient: 180
+*   DaeChang Seat Company: 135
+*   Denkai America: 50
+*   GLOVIS Georgia LLC: 90
+*   DeKalb Tool &amp; Die Inc.: 70
+*   Total: 525
+Top 3 EV Supply Chain Roles by Total Employment:
+1.  Materials: 622
+2.  General Automotive: 525
+The workbook evidence is incomplete as it does not contain data for all possible EV Supply Chain Roles.</t>
+  </si>
+  <si>
+    <t>Here's a breakdown of how to calculate total employment for each EV Supply Chain Role and identify the top 3 roles, assuming you have a dataset with this information:
+**1. Calculate Total Employment for Each Role:**
+*   **Group by Role:** You'll need to group your data by the "EV Supply Chain Role" column.
+*   **Sum Employment:** Within each group (each role), sum the values in the "Employment" column. This will give you the total employment for each specific role.
+**2. Identify the Top 3 Roles by Total Employment:**
+*   **Sort:** Sort the results from step 1 in descending order based on the "Total Employment" calculated.
+*   **Select Top 3:** Take the first three rows from the sorted results. These represent the roles with the highest total employment.
+**General Considerations (Without Specific Data):**
+Without the actual data, I can't provide specific role names or employment numbers. However, common EV Supply Chain roles that *might* appear in such a dataset and potentially have high employment include:
+*   **Battery Manufacturing Technicians:**  Battery production is a labor-intensive process.
+*   **Electric Motor Manufacturing Workers:**  Electric motors are a core component of EVs.
+*   **Software Engineers (EV-related):**  Software is critical for battery management, autonomous driving, and vehicle control.
+*   **Materials Scientists/Engineers:**  Focusing on battery materials and other EV components.
+*   **Supply Chain Managers:**  Managing the complex flow of materials and components.
+**Uncertainty:** The actual top 3 roles and their employment numbers will depend entirely on the specific data in your workbook.</t>
+  </si>
+  <si>
+    <t>*   **General Automotive:** 
+    *   Adient: 180
+    *   DaeChang Seat Company: 135
+    *   Denkai America: 50
+    *   DeKalb Tool &amp; Die Inc.: 70
+    *   GLOVIS Georgia LLC: 90
+    *   Total Employment: 525
+*   **Materials:** 
+    *   Blue Bird Corp.: 275
+    *   Bosch (Automotive Division): 250
+    *   Daesol Ausys: 97
+    *   Total Employment: 622
+**Top 3 Roles by Total Employment:**
+1.  Materials: 622
+2.  General Automotive: 525</t>
+  </si>
+  <si>
+    <t>I cannot calculate the total employment for each EV Supply Chain Role or identify the top 3 roles by total employment without access to the specific workbook data. This information is unique to your dataset.</t>
+  </si>
+  <si>
+    <t>Within Tier 1 suppliers, what is the Employment range (min and max) and which companies correspond to those extremes?</t>
+  </si>
+  <si>
+    <t>Tier 1 Employment range: min = 50, max = 900. Min-employment companies: Stryten Energy | Employment: 50 | Location: Troup County | EV Supply Chain Role: General Automotive Suhner Manufacturing Corp. | Employment: 50 | Location: Douglas, Coffee County | EV Supply Chain Role: General Automotive Sumitomo Electric Wiring Systems | Employment: 50 | Location: Baxley, Appling County | EV Supply Chain Role: Materials Max-employment companies: Jefferson Southern Corporation | Employment: 900 | Location: Monroe, Walton County | EV Supply Chain Role: General Automotive Joon Georgia, Inc. | Employment: 900 | Location: Troup County | EV Supply Chain Role: General Automotive</t>
+  </si>
+  <si>
+    <t>For Tier 1 suppliers, the Employment range and corresponding companies are as follows:
+- **General Automotive**:
+  - Minimum Employment: 730 (Kumho Tire USA Inc.)
+  - Maximum Employment: 900 (Jefferson Southern Corporation, Joon Georgia, Inc.)
+Note that there is no variation in employment for other roles beyond General Automotive within the provided evidence.</t>
+  </si>
+  <si>
+    <t>To answer this question accurately, I would need specific data from an Excel workbook or a similar structured dataset that includes employment numbers for Tier 1 suppliers. Without such detailed information, I can't provide exact figures. However, generally speaking, if you have a list of Tier 1 suppliers with their respective employment numbers, the Employment range (minimum and maximum) would be determined by identifying the supplier with the least number of employees as the minimum value and the supplier with the most employees as the maximum value.
+For example:
+- If Supplier A has 500 employees and Supplier B has 20,000 employees among Tier 1 suppliers, then the Employment range would be from 500 to 20,000, with Supplier A corresponding to the minimum employment number and Supplier B corresponding to the maximum.
+Please provide specific data or numbers if you need a precise answer.</t>
+  </si>
+  <si>
+    <t>The Employment range for Tier 1 suppliers is 730 to 900.
+*   **Minimum Employment (730):** Kumho Tire USA Inc.
+*   **Maximum Employment (900):** Jefferson Southern Corporation and Joon Georgia, Inc.
+Here's a breakdown by EV Supply Chain Role:
+**Charging Infrastructure:** Morgan Corp.
+**General Automotive:** JTEKT North America Corp., Jefferson Southern Corporation, Joon Georgia, Inc., KTX America Corporation, Kautex Inc., Kumho Tire USA Inc., Kyungshin America Corp., Lark United Manufacturing Inc. + 59 more companies
+**Materials:** PHA Body Systems LLC, Panasonic Automotive Systems Co., SK Battery America, Sumitomo Electric Wiring Systems
+**Thermal Management:** Novelis Inc., Peerless-Winsmith Inc.</t>
+  </si>
+  <si>
+    <t>I am sorry, but I do not have access to the workbook to provide the employment range and corresponding companies within Tier 1 suppliers.</t>
+  </si>
+  <si>
+    <t>The minimum employment within Tier 1 suppliers is 590, corresponding to Lear Corporation. The maximum employment is 900, corresponding to Jefferson Southern Corporation and Joon Georgia, Inc.
+Other companies and their employment within Tier 1 suppliers include:
+* JTEKT North America Corp.: 860
+* Kautex Inc.: 800
+* KTX America Corporation: 740
+* Kumho Tire USA Inc.: 730</t>
+  </si>
+  <si>
+    <t>I cannot answer this question without the specific workbook data. To determine the employment range (min and max) within Tier 1 suppliers and identify the corresponding companies, I need access to the "Tier 1 suppliers" data, which would include employment figures for each company.</t>
+  </si>
+  <si>
+    <t>Within Tier 2/3 suppliers, what is the average Employment by Industry Group?</t>
+  </si>
+  <si>
+    <t>Average Employment by Industry Group within Tier 2/3: Miscellaneous Manufacturing Industries [n=1]: 650.00 Machinery Except Electrical [n=7]: 249.57 Rubber and Miscellaneous Plastic Products [n=28]: 225.07 Primary Metal Industries [n=15]: 208.87 Textile Products [n=6]: 180.83 Fabricated Metal Products [n=11]: 179.55 Chemicals and Allied Products [n=3]: 173.33 Paper and Allied Products [n=1]: 140.00 Stone, Clay, Glass and Concrete Products [n=2]: 82.50</t>
+  </si>
+  <si>
+    <t>The provided evidence does not contain Employment data grouped by Industry Group. It only provides employment numbers for individual companies under the Tier 2/3 category without specifying their respective industry groups. Therefore, calculating an average employment figure by Industry Group is not possible with the given information.</t>
+  </si>
+  <si>
+    <t>To answer this question accurately, I would need specific data from an Excel workbook or a similar dataset that includes employment numbers categorized by industry group for Tier 2/3 suppliers. Without such detailed information, it's not possible to provide an exact figure.
+However, generally speaking, the average employment across different industry groups within Tier 2/3 suppliers can vary widely depending on factors like the specific industries involved (e.g., manufacturing vs. services), geographic location, and economic conditions. If you could share more details or a summary of the data available, I could provide a more tailored response based on that information.</t>
+  </si>
+  <si>
+    <t>The workbook evidence groups Tier 2/3 suppliers by EV Supply Chain Role, but does not include Industry Group for all companies. Here's the breakdown of Employment by EV Supply Chain Role:
+**General Automotive:** ACM Georgia LLC (400), Adient (180), ADVICS Manufacturing Georgia LLC (150), Ajin Georgia (143), ALBAform Inc. (130), Anovion Technologies (82) + 44 more companies.
+**Materials:** Ascend Elements, Aspen Aerogels, Aurubis, Beaver Manufacturing Co. Inc., Blue Bird Corp. (275), Blue Ridge Manufacturing, Boogook Industries, Bosch (Automotive Division) + 11 more companies.
+**Power Electronics:** GSC Steel Stamping LLC
+**Thermal Management:** Freudenberg-NOK</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the relevant workbook data. The question asks for the average Employment by Industry Group specifically within Tier 2/3 suppliers, which requires data from a structured source.</t>
+  </si>
+  <si>
+    <t>The workbook evidence is incomplete for this question. The available data does not include 'Industry Group' for all companies within the 'Tier 2/3' category, and therefore, the average employment by 'Industry Group' cannot be calculated.
+However, for the companies where 'Industry Group' is available:
+*   **Rubber and Miscellaneous Plastic Products:** Blue Bird Corp. has an employment of 275.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 982.616726ms.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '0s'}]}}</t>
+  </si>
+  <si>
+    <t>Which counties have the highest total Employment among Tier 1 suppliers only?</t>
+  </si>
+  <si>
+    <t>Total Employment by county among Tier 1 suppliers only: Troup County: 3,603 Hall County: 1,715 Chatham County: 1,677 Gwinnett County: 1,560 Floyd County: 1,330 Carroll County: 945 Bartow County: 935 Walton County: 900 Cherokee County: 860 Effingham County: 810 Bulloch County: 660 Meriwether County: 600 Laurens County: 535 Haralson County: 500 Richmond County: 500 Whitfield County: 500 Harris County: 440 Dade County: 405 Walker County: 400 Polk County: 400 Stephens County: 350 Newton County: 310 Candler County: 300 Hart County: 225 Crisp County: 200 Coweta County: 200 Franklin County: 200 Liberty County: 180 Davis County: 170 Pike County: 157 Fulton County: 140 Grady County: 125 Gordon County: 120 Fayette County: 110 Bibb County: 80 Cobb County: 75 Clarke County: 75 Fannin County: 68 Appling County: 50 Coffee County: 50 Top 5 counties: Troup County: 3,603 Hall County: 1,715 Chatham County: 1,677 Gwinnett County: 1,560 Floyd County: 1,330</t>
+  </si>
+  <si>
+    <t>Walton County and Troup County have the highest total Employment among Tier 1 suppliers based on the provided evidence:
+- **Walton County**: Jefferson Southern Corporation (900)
+- **Troup County**: Joon Georgia, Inc. (900), Kumho Tire USA Inc. (730)
+Note: Canton in Cherokee County has one company with employment of 860, but it does not surpass the total Employment in Walton and Troup Counties.</t>
+  </si>
+  <si>
+    <t>To determine which counties have the highest total employment among Tier 1 suppliers, I would need specific data about the locations of these suppliers and their respective employment numbers. Since no workbook evidence is provided, I can't give an exact answer based on your dataset.
+However, generally speaking, you would filter the list to include only Tier 1 suppliers, then group them by county, summing up the total employment for each county. The counties with the highest sums would be the ones with the most significant total employment among Tier 1 suppliers.
+If you have specific data or a workbook available, I can guide you through the process of analyzing it to find this information.</t>
+  </si>
+  <si>
+    <t>Based on the provided evidence, the counties with the highest total employment among Tier 1 suppliers are:
+*   **Walton County:** Jefferson Southern Corporation (900)
+*   **Troup County:** Joon Georgia, Inc. (900), Kumho Tire USA Inc. (730), Linde + Wiemann (515)
+*   **Cherokee County:** JTEKT North America Corp. (860)
+*   **Carroll County:** Kautex Inc. (800)
+*   **Effingham County:** KTX America Corporation (740)
+The workbook evidence is incomplete, as it does not list the employment numbers for all Tier 1 suppliers.</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I cannot definitively answer which counties have the highest total employment among Tier 1 suppliers. Generally, areas with a high concentration of manufacturing or industries served by these suppliers (like automotive, aerospace, or technology) would likely have higher employment numbers.</t>
+  </si>
+  <si>
+    <t>The workbook evidence is incomplete to answer which counties have the highest total employment among Tier 1 suppliers only. The available evidence lists individual companies, their employment, and their county, but does not provide a sum of employment per county.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 853.839734ms.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '0s'}]}}</t>
+  </si>
+  <si>
+    <t>In Gwinnett County, which company has the highest Employment and what is its EV Supply Chain Role?</t>
+  </si>
+  <si>
+    <t>Highest-employment company in Gwinnett County [1]: Grudem | Employment: 807 | EV Supply Chain Role: General Automotive | Category: Tier 2/3</t>
+  </si>
+  <si>
+    <t>In Gwinnett County, Grudem has the highest Employment of 807 and its EV Supply Chain Role is General Automotive.</t>
+  </si>
+  <si>
+    <t>Without specific data from an Excel workbook or another detailed source about companies in Gwinnett County, I can't provide exact figures. However, based on general knowledge, a notable company often associated with high employment numbers in Gwinnett County is UPS (United Parcel Service), which has a large distribution center there. UPS plays a significant role in the supply chain as a logistics and delivery service provider. For precise details about employment numbers and specific EV supply chain roles, you would need to consult current data from reliable sources like company reports or local economic development websites for Gwinnett County.</t>
+  </si>
+  <si>
+    <t>Grudem has the highest employment at 807 and its EV Supply Chain Role is General Automotive.</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I cannot definitively answer which company in Gwinnett County has the highest employment or its EV Supply Chain Role. However, Gwinnett County is a significant hub for many industries, and major employers could include companies in advanced manufacturing, logistics, or technology. To determine the specific company and its role, I would need to consult the data within the workbook.</t>
+  </si>
+  <si>
+    <t>In Gwinnett County, Grudem has the highest employment with 807 employees, and its EV Supply Chain Role is General Automotive.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 719.356402ms.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-2.5-flash', 'location': 'global'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '0s'}]}}</t>
+  </si>
+  <si>
+    <t>Among companies with Primary Facility Type = R&amp;D, which one has the highest Employment and what is its Location?</t>
+  </si>
+  <si>
+    <t>Racemark International LLC has the highest Employment among R&amp;D entries (and is the only R&amp;D entry): Employment 120 | Location: Calhoun, Gordon County.</t>
+  </si>
+  <si>
+    <t>Among companies with Primary Facility Type = R&amp;D, Racemark International LLC has the highest Employment of 120 and its Location is Calhoun, Gordon County.</t>
+  </si>
+  <si>
+    <t>Without specific data from an Excel workbook or another detailed source, I cannot provide the exact company name, employment numbers, or location. However, to answer such a question, you would typically filter companies by their Primary Facility Type set to "R&amp;D," then sort them based on Employment in descending order to find the one with the highest number of employees, and finally identify its Location.
+If you have an Excel workbook containing this information, you can use filters and sorting functions to easily find the answer. If you need help with specific Excel commands or formulas for this task, feel free to ask!</t>
+  </si>
+  <si>
+    <t>Racemark International LLC has the highest Employment (120) among companies with a Primary Facility Type of R&amp;D. Its Location is Calhoun, Gordon County.</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I cannot definitively answer this question. However, generally, among companies with a Primary Facility Type of R&amp;D, the one with the highest employment would likely be a major pharmaceutical company, a large technology firm, or a significant research institution. The location would depend on where that company is headquartered or has its primary research facilities – possibilities include locations like Cambridge (MA), San Francisco (CA), Boston (MA), or Research Triangle Park (NC) in the United States, or similar hubs in other countries.</t>
+  </si>
+  <si>
+    <t>Racemark International LLC has the highest employment among companies with Primary Facility Type = R&amp;D, with 120 employees. Its location is Calhoun, Gordon County.</t>
+  </si>
+  <si>
+    <t>I cannot answer this question without the workbook. The question asks for specific information about companies, employment, and locations that would be contained within the workbook.</t>
+  </si>
+  <si>
+    <t>List all companies with Employment between 200 and 500 (inclusive) that are EV / Battery Relevant = Yes.</t>
+  </si>
+  <si>
+    <t>EV / Battery Relevant = Yes with Employment 200-500 [9]: Duckyang | Employment: 250 | Location: Augusta, Richmond County | Category: Tier 2/3 | EV Supply Chain Role: General Automotive Volvo Group North America | Employment: 251 | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: Stamped metal components for OEMs Valeo | Employment: 269 | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: Tier 1 automotive components Trenton Pressing Inc. | Employment: 298 | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: Machined components supporting EV and ICE vehicles GSC Steel Stamping LLC | Employment: 350 | Location: Gainesville, Hall County | Category: Tier 2/3 | EV Supply Chain Role: Power Electronics Trenton Pressing | Employment: 350 | Location: Georgia | Category: OEM (Footprint) | EV Supply Chain Role: OEM corporate footprint and supplier integration Hollingsworth &amp; Vose Co. | Employment: 400 | Location: Bainbridge, Decatur County | Category: Tier 1/2 | EV Supply Chain Role: Battery Pack Honda Development &amp; Manufacturing | Employment: 400 | Location: Pembroke, Bryan County | Category: Tier 1/2 | EV Supply Chain Role: Battery Cell Volvo Cars USA | Employment: 456 | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: Plastic components for EV and ICE vehicles</t>
+  </si>
+  <si>
+    <t>No companies match the criteria of having Employment between 200 and 500 (inclusive) with EV / Battery Relevant = Yes based on the provided evidence.</t>
+  </si>
+  <si>
+    <t>Based on the criteria you've provided—companies with employment numbers between 200 and 500 inclusive, and those marked as "EV/Battery Relevant" equal to yes—I would need specific data from an Excel workbook or a similar structured dataset to provide exact company names. Without access to such detailed information, I can't list the companies directly. However, if you have this data in an Excel workbook, you could use a filter or a formula like `FILTER` combined with conditions to extract these companies.
+For example, using Google Sheets or Excel formulas, you might use something along the lines of:
+```
+=FILTER(Companies!A2:A, (Companies!C2:C &gt;= 200) * (Companies!C2:C &lt;= 500) * (Companies!D2:D = "Yes"))
+```
+This formula assumes that column A contains company names, column C employment numbers, and column D the EV/Battery relevance indicator.
+If you can provide more details or a specific dataset, I could give a more precise answer. Otherwise, this is how you would approach finding such companies in a structured data set.</t>
+  </si>
+  <si>
+    <t>*   Hitachi Astemo Americas Inc. (Employment: 723)
+*   Woory Industrial Co. (Employment: 87000)</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the relevant workbook data. The question requires specific information about companies, their employment numbers, and whether they are EV/Battery Relevant.</t>
+  </si>
+  <si>
+    <t>Hitachi Astemo Americas Inc. (Employment: 723) is the only company that is EV / Battery Relevant = Yes. However, its employment is not between 200 and 500.
+No companies with employment between 200 and 500 (inclusive) are EV / Battery Relevant = Yes.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 32.874652588s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '32s'}]}}</t>
+  </si>
+  <si>
+    <t>Which Industry Group has the highest total Employment across all companies?</t>
+  </si>
+  <si>
+    <t>Automotive wiring systems has the highest total Employment: 250,000.</t>
+  </si>
+  <si>
+    <t>The Industry Group with the highest total Employment across all companies is Commercial vehicles and powertrains, with a total of 18100 employees from Toyota Industries Group (TACG-TICA). The next highest Employment is found in the Industry Group Rubber and Miscellaneous Plastic Products, which includes Blue Bird Corp. (275), Bosch (Automotive Division) (250), DaeChang Seat Company (135), Daesol Ausys (97), and Denkai America (50), totaling 807 employees. The Industry Group Transportation Equipment has a total Employment of 130 from PIOLAX Corp. and 1800 from Teklas USA, totaling 1930 employees.</t>
+  </si>
+  <si>
+    <t>To determine which industry group has the highest total employment across all companies without specific data from an Excel workbook, I would need to rely on general knowledge or hypothetical scenarios. Typically, industries such as manufacturing, healthcare, retail, and technology often have high employment numbers due to their scale and diversity of roles. Without exact figures, it's challenging to pinpoint a single industry group definitively. However, if we consider broad trends, the manufacturing or service sectors (including healthcare and information technology) might lead in total employment depending on the country or region in question. For precise data, reviewing an Excel workbook with detailed company employment statistics would be necessary.</t>
+  </si>
+  <si>
+    <t>The Industry Group with the highest total Employment is Transportation Equipment, with a total of 18,330 employees across PIOLAX Corp. (130), Teklas USA (1800), and Toyota Industries Group (TACG-TICA) (18,100).</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I cannot definitively determine which Industry Group has the highest total employment. Generally, sectors like Technology, Healthcare, or Finance often have high employment numbers, but the specific workbook data would be needed to provide an accurate answer.</t>
+  </si>
+  <si>
+    <t>The Industry Group with the highest total employment is Transportation Equipment, with a total of 19,930 employees.
+*   **Transportation Equipment**: 19,930
+    *   Toyota Industries Group (TACG-TICA): 18,100
+    *   Teklas USA: 1,800
+    *   PIOLAX Corp.: 130
+The Rubber and Miscellaneous Plastic Products Industry Group has a total of 807 employees.
+*   **Rubber and Miscellaneous Plastic Products**: 807
+    *   Blue Bird Corp.: 275
+    *   Bosch (Automotive Division): 250
+    *   DaeChang Seat Company: 135
+    *   Daesol Ausys: 97
+    *   Denkai America: 50</t>
+  </si>
+  <si>
+    <t>I cannot answer this question without access to the workbook. The question asks for the "Industry Group" with the highest "total Employment across all companies," which requires specific data from your workbook. Please upload the workbook or provide the necessary data.</t>
+  </si>
+  <si>
+    <t>For each Category, compute the average Employment and identify which Category has the highest average.</t>
+  </si>
+  <si>
+    <t>Average Employment by Category: OEM Footprint: 175419.7 OEM Supply Chain: 52719.5 OEM (Footprint): 11930.0 OEM: 2471.4 Tier 1: 287.9 Tier 1/2: 264.2 Tier 2/3: 212.4 Highest average: OEM Footprint (175419.7).</t>
+  </si>
+  <si>
+    <t>For each Category, the average Employment and the highest average Employment Category are as follows:
+**Tier 2/3**
+- Companies: Blue Bird Corp., Bosch (Automotive Division), DaeChang Seat Company, Daesol Ausys, Denkai America, GLOVIS Georgia LLC
+- Average Employment: (275 + 250 + 135 + 97 + 50 + 90) / 6 = 148.33
+**Tier 1**
+- Companies: Peterson Spring
+- Average Employment: 150
+The Category with the highest average Employment is Tier 2/3 with an average of approximately 148 employees.</t>
+  </si>
+  <si>
+    <t>To address this question without specific workbook data, I'll outline how you would approach calculating the average employment for each category and identifying the category with the highest average:
+1. **Summarize Employment by Category**: First, you need to sum up the total employment numbers within each category.
+2. **Count Categories**: Count how many entries there are in each category.
+3. **Calculate Average Employment**: Divide the total employment number for a given category by the count of entries in that category to get the average employment per category.
+4. **Identify Highest Average**: Compare the averages across all categories and identify which one has the highest value.
+Without specific data, I can't provide exact numbers or names of categories. However, if you have an Excel workbook with columns like "Category" and "Employment," you could use formulas such as `AVERAGEIF` to calculate these values for each category.
+For example:
+- Use `SUMIF(range, criteria, sum_range)` to get the total employment per category.
+- Count entries in a category using `COUNTIF`.
+- Divide the totals by counts to find averages.
+- Compare results to identify the highest average.
+If you provide specific data or structure of your workbook, I can give more precise instructions.</t>
+  </si>
+  <si>
+    <t>Here's the breakdown of average employment by Category, based on the provided evidence:
+**Category Analysis:**
+*   **Tier 1:**
+    *   Companies: Peterson Spring
+    *   Average Employment: 150
+*   **Tier 2/3:**
+    *   Companies: Blue Bird Corp., Bosch (Automotive Division), DaeChang Seat Company, Daesol Ausys, Denkai America, GLOVIS Georgia LLC
+    *   Average Employment: 131.83 (calculated as (275 + 250 + 135 + 97 + 50 + 90) / 6)
+**Conclusion:**
+The Category with the highest average employment is **Tier 1**, with an average of 150 employees, compared to Tier 2/3's average of 131.83.</t>
+  </si>
+  <si>
+    <t>Please provide the data so I can compute the average Employment for each Category and identify the Category with the highest average.</t>
+  </si>
+  <si>
+    <t>- **Tier 1**:
+  - Average Employment: 150
+  - Companies: Peterson Spring
+- **Tier 2/3**:
+  - Average Employment: 149.5
+  - Companies: Blue Bird Corp., Bosch (Automotive Division), DaeChang Seat Company, Daesol Ausys, Denkai America, GLOVIS Georgia LLC
+Tier 1 has the highest average employment.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 31.943166022s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '31s'}]}}</t>
+  </si>
+  <si>
+    <t>Identify companies with Employment &gt;= 10,000 and list their Category and Classification</t>
+  </si>
+  <si>
+    <t>Based on the provided evidence, there is only one company with employment greater than or equal to 10,000:
+- **Company:** Toyota Industries Group (TACG-TICA)
+  - **Category:** OEM (Footprint)
+  - **Classification Method:** Public OEM footprint / supplier listing
+All other companies listed have employment numbers below 10,000.</t>
+  </si>
+  <si>
+    <t>Company: Toyota Industries Group (TACG-TICA) | Category: OEM (Footprint) | Classification Method: Public OEM footprint / supplier listing</t>
+  </si>
+  <si>
+    <t>To identify companies with employment numbers of at least 10,000 employees and to list their categories and classifications, I would typically look for specific data in an Excel workbook or a similar structured dataset. Since no workbook evidence is provided here, I can't give exact company names, categories, or classifications.
+However, based on general knowledge, companies with such large employment numbers are often found in industries like manufacturing (e.g., automotive), technology, retail, and finance. Categories might include "Large Enterprises," "Fortune 500 Companies," etc., while classification could be more specific to the industry sector they operate within.
+For a precise answer, you would need to filter your dataset for companies with employment figures of at least 10,000 employees and then extract their corresponding categories and classifications. If you have an Excel workbook or similar data source available, applying these filters should yield the exact information you're looking for.</t>
+  </si>
+  <si>
+    <t>Toyota Industries Group (TACG-TICA) has Employment of 18100, Category: OEM (Footprint), and Classification Method: Public OEM footprint / supplier listing.</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the relevant workbook data. The request requires specific information about companies, their employment numbers, categories, and classifications, which are only available within the Excel workbooks.</t>
+  </si>
+  <si>
+    <t>Toyota Industries Group (TACG-TICA) - Category: OEM (Footprint), Classification: Public OEM footprint / supplier listing</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 31.809574998s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-2.5-flash', 'location': 'global'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '31s'}]}}</t>
+  </si>
+  <si>
+    <t>Method.</t>
+  </si>
+  <si>
+    <t>The question "Method." is too vague and does not provide enough context to determine what specific information is being requested. It could refer to various aspects such as classification methods, manufacturing methods, or other processes related to the companies listed in the evidence.
+To provide a helpful response, please clarify what you are asking about. For example:
+- Are you asking about the classification methods used for these companies?
+- Are you inquiring about the manufacturing methods or processes used by these companies?
+- Or is there another specific method you are referring to?</t>
+  </si>
+  <si>
+    <t>Classification Method: Supplier
+Companies:
+- ACM Georgia LLC
+- Adient
+- ADVICS Manufacturing Georgia LLC
+- Ajin Georgia
+- ALBAform Inc.
+- Anovion Technologies
+- DAS Corp.
+- DAEHAN Solution Georgia LLC</t>
+  </si>
+  <si>
+    <t>It seems like you might be asking about a specific method related to Excel workbooks or a particular process within them. Could you please clarify what method you're referring to? For example, are you looking for information on how to perform a certain task in Excel (like data sorting, formula creation, etc.) or are you asking about a business method that involves the use of Excel workbooks?</t>
+  </si>
+  <si>
+    <t>The Classification Method is Supplier for ACM Georgia LLC, Adient, ADVICS Manufacturing Georgia LLC, Ajin Georgia, ALBAform Inc., Anovion Technologies, DAS Corp., and DAEHAN Solution Georgia LLC.</t>
+  </si>
+  <si>
+    <t>Please provide more context. "Method" is a very broad term. To answer your question, I need to know what you're referring to. For example, are you asking about:
+*   A method in a specific process?
+*   A method in a scientific experiment?
+*   A method in a programming context?
+*   Something else entirely?
+Once you clarify what you're asking about, I can give you a helpful answer.</t>
+  </si>
+  <si>
+    <t>The classification method for the following companies is "Supplier":
+*   ACM Georgia LLC
+*   Adient
+*   ADVICS Manufacturing Georgia LLC
+*   Ajin Georgia
+*   ALBAform Inc.
+*   Anovion Technologies
+*   DAS Corp.
+*   DAEHAN Solution Georgia LLC</t>
+  </si>
+  <si>
+    <t>A method is a way or process for accomplishing something. It can refer to a specific procedure, technique, or approach used to achieve a particular goal. In various fields, methods are formalized and documented to ensure consistency, reproducibility, and effectiveness.</t>
+  </si>
+  <si>
+    <t>Among OEM categories (OEM, OEM Supply Chain, OEM Footprint, OEM (Footprint)), which has the highest total Employment?</t>
+  </si>
+  <si>
+    <t>Total Employment by OEM category: OEM Supply Chain: 896,232 OEM Footprint: 526,259 OEM (Footprint): 59,650 OEM: 29,657 Highest total Employment: OEM Supply Chain (896,232).</t>
+  </si>
+  <si>
+    <t>Among OEM categories, the category "OEM" has the highest total Employment. Companies under this role include:
+- Kia Georgia Inc., Superior Essex Inc., Suzuki Manufacturing of America Corp., TCI Powder Coatings, TDK Components USA Inc., TE Connectivity, Teklas USA, Textron Specialized Vehicles
+Total Employment for these companies:
+- Kia Georgia Inc.: 777
+- Superior Essex Inc.: 8100
+- Suzuki Manufacturing of America Corp.: 7500
+- TCI Powder Coatings: 3000
+- TDK Components USA Inc.: 1000
+Total Employment for the "OEM" category is 20477.</t>
+  </si>
+  <si>
+    <t>Without specific data from an Excel workbook or additional context, I cannot provide exact employment numbers for each of the OEM categories you mentioned. However, generally speaking, if we consider "OEM" to refer to Original Equipment Manufacturer operations directly and "OEM Footprint" to include all related activities and possibly more indirect roles such as supply chain management and logistics, it's likely that "OEM (Footprint)" could have the highest total employment due to its broader scope. This would encompass not just direct manufacturing but also associated functions which can be quite extensive in terms of workforce. For precise figures, reviewing the specific data within your workbook is necessary.</t>
+  </si>
+  <si>
+    <t>The OEM category with the highest total employment is Vehicle Assembly, with a combined employment of 16,777. This includes Kia Georgia Inc. (777), Superior Essex Inc. (8100), Suzuki Manufacturing of America Corp. (7500), and TCI Powder Coatings (3000).</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I cannot definitively determine which OEM category has the highest total Employment. However, based on common industry structures, "OEM Footprint" likely has the highest employment. This is because it would encompass the workforce directly involved in manufacturing and operating facilities associated with the OEM.</t>
+  </si>
+  <si>
+    <t>The total employment for the OEM categories are:
+*   **OEM**: 22,577
+*   **OEM (Footprint)**: 350
+*   **OEM Supply Chain**: No employment information is available in the provided data.
+*   **OEM Footprint**: No employment information is available in the provided data.
+Therefore, the **OEM** category has the highest total employment.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 3.100718498s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '3s'}]}}</t>
+  </si>
+  <si>
+    <t>Which EV Supply Chain Role is most concentrated in a single county (i.e., the role where one county contains the largest share of that role's companies)?</t>
+  </si>
+  <si>
+    <t>Highest county concentration is a tie at 100.0%: Charging Infrastructure | County: Gwinnett County | Share: 100.0% (1/1) | Company: Morgan Corp. OEM corporate and engineering footprint (electrification) | County: Greene County | Share: 100.0% (1/1) | Company: Tie Down Engineering OEM corporate footprint influencing EV strategy | County: Fulton County | Share: 100.0% (1/1) | Company: TI Fluid Systems Power Electronics | County: Hall County | Share: 100.0% (1/1) | Company: GSC Steel Stamping LLC</t>
+  </si>
+  <si>
+    <t>General Automotive
+Companies:
+- Lear Corporation (Cartersville, Bartow County)
+- PPG Industries Inc. (Troup County)
+- Stryten Energy (Troup County)
+- Elan Technology Inc. (Atlanta, Fulton County)
+- OTR Wheel Engineering Inc. (Cordele, Crisp County)
+- Seoyon E-HWA (Hazlehurst, Davis County)
+The "General Automotive" role is the most concentrated in a single county, with multiple companies located in Troup County.</t>
+  </si>
+  <si>
+    <t>Without specific data from an Excel workbook or other detailed sources, it's challenging to pinpoint which EV supply chain role is most concentrated in a single county. However, generally speaking, specialized roles such as battery manufacturing, electric motor production, or rare earth metal refining might be more likely to have a high concentration within one county due to the presence of large industrial facilities and supporting infrastructure. For an exact answer, detailed data on EV supply chain companies' locations would be necessary.</t>
+  </si>
+  <si>
+    <t>The "General Automotive" EV Supply Chain Role is most concentrated in Troup County, which contains PPG Industries Inc., and Stryten Energy.</t>
+  </si>
+  <si>
+    <t>I am unable to answer the question because I do not have access to the relevant data regarding EV Supply Chain roles and their geographic distribution.</t>
+  </si>
+  <si>
+    <t>Based on the provided evidence, the EV Supply Chain Role most concentrated in a single county is **General Automotive**.
+**Troup County** has the largest share of companies within the "General Automotive" role, with the following companies:
+*   PPG Industries Inc.
+*   Stryten Energy</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 2.962033137s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '2s'}]}}</t>
+  </si>
+  <si>
+    <t>Identify EV Supply Chain Roles that have only one company in the dataset, and list the company for each such role.</t>
+  </si>
+  <si>
+    <t>EV Supply Chain Roles with only one company [28]: Advanced electrical architecture for EVs -&gt; Yamaha Motor Manufacturing Corp. Body and chassis components for EV and ICE OEMs -&gt; Vanguard National Trailer Corp. Charging Infrastructure -&gt; Morgan Corp. EV and ICE component manufacturing -&gt; Vista Metals Corp. EV and ICE powertrain and HVAC components -&gt; Voestalpine Automotive Body Parts Inc. EV body, powertrain, and thermal components -&gt; ZF Gainesville LLC EV electrical distribution and interior systems -&gt; Yachiyo Manufacturing of America LLC EV sensors, braking, and control systems -&gt; YKK USA Inc. EV thermal management and power electronics -&gt; ZF Gainesville LLC EV thermal systems and electronics -&gt; ZF Gainesville LLC EV wiring harnesses and power distribution -&gt; Woodbridge Foam Corp. HV and LV wiring harnesses for EVs and ICE vehicles -&gt; WIKA USA High‑voltage EV connectors and electronics -&gt; Woory Industrial Co. Interior and exterior plastic parts -&gt; Wabash National Corp. Interior trim and textile components -&gt; Wheelabrator Group Inc. Machined components supporting EV and ICE vehicles -&gt; Trenton Pressing Inc. OEM corporate and engineering footprint (electrification) -&gt; Tie Down Engineering OEM corporate footprint and supplier integration -&gt; Trenton Pressing OEM corporate footprint influencing EV strategy -&gt; TI Fluid Systems OEM parent group footprint (EV + HD electrification) -&gt; TN Americas Holding Inc. OEM parent group footprint (electric truck strategy) -&gt; Toyota Industries Group (TACG-TICA) Plastic components for EV and ICE vehicles -&gt; Volvo Cars USA Power Electronics -&gt; GSC Steel Stamping LLC Power electronics, sensors, and EV systems -&gt; Yazaki North America Stamped and welded assemblies for OEMs -&gt; Vernay Stamped metal components for OEMs -&gt; Volvo Group North America Tier 1 automotive components -&gt; Valeo Vehicle safety systems OEM (EV + ICE) -&gt; TI Fluid Systems</t>
+  </si>
+  <si>
+    <t>General Automotive: Peterson Spring
+Materials: Blue Bird Corp., Bosch (Automotive Division), Daesol Ausys, Denkai America, GLOVIS Georgia LLC
+Since "General Automotive" and "Materials" roles have multiple companies listed, the only role that has exactly one company in the dataset is:
+General Automotive: Peterson Spring</t>
+  </si>
+  <si>
+    <t>Without specific data from an Excel workbook or a detailed dataset to reference, I can't provide exact roles and companies. However, generally speaking, if you're looking for supply chain roles where there is only one company associated with that role in your dataset, you would need to:
+1. List all unique supply chain roles present.
+2. Count the number of companies associated with each role.
+3. Identify those roles which have exactly one company listed.
+For example, if your dataset includes a role like "EV Battery Supplier" and only one company is listed under this role, then that would be an instance where you'd note both the role and the single company name.
+To give you precise information, I would need access to the specific dataset or workbook details.</t>
+  </si>
+  <si>
+    <t>*   **General Automotive:** Lear Corporation
+*   **Materials:** Blue Bird Corp., Bosch (Automotive Division), Daesol Ausys
+*   **General Automotive:** DaeChang Seat Company, Denkai America, GLOVIS Georgia LLC</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the dataset. The question asks for specific roles and companies listed within a dataset, which I do not have.</t>
+  </si>
+  <si>
+    <t>Based on the provided data, there are no EV Supply Chain Roles that have only one company in the dataset. All listed EV Supply Chain Roles are associated with multiple companies.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 2.823028498s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '2s'}]}}</t>
+  </si>
+  <si>
+    <t>Which counties have the fewest companies overall (excluding rows with Location = Georgia)? Provide the bottom 5 counties by company count.</t>
+  </si>
+  <si>
+    <t>Bottom 5 counties by company count (alphabetical among ties): Appling County: 1 Candler County: 1 Catoosa County: 1 Clayton County: 1 Coffee County: 1 Note: 29 counties are tied at the minimum count of 1.</t>
+  </si>
+  <si>
+    <t>Laurens County:
+- GLOVIS Georgia LLC
+Troup County (excluding Sejong Georgia LLC and Joon Georgia, Inc.):
+- ADVICS Manufacturing Georgia LLC
+McDuffie County:
+- Bosch (Automotive Division)
+Elbert County:
+- Blue Bird Corp.
+Gwinnett County:
+- Continental Tire the Americas LLC</t>
+  </si>
+  <si>
+    <t>To answer which counties have the fewest companies overall excluding rows where the location is listed as "Georgia," we would need specific data from an Excel workbook or a similar dataset. Since no such data has been provided, I can't give you exact county names and counts. However, if you had this information in your workbook, here's how you could approach finding the bottom 5 counties by company count:
+1. Filter out all rows where "Location" is equal to "Georgia."
+2. Count the number of companies per remaining county.
+3. Sort these counts in ascending order.
+4. Identify and list the top (bottom) five counties with the lowest counts.
+Without specific data, I can't provide exact names or numbers but this method would help you find your answer if applied to a dataset containing company locations by county.</t>
+  </si>
+  <si>
+    <t>Here's a breakdown of the counties with the fewest companies, based on the provided evidence:
+1.  **McDuffie County:** 1 company (Bosch (Automotive Division))
+2.  **Elbert County:** 1 company (Blue Bird Corp.)
+3.  **Gwinnett County:** 1 company (Continental Tire the Americas LLC)
+4.  **Laurens County:** 1 company (GLOVIS Georgia LLC)
+5.  **Coweta County:** 1 company (Dongwon Autopart Technology Georgia LLC)
+The workbook evidence is limited and does not provide a comprehensive list of all companies in Georgia.</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I cannot provide the exact bottom 5 counties with the fewest companies, excluding those in Georgia. However, generally, the counties with fewer companies tend to be rural or less developed areas. 
+To determine the specific counties, I would need to analyze the data and sort by company count after filtering out the Georgia locations.</t>
+  </si>
+  <si>
+    <t>Based on the provided evidence, the following counties have the fewest companies:
+1.  **Coweta County:** 1 company
+    *   Dongwon Autopart Technology Georgia LLC
+2.  **Elbert County:** 1 company
+    *   Blue Bird Corp.
+3.  **Gwinnett County:** 1 company
+    *   Continental Tire the Americas LLC
+4.  **Laurens County:** 1 company
+    *   GLOVIS Georgia LLC
+5.  **McDuffie County:** 1 company
+    *   Bosch (Automotive Division)</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 2.695870341s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '2s'}]}}</t>
+  </si>
+  <si>
+    <t>For Tier 1 suppliers, identify any counties that have only one Tier 1 supplier and name that supplier.</t>
+  </si>
+  <si>
+    <t>Counties with exactly one Tier 1 supplier [21]: Appling County: Sumitomo Electric Wiring Systems | Location: Baxley, Appling County | EV Supply Chain Role: Materials Bibb County: Seoyon E-Hwa Interior Systems | Location: Macon, Bibb County | EV Supply Chain Role: General Automotive Candler County: Nidec Elesys Americas Corp. | Location: Metter, Candler County | EV Supply Chain Role: General Automotive Cherokee County: JTEKT North America Corp. | Location: Canton, Cherokee County | EV Supply Chain Role: General Automotive Clarke County: Sewon America Inc. | Location: Athens, Clarke County | EV Supply Chain Role: General Automotive Cobb County: Sewon America Inc. | Location: Marietta, Cobb County | EV Supply Chain Role: General Automotive Coffee County: Suhner Manufacturing Corp. | Location: Douglas, Coffee County | EV Supply Chain Role: General Automotive Crisp County: OTR Wheel Engineering Inc. | Location: Cordele, Crisp County | EV Supply Chain Role: General Automotive Fannin County: Southern Switches Corp. | Location: Blue Ridge, Fannin County | EV Supply Chain Role: General Automotive Fayette County: RealTruck | Location: Fayetteville, Fayette County | EV Supply Chain Role: General Automotive Gordon County: Racemark International LLC | Location: Calhoun, Gordon County | EV Supply Chain Role: General Automotive Grady County: Porsche Cars North America Inc. | Location: Cairo, Grady County | EV Supply Chain Role: General Automotive Haralson County: Lyle Industries Inc. | Location: Buchanan, Haralson County | EV Supply Chain Role: General Automotive Liberty County: Panasonic Automotive Systems Co. | Location: Hinesville, Liberty County | EV Supply Chain Role: General Automotive Newton County: Murata Electronics North America Inc. | Location: Covington, Newton County | EV Supply Chain Role: General Automotive Pike County: Perkins Small Engines LLC | Location: Zebulon, Pike County | EV Supply Chain Role: General Automotive Polk County: Mercedes-Benz USA LLC | Location: Cedartown, Polk County | EV Supply Chain Role: General Automotive Richmond County: Magna International | Location: Augusta, Richmond County | EV Supply Chain Role: General Automotive Stephens County: MollerTech LLC | Location: Toccoa, Stephens County | EV Supply Chain Role: General Automotive Walker County: Maxxis International USA | Location: La Fayette, Walker County | EV Supply Chain Role: General Automotive Walton County: Jefferson Southern Corporation | Location: Monroe, Walton County | EV Supply Chain Role: General Automotive</t>
+  </si>
+  <si>
+    <t>General Automotive:
+- Jefferson Southern Corporation (Walton County)
+- Joon Georgia, Inc. (Troup County)
+Charging Infrastructure:
+- Morgan Corp. (no specific county mentioned but unique within its role)</t>
+  </si>
+  <si>
+    <t>To answer this question accurately, I would need specific data about the locations of Tier 1 suppliers and their distribution across different counties. Since no workbook evidence is provided, I can't give an exact list of counties with a single Tier 1 supplier or identify those suppliers directly. However, if you have such information in your Excel workbook, you could use filters or pivot tables to count the number of Tier 1 suppliers per county and then filter for counties where that count equals one.
+If you need help with how to perform these steps in Excel, feel free to ask!</t>
+  </si>
+  <si>
+    <t>Here's a list of counties with only one Tier 1 supplier, based on the provided evidence:
+*   **Cherokee County:** JTEKT North America Corp.
+*   **Carroll County:** Kautex Inc.
+*   **Effingham County:** KTX America Corporation
+*   **Hall County:** Mobis Alabama LLC
+*   **Walton County:** Jefferson Southern Corporation</t>
+  </si>
+  <si>
+    <t>Based on the provided evidence, the following counties have only one Tier 1 supplier:
+*   **Cherokee County:** JTEKT North America Corp.
+*   **Effingham County:** KTX America Corporation
+*   **Hall County:** Mobis Alabama LLC
+*   **Walton County:** Jefferson Southern Corporation</t>
+  </si>
+  <si>
+    <t>I cannot answer this question without the workbook. The question asks for specific information about "Tier 1 suppliers" and their locations within "counties," as well as identifying individual suppliers. This kind of detailed data is contained within the workbook and is not something I can access from general knowledge.</t>
+  </si>
+  <si>
+    <t>Identify any companies that appear multiple times in the dataset, and for each, list the distinct EV Supply Chain Roles recorded.</t>
+  </si>
+  <si>
+    <t>Companies appearing multiple times and their distinct EV Supply Chain Roles: Arising Industries Inc. [2 rows] -&gt; Roles: General Automotive Freudenberg-NOK [2 rows] -&gt; Roles: General Automotive, Thermal Management Haering Precision USA LP [2 rows] -&gt; Roles: General Automotive, Materials Lyle Industries Inc. [2 rows] -&gt; Roles: General Automotive Novelis Inc. [3 rows] -&gt; Roles: General Automotive, Thermal Management Panasonic Automotive Systems Co. [2 rows] -&gt; Roles: General Automotive, Materials Sewon America Inc. [3 rows] -&gt; Roles: General Automotive TI Fluid Systems [2 rows] -&gt; Roles: OEM corporate footprint influencing EV strategy, Vehicle safety systems OEM (EV + ICE) ZF Gainesville LLC [3 rows] -&gt; Roles: EV body, powertrain, and thermal components, EV thermal management and power electronics, EV thermal systems and electronics</t>
+  </si>
+  <si>
+    <t>There are no companies appearing multiple times in the provided dataset with distinct EV Supply Chain Roles recorded. Each company listed has only one entry and thus does not repeat any EV Supply Chain Role information.</t>
+  </si>
+  <si>
+    <t>To identify companies that appear multiple times in a dataset and to list the distinct EV Supply Chain Roles associated with each company, you would typically follow these steps:
+1. **Identify Duplicate Companies**: Look through the data to find any company names that are repeated.
+2. **Extract Unique Roles for Each Company**: For each duplicate company identified, extract all unique roles related to the EV supply chain.
+Since no specific dataset or workbook is provided here, I can't give you exact companies and their roles from a particular file. However, if you have an Excel workbook with columns like "Company Name" and "EV Supply Chain Role," you could use formulas or pivot tables in Excel to achieve this:
+- Use the `COUNTIF` function to find duplicate company names.
+- Utilize the `UNIQUE` function (available in newer versions of Excel) along with `FILTER` to list unique roles for each company.
+If you provide more details about your dataset structure, I can give a more tailored response or even an example formula.</t>
+  </si>
+  <si>
+    <t>There are no companies that appear multiple times in the provided dataset. Each company appears only once.</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the dataset. My response would depend on identifying companies appearing more than once and then listing the unique EV Supply Chain Roles associated with each.</t>
+  </si>
+  <si>
+    <t>Based on the provided evidence, no companies appear multiple times in the dataset. Each company listed (Lear Corporation, Blue Bird Corp., Bosch (Automotive Division), DaeChang Seat Company, Daesol Ausys, Denkai America, GLOVIS Georgia LLC, Peterson Spring) appears only once.</t>
+  </si>
+  <si>
+    <t>I cannot identify companies that appear multiple times in the dataset or list their distinct EV Supply Chain Roles without access to the specific dataset you are referring to. This kind of analysis requires examining the content of your workbook.</t>
+  </si>
+  <si>
+    <t>For the company 'ZF Gainesville LLC', list all rows and compare their Categories, EV Supply Chain Roles, and Locations.</t>
+  </si>
+  <si>
+    <t>ZF Gainesville LLC rows [3]: Category: OEM Supply Chain | EV Supply Chain Role: EV body, powertrain, and thermal components | Location: Georgia | Primary Facility Type: Manufacturing | Employment: 170,000 Category: OEM Supply Chain | EV Supply Chain Role: EV thermal management and power electronics | Location: Georgia | Primary Facility Type: Manufacturing | Employment: 17,500 Category: OEM Footprint | EV Supply Chain Role: EV thermal systems and electronics | Location: Georgia | Primary Facility Type: Engineering / Operations | Employment: 106,100</t>
+  </si>
+  <si>
+    <t>**ZF Gainesville LLC**
+- **Category:** OEM Supply Chain  
+  - **EV Supply Chain Role:** EV body, powertrain, and thermal components  
+  - **Location:** Georgia
+- **Category:** OEM Supply Chain  
+  - **EV Supply Chain Role:** EV thermal management and power electronics  
+  - **Location:** Georgia
+- **Category:** OEM Footprint  
+  - **EV Supply Chain Role:** EV thermal systems and electronics  
+  - **Location:** Georgia</t>
+  </si>
+  <si>
+    <t>Without specific workbook evidence provided for "ZF Gainesville LLC," I can't provide exact details about the categories, supply chain roles, or locations listed in a particular Excel sheet. However, typically such information would be organized with each row representing a different category, role, or location associated with ZF Gainesville LLC.
+For example:
+- Row 1 might have Category: Manufacturing, EV Supply Chain Role: Assembly Line Manager, Location: Gainesville, GA.
+- Row 2 could show Category: Logistics, EV Supply Chain Role: Inventory Control Specialist, Location: Atlanta, GA (if there's a logistics center nearby).
+To give you an accurate comparison of the rows for ZF Gainesville LLC, I would need to see the actual data from your workbook. If you have specific details or can provide more context about what is in the workbook, I could offer a more tailored response based on general guidance and structure.</t>
+  </si>
+  <si>
+    <t>Here's a comparison of the rows for 'ZF Gainesville LLC' based on the provided evidence:
+**Row 1:**
+*   Category: OEM Supply Chain
+*   EV Supply Chain Role: EV body, powertrain, and thermal components
+*   Location: Georgia
+*   Employment: 170000
+**Row 2:**
+*   Category: OEM Supply Chain
+*   EV Supply Chain Role: EV thermal management and power electronics
+*   Location: Georgia
+*   Employment: 17500
+**Row 3:**
+*   Category: OEM Footprint
+*   EV Supply Chain Role: EV thermal systems and electronics
+*   Location: Georgia
+*   Employment: 106100</t>
+  </si>
+  <si>
+    <t>I cannot fulfill this request. I do not have access to any workbooks and therefore cannot provide information about 'ZF Gainesville LLC', its Categories, EV Supply Chain Roles, or Locations.</t>
+  </si>
+  <si>
+    <t>For ZF Gainesville LLC, the categories, EV Supply Chain Roles, and locations are as follows:
+*   **Category**: OEM Supply Chain, **EV Supply Chain Role**: EV body, powertrain, and thermal components, **Location**: Georgia
+*   **Category**: OEM Supply Chain, **EV Supply Chain Role**: EV thermal management and power electronics, **Location**: Georgia
+*   **Category**: OEM Footprint, **EV Supply Chain Role**: EV thermal systems and electronics, **Location**: Georgia</t>
+  </si>
+  <si>
+    <t>I cannot access external workbooks or files, including the one you are referencing. Therefore, I cannot list the rows for 'ZF Gainesville LLC' or compare their Categories, EV Supply Chain Roles, and Locations.</t>
+  </si>
+  <si>
+    <t>For the company 'Novelis Inc.', list the different Locations and Primary Facility Types recorded.</t>
+  </si>
+  <si>
+    <t>Novelis Inc. recorded Locations and Primary Facility Types: Gainesville, Hall County | Primary Facility Type: Manufacturing Plant Trenton, Dade County | Primary Facility Type: Manufacturing Plant Lawrenceville, Gwinnett County | Primary Facility Type: Manufacturing Plant</t>
+  </si>
+  <si>
+    <t>**General Automotive**
+- Location: Gainesville, Hall County | Primary Facility Type: Not specified
+- Location: Trenton, Dade County | Primary Facility Type: Not specified
+**Thermal Management**
+- Location: Lawrenceville, Gwinnett County | Primary Facility Type: Not specified</t>
+  </si>
+  <si>
+    <t>Without specific workbook evidence provided for Novelis Inc., I can't list exact locations and primary facility types. However, generally speaking, companies like Novelis Inc. typically have various locations such as manufacturing plants, offices, and distribution centers spread across multiple countries. The primary facility types might include aluminum rolling mills, recycling facilities, and administrative offices.
+For precise details about Novelis Inc., you would need to refer to their official company records or the specific workbook containing this information.</t>
+  </si>
+  <si>
+    <t>Novelis Inc. has the following Locations: Gainesville, Hall County; Trenton, Dade County; and Lawrenceville, Gwinnett County. The Primary Facility Type is not specified for Novelis Inc. in the provided evidence.</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I can't provide the specific Locations and Primary Facility Types recorded for Novelis Inc. However, Novelis Inc. is a major aluminum rolling and recycling company, so locations would likely include manufacturing plants and recycling facilities across North America, Europe, and Asia. Facility types would likely include rolling mills, recycling centers, and potentially research and development centers.</t>
+  </si>
+  <si>
+    <t>For Novelis Inc., the recorded locations are:
+*   Gainesville, Hall County
+*   Trenton, Dade County
+*   Lawrenceville, Gwinnett County
+The workbook evidence does not contain information on the 'Primary Facility Type' for Novelis Inc.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 36.065428442s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-2.5-flash', 'location': 'global'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '36s'}]}}</t>
+  </si>
+  <si>
+    <t>For the company 'Sewon America Inc.', list each recorded Product / Service and the associated Location.</t>
+  </si>
+  <si>
+    <t>Sewon America Inc. Product / Service by Location: Atlanta, Fulton County -&gt; Automotive aftermarket parts Athens, Clarke County -&gt; Motor vehicle engines and parts Marietta, Cobb County -&gt; Fire truck bodies</t>
+  </si>
+  <si>
+    <t>**General Automotive**
+- **Product / Service:** Automotive aftermarket parts  
+  **Location:** Atlanta, Fulton County
+- **Product / Service:** Motor vehicle engines and parts  
+  **Location:** Athens, Clarke County
+**Fire truck bodies**
+- **Product / Service:** Fire truck bodies  
+  **Location:** Marietta, Cobb County</t>
+  </si>
+  <si>
+    <t>Without specific workbook evidence provided for "Sewon America Inc.", I can't list the exact products/services and their associated locations. However, typically such information would be found in a table or spreadsheet where each row represents a product/service entry with columns specifying the name of the product/service and its location (e.g., warehouse, store, distribution center). If you have specific details about the structure of your workbook, I can provide guidance on how to extract this kind of data.</t>
+  </si>
+  <si>
+    <t>For Sewon America Inc., the recorded Product / Service and associated Location are:
+*   **Automotive aftermarket parts:** Atlanta, Fulton County
+*   **Motor vehicle engines and parts:** Athens, Clarke County
+*   **Fire truck bodies:** Marietta, Cobb County</t>
+  </si>
+  <si>
+    <t>I cannot answer this question. I do not have access to any workbooks or data related to "Sewon America Inc." and their products/services and locations.</t>
+  </si>
+  <si>
+    <t>- Automotive aftermarket parts: Atlanta, Fulton County
+- Motor vehicle engines and parts: Athens, Clarke County
+- Fire truck bodies: Marietta, Cobb County</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 35.939871902s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '35s'}]}}</t>
+  </si>
+  <si>
+    <t>Which Industry Groups have both Tier 1 and Tier 2/3 suppliers present? Provide the Industry Group names.</t>
+  </si>
+  <si>
+    <t>None. No Industry Group in the workbook has both Tier 1 and Tier 2/3 suppliers recorded.</t>
+  </si>
+  <si>
+    <t>The provided evidence does not contain any companies categorized under Tier 1. Therefore, there are no Industry Groups with both Tier 1 and Tier 2/3 suppliers present based on the given data.</t>
+  </si>
+  <si>
+    <t>To accurately determine which industry groups have both Tier 1 and Tier 2/3 suppliers without specific workbook evidence, I would need to rely on general knowledge or hypothetical scenarios. Typically, in supply chain management contexts, many industry groups such as automotive, electronics, aerospace, and consumer goods often include companies that are categorized into different tiers based on their position within the supply network.
+Without exact data from a provided workbook, it's challenging to name specific industry groups with certainty. However, if we consider common practices across various industries:
+1. Automotive
+2. Electronics
+3. Aerospace
+These industry groups commonly have both Tier 1 and Tier 2/3 suppliers as part of their supply chain structure.</t>
+  </si>
+  <si>
+    <t>The provided evidence does not contain information about Industry Groups that have both Tier 1 and Tier 2/3 suppliers. It only lists EV Supply Chain Roles and the companies associated with them.</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I cannot definitively answer which Industry Groups have both Tier 1 and Tier 2/3 suppliers. Generally, this would depend on the workbook's data structure and how supplier tiers are categorized within it. 
+However, in many supply chain analyses, common Industry Groups that often have a mix of Tier 1 and Tier 2/3 suppliers include:
+*   **Automotive**
+*   **Aerospace &amp; Defense**
+*   **Electronics**
+*   **Industrial Machinery**
+*   **Pharmaceuticals**
+Please provide the workbook if you need a precise answer based on the data it contains.</t>
+  </si>
+  <si>
+    <t>The provided workbook evidence does not contain information about Industry Groups for Tier 1 suppliers, only for Tier 2/3 suppliers. Therefore, it is not possible to determine which Industry Groups have both Tier 1 and Tier 2/3 suppliers present.</t>
+  </si>
+  <si>
+    <t>I cannot answer this question without the workbook. The question asks for specific information about "Tier 1" and "Tier 2/3" suppliers within "Industry Groups," which are categories likely defined and populated within the provided workbook. To answer, I would need to analyze the data in the workbook to identify which Industry Groups contain both types of suppliers.</t>
+  </si>
+  <si>
+    <t>Within Materials companies, which county has the highest number of Materials entries, and what are the companies?</t>
+  </si>
+  <si>
+    <t>Highest number of Materials entries is a tie at 2. Top counties and companies: Bartow County [2]: Constellium Automotive USA, Panasonic Automotive Systems Co. Hall County [2]: Boogook Industries, DAS Corp. Richmond County [2]: Bridgestone Bandag, EVCO Plastics Troup County [2]: Aspen Aerogels, Aurubis</t>
+  </si>
+  <si>
+    <t>Troup County has the highest number of Materials entries:
+- Aspen Aerogels | Location: Troup County | Employment: 414 | EV / Battery Relevant: No
+- Aurubis | Location: Troup County | Employment: 400 | EV / Battery Relevant: Indirect</t>
+  </si>
+  <si>
+    <t>Without specific data from an Excel workbook or another detailed source, I can't provide precise information about which county within materials companies has the highest number of entries. However, generally speaking, counties with major industrial hubs or those near natural resource deposits often host a higher concentration of materials companies.
+For example, if we were looking at U.S. data, Maricopa County in Arizona might be one such location due to its significant mining and manufacturing activities. Companies could include ASARCO LLC (a copper producer) and Freeport-McMoRan Inc., though this is speculative without specific workbook evidence.
+To provide an exact answer, you would need to analyze the relevant Excel data that includes company locations and categorizations by industry sector.</t>
+  </si>
+  <si>
+    <t>Troup County has the highest number of Materials entries, with three companies: Aspen Aerogels, Aurubis, and Beaver Manufacturing Co. Inc.</t>
+  </si>
+  <si>
+    <t>I cannot answer this question. I do not have access to any data regarding Materials companies or their locations.</t>
+  </si>
+  <si>
+    <t>Troup County has the highest number of Materials entries, with the following companies:
+*   Aspen Aerogels
+*   Aurubis</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 48.759738268s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '48s'}]}}</t>
+  </si>
+  <si>
+    <t>Which counties have Battery Pack or Battery Cell activity, and how many companies are in each of those roles per county?</t>
+  </si>
+  <si>
+    <t>Counties with Battery Pack or Battery Cell activity: Bryan County: Battery Pack=0, Battery Cell=1 | Companies: Honda Development &amp; Manufacturing (Battery Cell) Coweta County: Battery Pack=0, Battery Cell=1 | Companies: Hitachi Astemo Americas Inc. (Battery Cell) Decatur County: Battery Pack=1, Battery Cell=0 | Companies: Hollingsworth &amp; Vose Co. (Battery Pack) Henry County: Battery Pack=1, Battery Cell=0 | Companies: Hyundai Motor Group (Battery Pack) Jackson County: Battery Pack=1, Battery Cell=0 | Companies: IMMI (Battery Pack) Stephens County: Battery Pack=1, Battery Cell=0 | Companies: F&amp;P Georgia Manufacturing (Battery Pack)</t>
+  </si>
+  <si>
+    <t>**Battery Pack Activity:**
+- **Stephens County:** F&amp;P Georgia Manufacturing (1 company)
+- **Decatur County:** Hollingsworth &amp; Vose Co. (1 company)
+- **Henry County:** Hyundai Motor Group (1 company)
+- **Jackson County:** IMMI (1 company)
+**Battery Cell Activity:**
+- **Coweta County:** Hitachi Astemo Americas Inc. (1 company)
+- **Bryan County:** Honda Development &amp; Manufacturing (1 company)</t>
+  </si>
+  <si>
+    <t>Without specific data from an Excel workbook or other detailed sources, I can't provide the exact number of companies involved in battery pack or battery cell activities by county. However, typically such information would be found through industry reports, government databases, or company registries that track manufacturing locations and specializations.
+For example, if we were to look at a hypothetical scenario based on general knowledge:
+- County A might have 5 companies involved in Battery Pack assembly.
+- County B could have 3 companies focusing on Battery Cell production.
+To get precise figures, you would need to consult specific datasets or reports that detail the manufacturing activities and company locations for battery components.</t>
+  </si>
+  <si>
+    <t>Here's a breakdown of counties with Battery Pack or Battery Cell activity and the number of companies in each role, based on the provided evidence:
+**Coweta County:**
+*   EV Supply Chain Role: Battery Cell
+*   Company: Hitachi Astemo Americas Inc. (1 company)
+**Bryan County:**
+*   EV Supply Chain Role: Battery Cell
+*   Company: Honda Development &amp; Manufacturing (1 company)
+**Henry County:**
+*   EV Supply Chain Role: Battery Pack
+*   Company: Hyundai Motor Group (1 company)
+**Jackson County:**
+*   EV Supply Chain Role: Battery Pack
+*   Company: IMMI (1 company)
+**Stephens County:**
+*   EV Supply Chain Role: Battery Pack
+*   Company: F&amp;P Georgia Manufacturing (1 company)
+**Decatur County:**
+*   EV Supply Chain Role: Battery Pack
+*   Company: Hollingsworth &amp; Vose Co. (1 company)
+The workbook evidence is limited and may not represent all counties or companies involved in Battery Pack or Battery Cell activity.</t>
+  </si>
+  <si>
+    <t>**Battery Pack:**
+*   **Stephens County:** F&amp;P Georgia Manufacturing (1 company)
+*   **Decatur County:** Hollingsworth &amp; Vose Co. (1 company)
+*   **Henry County:** Hyundai Motor Group (1 company)
+*   **Jackson County:** IMMI (1 company)
+**Battery Cell:**
+*   **Coweta County:** Hitachi Astemo Americas Inc. (1 company)
+*   **Bryan County:** Honda Development &amp; Manufacturing (1 company)</t>
+  </si>
+  <si>
+    <t>I cannot answer this question without more information. To tell you which counties have Battery Pack or Battery Cell activity and how many companies are in each of those roles per county, I would need access to a database or spreadsheet containing company information, their roles (e.g., Battery Pack, Battery Cell), and their corresponding county locations.</t>
+  </si>
+  <si>
+    <t>Identify companies marked as EV / Battery Relevant = No but still categorized as Tier 1 or Tier 1/2; list them with their Product / Service.</t>
+  </si>
+  <si>
+    <t>EV / Battery Relevant = No but Category is Tier 1 or Tier 1/2 [48 rows]: Jefferson Southern Corporation | Category: Tier 1 | Product / Service: Stamped metal automobile body parts Joon Georgia, Inc. | Category: Tier 1 | Product / Service: Seats and seat foam pads KTX America Corporation | Category: Tier 1 | Product / Service: Stamped components and decorative trim Kumho Tire USA Inc. | Category: Tier 1 | Product / Service: Stamped components and decorative trim Kyungshin America Corp. | Category: Tier 1 | Product / Service: Front-end modules, front-rolling chassis modules, rear-chassis modules Lear Corporation | Category: Tier 1 | Product / Service: Pressed parts in the body-in-white segment and structural components Lehigh Technologies Inc. | Category: Tier 1 | Product / Service: Suspension related functional components Linde + Wiemann | Category: Tier 1 | Product / Service: 6-speed automatic transmissions Lund International Inc./Ventshade Division | Category: Tier 1 | Product / Service: Industrial trailers and truck bodies Lyle Industries Inc. | Category: Tier 1 | Product / Service: Automatic transmissions Lyle Industries Inc. | Category: Tier 1 | Product / Service: Molded injection auto parts Magna International | Category: Tier 1 | Product / Service: Ceramic fiber insulation blankets Master Craft Engineering Inc. | Category: Tier 1 | Product / Service: Door modules, tailgate latches, and hood latches Maxxis International USA | Category: Tier 1 | Product / Service: Brake systems MollerTech LLC | Category: Tier 1 | Product / Service: Injection molded components NIFCO KTW America Corp. | Category: Tier 1 | Product / Service: Inventory management for Kia Nidec Elesys Americas Corp. | Category: Tier 1 | Product / Service: Seating systems Nile Automotive | Category: Tier 1 | Product / Service: Window regulators and door frames Nisshinbo Automotive Manufacturing Inc. | Category: Tier 1 | Product / Service: Braking and suspension products Nivel Parts &amp; Manufacturing Co. LLC | Category: Tier 1 | Product / Service: Industrial trailers and truck bodies Novelis Inc. | Category: Tier 1 | Product / Service: Seat, interior, and precision metal stamping OTR Wheel Engineering Inc. | Category: Tier 1 | Product / Service: Single axle trailers PAI Industries Inc. | Category: Tier 1 | Product / Service: Brake pads PHA Body Systems LLC | Category: Tier 1 | Product / Service: Plastic fuel tanks and sunroofs PPG Industries Inc. | Category: Tier 1 | Product / Service: Muffler and exhaust systems Paccar | Category: Tier 1 | Product / Service: Semi-trailers Pak-Lite Inc. | Category: Tier 1 | Product / Service: Tires, wheels and rubber tracks Panasonic Automotive Systems Co. | Category: Tier 1 | Product / Service: Axle bearings Panduit Corp. | Category: Tier 1 | Product / Service: Truck bodies and parts Peerless-Winsmith Inc. | Category: Tier 1 | Product / Service: Thermal solutions Piedmont Automotive Products Inc. | Category: Tier 1 | Product / Service: Interior components and accessories QSR Inc. | Category: Tier 1 | Product / Service: Functional aftermarket accessories for trucks and SUVs Rivian Automotive | Category: Tier 1 | Product / Service: Custom metal components SAFT America Inc. | Category: Tier 1 | Product / Service: Arm and head rests SKF USA Inc. | Category: Tier 1 | Product / Service: Exhaust systems and parts SRG Global Inc. | Category: Tier 1 | Product / Service: Products for marine, mobile home, and other industries Sejong Georgia LLC | Category: Tier 1 | Product / Service: NVH parts and interior components Seohan Auto USA | Category: Tier 1 | Product / Service: Custom made cargo trailers Ben Seoyon E-HWA | Category: Tier 1 | Product / Service: Custom made cargo trailers Jeff Seoyon E-Hwa Interior Systems | Category: Tier 1 | Product / Service: Fluid-carrying systems Sewon America Inc. | Category: Tier 1 | Product / Service: Fire truck bodies Southern Switches Corp. | Category: Tier 1 | Product / Service: Commercial truck bodies Suhner Manufacturing Corp. | Category: Tier 1 | Product / Service: Truck trailers Hitachi Astemo | Category: Tier 1/2 | Product / Service: Car audio systems Hwashin | Category: Tier 1/2 | Product / Service: Modules and storage systems Hyundai &amp; LG Energy Solution (LGES) | Category: Tier 1/2 | Product / Service: Storage batteries IMS Gear Georgia Inc. | Category: Tier 1/2 | Product / Service: Car audio systems JAC Products Inc. | Category: Tier 1/2 | Product / Service: Switches, resistors and related products</t>
+  </si>
+  <si>
+    <t>General Automotive:
+- Fouts Brothers Fire Equipment | Automotive body parts and electronics Cylinder-head and specialty gaskets, housing modules and shielding systems for engines, transmissions, exhaust systems and auxiliary units
+Battery Cell:
+- Hitachi Astemo | Car audio systems
+Note: The company "Hitachi Astemo" is listed under both Battery Cell and General Automotive roles. However, only the role where EV / Battery Relevant = No (General Automotive) is included in this list.</t>
+  </si>
+  <si>
+    <t>Without specific workbook evidence, I can't provide an exact list of companies that are marked as "EV / Battery Relevant = No" but are still categorized as Tier 1 or Tier 1/2 along with their products/services. However, in general terms, you would look for entries where the company is not involved directly in electric vehicle (EV) batteries or EV production according to your criteria ("EV / Battery Relevant = No"), yet they hold a significant position within the supply chain as indicated by their tier classification.
+To find such companies manually:
+1. Filter the list of companies based on "Tier 1" and "Tier 1/2".
+2. From this filtered list, identify those marked with "No" in the "EV / Battery Relevant" column.
+3. Note down these companies along with their associated products or services.
+If you have specific data available, applying these steps should help you compile the required information accurately.</t>
+  </si>
+  <si>
+    <t>The following companies are categorized as Tier 1 or Tier 1/2 and marked as EV / Battery Relevant = No:
+*   **Hitachi Astemo:** Car audio systems
+*   **Hwashin:** Modules and storage systems</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question. It requires information about companies categorized as "EV / Battery Relevant = No" and their "Product / Service" based on a specific classification of "Tier 1" or "Tier 1/2." This data is only available within the Excel workbook you mentioned, and I do not have access to it.</t>
+  </si>
+  <si>
+    <t>**General Automotive**
+*   **Hitachi Astemo:** Car audio systems
+*   **Hwashin:** Modules and storage systems</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 47.864725072s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-2.5-flash', 'location': 'global'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '47s'}]}}</t>
+  </si>
+  <si>
+    <t>Which Supplier or Affiliation Type categories exist in the dataset, and how many companies fall under each?</t>
+  </si>
+  <si>
+    <t>Supplier or Affiliation Type categories and counts: Automotive supply chain participant: 170 Blank / Missing: 26 Original Equipment Manufacturer: 11</t>
+  </si>
+  <si>
+    <t>The Supplier or Affiliation Type categories and corresponding company counts from the dataset are as follows:
+- Automotive supply chain participant: 8 (DeKalb Tool &amp; Die Inc., Lear Corporation, Bosch (Automotive Division), Blue Bird Corp., Continental Tire the Americas LLC, DaeChang Seat Company, Daesol Ausys)</t>
+  </si>
+  <si>
+    <t>Without specific workbook evidence, I can't provide an exact count of supplier types or affiliations. However, typically such datasets might include categories like "Direct Supplier," "Indirect Supplier," "Strategic Partner," "Vendor," and "Affiliate." To give you precise numbers for each category, we would need to analyze the actual dataset provided in your workbook. Can you provide more details about the specific categories mentioned in your data?</t>
+  </si>
+  <si>
+    <t>The Supplier or Affiliation Type categories in the dataset are:
+*   **Automotive supply chain participant:** DeKalb Tool &amp; Die Inc., Lear Corporation, Bosch (Automotive Division), Blue Bird Corp., Continental Tire the Americas LLC, DaeChang Seat Company, Daesol Ausys</t>
+  </si>
+  <si>
+    <t>I cannot answer this question without access to the dataset. The question asks for specific categories and counts from a dataset, which I do not have.</t>
+  </si>
+  <si>
+    <t>The dataset contains companies classified as "Automotive supply chain participant". The following companies fall under this category:
+*   DeKalb Tool &amp; Die Inc.
+*   Lear Corporation
+*   Bosch (Automotive Division)
+*   Blue Bird Corp.
+*   Continental Tire the Americas LLC
+*   DaeChang Seat Company
+*   Daesol Ausys</t>
+  </si>
+  <si>
+    <t>I cannot tell you which Supplier or Affiliation Type categories exist in the dataset or how many companies fall under each without access to the specific dataset. This information would be contained within the workbook itself.</t>
+  </si>
+  <si>
+    <t>Among entries with Supplier or Affiliation Type = Original Equipment Manufacturer, what EV Supply Chain Roles are represented?</t>
+  </si>
+  <si>
+    <t>EV Supply Chain Roles represented among Original Equipment Manufacturer entries: Vehicle Assembly: 10 General Automotive: 1 Companies by role: Vehicle Assembly -&gt; Kia Georgia Inc., Superior Essex Inc., Suzuki Manufacturing of America Corp., TCI Powder Coatings, TDK Components USA Inc., TE Connectivity, Teklas USA, Textron Specialized Vehicles, Thermal Ceramics Inc., Thomson Plastics Inc. General Automotive -&gt; Minebea AccessSolutions USA Inc.</t>
+  </si>
+  <si>
+    <t>Vehicle Assembly:
+- Kia Georgia Inc.
+- Superior Essex Inc.
+- Suzuki Manufacturing of America Corp.
+- TCI Powder Coatings
+General Automotive:
+- Minebea AccessSolutions USA Inc.</t>
+  </si>
+  <si>
+    <t>Among entries where the Supplier or Affiliation Type is listed as "Original Equipment Manufacturer," typical EV (Electric Vehicle) supply chain roles that might be represented include:
+- **Component Supplier**: These manufacturers produce specific parts such as batteries, motors, and electronic control units.
+- **Battery Manufacturer**: Specializes in producing battery packs for electric vehicles.
+- **Motor Producer**: Focuses on manufacturing the electric motor used to drive the vehicle's wheels.
+- **Drive System Developer**: Engages in developing the entire propulsion system including the motor and associated electronics.
+These roles can vary depending on the specific context of each Original Equipment Manufacturer (OEM) within the EV supply chain. OEMs may also engage directly in assembly or act as integrators, combining various components to produce complete electric vehicles.</t>
+  </si>
+  <si>
+    <t>The EV Supply Chain Roles represented among companies with a Supplier or Affiliation Type of Original Equipment Manufacturer are: Vehicle Assembly, General Automotive, and Electric vehicles and batteries.
+Specifically:
+*   Kia Georgia Inc. - Vehicle Assembly
+*   Minebea AccessSolutions USA Inc. - General Automotive
+*   Superior Essex Inc. - Vehicle Assembly
+*   Suzuki Manufacturing of America Corp. - Vehicle Assembly
+*   TCI Powder Coatings - Vehicle Assembly
+*   TDK Components USA Inc. - Vehicle Assembly</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I can't provide a definitive list of EV Supply Chain Roles represented among entries with a Supplier or Affiliation Type of Original Equipment Manufacturer (OEM). However, generally, OEM relationships in the EV supply chain would likely involve roles such as:
+*   **Engineering/Design:** OEMs often engage with suppliers for design and engineering support.
+*   **Manufacturing:** This is a core role, as OEMs contract manufacturers to produce components or entire systems.
+*   **Quality Assurance/Control:** OEMs require rigorous quality control from their suppliers.
+*   **Supply Planning:** OEMs need suppliers to adhere to production schedules and forecasts.
+*   **Procurement:** The role of sourcing and purchasing components from OEMs.
+The specific roles present would depend on the nature of the OEM's relationship with the supplier.</t>
+  </si>
+  <si>
+    <t>Among entries with Supplier or Affiliation Type = Original Equipment Manufacturer, the following EV Supply Chain Roles are represented:
+*   **Vehicle Assembly:**
+    *   Kia Georgia Inc.
+    *   Superior Essex Inc.
+    *   Suzuki Manufacturing of America Corp.
+    *   TCI Powder Coatings
+    *   TDK Components USA Inc.
+*   **General Automotive:**
+    *   Minebea AccessSolutions USA Inc.</t>
+  </si>
+  <si>
+    <t>I cannot answer this question without the workbook. This question requires me to filter entries by "Supplier or Affiliation Type" and then identify the "EV Supply Chain Roles" within that filtered set. This is specific data contained within the workbook.</t>
+  </si>
+  <si>
+    <t>Which companies have missing Primary OEMs, and what EV Supply Chain Role do they have?</t>
+  </si>
+  <si>
+    <t>Missing Primary OEMs [26 rows]: TI Fluid Systems | EV Supply Chain Role: OEM corporate footprint influencing EV strategy | Category: OEM (Footprint) | Location: Atlanta, Fulton County TI Fluid Systems | EV Supply Chain Role: Vehicle safety systems OEM (EV + ICE) | Category: OEM | Location: Georgia (facility presence) TN Americas Holding Inc. | EV Supply Chain Role: OEM parent group footprint (EV + HD electrification) | Category: OEM (Footprint) | Location: Georgia Tie Down Engineering | EV Supply Chain Role: OEM corporate and engineering footprint (electrification) | Category: OEM (Footprint) | Location: Greensboro, Greene County Toyota Industries Group (TACG-TICA) | EV Supply Chain Role: OEM parent group footprint (electric truck strategy) | Category: OEM (Footprint) | Location: Georgia Trenton Pressing | EV Supply Chain Role: OEM corporate footprint and supplier integration | Category: OEM (Footprint) | Location: Georgia Trenton Pressing Inc. | EV Supply Chain Role: Machined components supporting EV and ICE vehicles | Category: OEM Supply Chain | Location: Georgia Valeo | EV Supply Chain Role: Tier 1 automotive components | Category: OEM Supply Chain | Location: Georgia Vanguard National Trailer Corp. | EV Supply Chain Role: Body and chassis components for EV and ICE OEMs | Category: OEM Supply Chain | Location: Georgia Vernay | EV Supply Chain Role: Stamped and welded assemblies for OEMs | Category: OEM Supply Chain | Location: Georgia Vista Metals Corp. | EV Supply Chain Role: EV and ICE component manufacturing | Category: OEM Supply Chain | Location: Georgia Voestalpine Automotive Body Parts Inc. | EV Supply Chain Role: EV and ICE powertrain and HVAC components | Category: OEM Supply Chain | Location: Georgia Volvo Cars USA | EV Supply Chain Role: Plastic components for EV and ICE vehicles | Category: OEM Supply Chain | Location: Georgia Volvo Group North America | EV Supply Chain Role: Stamped metal components for OEMs | Category: OEM Supply Chain | Location: Georgia WIKA USA | EV Supply Chain Role: HV and LV wiring harnesses for EVs and ICE vehicles | Category: OEM Supply Chain | Location: Georgia Wabash National Corp. | EV Supply Chain Role: Interior and exterior plastic parts | Category: OEM Supply Chain | Location: Georgia Wheelabrator Group Inc. | EV Supply Chain Role: Interior trim and textile components | Category: OEM Supply Chain | Location: Georgia Woodbridge Foam Corp. | EV Supply Chain Role: EV wiring harnesses and power distribution | Category: OEM Supply Chain | Location: Georgia Woory Industrial Co. | EV Supply Chain Role: High‑voltage EV connectors and electronics | Category: OEM Supply Chain | Location: Georgia YKK USA Inc. | EV Supply Chain Role: EV sensors, braking, and control systems | Category: OEM Footprint | Location: Georgia Yachiyo Manufacturing of America LLC | EV Supply Chain Role: EV electrical distribution and interior systems | Category: OEM Supply Chain | Location: Georgia Yamaha Motor Manufacturing Corp. | EV Supply Chain Role: Advanced electrical architecture for EVs | Category: OEM Supply Chain | Location: Georgia Yazaki North America | EV Supply Chain Role: Power electronics, sensors, and EV systems | Category: OEM Footprint | Location: Georgia ZF Gainesville LLC | EV Supply Chain Role: EV body, powertrain, and thermal components | Category: OEM Supply Chain | Location: Georgia ZF Gainesville LLC | EV Supply Chain Role: EV thermal management and power electronics | Category: OEM Supply Chain | Location: Georgia ZF Gainesville LLC | EV Supply Chain Role: EV thermal systems and electronics | Category: OEM Footprint | Location: Georgia</t>
+  </si>
+  <si>
+    <t>Minebea AccessSolutions USA Inc. - General Automotive  
+TDK Components USA Inc. - Vehicle Assembly</t>
+  </si>
+  <si>
+    <t>Without specific workbook evidence, I can't name particular companies with missing Primary Original Equipment Manufacturer (OEM) information. However, generally speaking, if a company's primary OEM is missing in an Excel sheet related to the electric vehicle supply chain, it would typically mean that there's incomplete data for that supplier or manufacturer regarding their main OEM client. The EV Supply Chain Role of such companies could vary widely depending on their specific function within the industry (e.g., battery manufacturing, motor production, etc.). To provide exact details, I'd need to see the actual workbook and its contents.</t>
+  </si>
+  <si>
+    <t>The following companies have missing Primary OEMs:
+*   **Adient:** General Automotive
+*   **Minebea AccessSolutions USA Inc.:** General Automotive
+*   **TDK Components USA Inc.:** Vehicle Assembly</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question. It requires information about companies, Primary OEMs, and EV Supply Chain Roles, which are not available to me.</t>
+  </si>
+  <si>
+    <t>This workbook evidence does not contain any companies with missing Primary OEMs.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 45.011370065s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '45s'}]}}</t>
+  </si>
+  <si>
+    <t>List all companies whose Product / Service text mentions 'lithium' and include their EV Supply Chain Role and Location.</t>
+  </si>
+  <si>
+    <t>Product / Service mentions 'lithium' [4]: Down 2 Earth Trailers | EV Supply Chain Role: General Automotive | Location: Cartersville, Bartow County Enplas USA Inc. | EV Supply Chain Role: General Automotive | Location: Covington, Newton County F&amp;P Georgia Manufacturing | EV Supply Chain Role: Battery Pack | Location: Toccoa, Stephens County Hollingsworth &amp; Vose Co. | EV Supply Chain Role: Battery Pack | Location: Bainbridge, Decatur County</t>
+  </si>
+  <si>
+    <t>**Battery Pack**
+- F&amp;P Georgia Manufacturing | Location: Toccoa, Stephens County
+- Hollingsworth &amp; Vose Co. | Location: Bainbridge, Decatur County
+**General Automotive**
+- Enplas USA Inc. | Location: Covington, Newton County</t>
+  </si>
+  <si>
+    <t>Without specific workbook evidence, I can't list exact companies that mention "lithium" in their product or service descriptions along with their EV supply chain roles and locations. However, typically such a list would involve identifying companies involved in lithium extraction, refining, battery production, or other parts of the electric vehicle supply chain where lithium is a key component.
+For example:
+- A company might be listed as "Lithium Miner" located in Australia.
+- Another could be described as "Battery Manufacturer" with a role like "Cathode Supplier," based in China.
+To provide an accurate list, you would need to search through the relevant workbook data for companies mentioning "lithium" and then cross-reference their roles and locations.</t>
+  </si>
+  <si>
+    <t>Here are the companies whose Product / Service text mentions 'lithium', along with their EV Supply Chain Role and Location:
+*   **F&amp;P Georgia Manufacturing:** Battery Pack, Toccoa, Stephens County
+*   **Hollingsworth &amp; Vose Co.:** Battery Pack, Bainbridge, Decatur County
+*   **Enplas USA Inc.:** General Automotive, Covington, Newton County</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the Excel workbook. The question requests specific data points (company name, EV Supply Chain Role, and Location) that are linked to a "Product / Service" text field containing "lithium." This information can only be extracted from the workbook itself.</t>
+  </si>
+  <si>
+    <t>* **Down 2 Earth Trailers** - EV Supply Chain Role: General Automotive, Location: Cartersville, Bartow County
+* **F&amp;P Georgia Manufacturing** - EV Supply Chain Role: Battery Pack, Location: Toccoa, Stephens County
+* **Hollingsworth &amp; Vose Co.** - EV Supply Chain Role: Battery Pack, Location: Bainbridge, Decatur County
+* **Enplas USA Inc.** - EV Supply Chain Role: General Automotive, Location: Covington, Newton County</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 44.875239262s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '44s'}]}}</t>
+  </si>
+  <si>
+    <t>Which companies are described as a recycler in Product / Service, and what are their Categories?</t>
+  </si>
+  <si>
+    <t>Product / Service describes a recycler [3]: EVCO Plastics | Category: Tier 2/3 | Product / Service: Recycler of copper, precious metals, and non-ferrous materials Enplas USA Inc. | Category: Tier 2/3 | Product / Service: Recycler of lithium ion batteries F&amp;P Georgia Manufacturing | Category: Tier 1/2 | Product / Service: Lithium-ion battery recycler and raw materials provider</t>
+  </si>
+  <si>
+    <t>Companies described as a recycler in Product / Service and their Categories:
+- **EVCO Plastics** | Category: Tier 2/3
+- **F&amp;P Georgia Manufacturing** | Category: Tier 1/2
+- **Enplas USA Inc.** | Category: Tier 2/3</t>
+  </si>
+  <si>
+    <t>Without specific workbook evidence, I can't provide an exact list of companies described as recyclers or their corresponding categories. However, generally speaking, if you have an Excel workbook where the "Product/Service" column lists companies involved in recycling activities, those entries would be labeled with terms like "recycler," "waste management," "material recovery," etc. The associated "Categories" could include environmental services, waste and disposal services, or similar classifications depending on the context of your data.
+For a precise answer, you'd need to review the specific workbook where this information is stored.</t>
+  </si>
+  <si>
+    <t>The following companies are described as recyclers in Product / Service:
+*   **EVCO Plastics:** Category: Tier 2/3
+*   **F&amp;P Georgia Manufacturing:** Category: Tier 1/2
+*   **Enplas USA Inc.:** Category: Tier 2/3</t>
+  </si>
+  <si>
+    <t>* **EVCO Plastics:** Tier 2/3
+* **F&amp;P Georgia Manufacturing:** Tier 1/2
+* **Enplas USA Inc.:** Tier 2/3</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 44.743738399s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '44s'}]}}</t>
+  </si>
+  <si>
+    <t>Find companies whose Product / Service mentions 'wiring harness' or 'wire harness' and provide their Primary OEMs.</t>
+  </si>
+  <si>
+    <t>Product / Service mentions 'wiring harness' / 'wire harness' [3]: Solvay Specialty Polymers USA LLC | Primary OEMs: Multiple OEMs WIKA USA | Primary OEMs: Blank / Missing Woodbridge Foam Corp. | Primary OEMs: Blank / Missing</t>
+  </si>
+  <si>
+    <t>No companies were found whose Product / Service mentions 'wiring harness' or 'wire harness'. The provided evidence does not include any matches for these terms.</t>
+  </si>
+  <si>
+    <t>Based on general knowledge, companies that manufacture wiring harnesses often serve as primary suppliers to Original Equipment Manufacturers (OEMs) in the automotive, aerospace, and electronics industries. However, without specific workbook data, I cannot name exact companies or their corresponding primary OEM clients. Typically, well-known companies in this sector include Yazaki Corporation, Sumitomo Wiring Systems, and Leoni AG. These firms are likely to be primary suppliers for major car manufacturers such as Toyota, Honda, BMW, and others. For precise information, you would need to refer to the specific workbook or a detailed industry report.</t>
+  </si>
+  <si>
+    <t>The provided workbook evidence does not contain any companies whose Product / Service mentions 'wiring harness' or 'wire harness'. Therefore, I cannot fulfill the request to list their Primary OEMs.</t>
+  </si>
+  <si>
+    <t>Okay, I can help with that. However, I need the Excel workbook to identify the companies and their Primary OEMs based on the "Product / Service" column containing "wiring harness" or "wire harness."
+Without the workbook, I can only provide a general answer. Companies that commonly deal with wiring harnesses or wire harnesses include those in the automotive, aerospace, industrial equipment, and electronics sectors. Potential Primary OEMs (Original Equipment Manufacturers) for these companies could be:
+*   **Automotive:** Ford, General Motors, Toyota, BMW, Volkswagen, Tesla, etc.
+*   **Aerospace:** Boeing, Airbus, Lockheed Martin, etc.
+*   **Industrial Equipment:** Caterpillar, John Deere, Siemens, etc.
+*   **Electronics:** Apple, Samsung, HP, Dell, etc.
+Please provide the workbook so I can give you a precise list.</t>
+  </si>
+  <si>
+    <t>No companies with 'wiring harness' or 'wire harness' in their Product / Service were found in the provided evidence.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 44.602415002s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-2.5-flash', 'location': 'global'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '44s'}]}}</t>
+  </si>
+  <si>
+    <t>Which companies mention 'connectors' in Product / Service, and what is their EV / Battery Relevant status?</t>
+  </si>
+  <si>
+    <t>Product / Service mentions 'connectors' [2]: WIKA USA | EV / Battery Relevant: Yes | EV Supply Chain Role: HV and LV wiring harnesses for EVs and ICE vehicles Woory Industrial Co. | EV / Battery Relevant: Yes | EV Supply Chain Role: High‑voltage EV connectors and electronics</t>
+  </si>
+  <si>
+    <t>Woory Industrial Co. | Connectors, terminals, sensors, and power/data components | Yes
+WIKA USA | Vehicle power &amp; data solutions; wiring harnesses and connectors | Yes</t>
+  </si>
+  <si>
+    <t>Without specific workbook evidence, I can't provide an exact list of companies mentioning "connectors" in the Product/Service field or their corresponding EV/Battery Relevant statuses. However, generally speaking, companies that manufacture connectors might be relevant to electric vehicle (EV) and battery industries if those connectors are used in EV components such as batteries, charging systems, or wiring harnesses.
+To find this information accurately, you would need to:
+1. Search for entries where "connectors" appear under the Product/Service column.
+2. Check the corresponding EV/Battery Relevant status for each company listed.
+If you have access to a specific workbook, you can follow these steps to gather the required data. Otherwise, I recommend reviewing your workbook or dataset carefully to extract this information accurately.</t>
+  </si>
+  <si>
+    <t>Woory Industrial Co. provides Automotive connectors, terminals, sensors, and power/data components and is EV / Battery Relevant: Yes.
+WIKA USA provides Vehicle power &amp; data solutions; wiring harnesses and connectors and is EV / Battery Relevant: Yes.</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the relevant Excel workbook. The question asks for specific information about companies, their products/services, and their EV/Battery Relevant status, which can only be determined by examining the data within the workbook.</t>
+  </si>
+  <si>
+    <t>Woory Industrial Co. - Automotive connectors, terminals, sensors, and power/data components (EV / Battery Relevant: Yes)
+WIKA USA - Vehicle power &amp; data solutions; wiring harnesses and connectors (EV / Battery Relevant: Yes)</t>
+  </si>
+  <si>
+    <t>I cannot answer this question without access to the workbook. The question asks for specific information about companies, their products/services, and their EV/Battery Relevant status, which would be contained within the workbook's data.</t>
+  </si>
+  <si>
+    <t>Identify companies whose Product / Service mentions 'thermal' and list their EV Supply Chain Role and Primary Facility Type.</t>
+  </si>
+  <si>
+    <t>Product / Service mentions 'thermal' [5]: Freudenberg-NOK | EV Supply Chain Role: Thermal Management | Primary Facility Type: Manufacturing Plant Novelis Inc. | EV Supply Chain Role: Thermal Management | Primary Facility Type: Manufacturing Plant Peerless-Winsmith Inc. | EV Supply Chain Role: Thermal Management | Primary Facility Type: Manufacturing Plant ZF Gainesville LLC | EV Supply Chain Role: EV thermal management and power electronics | Primary Facility Type: Manufacturing ZF Gainesville LLC | EV Supply Chain Role: EV thermal systems and electronics | Primary Facility Type: Engineering / Operations</t>
+  </si>
+  <si>
+    <t>**EV Thermal Management and Power Electronics**
+- ZF Gainesville LLC
+  - Primary Facility Type: Manufacturing
+**High-voltage EV connectors and electronics**
+- Woory Industrial Co.
+  - Primary Facility Type: Manufacturing / Engineering
+**Thermal Management**
+- Hyundai Transys Georgia Powertrain
+  - Primary Facility Type: Manufacturing Plant
+- Novelis Inc.
+  - Primary Facility Type: Manufacturing Plant</t>
+  </si>
+  <si>
+    <t>To identify companies whose product or service mentions "thermal" and to list their EV supply chain role and primary facility type, I would need specific data from an Excel workbook or a similar structured dataset. Since no such evidence is provided here, I can't give you exact company names, roles, or facility types.
+However, based on general knowledge in the context of electric vehicle (EV) supply chains, companies that might be involved with thermal products/services could include manufacturers of battery cooling systems, heat exchangers, and other components related to managing temperature within EVs. These companies would likely have an EV Supply Chain Role such as "Battery Component Manufacturer" or "Thermal Management System Supplier," and their Primary Facility Type might be a manufacturing plant.
+For precise information, you should refer to the specific Excel workbook that contains this data. If you can provide more details about the structure of your workbook or any sample entries, I could give you a more tailored response based on general guidelines.</t>
+  </si>
+  <si>
+    <t>Here's a list of companies whose Product / Service mentions 'thermal', along with their EV Supply Chain Role and Primary Facility Type, based on the provided evidence:
+*   **ZF Gainesville LLC:** EV thermal management and power electronics, Manufacturing
+*   **ZF Gainesville LLC:** EV thermal systems and electronics, Engineering / Operations
+*   **Hyundai Transys Georgia Powertrain:** Thermal Management, Manufacturing Plant
+*   **Novelis Inc.:** Thermal Management, Manufacturing Plant</t>
+  </si>
+  <si>
+    <t>Okay, I can help with that. However, I need the Excel workbook data to identify the companies, their EV Supply Chain Role, and Primary Facility Type based on whether their Product/Service mentions "thermal." 
+Without the workbook, I can only provide a general response. Companies involved in thermal management for EVs might include:
+*   **Companies providing thermal management systems:** These could be manufacturers of heat pumps, battery thermal management systems, or cabin climate control systems. Their EV Supply Chain Role would likely be a **Tier 1 Supplier** or **Component Manufacturer**. Their Primary Facility Type could be a **Manufacturing Plant** or **Engineering/Design Center**.
+*   **Material suppliers:** Companies providing materials for thermal insulation or heat transfer. Their role would be **Material Supplier**, and facility type **Manufacturing Plant**.
+*   **Battery Manufacturers:** Some battery manufacturers may offer thermal solutions as part of their battery packs. Their role would be **Battery Manufacturer**, and facility type **Manufacturing Plant**.
+**Please provide the Excel workbook so I can give you a precise list.**</t>
+  </si>
+  <si>
+    <t>* **ZF Gainesville LLC**
+  * EV Supply Chain Role: EV thermal management and power electronics
+  * Primary Facility Type: Manufacturing
+* **ZF Gainesville LLC**
+  * EV Supply Chain Role: EV thermal systems and electronics
+  * Primary Facility Type: Engineering / Operations
+* **Hyundai Transys Georgia Powertrain**
+  * EV Supply Chain Role: Thermal Management
+  * Primary Facility Type: Manufacturing Plant
+* **Novelis Inc.**
+  * EV Supply Chain Role: Thermal Management
+  * Primary Facility Type: Manufacturing Plant</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 35.735871826s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '35s'}]}}</t>
+  </si>
+  <si>
+    <t>List companies whose Product / Service mentions 'powder coatings' and include their Category and Location.</t>
+  </si>
+  <si>
+    <t>Product / Service mentions 'powder coatings' [1]: Archer Aviation Inc. | Category: Tier 2/3 | Location: Ellaville, Schley County</t>
+  </si>
+  <si>
+    <t>**Powder Coatings for Automotive and Other Industries**
+- Company: Archer Aviation Inc.
+  - Category: Tier 2/3
+  - Location: Ellaville, Schley County
+**Automotive Assembly Plant (Indirect powder coatings)**
+- Company: TCI Powder Coatings
+  - Category: OEM
+  - Location: Troup County</t>
+  </si>
+  <si>
+    <t>Based on the information you've requested, without specific data from an Excel workbook or another detailed source, I can't provide a precise list of companies that offer products or services related to "powder coatings," along with their categories and locations. However, generally speaking, companies involved in powder coatings are often categorized under industries such as Coatings &amp; Finishes, Industrial Manufacturing, Chemicals, and Plastics &amp; Polymers. They might be located in various regions around the world where manufacturing is prevalent.
+For a specific list, you would need to look at databases or directories that specialize in industrial products and services, which typically include detailed company profiles with product/service descriptions, industry categories, and geographical locations.</t>
+  </si>
+  <si>
+    <t>Archer Aviation Inc. - Category: Tier 2/3, Location: Ellaville, Schley County.</t>
+  </si>
+  <si>
+    <t>I am sorry, but I do not have access to the necessary information to fulfill this request. I need to be provided with the Excel workbook to identify companies, their product/service offerings, categories, and locations.</t>
+  </si>
+  <si>
+    <t>* Archer Aviation Inc. - Category: Tier 2/3, Location: Ellaville, Schley County
+* TCI Powder Coatings - Category: OEM, Location: Troup County
+* DAS Corp. - Category: Tier 2/3, Location: Gainesville, Hall County</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 35.588562679s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '35s'}]}}</t>
+  </si>
+  <si>
+    <t>Which companies mention 'sensors' in Product / Service, and what EV Supply Chain Role are they assigned?</t>
+  </si>
+  <si>
+    <t>Product / Service mentions 'sensors' [2]: Grudem | EV Supply Chain Role: General Automotive Woory Industrial Co. | EV Supply Chain Role: High‑voltage EV connectors and electronics</t>
+  </si>
+  <si>
+    <t>**Companies mentioning 'sensors' in Product / Service and their EV Supply Chain Role:**
+- **Woory Industrial Co.**
+  - EV Supply Chain Role: High-voltage EV connectors and electronics
+- **Yazaki North America**
+  - EV Supply Chain Role: Power electronics, sensors, and EV systems
+- **YKK USA Inc.**
+  - EV Supply Chain Role: EV sensors, braking, and control systems</t>
+  </si>
+  <si>
+    <t>Without specific workbook evidence, I can't provide an exact list of companies mentioning "sensors" in the Product/Service field or their corresponding EV Supply Chain Roles. However, typically such information would be found by searching through a database or spreadsheet where each company's products/services are listed alongside their role in the electric vehicle supply chain.
+To give you this specific information, I would need access to the exact workbook or dataset containing these details. If you have a list of companies and their roles, you could filter for entries that include "sensors" under Product/Service to find your answer.</t>
+  </si>
+  <si>
+    <t>The following companies mention 'sensors' in their Product / Service and their assigned EV Supply Chain Role:
+*   **Woory Industrial Co.** - EV Supply Chain Role: High‑voltage EV connectors and electronics
+*   **Yazaki North America** - EV Supply Chain Role: Power electronics, sensors, and EV systems
+*   **YKK USA Inc.** - EV Supply Chain Role: EV sensors, braking, and control systems
+*   **Grudem** - EV Supply Chain Role: General Automotive</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the relevant Excel workbook. The question asks for specific company names and their assigned EV Supply Chain Roles based on whether they mention "sensors" in their Product/Service. This information is only available within the data of the workbook.</t>
+  </si>
+  <si>
+    <t>* **High-voltage EV connectors and electronics:**
+    * Woory Industrial Co. (Automotive connectors, terminals, sensors, and power/data components)
+* **Power electronics, sensors, and EV systems:**
+    * Yazaki North America (Automotive supplier division (mobility solutions: ADAS, powertrain, electronics))
+* **EV sensors, braking, and control systems:**
+    * YKK USA Inc. (Automotive technologies (ADAS, braking, connectivity, tires &amp; components))
+* **General Automotive:**
+    * Grudem (Sensors for mobile hydraulic applications)</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 35.450436115s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '35s'}]}}</t>
+  </si>
+  <si>
+    <t>For each Classification Method, count the number of companies and list the top 5 companies by Employment within each method.</t>
+  </si>
+  <si>
+    <t>Classification Method counts and top 5 companies by Employment: Supplier: 170 Top 5 by Employment: Jefferson Southern Corporation (900); Joon Georgia, Inc. (900); JTEKT North America Corp. (860); Grudem (807); Hitachi Astemo (800) Public OEM footprint / supplier listing: 26 Top 5 by Employment: WIKA USA (250,000); Yazaki North America (230,000); YKK USA Inc. (190,159); Yamaha Motor Manufacturing Corp. (190,000); Yachiyo Manufacturing of America LLC (173,700) Direct Manufacturer: 11 Top 5 by Employment: Superior Essex Inc. (8,100); Suzuki Manufacturing of America Corp. (7,500); TCI Powder Coatings (3,000); Thermal Ceramics Inc. (3,000); TE Connectivity (1,900)</t>
+  </si>
+  <si>
+    <t>Classification Method: Supplier
+Number of companies: 8
+Top 5 companies by Employment:
+1. Blue Bird Corp. - Employment: 275
+2. Peterson Spring - Employment: 150
+3. EVCO Plastics - Employment: 125
+4. Bosch (Automotive Division) - Employment: 250
+5. DaeChang Seat Company - Employment: 135
+Note: The company "Bosch (Automotive Division)" is listed twice in the top 5 due to having the second-highest employment number, but it's only counted once for clarity.</t>
+  </si>
+  <si>
+    <t>To address this request without specific workbook data, I'll provide a generalized approach to how you would achieve this in Excel:
+1. **Classification Method Count**: Use the `COUNTIF` function or `SUMPRODUCT` to count the number of unique companies for each Classification Method.
+2. **Top 5 Companies by Employment**: For each Classification Method, sort the companies based on employment numbers and then use a combination of functions like `LARGE`, `INDEX`, and `MATCH` to list the top 5 companies.
+Here's an example outline:
+- Assume you have columns A (Company Name), B (Classification Method), and C (Employment).
+- To count unique companies for each Classification Method, you could use:
+  ```excel
+  =SUMPRODUCT((B:B=B2)/COUNTIF(B:B,B:B))
+  ```
+  Place this formula in a new column next to your data or in another sheet.
+- For listing the top 5 companies by Employment within each method, you might need an array formula (in Excel versions before Office 365) or use dynamic arrays (Excel 2019 and later):
+  ```excel
+  =SORT(FILTER(A:C, B:B=B2), 3, -1)[[#,2]]
+  ```
+  This will sort the companies by Employment for a given Classification Method in descending order. You can then manually list or use additional formulas to extract the top 5.
+Without specific data, it's challenging to provide exact numbers and company names. If you have specific data ranges or need help with Excel functions tailored to your dataset, feel free to ask!</t>
+  </si>
+  <si>
+    <t>Here's a breakdown of the companies by Classification Method and their employment numbers, listing the top 5 by employment within each method:
+**Classification Method: Supplier**
+*   **Number of Companies:** 8
+*   **Top 5 by Employment:**
+    1.  Blue Bird Corp. (275)
+    2.  Bosch (Automotive Division) (250)
+    3.  EVCO Plastics (125)
+    4.  DaeChang Seat Company (135)
+    5.  Daesol Ausys (97)
+**Classification Method: Supplier**
+*   Companies included: Blue Bird Corp., Bosch (Automotive Division), DaeChang Seat Company, Daesol Ausys, Denkai America, EVCO Plastics, Peterson Spring.
+**Note:** The workbook evidence is incomplete for a full analysis. It only provides data for 8 companies classified as "Supplier."</t>
+  </si>
+  <si>
+    <t>Please provide the Excel workbook so I can answer your question about Classification Methods, company counts, and top 5 companies by employment. Without the data, I cannot provide specific details.</t>
+  </si>
+  <si>
+    <t>**Supplier**
+*   **Companies:** 8
+*   **Top 5 Companies by Employment:**
+    1.  Blue Bird Corp. (275)
+    2.  Bosch (Automotive Division) (250)
+    3.  Peterson Spring (150)
+    4.  DaeChang Seat Company (135)
+    5.  EVCO Plastics (125)</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 35.30737555s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '35s'}]}}</t>
+  </si>
+  <si>
+    <t>Identify entries classified as 'Public OEM footprint / supplier listing' and summarize their Categories and EV / Battery Relevant status.</t>
+  </si>
+  <si>
+    <t>Public OEM footprint / supplier listing [26 rows]: Category summary: OEM Supply Chain: 17; OEM (Footprint): 5; OEM Footprint: 3; OEM: 1 EV / Battery Relevant summary: Yes: 26 Companies: TI Fluid Systems; TI Fluid Systems; Tie Down Engineering; TN Americas Holding Inc.; Toyota Industries Group (TACG-TICA); Trenton Pressing; Trenton Pressing Inc.; Valeo; Vanguard National Trailer Corp.; Vernay; Vista Metals Corp.; Voestalpine Automotive Body Parts Inc.; Volvo Cars USA; Volvo Group North America; Wabash National Corp.; Wheelabrator Group Inc.; WIKA USA; Woodbridge Foam Corp.; Woory Industrial Co.; Yachiyo Manufacturing of America LLC; Yamaha Motor Manufacturing Corp.; Yazaki North America; YKK USA Inc.; ZF Gainesville LLC; ZF Gainesville LLC; ZF Gainesville LLC</t>
+  </si>
+  <si>
+    <t>Grouped by EV Supply Chain Role:
+- OEM parent group footprint (EV + HD electrification): TN Americas Holding Inc. (Yes)</t>
+  </si>
+  <si>
+    <t>Based on the information provided in your question, there is no specific data or context given about an Excel workbook or any dataset that contains entries classified as "Public OEM footprint / supplier listing." Therefore, I cannot provide a summary of categories and EV/Battery Relevant statuses without additional details. 
+If you have a specific dataset or workbook with this classification, please share more information or the relevant parts of it so I can assist further. Otherwise, if you need general guidance on how to identify such entries in an Excel workbook or what these classifications might typically include, feel free to ask!</t>
+  </si>
+  <si>
+    <t>The following companies are classified as 'Public OEM footprint / supplier listing':
+*   **TN Americas Holding Inc.** - Category: OEM (Footprint), EV / Battery Relevant: Yes</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I cannot identify specific entries classified as 'Public OEM footprint / supplier listing' or summarize their Categories and EV / Battery Relevant status. This information is dependent on the data within the workbook.
+Generally, entries with that classification would likely represent a list of Original Equipment Manufacturers (OEMs) and their suppliers that are publicly available. The "Categories" column would likely detail the type of products or services these OEMs and suppliers offer. The "EV / Battery Relevant" status would indicate whether their offerings are related to electric vehicles or battery technology.</t>
+  </si>
+  <si>
+    <t>TN Americas Holding Inc. is classified as 'Public OEM footprint / supplier listing'. Its Category is OEM (Footprint) and its EV / Battery Relevant status is Yes.</t>
+  </si>
+  <si>
+    <t>I cannot access the workbook to identify entries classified as 'Public OEM footprint / supplier listing' and summarize their Categories and EV / Battery Relevant status. If you can provide the data, I would be happy to help.</t>
+  </si>
+  <si>
+    <t>Which companies are classified as Direct Manufacturer, and what EV Supply Chain Roles do they cover?</t>
+  </si>
+  <si>
+    <t>Direct Manufacturer entries [11]: Kia Georgia Inc. | EV Supply Chain Role: Vehicle Assembly Minebea AccessSolutions USA Inc. | EV Supply Chain Role: General Automotive Superior Essex Inc. | EV Supply Chain Role: Vehicle Assembly Suzuki Manufacturing of America Corp. | EV Supply Chain Role: Vehicle Assembly TCI Powder Coatings | EV Supply Chain Role: Vehicle Assembly TDK Components USA Inc. | EV Supply Chain Role: Vehicle Assembly TE Connectivity | EV Supply Chain Role: Vehicle Assembly Teklas USA | EV Supply Chain Role: Vehicle Assembly Textron Specialized Vehicles | EV Supply Chain Role: Vehicle Assembly Thermal Ceramics Inc. | EV Supply Chain Role: Vehicle Assembly Thomson Plastics Inc. | EV Supply Chain Role: Vehicle Assembly</t>
+  </si>
+  <si>
+    <t>**General Automotive**
+- Minebea AccessSolutions USA Inc. (Headquarters and distribution location)
+**Vehicle Assembly**
+- Superior Essex Inc. (Electric vehicles and batteries)
+- TE Connectivity (Truck and bus bodies)
+- Teklas USA (Golf carts and all-terrain vehicles)
+- Thomson Plastics Inc. (Electric vertical takeoff and landing (eVTOL) aircraft manufacturing)
+- Kia Georgia Inc. (Golf carts, various off-road vehicles, electric on-road vehicles)
+- Suzuki Manufacturing of America Corp. (Electric vehicle assembly plant)
+- TCI Powder Coatings (Automotive assembly plant)</t>
+  </si>
+  <si>
+    <t>Without specific workbook evidence, I can't provide an exact list of companies classified as Direct Manufacturers or their specific roles in the EV supply chain. However, generally speaking, direct manufacturers in the context of electric vehicles (EVs) are companies that produce key components such as batteries, motors, and power electronics, or those that assemble complete EVs. Common roles for these companies might include Battery Manufacturer, Motor Producer, Vehicle Assembler, etc.
+For precise information, you would need to refer to the specific data provided in your workbook or another detailed source about EV manufacturers and their supply chain roles.</t>
+  </si>
+  <si>
+    <t>The following companies are classified as Direct Manufacturers:
+*   **Minebea AccessSolutions USA Inc.** - General Automotive
+*   **Superior Essex Inc.** - Vehicle Assembly
+*   **TE Connectivity** - Vehicle Assembly
+*   **Teklas USA** - Vehicle Assembly
+*   **Thomson Plastics Inc.** - Vehicle Assembly
+*   **Kia Georgia Inc.** - Vehicle Assembly
+*   **Suzuki Manufacturing of America Corp.** - Vehicle Assembly
+*   **TCI Powder Coatings** - Vehicle Assembly</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I cannot provide a definitive list of companies classified as "Direct Manufacturer" and their associated EV Supply Chain Roles. This information is specific to the data within the workbook.
+However, generally speaking, a "Direct Manufacturer" in the EV supply chain would likely refer to companies that directly produce components or materials used in electric vehicles, rather than acting as assemblers or distributors. Common examples *could* include:
+*   **Battery Manufacturers:** Companies producing battery cells, modules, or packs (e.g., CATL, LG Energy Solution, Panasonic). Their roles would cover Battery Cell Production, Battery Module/Pack Assembly, and potentially Battery Material Processing.
+*   **Motor Manufacturers:** Companies producing electric motors (e.g., Tesla, Nidec). Their roles would cover Electric Motor Design &amp; Manufacturing.
+*   **Semiconductor Manufacturers:** Companies producing chips for vehicle control systems (e.g., TSMC, Samsung). Their roles would cover Semiconductor Fabrication.
+*   **Material Suppliers:** Companies producing raw materials like lithium, nickel, cobalt, aluminum, or copper (e.g., BHP, Glencore). Their roles would cover Raw Material Extraction &amp; Processing.
+**Please note:** The specific companies and roles would depend entirely on the classifications used in the workbook.</t>
+  </si>
+  <si>
+    <t>The companies classified as Direct Manufacturer and their EV Supply Chain Roles are:
+*   **General Automotive:**
+    *   Minebea AccessSolutions USA Inc.
+*   **Vehicle Assembly:**
+    *   Superior Essex Inc.
+    *   TE Connectivity
+    *   Teklas USA
+    *   Thomson Plastics Inc.
+    *   Kia Georgia Inc.
+    *   Suzuki Manufacturing of America Corp.
+    *   TCI Powder Coatings</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 37.330201329s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '37s'}]}}</t>
+  </si>
+  <si>
+    <t>Among companies classified as Supplier, which EV Supply Chain Role appears most frequently?</t>
+  </si>
+  <si>
+    <t>Among companies classified as Supplier, the most frequent EV Supply Chain Role is General Automotive (135 rows).</t>
+  </si>
+  <si>
+    <t>General Automotive appears most frequently among companies classified as Supplier:
+- ACM Georgia LLC
+- Adient
+- ADVICS Manufacturing Georgia LLC
+- Ajin Georgia
+- ALBAform Inc.</t>
+  </si>
+  <si>
+    <t>Based on general knowledge without specific workbook data, in the context of electric vehicles (EVs), suppliers typically play various roles within the supply chain. Common roles for supplier companies include "Component Manufacturer," "Battery Producer," and "Material Supplier." Without exact details from a specific workbook, it's challenging to pinpoint which role appears most frequently among classified suppliers. However, if I had to make an educated guess based on industry trends, "Component Manufacturer" might be one of the more prevalent roles due to the diverse components required for EV manufacturing.</t>
+  </si>
+  <si>
+    <t>The most frequent EV Supply Chain Role among companies classified as Supplier is General Automotive. This role is associated with the following companies: ACM Georgia LLC, Adient, ADVICS Manufacturing Georgia LLC, Ajin Georgia, and ALBAform Inc.</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I cannot definitively determine which EV Supply Chain Role appears most frequently among companies classified as "Supplier." However, generally, roles like "Procurement Specialist," "Logistics Coordinator," or "Quality Control Inspector" are commonly found within supplier organizations supporting the EV supply chain. The specific most frequent role would depend on the particular suppliers and their operations.</t>
+  </si>
+  <si>
+    <t>General Automotive appears most frequently. The following companies are classified as Supplier and have an EV Supply Chain Role of General Automotive:
+*   ACM Georgia LLC
+*   Adient
+*   ADVICS Manufacturing Georgia LLC
+*   Ajin Georgia
+*   ALBAform Inc.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 37.202865455s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '37s'}]}}</t>
+  </si>
+  <si>
+    <t>Find any companies where Category indicates an OEM-related class (starts with 'OEM') but Supplier or Affiliation Type is not filled; list those companies.</t>
+  </si>
+  <si>
+    <t>OEM-related Category with blank Supplier or Affiliation Type [23 companies]: TI Fluid Systems | Categories: OEM, OEM (Footprint) TN Americas Holding Inc. | Categories: OEM (Footprint) Tie Down Engineering | Categories: OEM (Footprint) Toyota Industries Group (TACG-TICA) | Categories: OEM (Footprint) Trenton Pressing | Categories: OEM (Footprint) Trenton Pressing Inc. | Categories: OEM Supply Chain Valeo | Categories: OEM Supply Chain Vanguard National Trailer Corp. | Categories: OEM Supply Chain Vernay | Categories: OEM Supply Chain Vista Metals Corp. | Categories: OEM Supply Chain Voestalpine Automotive Body Parts Inc. | Categories: OEM Supply Chain Volvo Cars USA | Categories: OEM Supply Chain Volvo Group North America | Categories: OEM Supply Chain WIKA USA | Categories: OEM Supply Chain Wabash National Corp. | Categories: OEM Supply Chain Wheelabrator Group Inc. | Categories: OEM Supply Chain Woodbridge Foam Corp. | Categories: OEM Supply Chain Woory Industrial Co. | Categories: OEM Supply Chain YKK USA Inc. | Categories: OEM Footprint Yachiyo Manufacturing of America LLC | Categories: OEM Supply Chain Yamaha Motor Manufacturing Corp. | Categories: OEM Supply Chain Yazaki North America | Categories: OEM Footprint ZF Gainesville LLC | Categories: OEM Footprint, OEM Supply Chain</t>
+  </si>
+  <si>
+    <t>Vehicle Assembly:
+- Kia Georgia Inc. | Employment: 777 | EV / Battery Relevant: Yes
+- Superior Essex Inc. | Employment: 8100 | EV / Battery Relevant: Yes
+- Suzuki Manufacturing of America Corp. | Employment: 7500 | EV / Battery Relevant: Yes
+- TCI Powder Coatings | Employment: 3000 | EV / Battery Relevant: Indirect
+General Automotive:
+- Minebea AccessSolutions USA Inc. | Employment: 400 | EV / Battery Relevant: No
+Vehicle Assembly:
+- TE Connectivity | Employment: 1900
+- Teklas USA | Employment: 1800
+Note: TDK Components USA Inc. is listed under Vehicle Assembly but has "EV / Battery Relevant" as No, and its Supplier or Affiliation Type is not filled.
+The evidence does not provide a clear field for "Supplier or Affiliation Type," so the answer includes companies where this information is missing based on the given criteria.</t>
+  </si>
+  <si>
+    <t>Based on your criteria, I would look for entries in the Excel workbook where the "Category" field starts with "OEM" and either the "Supplier" or "Affiliation Type" fields are left blank. Since no specific data was provided, I cannot give you a list of companies that match this description. However, if you have such a dataset, filtering it for these conditions would help identify any OEM-related companies lacking information in their supplier or affiliation type fields. Please ensure to check your workbook using the specified criteria for an accurate result.</t>
+  </si>
+  <si>
+    <t>The workbook evidence does not contain any companies where the Category indicates an OEM-related class but the Supplier or Affiliation Type is not filled. All listed OEM companies have a defined EV Supply Chain Role.</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the Excel workbook. I need to examine the "Category," "Supplier," and "Affiliation Type" columns to identify companies meeting those criteria.</t>
+  </si>
+  <si>
+    <t>The workbook evidence does not contain a column for 'Supplier or Affiliation Type', so it is not possible to identify companies based on whether this field is filled.</t>
+  </si>
+  <si>
+    <t>I cannot access the workbook to find companies where the Category indicates an OEM-related class and Supplier or Affiliation Type is not filled. To get this information, please provide the workbook or the relevant data.</t>
+  </si>
+  <si>
+    <t>According to the Methodology sheet, what is the minimum employment threshold used to include companies in this dataset?</t>
+  </si>
+  <si>
+    <t>Minimum employment threshold: 50 or more employees.</t>
+  </si>
+  <si>
+    <t>The minimum employment threshold used to include companies in this dataset is 50 or more employees.</t>
+  </si>
+  <si>
+    <t>According to the information you're asking for, without specific details from the "Methodology" sheet of the workbook, I can't provide an exact number. Typically, such datasets have a defined minimum employment threshold (e.g., 50 employees, 100 employees) to ensure that only companies above a certain size are included. To give you the precise figure, please refer directly to the "Methodology" sheet in your workbook where this detail should be specified.</t>
+  </si>
+  <si>
+    <t>According to the Methodology sheet, the minimum employment threshold used to include companies in this dataset is 100 employees.</t>
+  </si>
+  <si>
+    <t>This dataset compiles automotive OEMs and suppliers with 50 or more employees operating in Georgia.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 36.418533363s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-2.5-flash', 'location': 'global'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '36s'}]}}</t>
+  </si>
+  <si>
+    <t>According to the Definitions sheet, how is the Location field formatted and how are City values standardized?</t>
+  </si>
+  <si>
+    <t>Location is formatted as City, County. City values use county seats as a standardized geographic point.</t>
+  </si>
+  <si>
+    <t>Location is reported as City and County. City values use county seats as a standardized geographic point.</t>
+  </si>
+  <si>
+    <t>According to common practices in Excel workbooks, the "Location" field typically includes details such as city, state (or province), country, and sometimes postal code. If we consider standardization of city values, it usually involves ensuring that cities are spelled consistently across all entries. This might include:
+1. Using standardized abbreviations or full names for cities.
+2. Ensuring consistent capitalization (e.g., "New York" vs. "new york").
+3. Removing any unnecessary characters like commas or periods within the city name.
+Without specific details from the Definitions sheet, I can't provide exact formatting rules or standardization methods used in your workbook. However, these are typical approaches to handling such data fields.</t>
+  </si>
+  <si>
+    <t>The Location field reports City and County in one field formatted as City, County. City values use county seats as a standardized geographic point.</t>
+  </si>
+  <si>
+    <t>I am sorry, but I do not have access to the Definitions sheet to answer your question.</t>
+  </si>
+  <si>
+    <t>Location reports City and County in one field formatted as City, County. City values use county seats as a standardized geographic point.</t>
+  </si>
+  <si>
+    <t>I am sorry, but I do not have access to a "Definitions" sheet or any other specific workbook content. Therefore, I cannot tell you how the Location field is formatted or how City values are standardized within that particular workbook.
+In general, the "Location" field in a spreadsheet could be formatted in various ways, such as:
+*   **Text:** Allowing free-form entry of location information.
+*   **Concatenated:** Combining city, state, and country into a single text string.
+*   **Separate Columns:** Having distinct columns for City, State/Province, Country, Zip/Postal Code, etc.
+City values are often standardized to ensure consistency and facilitate analysis. Common standardization methods include:
+*   **Using a predefined list:** Restricting entries to a dropdown list of valid cities.
+*   **Consistent capitalization:** E.g., "New York" instead of "new york" or "NEW YORK".
+*   **Full names vs. abbreviations:** E.g., "Los Angeles" instead of "LA".
+*   **Removing extra spaces or special characters.**
+*   **Mapping variations to a standard name:** E.g., "NYC" to "New York City".
+To get the exact answer for your workbook, you would need to consult the "Definitions" sheet directly.</t>
+  </si>
+  <si>
+    <t>According to the Definitions sheet, what controlled vocabulary is used for EV Supply Chain Role (list the roles mentioned in the definition)?</t>
+  </si>
+  <si>
+    <t>Controlled vocabulary listed in Definitions for EV Supply Chain Role: vehicle assembly; battery cell; battery pack; power electronics; charging infrastructure; thermal management; materials; general automotive.</t>
+  </si>
+  <si>
+    <t>The controlled vocabulary used for EV Supply Chain Role includes:
+- Vehicle assembly
+- Battery cell
+- Battery pack
+- Power electronics
+- Charging infrastructure
+- Thermal management
+- Materials
+- General Automotive</t>
+  </si>
+  <si>
+    <t>Based on the information you're asking about, without specific details from the "Definitions" sheet of the workbook, I can't provide an exact list of roles. However, typically a controlled vocabulary for an "EV Supply Chain Role" might include roles such as Supplier, Manufacturer, Distributor, Retailer, Logistics Provider, and others relevant to managing the supply chain in the electric vehicle industry. For precise details, you would need to refer directly to the Definitions sheet in your workbook.</t>
+  </si>
+  <si>
+    <t>The EV Supply Chain Role is classified using a controlled vocabulary that includes vehicle assembly, battery cell, battery pack, power electronics, charging infrastructure, thermal management, materials, or general automotive.</t>
+  </si>
+  <si>
+    <t>I am sorry, but I do not have access to the Definitions sheet to provide the controlled vocabulary used for EV Supply Chain Role and the roles mentioned in the definition.</t>
+  </si>
+  <si>
+    <t>EV Supply Chain Role categorizes firms into vehicle assembly, battery cell, battery pack, power electronics, charging infrastructure, thermal management, materials, or general automotive.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 2.174444886s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-2.5-flash', 'location': 'global'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '2s'}]}}</t>
+  </si>
+  <si>
+    <t>List all companies in Category = OEM Footprint and provide their Employment and EV Supply Chain Role.</t>
+  </si>
+  <si>
+    <t>Category = OEM Footprint [3]: YKK USA Inc. | Employment: 190,159 | EV Supply Chain Role: EV sensors, braking, and control systems Yazaki North America | Employment: 230,000 | EV Supply Chain Role: Power electronics, sensors, and EV systems ZF Gainesville LLC | Employment: 106,100 | EV Supply Chain Role: EV thermal systems and electronics</t>
+  </si>
+  <si>
+    <t>OEM parent group footprint (EV + HD electrification):
+- TN Americas Holding Inc. | Employment: 19600
+OEM corporate and engineering footprint (electrification):
+- Tie Down Engineering
+OEM corporate footprint and supplier integration:
+- Trenton Pressing
+OEM corporate footprint influencing EV strategy:
+- TI Fluid Systems
+OEM parent group footprint (electric truck strategy):
+- Toyota Industries Group (TACG-TICA)</t>
+  </si>
+  <si>
+    <t>Without specific workbook evidence, I can't list exact companies under the category "OEM Footprint" or provide precise employment numbers and supply chain roles. However, typically in such categories, you might find companies that are Original Equipment Manufacturers (OEMs) involved in producing components for larger products made by other manufacturers. These companies often have specific roles within the electric vehicle (EV) supply chain, such as battery manufacturing, motor production, or component assembly.
+For a precise list and details, you would need to refer directly to the workbook data provided. If you can share more general information about the companies involved in this category, I could offer additional insights based on that.</t>
+  </si>
+  <si>
+    <t>Here's a list of companies in Category = OEM Footprint, their Employment, and EV Supply Chain Role, based on the provided evidence:
+**EV sensors, braking, and control systems:** YKK USA Inc.
+**EV thermal systems and electronics:** ZF Gainesville LLC
+**OEM corporate and engineering footprint (electrification):** Tie Down Engineering
+**OEM corporate footprint and supplier integration:** Trenton Pressing
+**OEM corporate footprint influencing EV strategy:** TI Fluid Systems
+**OEM parent group footprint (EV + HD electrification):** TN Americas Holding Inc. (Employment: 19600)
+**OEM parent group footprint (electric truck strategy):** Toyota Industries Group (TACG-TICA)
+**Power electronics, sensors, and EV systems:** Yazaki North America</t>
+  </si>
+  <si>
+    <t>I am sorry, but I do not have access to the requested information. I do not have access to the workbook and cannot list the companies in Category = OEM Footprint, along with their Employment and EV Supply Chain Role.</t>
+  </si>
+  <si>
+    <t>Here are the companies in the 'OEM (Footprint)', 'OEM Footprint', or 'OEM' category, along with their Employment and EV Supply Chain Role:
+*   **EV sensors, braking, and control systems:**
+    *   YKK USA Inc.
+*   **EV thermal systems and electronics:**
+    *   ZF Gainesville LLC
+*   **General Automotive:**
+    *   Minebea AccessSolutions USA Inc. (Employment: 400)
+*   **OEM corporate and engineering footprint (electrification):**
+    *   Tie Down Engineering
+*   **OEM corporate footprint and supplier integration:**
+    *   Trenton Pressing
+*   **OEM corporate footprint influencing EV strategy:**
+    *   TI Fluid Systems
+*   **OEM parent group footprint (EV + HD electrification):**
+    *   TN Americas Holding Inc. (Employment: 19600)
+*   **OEM parent group footprint (electric truck strategy):**
+    *   Toyota Industries Group (TACG-TICA)
+*   **Power electronics, sensors, and EV systems:**
+    *   Yazaki North America
+*   **Vehicle Assembly:**
+    *   Kia Georgia Inc. (Employment: 777)
+    *   Superior Essex Inc. (Employment: 8100)
+    *   Suzuki Manufacturing of America Corp. (Employment: 7500)
+    *   TCI Powder Coatings (Employment: 3000)
+    *   TDK Components USA Inc. (Employment: 1000)
+    *   TE Connectivity
+    *   Teklas USA
+    *   Textron Specialized Vehicles
+*   **Vehicle safety systems OEM (EV + ICE):**
+    *   TI Fluid Systems
+Employment information is not available for all companies in the provided evidence.</t>
+  </si>
+  <si>
+    <t>I cannot provide a list of companies, their employment numbers, and EV Supply Chain Roles specifically for the "OEM Footprint" category without access to the workbook data. This information is specific to the content of your Excel file.</t>
+  </si>
+  <si>
+    <t>Which companies have Primary Facility Type = Regional corporate operations, and what are their Categories and Locations?</t>
+  </si>
+  <si>
+    <t>Primary Facility Type = Regional corporate operations [1]: Trenton Pressing | Category: OEM (Footprint) | Location: Georgia | EV Supply Chain Role: OEM corporate footprint and supplier integration</t>
+  </si>
+  <si>
+    <t>Trenton Pressing Inc.:
+- Category: OEM Supply Chain
+- Location: Georgia
+No other companies have Primary Facility Type = Regional corporate operations according to the provided evidence.</t>
+  </si>
+  <si>
+    <t>Without specific workbook evidence, I can't provide an exact list of companies with a "Primary Facility Type" of "Regional corporate operations," nor can I specify their categories or locations. However, generally speaking, regional corporate operation facilities are typically owned by larger corporations and serve as hubs for managing local business activities within a defined geographic area. These could include administrative offices, distribution centers, or other operational support structures.
+For an accurate list, you would need to filter the data in your Excel workbook based on the "Primary Facility Type" field set to "Regional corporate operations." This will allow you to see all companies that fit this description along with their respective categories and locations.</t>
+  </si>
+  <si>
+    <t>Trenton Pressing has a Category of OEM (Footprint) and a Location of Georgia.
+Toyota Industries Group (TACG-TICA) has a Category of OEM (Footprint) and a Location of Georgia.</t>
+  </si>
+  <si>
+    <t>I cannot answer this question. It requires information about companies, their facility types, categories, and locations, which are specific details found within an Excel workbook. Without access to that workbook, I cannot provide the requested information.</t>
+  </si>
+  <si>
+    <t>Trenton Pressing:
+* Category: OEM (Footprint)
+* Location: Georgia</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 1.311185983s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-2.5-flash', 'location': 'global'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '1s'}]}}</t>
+  </si>
+  <si>
+    <t>Among EV / Battery Relevant = Yes companies, which Industry Groups are represented and how many companies are in each?</t>
+  </si>
+  <si>
+    <t>Industry Groups represented among EV / Battery Relevant = Yes companies: Electronic and Other Electrical Equipment and Components: 6 Transportation Equipment: 6 Primary Metal Industries: 3 Commercial vehicles and powertrains: 2 Machinery Except Electrical: 1 Automotive safety systems and restraints: 1 Passenger vehicles (EV + ICE): 1 Heavy-duty trucks: 1 Commercial vehicles (Kenworth, Peterbilt): 1 Automotive precision components: 1 Automotive parts manufacturing: 1 Automotive structural components: 1 Automotive stamping and assemblies: 1 Automotive modules and components: 1 Automotive components: 1 Automotive plastics: 1 Metal stamping and assemblies: 1 Automotive plastic components: 1 Automotive textiles and interiors: 1 Automotive wiring systems: 1 Automotive electrical systems: 1 Electrical connectors and sensors: 1 Automotive seating and E‑systems: 1 Automotive electronics: 1 Automotive electronics and systems: 1 Automotive electronics and safety systems: 1 Automotive systems and components: 1 Automotive thermal and electronics systems: 1 Automotive powertrain and thermal systems: 1</t>
+  </si>
+  <si>
+    <t>Primary Metal Industries:
+- F&amp;P Georgia Manufacturing
+Electronic and Other Electrical Equipment and Components:
+- Hitachi Astemo Americas Inc.
+- Hollingsworth &amp; Vose Co.
+- Honda Development &amp; Manufacturing</t>
+  </si>
+  <si>
+    <t>Without specific data from an Excel workbook or additional context, I can't provide the exact industry groups and counts for companies with "EV/Battery Relevant" set to "Yes." However, typically such a list might include industry groups like Automotive Manufacturers, Battery Producers, Electric Vehicle Startups, and Energy Storage Companies. Each group would have a count of companies that fall under their respective categories based on the criteria provided in your dataset.
+For an accurate answer, you'd need to filter your Excel workbook for "EV/Battery Relevant = Yes" and then categorize these companies by industry groups manually or using data analysis tools within Excel.</t>
+  </si>
+  <si>
+    <t>The following Industry Groups are represented among EV / Battery Relevant = Yes companies:
+*   **Transportation Equipment:** 1 company (Lear Corporation)
+*   **Primary Metal Industries:** 1 company (F&amp;P Georgia Manufacturing)
+*   **Electronic and Other Electrical Equipment and Components:** 3 companies (Hitachi Astemo Americas Inc., Hollingsworth &amp; Vose Co., Honda Development &amp; Manufacturing)</t>
+  </si>
+  <si>
+    <t>Without access to the workbook, I cannot provide the exact Industry Groups represented among EV/Battery Relevant = Yes companies and the number of companies in each. However, generally, these companies would likely fall into Industry Groups such as:
+*   **Automotive:** This is a primary group, encompassing EV manufacturers and suppliers.
+*   **Chemicals:** Battery materials (lithium, electrolytes, etc.) are chemical products.
+*   **Metals and Mining:** Lithium, nickel, cobalt, and other battery metals are mined and processed.
+*   **Machinery:** Includes companies that manufacture equipment for battery production or EV assembly.
+*   **Electrical Equipment:** Companies producing components for EVs, such as motors and power electronics.
+*   **Technology/Electronics:** Companies involved in battery management systems, charging infrastructure, and related technologies.
+The specific Industry Groups and the number of companies in each would depend on the specific categorization used in the workbook.</t>
+  </si>
+  <si>
+    <t>* **Electronic and Other Electrical Equipment and Components**: 3 companies
+  * Hitachi Astemo Americas Inc.
+  * Hollingsworth &amp; Vose Co.
+  * Honda Development &amp; Manufacturing
+* **Primary Metal Industries**: 1 company
+  * F&amp;P Georgia Manufacturing</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 1.175311372s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '1s'}]}}</t>
+  </si>
+  <si>
+    <t>Find the counties that contain at least one Battery Pack company and list the Battery Pack companies in each county.</t>
+  </si>
+  <si>
+    <t>Decatur County: Hollingsworth &amp; Vose Co. Henry County: Hyundai Motor Group Jackson County: IMMI Stephens County: F&amp;P Georgia Manufacturing</t>
+  </si>
+  <si>
+    <t>Stephens County:
+- F&amp;P Georgia Manufacturing
+Decatur County:
+- Hollingsworth &amp; Vose Co.
+Henry County:
+- Hyundai Motor Group
+Jackson County:
+- IMMI</t>
+  </si>
+  <si>
+    <t>To answer this question accurately, I would need specific data from an Excel workbook or another structured dataset containing information about companies and their locations. Since no such evidence is provided here, I can't give you exact names of counties and battery pack companies. However, if you have a list of companies that manufacture battery packs along with the county they are located in, you could follow these steps:
+1. Create a list or table of all Battery Pack companies.
+2. For each company, note down its location (county).
+3. Compile a list of unique counties where at least one Battery Pack company is found.
+4. List out all Battery Pack companies for each county.
+If you can provide more details about the structure of your data or any specific examples, I could give you a more tailored response or guide on how to achieve this using Excel functions like `COUNTIF`, `UNIQUE`, and `FILTER`.</t>
+  </si>
+  <si>
+    <t>Here's a list of counties containing Battery Pack companies, along with the companies located in each:
+*   **Toccoa, Stephens County:** F&amp;P Georgia Manufacturing
+*   **Bainbridge, Decatur County:** Hollingsworth &amp; Vose Co.
+*   **McDonough, Henry County:** Hyundai Motor Group
+*   **Jefferson, Jackson County:** IMMI</t>
+  </si>
+  <si>
+    <t>I am sorry, but I do not have access to the necessary information to answer your question. I need to be provided with the Excel workbook to identify the counties containing Battery Pack companies and list those companies.</t>
+  </si>
+  <si>
+    <t>**Step 1: Identify all companies with the EV Supply Chain Role of "Battery Pack" and their corresponding counties.**
+Based on the provided evidence, the following companies have an EV Supply Chain Role of "Battery Pack":
+*   **F&amp;P Georgia Manufacturing:** Toccoa, Stephens County
+*   **Hollingsworth &amp; Vose Co.:** Bainbridge, Decatur County
+*   **Hyundai Motor Group:** McDonough, Henry County
+*   **IMMI:** Jefferson, Jackson County
+**Step 2: Group the companies by county.**
+*   **Stephens County:**
+    *   F&amp;P Georgia Manufacturing
+*   **Decatur County:**
+    *   Hollingsworth &amp; Vose Co.
+*   **Henry County:**
+    *   Hyundai Motor Group
+*   **Jackson County:**
+    *   IMMI</t>
+  </si>
+  <si>
+    <t>I cannot provide a list of counties and companies from a workbook because I do not have access to it. If you upload the workbook, I can help you with that information.</t>
+  </si>
+  <si>
+    <t>Which county has the highest total Employment across all companies? Provide the county and the summed Employment.</t>
+  </si>
+  <si>
+    <t>Fulton County | Total Employment: 21,300</t>
+  </si>
+  <si>
+    <t>Coweta County has the highest total Employment across all companies with 1800 employees from Teklas USA.</t>
+  </si>
+  <si>
+    <t>To accurately determine which county has the highest total employment across all companies from an Excel workbook, I would need to analyze the specific data provided in that workbook. Since no workbook evidence is given here, I can't provide a precise answer with exact numbers or a particular county name. However, generally speaking, you would sum up the employment figures for each company located in different counties and then identify which county has the highest total.
+If you have an Excel workbook with this information, you could use a formula like `SUMIF` to add up employment across all companies within each county, or create a pivot table to summarize the data by county. Once you've done that, simply look for the maximum value in your summary list to find the county with the highest total Employment.
+Without specific workbook details, I can't give you an exact answer regarding which county has the highest employment and what that number is. If you have a specific dataset or more information about the companies and their locations, feel free to share it!</t>
+  </si>
+  <si>
+    <t>Coweta County has the highest total Employment with 1800 employees at Teklas USA.</t>
+  </si>
+  <si>
+    <t>I cannot answer the question because I do not have access to the Excel workbook containing company and employment data.</t>
+  </si>
+  <si>
+    <t>Coweta County has the highest total employment with 1800.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 44.779025351s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '44s'}]}}</t>
+  </si>
+  <si>
+    <t>Compute total Employment by EV Supply Chain Role for companies located in Fulton County.</t>
+  </si>
+  <si>
+    <t>OEM corporate footprint influencing EV strategy: 19,600 Vehicle Assembly: 1,000 General Automotive: 700</t>
+  </si>
+  <si>
+    <t>General Automotive:
+- SRG Global Inc.: 60
+- Elan Technology Inc.: 160
+- Sewon America Inc.: 80
+Total Employment by EV Supply Chain Role "General Automotive" for companies located in Fulton County: 300</t>
+  </si>
+  <si>
+    <t>To compute the total employment by Electric Vehicle (EV) supply chain role for companies located in Fulton County, I would need specific data from an Excel workbook or a similar dataset that includes information on company locations and their respective employment numbers categorized by EV supply chain roles. Since no such workbook evidence is provided here, I can't give you an exact number.
+However, if you have this kind of data available, the process typically involves filtering for companies in Fulton County and then summing up the employment figures according to each role within the EV supply chain (e.g., battery manufacturing, vehicle assembly, charging infrastructure).
+If you could provide more details or specific numbers from your dataset, I'd be happy to help with a precise calculation.</t>
+  </si>
+  <si>
+    <t>Here's the total employment by EV Supply Chain Role for companies located in Fulton County, based on the provided evidence:
+**General Automotive:**
+*   SRG Global Inc.: 60
+*   Elan Technology Inc.: 160
+*   Sewon America Inc.: 80
+**OEM corporate footprint influencing EV strategy:**
+*   TI Fluid Systems: 19600
+Total Employment = 19840</t>
+  </si>
+  <si>
+    <t>I am unable to compute total Employment by EV Supply Chain Role for companies located in Fulton County because I do not have access to the relevant workbook data.</t>
+  </si>
+  <si>
+    <t>**OEM corporate footprint influencing EV strategy:**
+* TI Fluid Systems: 19600
+**General Automotive:**
+* SRG Global Inc.: 60
+* Elan Technology Inc.: 160
+* Sewon America Inc.: 80</t>
+  </si>
+  <si>
+    <t>I cannot compute the total Employment by EV Supply Chain Role for companies located in Fulton County without access to the specific workbook data. This calculation requires detailed information about company locations, their EV Supply Chain Roles, and employment figures, which would be contained within the workbook.</t>
+  </si>
+  <si>
+    <t>List companies whose Location is reported as Georgia (or Georgia (facility presence)) and summarize their Category and EV Supply Chain Role.</t>
+  </si>
+  <si>
+    <t>TI Fluid Systems | Location: Georgia (facility presence) | Category: OEM | EV Supply Chain Role: Vehicle safety systems OEM (EV + ICE) TN Americas Holding Inc. | Location: Georgia | Category: OEM (Footprint) | EV Supply Chain Role: OEM parent group footprint (EV + HD electrification) Toyota Industries Group (TACG-TICA) | Location: Georgia | Category: OEM (Footprint) | EV Supply Chain Role: OEM parent group footprint (electric truck strategy) Trenton Pressing | Location: Georgia | Category: OEM (Footprint) | EV Supply Chain Role: OEM corporate footprint and supplier integration Trenton Pressing Inc. | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: Machined components supporting EV and ICE vehicles Valeo | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: Tier 1 automotive components Vanguard National Trailer Corp. | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: Body and chassis components for EV and ICE OEMs Vernay | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: Stamped and welded assemblies for OEMs Vista Metals Corp. | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: EV and ICE component manufacturing Voestalpine Automotive Body Parts Inc. | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: EV and ICE powertrain and HVAC components Volvo Cars USA | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: Plastic components for EV and ICE vehicles Volvo Group North America | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: Stamped metal components for OEMs WIKA USA | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: HV and LV wiring harnesses for EVs and ICE vehicles Wabash National Corp. | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: Interior and exterior plastic parts Wheelabrator Group Inc. | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: Interior trim and textile components Woodbridge Foam Corp. | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: EV wiring harnesses and power distribution Woory Industrial Co. | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: High‑voltage EV connectors and electronics YKK USA Inc. | Location: Georgia | Category: OEM Footprint | EV Supply Chain Role: EV sensors, braking, and control systems Yachiyo Manufacturing of America LLC | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: EV electrical distribution and interior systems Yamaha Motor Manufacturing Corp. | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: Advanced electrical architecture for EVs Yazaki North America | Location: Georgia | Category: OEM Footprint | EV Supply Chain Role: Power electronics, sensors, and EV systems ZF Gainesville LLC | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: EV body, powertrain, and thermal components ZF Gainesville LLC | Location: Georgia | Category: OEM Supply Chain | EV Supply Chain Role: EV thermal management and power electronics ZF Gainesville LLC | Location: Georgia | Category: OEM Footprint | EV Supply Chain Role: EV thermal systems and electronics</t>
+  </si>
+  <si>
+    <t>**Companies Located in Georgia or Georgia (facility presence):**
+- **Toyota Industries Group (TACG-TICA)**
+  - Category: OEM (Footprint)
+  - EV Supply Chain Role: OEM parent group footprint (electric truck strategy)
+- **ZF Gainesville LLC**
+  - Category: OEM Supply Chain
+  - EV Supply Chain Role: EV thermal management and power electronics
+- **TI Fluid Systems**
+  - Category: OEM
+  - EV Supply Chain Role: Vehicle safety systems OEM (EV + ICE)
+- **Vernay**
+  - Category: OEM Supply Chain
+  - EV Supply Chain Role: Stamped and welded assemblies for OEMs</t>
+  </si>
+  <si>
+    <t>Without specific workbook evidence, I can't provide an exact list of companies located in Georgia or their respective categories and roles within the EV supply chain. However, generally speaking, if you were to look for such information in a typical dataset, you would filter entries where "Location" is listed as "Georgia" (or any variation that includes "Georgia facility presence"). For each company meeting this criterion, you'd then note their "Category" and "EV Supply Chain Role."
+For example:
+- Company A: Location - Georgia; Category - Battery Manufacturer; EV Supply Chain Role - Supplier
+- Company B: Location - Georgia (facility presence); Category - Electric Vehicle Assembler; EV Supply Chain Role - Integrator
+To get the exact details, you would need to refer back to your specific dataset or workbook.</t>
+  </si>
+  <si>
+    <t>Here's a list of companies located in Georgia (or with a facility presence in Georgia), along with their Category and EV Supply Chain Role:
+*   **Toyota Industries Group (TACG-TICA)**: Category: OEM (Footprint), EV Supply Chain Role: OEM parent group footprint (electric truck strategy)
+*   **ZF Gainesville LLC**: Category: OEM Supply Chain, EV Supply Chain Role: EV thermal management and power electronics
+*   **TI Fluid Systems**: Category: OEM, EV Supply Chain Role: Vehicle safety systems OEM (EV + ICE)
+*   **Vernay**: Category: OEM Supply Chain, EV Supply Chain Role: Stamped and welded assemblies for OEMs
+*   **ADVICS Manufacturing Georgia LLC**: Category: Tier 2/3, EV Supply Chain Role: General Automotive
+*   **Bosal Industries Georgia**: Category: Tier 2/3, EV Supply Chain Role: General Automotive
+*   **DAEHAN Solution Georgia LLC**: Category: Tier 2/3, EV Supply Chain Role: Materials
+*   **Daesol Material Georgia, LLC**: Category: Tier 2/3, EV Supply Chain Role: General Automotive</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the relevant workbook data. The question requests specific information about companies, their locations, categories, and EV supply chain roles, which can only be extracted from the data within the Excel workbooks.</t>
+  </si>
+  <si>
+    <t>* **TI Fluid Systems**
+  * Category: OEM
+  * EV Supply Chain Role: Vehicle safety systems OEM (EV + ICE)
+* **Toyota Industries Group (TACG-TICA)**
+  * Category: OEM (Footprint)
+  * EV Supply Chain Role: OEM parent group footprint (electric truck strategy)
+* **Vernay**
+  * Category: OEM Supply Chain
+  * EV Supply Chain Role: Stamped and welded assemblies for OEMs
+* **ZF Gainesville LLC**
+  * Category: OEM Supply Chain
+  * EV Supply Chain Role: EV thermal management and power electronics</t>
+  </si>
+  <si>
+    <t>I cannot provide a list of companies whose location is reported as Georgia (or Georgia (facility presence)) and summarize their Category and EV Supply Chain Role without access to the specific workbook data. This information is contained within the workbook you are referencing.</t>
+  </si>
+  <si>
+    <t>Show the distribution of companies by County for EV / Battery Relevant = Yes only.</t>
+  </si>
+  <si>
+    <t>Bryan County: 2 Jackson County: 2 Columbia County: 1 Coweta County: 1 Decatur County: 1 Forsyth County: 1 Fulton County: 1 Gordon County: 1 Greene County: 1 Hall County: 1 Henry County: 1 Laurens County: 1 Newton County: 1 Richmond County: 1 Stephens County: 1 Walton County: 1</t>
+  </si>
+  <si>
+    <t>**Battery Cell**
+- Pembroke, Bryan County: Honda Development &amp; Manufacturing (400)
+- Coweta County: Hitachi Astemo Americas Inc. (723)
+**Battery Pack**
+- McDonough, Henry County: Hyundai Motor Group (164)</t>
+  </si>
+  <si>
+    <t>To show the distribution of companies by County where "EV/Battery Relevant" is set to "Yes," you would typically follow these steps in Excel:
+1. Filter your data so that only rows with "Yes" in the "EV/Battery Relevant" column are visible.
+2. Use a pivot table or COUNTIF function to count how many companies fall into each county.
+Without specific workbook data, I can't provide exact numbers, but here's an example of what you might see:
+- County A: 15 companies
+- County B: 8 companies
+- County C: 3 companies
+This distribution would show which counties have the highest concentration of EV/battery-related companies. If you need help with specific Excel functions or steps to achieve this, feel free to ask!</t>
+  </si>
+  <si>
+    <t>Here's the distribution of companies by County for EV / Battery Relevant = Yes:
+*   **Bryan County:** Honda Development &amp; Manufacturing (400 employees)
+*   **Coweta County:** Hitachi Astemo Americas Inc. (723 employees)
+*   **Henry County:** Hyundai Motor Group (164 employees)</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the relevant workbook. The request asks for a distribution of companies by County, filtered for "EV / Battery Relevant = Yes." This requires examining the data within the workbook to perform the filtering and aggregation.</t>
+  </si>
+  <si>
+    <t>* **Bryan County**
+  * Honda Development &amp; Manufacturing (Battery Cell)
+* **Coweta County**
+  * Hitachi Astemo Americas Inc. (Battery Cell)
+* **Henry County**
+  * Hyundai Motor Group (Battery Pack)</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 43.292204909s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '43s'}]}}</t>
   </si>
 </sst>
 </file>
@@ -1090,8 +5086,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BCD81A3-2E82-2645-AA04-4C04A0786B01}">
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AA101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="59.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -1809,6 +5808,5691 @@
       </c>
       <c r="X11" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12">
+        <v>0.25</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="L12" t="s">
+        <v>111</v>
+      </c>
+      <c r="M12">
+        <v>0.25</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="T12" t="s">
+        <v>113</v>
+      </c>
+      <c r="U12">
+        <v>0.25</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0.625</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>118</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="L13" t="s">
+        <v>119</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0.8125</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="T13" t="s">
+        <v>121</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W13">
+        <v>1</v>
+      </c>
+      <c r="X13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>125</v>
+      </c>
+      <c r="E14">
+        <v>0.25</v>
+      </c>
+      <c r="F14">
+        <v>0.88235294117647056</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>126</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="L14" t="s">
+        <v>127</v>
+      </c>
+      <c r="M14">
+        <v>0.5</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="T14" t="s">
+        <v>129</v>
+      </c>
+      <c r="U14">
+        <v>0.5</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="W14">
+        <v>1</v>
+      </c>
+      <c r="X14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0.5</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>134</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="L15" t="s">
+        <v>135</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="T15" t="s">
+        <v>137</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0.5</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
+        <v>141</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>142</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="L16" t="s">
+        <v>143</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0.96153846153846156</v>
+      </c>
+      <c r="O16">
+        <v>0.5</v>
+      </c>
+      <c r="P16" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="T16" t="s">
+        <v>145</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="W16">
+        <v>1</v>
+      </c>
+      <c r="X16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>784</v>
+      </c>
+      <c r="B17" t="s">
+        <v>785</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>786</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>787</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="L17" t="s">
+        <v>788</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17" t="s">
+        <v>789</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="T17" t="s">
+        <v>790</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>0.9</v>
+      </c>
+      <c r="W17">
+        <v>1</v>
+      </c>
+      <c r="X17" t="s">
+        <v>791</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>792</v>
+      </c>
+      <c r="B18" t="s">
+        <v>793</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s">
+        <v>794</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0.5</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>795</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="L18" t="s">
+        <v>796</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0.5</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18" t="s">
+        <v>797</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="T18" t="s">
+        <v>798</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0.5</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>800</v>
+      </c>
+      <c r="B19" t="s">
+        <v>801</v>
+      </c>
+      <c r="C19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" t="s">
+        <v>802</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>803</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="L19" t="s">
+        <v>804</v>
+      </c>
+      <c r="M19">
+        <v>0.5</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19" t="s">
+        <v>805</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="T19" t="s">
+        <v>806</v>
+      </c>
+      <c r="U19">
+        <v>0.25</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+      <c r="X19" t="s">
+        <v>807</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>808</v>
+      </c>
+      <c r="B20" t="s">
+        <v>809</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" t="s">
+        <v>810</v>
+      </c>
+      <c r="E20">
+        <v>0.25</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>811</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="L20" t="s">
+        <v>812</v>
+      </c>
+      <c r="M20">
+        <v>0.25</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20" t="s">
+        <v>813</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="T20" t="s">
+        <v>814</v>
+      </c>
+      <c r="U20">
+        <v>0.25</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20" t="s">
+        <v>815</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>816</v>
+      </c>
+      <c r="B21" t="s">
+        <v>817</v>
+      </c>
+      <c r="C21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" t="s">
+        <v>818</v>
+      </c>
+      <c r="E21">
+        <v>0.25</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>819</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="L21" t="s">
+        <v>820</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21" t="s">
+        <v>821</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="T21" t="s">
+        <v>822</v>
+      </c>
+      <c r="U21">
+        <v>0.25</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B22" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" t="s">
+        <v>149</v>
+      </c>
+      <c r="D22" t="s">
+        <v>150</v>
+      </c>
+      <c r="E22">
+        <v>0.5</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>151</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="L22" t="s">
+        <v>152</v>
+      </c>
+      <c r="M22">
+        <v>0.25</v>
+      </c>
+      <c r="N22">
+        <v>0.875</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="T22" t="s">
+        <v>154</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>156</v>
+      </c>
+      <c r="B23" t="s">
+        <v>157</v>
+      </c>
+      <c r="C23" t="s">
+        <v>149</v>
+      </c>
+      <c r="D23" t="s">
+        <v>158</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>159</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="L23" t="s">
+        <v>160</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="T23" t="s">
+        <v>162</v>
+      </c>
+      <c r="U23">
+        <v>0.25</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23">
+        <v>1</v>
+      </c>
+      <c r="X23" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B24" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" t="s">
+        <v>166</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>167</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="L24" t="s">
+        <v>168</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="T24" t="s">
+        <v>170</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="W24">
+        <v>1</v>
+      </c>
+      <c r="X24" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>172</v>
+      </c>
+      <c r="B25" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" t="s">
+        <v>174</v>
+      </c>
+      <c r="E25">
+        <v>0.5</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25" t="s">
+        <v>175</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="L25" t="s">
+        <v>176</v>
+      </c>
+      <c r="M25">
+        <v>0.25</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <v>1</v>
+      </c>
+      <c r="P25" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="T25" t="s">
+        <v>178</v>
+      </c>
+      <c r="U25">
+        <v>0.25</v>
+      </c>
+      <c r="V25">
+        <v>1</v>
+      </c>
+      <c r="W25">
+        <v>1</v>
+      </c>
+      <c r="X25" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>180</v>
+      </c>
+      <c r="B26" t="s">
+        <v>181</v>
+      </c>
+      <c r="C26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" t="s">
+        <v>182</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26" t="s">
+        <v>183</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="L26" t="s">
+        <v>184</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="P26" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="T26" t="s">
+        <v>186</v>
+      </c>
+      <c r="U26">
+        <v>0.5</v>
+      </c>
+      <c r="V26">
+        <v>1</v>
+      </c>
+      <c r="W26">
+        <v>1</v>
+      </c>
+      <c r="X26" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>188</v>
+      </c>
+      <c r="B27" t="s">
+        <v>189</v>
+      </c>
+      <c r="C27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" t="s">
+        <v>190</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27" t="s">
+        <v>191</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="L27" t="s">
+        <v>192</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27">
+        <v>1</v>
+      </c>
+      <c r="P27" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="T27" t="s">
+        <v>194</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>1</v>
+      </c>
+      <c r="X27" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>196</v>
+      </c>
+      <c r="B28" t="s">
+        <v>197</v>
+      </c>
+      <c r="C28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" t="s">
+        <v>198</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0.58823529411764708</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28" t="s">
+        <v>199</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="L28" t="s">
+        <v>200</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>1</v>
+      </c>
+      <c r="O28">
+        <v>1</v>
+      </c>
+      <c r="P28" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="T28" t="s">
+        <v>202</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>1</v>
+      </c>
+      <c r="W28">
+        <v>1</v>
+      </c>
+      <c r="X28" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>204</v>
+      </c>
+      <c r="B29" t="s">
+        <v>205</v>
+      </c>
+      <c r="C29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" t="s">
+        <v>206</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29" t="s">
+        <v>207</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="L29" t="s">
+        <v>208</v>
+      </c>
+      <c r="M29">
+        <v>0.25</v>
+      </c>
+      <c r="N29">
+        <v>0.875</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="T29" t="s">
+        <v>210</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="W29">
+        <v>1</v>
+      </c>
+      <c r="X29" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>212</v>
+      </c>
+      <c r="B30" t="s">
+        <v>213</v>
+      </c>
+      <c r="C30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E30">
+        <v>0.25</v>
+      </c>
+      <c r="F30">
+        <v>0.8</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30" t="s">
+        <v>215</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="L30" t="s">
+        <v>216</v>
+      </c>
+      <c r="M30">
+        <v>0.75</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+      <c r="O30">
+        <v>1</v>
+      </c>
+      <c r="P30" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="T30" t="s">
+        <v>218</v>
+      </c>
+      <c r="U30">
+        <v>0.25</v>
+      </c>
+      <c r="V30">
+        <v>1</v>
+      </c>
+      <c r="W30">
+        <v>1</v>
+      </c>
+      <c r="X30" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>220</v>
+      </c>
+      <c r="B31" t="s">
+        <v>221</v>
+      </c>
+      <c r="C31" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" t="s">
+        <v>222</v>
+      </c>
+      <c r="E31">
+        <v>0.75</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31" t="s">
+        <v>223</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="L31" t="s">
+        <v>224</v>
+      </c>
+      <c r="M31">
+        <v>0.75</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+      <c r="O31">
+        <v>1</v>
+      </c>
+      <c r="P31" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="T31" t="s">
+        <v>226</v>
+      </c>
+      <c r="U31">
+        <v>0.75</v>
+      </c>
+      <c r="V31">
+        <v>1</v>
+      </c>
+      <c r="W31">
+        <v>1</v>
+      </c>
+      <c r="X31" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>228</v>
+      </c>
+      <c r="B32" t="s">
+        <v>229</v>
+      </c>
+      <c r="C32" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32" t="s">
+        <v>230</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0.5</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32" t="s">
+        <v>231</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="L32" t="s">
+        <v>232</v>
+      </c>
+      <c r="M32">
+        <v>0.25</v>
+      </c>
+      <c r="N32">
+        <v>1</v>
+      </c>
+      <c r="O32">
+        <v>1</v>
+      </c>
+      <c r="P32" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="T32" t="s">
+        <v>234</v>
+      </c>
+      <c r="U32">
+        <v>0.25</v>
+      </c>
+      <c r="V32">
+        <v>1</v>
+      </c>
+      <c r="W32">
+        <v>1</v>
+      </c>
+      <c r="X32" t="s">
+        <v>235</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>236</v>
+      </c>
+      <c r="B33" t="s">
+        <v>237</v>
+      </c>
+      <c r="C33" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" t="s">
+        <v>238</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33" t="s">
+        <v>239</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="L33" t="s">
+        <v>240</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="O33">
+        <v>1</v>
+      </c>
+      <c r="P33" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="T33" t="s">
+        <v>242</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="W33">
+        <v>1</v>
+      </c>
+      <c r="X33" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>244</v>
+      </c>
+      <c r="B34" t="s">
+        <v>245</v>
+      </c>
+      <c r="C34" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" t="s">
+        <v>246</v>
+      </c>
+      <c r="E34">
+        <v>0.5</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34" t="s">
+        <v>247</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="L34" t="s">
+        <v>248</v>
+      </c>
+      <c r="M34">
+        <v>0.25</v>
+      </c>
+      <c r="N34">
+        <v>1</v>
+      </c>
+      <c r="O34">
+        <v>1</v>
+      </c>
+      <c r="P34" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="T34" t="s">
+        <v>250</v>
+      </c>
+      <c r="U34">
+        <v>0.75</v>
+      </c>
+      <c r="V34">
+        <v>1</v>
+      </c>
+      <c r="W34">
+        <v>1</v>
+      </c>
+      <c r="X34" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>252</v>
+      </c>
+      <c r="B35" t="s">
+        <v>253</v>
+      </c>
+      <c r="C35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" t="s">
+        <v>254</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35" t="s">
+        <v>255</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="L35" t="s">
+        <v>256</v>
+      </c>
+      <c r="M35">
+        <v>1</v>
+      </c>
+      <c r="N35">
+        <v>1</v>
+      </c>
+      <c r="O35">
+        <v>1</v>
+      </c>
+      <c r="P35" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="T35" t="s">
+        <v>258</v>
+      </c>
+      <c r="U35">
+        <v>1</v>
+      </c>
+      <c r="V35">
+        <v>1</v>
+      </c>
+      <c r="W35">
+        <v>1</v>
+      </c>
+      <c r="X35" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>260</v>
+      </c>
+      <c r="B36" t="s">
+        <v>261</v>
+      </c>
+      <c r="C36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" t="s">
+        <v>262</v>
+      </c>
+      <c r="E36">
+        <v>0.5</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36" t="s">
+        <v>263</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="L36" t="s">
+        <v>264</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>1</v>
+      </c>
+      <c r="P36" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="T36" t="s">
+        <v>266</v>
+      </c>
+      <c r="U36">
+        <v>0.25</v>
+      </c>
+      <c r="V36">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W36">
+        <v>1</v>
+      </c>
+      <c r="X36" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>268</v>
+      </c>
+      <c r="B37" t="s">
+        <v>269</v>
+      </c>
+      <c r="C37" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" t="s">
+        <v>270</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37" t="s">
+        <v>271</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="L37" t="s">
+        <v>272</v>
+      </c>
+      <c r="M37">
+        <v>1</v>
+      </c>
+      <c r="N37">
+        <v>1</v>
+      </c>
+      <c r="O37">
+        <v>1</v>
+      </c>
+      <c r="P37" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="T37" t="s">
+        <v>274</v>
+      </c>
+      <c r="U37">
+        <v>1</v>
+      </c>
+      <c r="V37">
+        <v>1</v>
+      </c>
+      <c r="W37">
+        <v>1</v>
+      </c>
+      <c r="X37" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>276</v>
+      </c>
+      <c r="B38" t="s">
+        <v>277</v>
+      </c>
+      <c r="C38" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" t="s">
+        <v>278</v>
+      </c>
+      <c r="E38">
+        <v>0.25</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38" t="s">
+        <v>279</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="L38" t="s">
+        <v>280</v>
+      </c>
+      <c r="M38">
+        <v>0.25</v>
+      </c>
+      <c r="N38">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="O38">
+        <v>1</v>
+      </c>
+      <c r="P38" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="T38" t="s">
+        <v>282</v>
+      </c>
+      <c r="U38">
+        <v>0.25</v>
+      </c>
+      <c r="V38">
+        <v>1</v>
+      </c>
+      <c r="W38">
+        <v>1</v>
+      </c>
+      <c r="X38" t="s">
+        <v>283</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>284</v>
+      </c>
+      <c r="B39" t="s">
+        <v>285</v>
+      </c>
+      <c r="C39" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" t="s">
+        <v>286</v>
+      </c>
+      <c r="E39">
+        <v>0.75</v>
+      </c>
+      <c r="F39">
+        <v>0.875</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39" t="s">
+        <v>287</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="L39" t="s">
+        <v>288</v>
+      </c>
+      <c r="M39">
+        <v>0.25</v>
+      </c>
+      <c r="N39">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="O39">
+        <v>1</v>
+      </c>
+      <c r="P39" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="T39" t="s">
+        <v>290</v>
+      </c>
+      <c r="U39">
+        <v>0.5</v>
+      </c>
+      <c r="V39">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="W39">
+        <v>1</v>
+      </c>
+      <c r="X39" t="s">
+        <v>291</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>292</v>
+      </c>
+      <c r="B40" t="s">
+        <v>293</v>
+      </c>
+      <c r="C40" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" t="s">
+        <v>294</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0.76470588235294112</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40" t="s">
+        <v>295</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="L40" t="s">
+        <v>296</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>1</v>
+      </c>
+      <c r="O40">
+        <v>1</v>
+      </c>
+      <c r="P40" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="T40" t="s">
+        <v>298</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>1</v>
+      </c>
+      <c r="W40">
+        <v>1</v>
+      </c>
+      <c r="X40" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>300</v>
+      </c>
+      <c r="B41" t="s">
+        <v>301</v>
+      </c>
+      <c r="C41" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" t="s">
+        <v>302</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41" t="s">
+        <v>303</v>
+      </c>
+      <c r="I41">
+        <v>0.5</v>
+      </c>
+      <c r="L41" t="s">
+        <v>304</v>
+      </c>
+      <c r="M41">
+        <v>0.5</v>
+      </c>
+      <c r="N41">
+        <v>0.75</v>
+      </c>
+      <c r="O41">
+        <v>1</v>
+      </c>
+      <c r="P41" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="T41" t="s">
+        <v>306</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0.875</v>
+      </c>
+      <c r="W41">
+        <v>1</v>
+      </c>
+      <c r="X41" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>308</v>
+      </c>
+      <c r="B42" t="s">
+        <v>309</v>
+      </c>
+      <c r="C42" t="s">
+        <v>29</v>
+      </c>
+      <c r="D42" t="s">
+        <v>310</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42" t="s">
+        <v>311</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="L42" t="s">
+        <v>312</v>
+      </c>
+      <c r="M42">
+        <v>1</v>
+      </c>
+      <c r="N42">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="O42">
+        <v>1</v>
+      </c>
+      <c r="P42" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="T42" t="s">
+        <v>314</v>
+      </c>
+      <c r="U42">
+        <v>1</v>
+      </c>
+      <c r="V42">
+        <v>0.75</v>
+      </c>
+      <c r="W42">
+        <v>1</v>
+      </c>
+      <c r="X42" t="s">
+        <v>315</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>316</v>
+      </c>
+      <c r="B43" t="s">
+        <v>317</v>
+      </c>
+      <c r="C43" t="s">
+        <v>29</v>
+      </c>
+      <c r="D43" t="s">
+        <v>318</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43" t="s">
+        <v>319</v>
+      </c>
+      <c r="I43">
+        <v>0.25</v>
+      </c>
+      <c r="L43" t="s">
+        <v>320</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+      <c r="O43">
+        <v>1</v>
+      </c>
+      <c r="P43" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="T43" t="s">
+        <v>322</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0.8</v>
+      </c>
+      <c r="W43">
+        <v>1</v>
+      </c>
+      <c r="X43" t="s">
+        <v>323</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>324</v>
+      </c>
+      <c r="B44" t="s">
+        <v>325</v>
+      </c>
+      <c r="C44" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" t="s">
+        <v>326</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44" t="s">
+        <v>327</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="L44" t="s">
+        <v>328</v>
+      </c>
+      <c r="M44">
+        <v>1</v>
+      </c>
+      <c r="N44">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="O44">
+        <v>1</v>
+      </c>
+      <c r="P44" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="T44" t="s">
+        <v>330</v>
+      </c>
+      <c r="U44">
+        <v>0.75</v>
+      </c>
+      <c r="V44">
+        <v>1</v>
+      </c>
+      <c r="W44">
+        <v>1</v>
+      </c>
+      <c r="X44" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>332</v>
+      </c>
+      <c r="B45" t="s">
+        <v>333</v>
+      </c>
+      <c r="C45" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" t="s">
+        <v>334</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <v>0.875</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45" t="s">
+        <v>335</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="L45" t="s">
+        <v>336</v>
+      </c>
+      <c r="M45">
+        <v>1</v>
+      </c>
+      <c r="N45">
+        <v>0.9</v>
+      </c>
+      <c r="O45">
+        <v>1</v>
+      </c>
+      <c r="P45" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="T45" t="s">
+        <v>338</v>
+      </c>
+      <c r="U45">
+        <v>1</v>
+      </c>
+      <c r="V45">
+        <v>0.9</v>
+      </c>
+      <c r="W45">
+        <v>1</v>
+      </c>
+      <c r="X45" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>340</v>
+      </c>
+      <c r="B46" t="s">
+        <v>341</v>
+      </c>
+      <c r="C46" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" t="s">
+        <v>342</v>
+      </c>
+      <c r="E46">
+        <v>0.25</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46" t="s">
+        <v>343</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="L46" t="s">
+        <v>344</v>
+      </c>
+      <c r="M46">
+        <v>0.75</v>
+      </c>
+      <c r="N46">
+        <v>0.75</v>
+      </c>
+      <c r="O46">
+        <v>1</v>
+      </c>
+      <c r="P46" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="T46" t="s">
+        <v>346</v>
+      </c>
+      <c r="U46">
+        <v>0.75</v>
+      </c>
+      <c r="V46">
+        <v>1</v>
+      </c>
+      <c r="W46">
+        <v>1</v>
+      </c>
+      <c r="X46" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>348</v>
+      </c>
+      <c r="B47" t="s">
+        <v>349</v>
+      </c>
+      <c r="C47" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" t="s">
+        <v>368</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47" t="s">
+        <v>369</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="L47" t="s">
+        <v>370</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>1</v>
+      </c>
+      <c r="O47">
+        <v>1</v>
+      </c>
+      <c r="P47" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="T47" t="s">
+        <v>371</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0.76470588235294112</v>
+      </c>
+      <c r="W47">
+        <v>1</v>
+      </c>
+      <c r="X47" t="s">
+        <v>351</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>352</v>
+      </c>
+      <c r="B48" t="s">
+        <v>353</v>
+      </c>
+      <c r="C48" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" t="s">
+        <v>354</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>0.5</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48" t="s">
+        <v>355</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="L48" t="s">
+        <v>356</v>
+      </c>
+      <c r="M48">
+        <v>0.25</v>
+      </c>
+      <c r="N48">
+        <v>0.8</v>
+      </c>
+      <c r="O48">
+        <v>1</v>
+      </c>
+      <c r="P48" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q48">
+        <v>0.25</v>
+      </c>
+      <c r="T48" t="s">
+        <v>373</v>
+      </c>
+      <c r="U48">
+        <v>0.25</v>
+      </c>
+      <c r="V48">
+        <v>1</v>
+      </c>
+      <c r="W48">
+        <v>1</v>
+      </c>
+      <c r="X48" t="s">
+        <v>357</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>358</v>
+      </c>
+      <c r="B49" t="s">
+        <v>374</v>
+      </c>
+      <c r="C49" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" t="s">
+        <v>375</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49" t="s">
+        <v>376</v>
+      </c>
+      <c r="I49">
+        <v>0.25</v>
+      </c>
+      <c r="L49" t="s">
+        <v>377</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="O49">
+        <v>0.5</v>
+      </c>
+      <c r="P49" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="T49" t="s">
+        <v>360</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>362</v>
+      </c>
+      <c r="B50" t="s">
+        <v>363</v>
+      </c>
+      <c r="C50" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" t="s">
+        <v>378</v>
+      </c>
+      <c r="E50">
+        <v>0.75</v>
+      </c>
+      <c r="F50">
+        <v>0.72413793103448276</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50" t="s">
+        <v>379</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="L50" t="s">
+        <v>380</v>
+      </c>
+      <c r="M50">
+        <v>0.75</v>
+      </c>
+      <c r="N50">
+        <v>0.875</v>
+      </c>
+      <c r="O50">
+        <v>1</v>
+      </c>
+      <c r="P50" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="T50" t="s">
+        <v>382</v>
+      </c>
+      <c r="U50">
+        <v>1</v>
+      </c>
+      <c r="V50">
+        <v>0.8</v>
+      </c>
+      <c r="W50">
+        <v>1</v>
+      </c>
+      <c r="X50" t="s">
+        <v>383</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>364</v>
+      </c>
+      <c r="B51" t="s">
+        <v>365</v>
+      </c>
+      <c r="C51" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" t="s">
+        <v>384</v>
+      </c>
+      <c r="E51">
+        <v>0.25</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+      <c r="H51" t="s">
+        <v>385</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="L51" t="s">
+        <v>386</v>
+      </c>
+      <c r="M51">
+        <v>0.75</v>
+      </c>
+      <c r="N51">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="O51">
+        <v>1</v>
+      </c>
+      <c r="P51" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="T51" t="s">
+        <v>387</v>
+      </c>
+      <c r="U51">
+        <v>0.5</v>
+      </c>
+      <c r="V51">
+        <v>1</v>
+      </c>
+      <c r="W51">
+        <v>1</v>
+      </c>
+      <c r="X51" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>388</v>
+      </c>
+      <c r="B52" t="s">
+        <v>389</v>
+      </c>
+      <c r="C52" t="s">
+        <v>29</v>
+      </c>
+      <c r="D52" t="s">
+        <v>390</v>
+      </c>
+      <c r="E52">
+        <v>0.5</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+      <c r="H52" t="s">
+        <v>391</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="L52" t="s">
+        <v>392</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0.5</v>
+      </c>
+      <c r="O52">
+        <v>1</v>
+      </c>
+      <c r="P52" t="s">
+        <v>393</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="T52" t="s">
+        <v>394</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="W52">
+        <v>1</v>
+      </c>
+      <c r="X52" t="s">
+        <v>395</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>396</v>
+      </c>
+      <c r="B53" t="s">
+        <v>397</v>
+      </c>
+      <c r="C53" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" t="s">
+        <v>398</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53" t="s">
+        <v>399</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="L53" t="s">
+        <v>400</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0.75</v>
+      </c>
+      <c r="O53">
+        <v>0.5</v>
+      </c>
+      <c r="P53" t="s">
+        <v>401</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="T53" t="s">
+        <v>402</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>1</v>
+      </c>
+      <c r="W53">
+        <v>1</v>
+      </c>
+      <c r="X53" t="s">
+        <v>403</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>404</v>
+      </c>
+      <c r="B54" t="s">
+        <v>405</v>
+      </c>
+      <c r="C54" t="s">
+        <v>29</v>
+      </c>
+      <c r="D54" t="s">
+        <v>406</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54" t="s">
+        <v>407</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="L54" t="s">
+        <v>408</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0.1</v>
+      </c>
+      <c r="O54">
+        <v>0.5</v>
+      </c>
+      <c r="P54" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="T54" t="s">
+        <v>410</v>
+      </c>
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <v>0.8</v>
+      </c>
+      <c r="W54">
+        <v>1</v>
+      </c>
+      <c r="X54" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>412</v>
+      </c>
+      <c r="B55" t="s">
+        <v>413</v>
+      </c>
+      <c r="C55" t="s">
+        <v>29</v>
+      </c>
+      <c r="D55" t="s">
+        <v>414</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55" t="s">
+        <v>415</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="L55" t="s">
+        <v>416</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0.5</v>
+      </c>
+      <c r="O55">
+        <v>1</v>
+      </c>
+      <c r="P55" t="s">
+        <v>417</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="T55" t="s">
+        <v>418</v>
+      </c>
+      <c r="U55">
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <v>1</v>
+      </c>
+      <c r="W55">
+        <v>1</v>
+      </c>
+      <c r="X55" t="s">
+        <v>419</v>
+      </c>
+      <c r="Y55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>420</v>
+      </c>
+      <c r="B56" t="s">
+        <v>421</v>
+      </c>
+      <c r="C56" t="s">
+        <v>29</v>
+      </c>
+      <c r="D56" t="s">
+        <v>422</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56" t="s">
+        <v>423</v>
+      </c>
+      <c r="I56">
+        <v>0.5</v>
+      </c>
+      <c r="L56" t="s">
+        <v>424</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>1</v>
+      </c>
+      <c r="O56">
+        <v>1</v>
+      </c>
+      <c r="P56" t="s">
+        <v>425</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="T56" t="s">
+        <v>426</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <v>0.9</v>
+      </c>
+      <c r="W56">
+        <v>1</v>
+      </c>
+      <c r="X56" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>428</v>
+      </c>
+      <c r="B57" t="s">
+        <v>429</v>
+      </c>
+      <c r="C57" t="s">
+        <v>29</v>
+      </c>
+      <c r="D57" t="s">
+        <v>430</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0.5</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57" t="s">
+        <v>431</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="L57" t="s">
+        <v>432</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0.84210526315789469</v>
+      </c>
+      <c r="O57">
+        <v>1</v>
+      </c>
+      <c r="P57" t="s">
+        <v>433</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="T57" t="s">
+        <v>434</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <v>0.8</v>
+      </c>
+      <c r="W57">
+        <v>1</v>
+      </c>
+      <c r="X57" t="s">
+        <v>435</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>436</v>
+      </c>
+      <c r="B58" t="s">
+        <v>437</v>
+      </c>
+      <c r="C58" t="s">
+        <v>29</v>
+      </c>
+      <c r="D58" t="s">
+        <v>438</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58" t="s">
+        <v>439</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="L58" t="s">
+        <v>440</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>1</v>
+      </c>
+      <c r="O58">
+        <v>1</v>
+      </c>
+      <c r="P58" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="T58" t="s">
+        <v>442</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>1</v>
+      </c>
+      <c r="W58">
+        <v>1</v>
+      </c>
+      <c r="X58" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>444</v>
+      </c>
+      <c r="B59" t="s">
+        <v>445</v>
+      </c>
+      <c r="C59" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" t="s">
+        <v>446</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0.75</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59" t="s">
+        <v>447</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="L59" t="s">
+        <v>448</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>1</v>
+      </c>
+      <c r="O59">
+        <v>1</v>
+      </c>
+      <c r="P59" t="s">
+        <v>449</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="T59" t="s">
+        <v>450</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <v>0.8</v>
+      </c>
+      <c r="W59">
+        <v>1</v>
+      </c>
+      <c r="X59" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>452</v>
+      </c>
+      <c r="B60" t="s">
+        <v>453</v>
+      </c>
+      <c r="C60" t="s">
+        <v>29</v>
+      </c>
+      <c r="D60" t="s">
+        <v>454</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60" t="s">
+        <v>455</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="L60" t="s">
+        <v>456</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0.5</v>
+      </c>
+      <c r="O60">
+        <v>1</v>
+      </c>
+      <c r="P60" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+      <c r="T60" t="s">
+        <v>458</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="V60">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W60">
+        <v>1</v>
+      </c>
+      <c r="X60" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>460</v>
+      </c>
+      <c r="B61" t="s">
+        <v>461</v>
+      </c>
+      <c r="C61" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61" t="s">
+        <v>462</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61" t="s">
+        <v>463</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="L61" t="s">
+        <v>464</v>
+      </c>
+      <c r="M61">
+        <v>1</v>
+      </c>
+      <c r="N61">
+        <v>1</v>
+      </c>
+      <c r="O61">
+        <v>1</v>
+      </c>
+      <c r="P61" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+      <c r="T61" t="s">
+        <v>466</v>
+      </c>
+      <c r="U61">
+        <v>1</v>
+      </c>
+      <c r="V61">
+        <v>1</v>
+      </c>
+      <c r="W61">
+        <v>1</v>
+      </c>
+      <c r="X61" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>468</v>
+      </c>
+      <c r="B62" t="s">
+        <v>469</v>
+      </c>
+      <c r="C62" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" t="s">
+        <v>470</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <v>0.75</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62" t="s">
+        <v>471</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="L62" t="s">
+        <v>472</v>
+      </c>
+      <c r="M62">
+        <v>1</v>
+      </c>
+      <c r="N62">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="O62">
+        <v>1</v>
+      </c>
+      <c r="P62" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="T62" t="s">
+        <v>474</v>
+      </c>
+      <c r="U62">
+        <v>1</v>
+      </c>
+      <c r="V62">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="W62">
+        <v>1</v>
+      </c>
+      <c r="X62" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>476</v>
+      </c>
+      <c r="B63" t="s">
+        <v>477</v>
+      </c>
+      <c r="C63" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" t="s">
+        <v>478</v>
+      </c>
+      <c r="E63">
+        <v>0.5</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0.75</v>
+      </c>
+      <c r="H63" t="s">
+        <v>479</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="L63" t="s">
+        <v>480</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>1</v>
+      </c>
+      <c r="O63">
+        <v>1</v>
+      </c>
+      <c r="P63" t="s">
+        <v>481</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="T63" t="s">
+        <v>482</v>
+      </c>
+      <c r="U63">
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <v>0.6</v>
+      </c>
+      <c r="W63">
+        <v>1</v>
+      </c>
+      <c r="X63" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>484</v>
+      </c>
+      <c r="B64" t="s">
+        <v>485</v>
+      </c>
+      <c r="C64" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" t="s">
+        <v>486</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64" t="s">
+        <v>487</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="L64" t="s">
+        <v>488</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0.8</v>
+      </c>
+      <c r="O64">
+        <v>1</v>
+      </c>
+      <c r="P64" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="T64" t="s">
+        <v>490</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="W64">
+        <v>1</v>
+      </c>
+      <c r="X64" t="s">
+        <v>491</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>492</v>
+      </c>
+      <c r="B65" t="s">
+        <v>493</v>
+      </c>
+      <c r="C65" t="s">
+        <v>29</v>
+      </c>
+      <c r="D65" t="s">
+        <v>494</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65" t="s">
+        <v>495</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="L65" t="s">
+        <v>496</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="O65">
+        <v>1</v>
+      </c>
+      <c r="P65" t="s">
+        <v>497</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="T65" t="s">
+        <v>498</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>1</v>
+      </c>
+      <c r="W65">
+        <v>1</v>
+      </c>
+      <c r="X65" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>500</v>
+      </c>
+      <c r="B66" t="s">
+        <v>501</v>
+      </c>
+      <c r="C66" t="s">
+        <v>149</v>
+      </c>
+      <c r="D66" t="s">
+        <v>502</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66" t="s">
+        <v>503</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="L66" t="s">
+        <v>504</v>
+      </c>
+      <c r="M66">
+        <v>1</v>
+      </c>
+      <c r="N66">
+        <v>1</v>
+      </c>
+      <c r="O66">
+        <v>1</v>
+      </c>
+      <c r="P66" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="T66" t="s">
+        <v>506</v>
+      </c>
+      <c r="U66">
+        <v>1</v>
+      </c>
+      <c r="V66">
+        <v>1</v>
+      </c>
+      <c r="W66">
+        <v>1</v>
+      </c>
+      <c r="X66" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>508</v>
+      </c>
+      <c r="B67" t="s">
+        <v>509</v>
+      </c>
+      <c r="C67" t="s">
+        <v>149</v>
+      </c>
+      <c r="D67" t="s">
+        <v>510</v>
+      </c>
+      <c r="E67">
+        <v>0.25</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67" t="s">
+        <v>511</v>
+      </c>
+      <c r="I67">
+        <v>0.25</v>
+      </c>
+      <c r="L67" t="s">
+        <v>512</v>
+      </c>
+      <c r="M67">
+        <v>0.5</v>
+      </c>
+      <c r="N67">
+        <v>1</v>
+      </c>
+      <c r="O67">
+        <v>1</v>
+      </c>
+      <c r="P67" t="s">
+        <v>513</v>
+      </c>
+      <c r="Q67">
+        <v>0.5</v>
+      </c>
+      <c r="T67" t="s">
+        <v>514</v>
+      </c>
+      <c r="U67">
+        <v>0.25</v>
+      </c>
+      <c r="V67">
+        <v>1</v>
+      </c>
+      <c r="W67">
+        <v>1</v>
+      </c>
+      <c r="X67" t="s">
+        <v>515</v>
+      </c>
+      <c r="Y67">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>516</v>
+      </c>
+      <c r="B68" t="s">
+        <v>517</v>
+      </c>
+      <c r="C68" t="s">
+        <v>29</v>
+      </c>
+      <c r="D68" t="s">
+        <v>518</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68" t="s">
+        <v>519</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="L68" t="s">
+        <v>520</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="O68">
+        <v>1</v>
+      </c>
+      <c r="P68" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="T68" t="s">
+        <v>522</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>1</v>
+      </c>
+      <c r="W68">
+        <v>1</v>
+      </c>
+      <c r="X68" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>524</v>
+      </c>
+      <c r="B69" t="s">
+        <v>525</v>
+      </c>
+      <c r="C69" t="s">
+        <v>29</v>
+      </c>
+      <c r="D69" t="s">
+        <v>526</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0.875</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69" t="s">
+        <v>527</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="L69" t="s">
+        <v>528</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0.5</v>
+      </c>
+      <c r="O69">
+        <v>0.5</v>
+      </c>
+      <c r="P69" t="s">
+        <v>529</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="T69" t="s">
+        <v>530</v>
+      </c>
+      <c r="U69">
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <v>0.5</v>
+      </c>
+      <c r="W69">
+        <v>1</v>
+      </c>
+      <c r="X69" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>532</v>
+      </c>
+      <c r="B70" t="s">
+        <v>533</v>
+      </c>
+      <c r="C70" t="s">
+        <v>29</v>
+      </c>
+      <c r="D70" t="s">
+        <v>534</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0.5</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70" t="s">
+        <v>535</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="L70" t="s">
+        <v>536</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="O70">
+        <v>1</v>
+      </c>
+      <c r="P70" t="s">
+        <v>537</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="T70" t="s">
+        <v>538</v>
+      </c>
+      <c r="U70">
+        <v>0</v>
+      </c>
+      <c r="V70">
+        <v>1</v>
+      </c>
+      <c r="W70">
+        <v>1</v>
+      </c>
+      <c r="X70" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>540</v>
+      </c>
+      <c r="B71" t="s">
+        <v>541</v>
+      </c>
+      <c r="C71" t="s">
+        <v>29</v>
+      </c>
+      <c r="D71" t="s">
+        <v>542</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71" t="s">
+        <v>543</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="L71" t="s">
+        <v>544</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="O71">
+        <v>1</v>
+      </c>
+      <c r="P71" t="s">
+        <v>545</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="T71" t="s">
+        <v>546</v>
+      </c>
+      <c r="U71">
+        <v>0</v>
+      </c>
+      <c r="V71">
+        <v>1</v>
+      </c>
+      <c r="W71">
+        <v>1</v>
+      </c>
+      <c r="X71" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>548</v>
+      </c>
+      <c r="B72" t="s">
+        <v>549</v>
+      </c>
+      <c r="C72" t="s">
+        <v>29</v>
+      </c>
+      <c r="D72" t="s">
+        <v>550</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72" t="s">
+        <v>551</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="L72" t="s">
+        <v>552</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0.5</v>
+      </c>
+      <c r="O72">
+        <v>1</v>
+      </c>
+      <c r="P72" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="T72" t="s">
+        <v>553</v>
+      </c>
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <v>1</v>
+      </c>
+      <c r="W72">
+        <v>1</v>
+      </c>
+      <c r="X72" t="s">
+        <v>554</v>
+      </c>
+      <c r="Y72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>555</v>
+      </c>
+      <c r="B73" t="s">
+        <v>556</v>
+      </c>
+      <c r="C73" t="s">
+        <v>29</v>
+      </c>
+      <c r="D73" t="s">
+        <v>557</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73" t="s">
+        <v>558</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="L73" t="s">
+        <v>559</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>1</v>
+      </c>
+      <c r="O73">
+        <v>1</v>
+      </c>
+      <c r="P73" t="s">
+        <v>560</v>
+      </c>
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="T73" t="s">
+        <v>561</v>
+      </c>
+      <c r="U73">
+        <v>0</v>
+      </c>
+      <c r="V73">
+        <v>1</v>
+      </c>
+      <c r="W73">
+        <v>1</v>
+      </c>
+      <c r="X73" t="s">
+        <v>562</v>
+      </c>
+      <c r="Y73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>563</v>
+      </c>
+      <c r="B74" t="s">
+        <v>564</v>
+      </c>
+      <c r="C74" t="s">
+        <v>29</v>
+      </c>
+      <c r="D74" t="s">
+        <v>565</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74" t="s">
+        <v>566</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="L74" t="s">
+        <v>567</v>
+      </c>
+      <c r="M74">
+        <v>1</v>
+      </c>
+      <c r="N74">
+        <v>1</v>
+      </c>
+      <c r="O74">
+        <v>1</v>
+      </c>
+      <c r="P74" t="s">
+        <v>568</v>
+      </c>
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="T74" t="s">
+        <v>569</v>
+      </c>
+      <c r="U74">
+        <v>0.75</v>
+      </c>
+      <c r="V74">
+        <v>1</v>
+      </c>
+      <c r="W74">
+        <v>1</v>
+      </c>
+      <c r="X74" t="s">
+        <v>570</v>
+      </c>
+      <c r="Y74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>571</v>
+      </c>
+      <c r="B75" t="s">
+        <v>572</v>
+      </c>
+      <c r="C75" t="s">
+        <v>29</v>
+      </c>
+      <c r="D75" t="s">
+        <v>573</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75" t="s">
+        <v>574</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="L75" t="s">
+        <v>575</v>
+      </c>
+      <c r="M75">
+        <v>0.25</v>
+      </c>
+      <c r="N75">
+        <v>1</v>
+      </c>
+      <c r="O75">
+        <v>1</v>
+      </c>
+      <c r="P75" t="s">
+        <v>576</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="T75" t="s">
+        <v>577</v>
+      </c>
+      <c r="U75">
+        <v>0.25</v>
+      </c>
+      <c r="V75">
+        <v>1</v>
+      </c>
+      <c r="W75">
+        <v>1</v>
+      </c>
+      <c r="X75" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>579</v>
+      </c>
+      <c r="B76" t="s">
+        <v>580</v>
+      </c>
+      <c r="C76" t="s">
+        <v>29</v>
+      </c>
+      <c r="D76" t="s">
+        <v>581</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76" t="s">
+        <v>582</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="L76" t="s">
+        <v>583</v>
+      </c>
+      <c r="M76">
+        <v>1</v>
+      </c>
+      <c r="N76">
+        <v>1</v>
+      </c>
+      <c r="O76">
+        <v>1</v>
+      </c>
+      <c r="P76" t="s">
+        <v>584</v>
+      </c>
+      <c r="Q76">
+        <v>0</v>
+      </c>
+      <c r="T76" t="s">
+        <v>585</v>
+      </c>
+      <c r="U76">
+        <v>1</v>
+      </c>
+      <c r="V76">
+        <v>1</v>
+      </c>
+      <c r="W76">
+        <v>1</v>
+      </c>
+      <c r="X76" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>587</v>
+      </c>
+      <c r="B77" t="s">
+        <v>588</v>
+      </c>
+      <c r="C77" t="s">
+        <v>29</v>
+      </c>
+      <c r="D77" t="s">
+        <v>589</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+      <c r="F77">
+        <v>0.5</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77" t="s">
+        <v>590</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="L77" t="s">
+        <v>591</v>
+      </c>
+      <c r="M77">
+        <v>1</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>1</v>
+      </c>
+      <c r="P77" t="s">
+        <v>592</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="T77" t="s">
+        <v>593</v>
+      </c>
+      <c r="U77">
+        <v>0.5</v>
+      </c>
+      <c r="V77">
+        <v>1</v>
+      </c>
+      <c r="W77">
+        <v>1</v>
+      </c>
+      <c r="X77" t="s">
+        <v>594</v>
+      </c>
+      <c r="Y77">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>595</v>
+      </c>
+      <c r="B78" t="s">
+        <v>596</v>
+      </c>
+      <c r="C78" t="s">
+        <v>29</v>
+      </c>
+      <c r="D78" t="s">
+        <v>597</v>
+      </c>
+      <c r="E78">
+        <v>0.25</v>
+      </c>
+      <c r="F78">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78" t="s">
+        <v>598</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="L78" t="s">
+        <v>599</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78" t="s">
+        <v>600</v>
+      </c>
+      <c r="Q78">
+        <v>0</v>
+      </c>
+      <c r="T78" t="s">
+        <v>601</v>
+      </c>
+      <c r="U78">
+        <v>0.25</v>
+      </c>
+      <c r="V78">
+        <v>0.5</v>
+      </c>
+      <c r="W78">
+        <v>1</v>
+      </c>
+      <c r="X78" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>603</v>
+      </c>
+      <c r="B79" t="s">
+        <v>604</v>
+      </c>
+      <c r="C79" t="s">
+        <v>29</v>
+      </c>
+      <c r="D79" t="s">
+        <v>605</v>
+      </c>
+      <c r="E79">
+        <v>0.75</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+      <c r="H79" t="s">
+        <v>606</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="L79" t="s">
+        <v>607</v>
+      </c>
+      <c r="M79">
+        <v>1</v>
+      </c>
+      <c r="N79">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="O79">
+        <v>1</v>
+      </c>
+      <c r="P79" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="T79" t="s">
+        <v>608</v>
+      </c>
+      <c r="U79">
+        <v>1</v>
+      </c>
+      <c r="V79">
+        <v>1</v>
+      </c>
+      <c r="W79">
+        <v>1</v>
+      </c>
+      <c r="X79" t="s">
+        <v>609</v>
+      </c>
+      <c r="Y79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>610</v>
+      </c>
+      <c r="B80" t="s">
+        <v>611</v>
+      </c>
+      <c r="C80" t="s">
+        <v>29</v>
+      </c>
+      <c r="D80" t="s">
+        <v>612</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80" t="s">
+        <v>613</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="L80" t="s">
+        <v>614</v>
+      </c>
+      <c r="M80">
+        <v>0.25</v>
+      </c>
+      <c r="N80">
+        <v>1</v>
+      </c>
+      <c r="O80">
+        <v>1</v>
+      </c>
+      <c r="P80" t="s">
+        <v>615</v>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="T80" t="s">
+        <v>616</v>
+      </c>
+      <c r="U80">
+        <v>0.25</v>
+      </c>
+      <c r="V80">
+        <v>0.875</v>
+      </c>
+      <c r="W80">
+        <v>1</v>
+      </c>
+      <c r="X80" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>618</v>
+      </c>
+      <c r="B81" t="s">
+        <v>619</v>
+      </c>
+      <c r="C81" t="s">
+        <v>29</v>
+      </c>
+      <c r="D81" t="s">
+        <v>620</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+      <c r="H81" t="s">
+        <v>621</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="L81" t="s">
+        <v>622</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>1</v>
+      </c>
+      <c r="O81">
+        <v>1</v>
+      </c>
+      <c r="P81" t="s">
+        <v>623</v>
+      </c>
+      <c r="Q81">
+        <v>0</v>
+      </c>
+      <c r="T81" t="s">
+        <v>624</v>
+      </c>
+      <c r="U81">
+        <v>0</v>
+      </c>
+      <c r="V81">
+        <v>1</v>
+      </c>
+      <c r="W81">
+        <v>1</v>
+      </c>
+      <c r="X81" t="s">
+        <v>625</v>
+      </c>
+      <c r="Y81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>626</v>
+      </c>
+      <c r="B82" t="s">
+        <v>627</v>
+      </c>
+      <c r="C82" t="s">
+        <v>29</v>
+      </c>
+      <c r="D82" t="s">
+        <v>628</v>
+      </c>
+      <c r="E82">
+        <v>0.75</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+      <c r="H82" t="s">
+        <v>629</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="L82" t="s">
+        <v>630</v>
+      </c>
+      <c r="M82">
+        <v>0.75</v>
+      </c>
+      <c r="N82">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="O82">
+        <v>1</v>
+      </c>
+      <c r="P82" t="s">
+        <v>631</v>
+      </c>
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="T82" t="s">
+        <v>632</v>
+      </c>
+      <c r="U82">
+        <v>0.75</v>
+      </c>
+      <c r="V82">
+        <v>1</v>
+      </c>
+      <c r="W82">
+        <v>1</v>
+      </c>
+      <c r="X82" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>634</v>
+      </c>
+      <c r="B83" t="s">
+        <v>635</v>
+      </c>
+      <c r="C83" t="s">
+        <v>29</v>
+      </c>
+      <c r="D83" t="s">
+        <v>636</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0.5</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+      <c r="H83" t="s">
+        <v>637</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="L83" t="s">
+        <v>638</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0.5</v>
+      </c>
+      <c r="O83">
+        <v>1</v>
+      </c>
+      <c r="P83" t="s">
+        <v>639</v>
+      </c>
+      <c r="Q83">
+        <v>0</v>
+      </c>
+      <c r="T83" t="s">
+        <v>640</v>
+      </c>
+      <c r="U83">
+        <v>0</v>
+      </c>
+      <c r="V83">
+        <v>0.5</v>
+      </c>
+      <c r="W83">
+        <v>1</v>
+      </c>
+      <c r="X83" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>642</v>
+      </c>
+      <c r="B84" t="s">
+        <v>643</v>
+      </c>
+      <c r="C84" t="s">
+        <v>29</v>
+      </c>
+      <c r="D84" t="s">
+        <v>644</v>
+      </c>
+      <c r="E84">
+        <v>0.75</v>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+      <c r="H84" t="s">
+        <v>645</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="L84" t="s">
+        <v>646</v>
+      </c>
+      <c r="M84">
+        <v>0.5</v>
+      </c>
+      <c r="N84">
+        <v>1</v>
+      </c>
+      <c r="O84">
+        <v>1</v>
+      </c>
+      <c r="P84" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q84">
+        <v>0</v>
+      </c>
+      <c r="T84" t="s">
+        <v>648</v>
+      </c>
+      <c r="U84">
+        <v>1</v>
+      </c>
+      <c r="V84">
+        <v>1</v>
+      </c>
+      <c r="W84">
+        <v>1</v>
+      </c>
+      <c r="X84" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>650</v>
+      </c>
+      <c r="B85" t="s">
+        <v>651</v>
+      </c>
+      <c r="C85" t="s">
+        <v>29</v>
+      </c>
+      <c r="D85" t="s">
+        <v>652</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+      <c r="H85" t="s">
+        <v>653</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="L85" t="s">
+        <v>654</v>
+      </c>
+      <c r="M85">
+        <v>0.5</v>
+      </c>
+      <c r="N85">
+        <v>1</v>
+      </c>
+      <c r="O85">
+        <v>1</v>
+      </c>
+      <c r="P85" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q85">
+        <v>0</v>
+      </c>
+      <c r="T85" t="s">
+        <v>655</v>
+      </c>
+      <c r="U85">
+        <v>0.25</v>
+      </c>
+      <c r="V85">
+        <v>1</v>
+      </c>
+      <c r="W85">
+        <v>1</v>
+      </c>
+      <c r="X85" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>657</v>
+      </c>
+      <c r="B86" t="s">
+        <v>658</v>
+      </c>
+      <c r="C86" t="s">
+        <v>29</v>
+      </c>
+      <c r="D86" t="s">
+        <v>659</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+      <c r="H86" t="s">
+        <v>660</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="L86" t="s">
+        <v>661</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O86">
+        <v>1</v>
+      </c>
+      <c r="P86" t="s">
+        <v>662</v>
+      </c>
+      <c r="Q86">
+        <v>0</v>
+      </c>
+      <c r="T86" t="s">
+        <v>663</v>
+      </c>
+      <c r="U86">
+        <v>0</v>
+      </c>
+      <c r="V86">
+        <v>0.5</v>
+      </c>
+      <c r="W86">
+        <v>1</v>
+      </c>
+      <c r="X86" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>665</v>
+      </c>
+      <c r="B87" t="s">
+        <v>666</v>
+      </c>
+      <c r="C87" t="s">
+        <v>29</v>
+      </c>
+      <c r="D87" t="s">
+        <v>667</v>
+      </c>
+      <c r="E87">
+        <v>1</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+      <c r="H87" t="s">
+        <v>668</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="L87" t="s">
+        <v>669</v>
+      </c>
+      <c r="M87">
+        <v>1</v>
+      </c>
+      <c r="N87">
+        <v>1</v>
+      </c>
+      <c r="O87">
+        <v>1</v>
+      </c>
+      <c r="P87" t="s">
+        <v>670</v>
+      </c>
+      <c r="Q87">
+        <v>0</v>
+      </c>
+      <c r="T87" t="s">
+        <v>671</v>
+      </c>
+      <c r="U87">
+        <v>1</v>
+      </c>
+      <c r="V87">
+        <v>1</v>
+      </c>
+      <c r="W87">
+        <v>1</v>
+      </c>
+      <c r="X87" t="s">
+        <v>672</v>
+      </c>
+      <c r="Y87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>673</v>
+      </c>
+      <c r="B88" t="s">
+        <v>674</v>
+      </c>
+      <c r="C88" t="s">
+        <v>29</v>
+      </c>
+      <c r="D88" t="s">
+        <v>675</v>
+      </c>
+      <c r="E88">
+        <v>0.5</v>
+      </c>
+      <c r="F88">
+        <v>0.875</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88" t="s">
+        <v>676</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="L88" t="s">
+        <v>677</v>
+      </c>
+      <c r="M88">
+        <v>0.25</v>
+      </c>
+      <c r="N88">
+        <v>0.875</v>
+      </c>
+      <c r="O88">
+        <v>1</v>
+      </c>
+      <c r="P88" t="s">
+        <v>678</v>
+      </c>
+      <c r="Q88">
+        <v>0</v>
+      </c>
+      <c r="T88" t="s">
+        <v>679</v>
+      </c>
+      <c r="U88">
+        <v>0.5</v>
+      </c>
+      <c r="V88">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W88">
+        <v>1</v>
+      </c>
+      <c r="X88" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>681</v>
+      </c>
+      <c r="B89" t="s">
+        <v>682</v>
+      </c>
+      <c r="C89" t="s">
+        <v>29</v>
+      </c>
+      <c r="D89" t="s">
+        <v>683</v>
+      </c>
+      <c r="E89">
+        <v>0.75</v>
+      </c>
+      <c r="F89">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89" t="s">
+        <v>684</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="L89" t="s">
+        <v>685</v>
+      </c>
+      <c r="M89">
+        <v>1</v>
+      </c>
+      <c r="N89">
+        <v>1</v>
+      </c>
+      <c r="O89">
+        <v>1</v>
+      </c>
+      <c r="P89" t="s">
+        <v>686</v>
+      </c>
+      <c r="Q89">
+        <v>0</v>
+      </c>
+      <c r="T89" t="s">
+        <v>687</v>
+      </c>
+      <c r="U89">
+        <v>0.75</v>
+      </c>
+      <c r="V89">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="W89">
+        <v>1</v>
+      </c>
+      <c r="X89" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>689</v>
+      </c>
+      <c r="B90" t="s">
+        <v>690</v>
+      </c>
+      <c r="C90" t="s">
+        <v>29</v>
+      </c>
+      <c r="D90" t="s">
+        <v>691</v>
+      </c>
+      <c r="E90">
+        <v>0.25</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+      <c r="H90" t="s">
+        <v>692</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="L90" t="s">
+        <v>693</v>
+      </c>
+      <c r="M90">
+        <v>0.25</v>
+      </c>
+      <c r="N90">
+        <v>1</v>
+      </c>
+      <c r="O90">
+        <v>1</v>
+      </c>
+      <c r="P90" t="s">
+        <v>694</v>
+      </c>
+      <c r="Q90">
+        <v>0</v>
+      </c>
+      <c r="T90" t="s">
+        <v>695</v>
+      </c>
+      <c r="U90">
+        <v>0.5</v>
+      </c>
+      <c r="V90">
+        <v>1</v>
+      </c>
+      <c r="W90">
+        <v>1</v>
+      </c>
+      <c r="X90" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>697</v>
+      </c>
+      <c r="B91" t="s">
+        <v>698</v>
+      </c>
+      <c r="C91" t="s">
+        <v>29</v>
+      </c>
+      <c r="D91" t="s">
+        <v>699</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0.8</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91" t="s">
+        <v>700</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="L91" t="s">
+        <v>701</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="O91">
+        <v>1</v>
+      </c>
+      <c r="P91" t="s">
+        <v>702</v>
+      </c>
+      <c r="Q91">
+        <v>0</v>
+      </c>
+      <c r="T91" t="s">
+        <v>703</v>
+      </c>
+      <c r="U91">
+        <v>0</v>
+      </c>
+      <c r="V91">
+        <v>1</v>
+      </c>
+      <c r="W91">
+        <v>1</v>
+      </c>
+      <c r="X91" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>705</v>
+      </c>
+      <c r="B92" t="s">
+        <v>706</v>
+      </c>
+      <c r="C92" t="s">
+        <v>29</v>
+      </c>
+      <c r="D92" t="s">
+        <v>707</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="H92" t="s">
+        <v>708</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="L92" t="s">
+        <v>709</v>
+      </c>
+      <c r="M92">
+        <v>0.5</v>
+      </c>
+      <c r="N92">
+        <v>1</v>
+      </c>
+      <c r="O92">
+        <v>1</v>
+      </c>
+      <c r="P92" t="s">
+        <v>710</v>
+      </c>
+      <c r="Q92">
+        <v>0</v>
+      </c>
+      <c r="T92" t="s">
+        <v>711</v>
+      </c>
+      <c r="U92">
+        <v>0.25</v>
+      </c>
+      <c r="V92">
+        <v>1</v>
+      </c>
+      <c r="W92">
+        <v>1</v>
+      </c>
+      <c r="X92" t="s">
+        <v>712</v>
+      </c>
+      <c r="Y92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>713</v>
+      </c>
+      <c r="B93" t="s">
+        <v>714</v>
+      </c>
+      <c r="C93" t="s">
+        <v>29</v>
+      </c>
+      <c r="D93" t="s">
+        <v>715</v>
+      </c>
+      <c r="E93">
+        <v>0.5</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+      <c r="H93" t="s">
+        <v>716</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="L93" t="s">
+        <v>717</v>
+      </c>
+      <c r="M93">
+        <v>0.75</v>
+      </c>
+      <c r="N93">
+        <v>1</v>
+      </c>
+      <c r="O93">
+        <v>1</v>
+      </c>
+      <c r="P93" t="s">
+        <v>718</v>
+      </c>
+      <c r="Q93">
+        <v>0</v>
+      </c>
+      <c r="T93" t="s">
+        <v>719</v>
+      </c>
+      <c r="U93">
+        <v>0.5</v>
+      </c>
+      <c r="V93">
+        <v>1</v>
+      </c>
+      <c r="W93">
+        <v>1</v>
+      </c>
+      <c r="X93" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>721</v>
+      </c>
+      <c r="B94" t="s">
+        <v>722</v>
+      </c>
+      <c r="C94" t="s">
+        <v>29</v>
+      </c>
+      <c r="D94" t="s">
+        <v>723</v>
+      </c>
+      <c r="E94">
+        <v>0.5</v>
+      </c>
+      <c r="F94">
+        <v>1</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+      <c r="H94" t="s">
+        <v>724</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="L94" t="s">
+        <v>725</v>
+      </c>
+      <c r="M94">
+        <v>1</v>
+      </c>
+      <c r="N94">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="O94">
+        <v>1</v>
+      </c>
+      <c r="P94" t="s">
+        <v>726</v>
+      </c>
+      <c r="Q94">
+        <v>0</v>
+      </c>
+      <c r="T94" t="s">
+        <v>727</v>
+      </c>
+      <c r="U94">
+        <v>0.5</v>
+      </c>
+      <c r="V94">
+        <v>1</v>
+      </c>
+      <c r="W94">
+        <v>1</v>
+      </c>
+      <c r="X94" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>729</v>
+      </c>
+      <c r="B95" t="s">
+        <v>730</v>
+      </c>
+      <c r="C95" t="s">
+        <v>29</v>
+      </c>
+      <c r="D95" t="s">
+        <v>731</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0.9</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+      <c r="H95" t="s">
+        <v>732</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="L95" t="s">
+        <v>733</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>1</v>
+      </c>
+      <c r="P95" t="s">
+        <v>734</v>
+      </c>
+      <c r="Q95">
+        <v>0</v>
+      </c>
+      <c r="T95" t="s">
+        <v>735</v>
+      </c>
+      <c r="U95">
+        <v>0</v>
+      </c>
+      <c r="V95">
+        <v>0</v>
+      </c>
+      <c r="W95">
+        <v>1</v>
+      </c>
+      <c r="X95" t="s">
+        <v>736</v>
+      </c>
+      <c r="Y95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>737</v>
+      </c>
+      <c r="B96" t="s">
+        <v>738</v>
+      </c>
+      <c r="C96" t="s">
+        <v>29</v>
+      </c>
+      <c r="D96" t="s">
+        <v>739</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+      <c r="F96">
+        <v>0.5</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+      <c r="H96" t="s">
+        <v>740</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="L96" t="s">
+        <v>739</v>
+      </c>
+      <c r="M96">
+        <v>1</v>
+      </c>
+      <c r="N96">
+        <v>0.5</v>
+      </c>
+      <c r="O96">
+        <v>1</v>
+      </c>
+      <c r="P96" t="s">
+        <v>741</v>
+      </c>
+      <c r="Q96">
+        <v>0</v>
+      </c>
+      <c r="T96" t="s">
+        <v>742</v>
+      </c>
+      <c r="U96">
+        <v>1</v>
+      </c>
+      <c r="V96">
+        <v>1</v>
+      </c>
+      <c r="W96">
+        <v>1</v>
+      </c>
+      <c r="X96" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>744</v>
+      </c>
+      <c r="B97" t="s">
+        <v>745</v>
+      </c>
+      <c r="C97" t="s">
+        <v>29</v>
+      </c>
+      <c r="D97" t="s">
+        <v>746</v>
+      </c>
+      <c r="E97">
+        <v>0.75</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+      <c r="H97" t="s">
+        <v>747</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="L97" t="s">
+        <v>748</v>
+      </c>
+      <c r="M97">
+        <v>1</v>
+      </c>
+      <c r="N97">
+        <v>1</v>
+      </c>
+      <c r="O97">
+        <v>1</v>
+      </c>
+      <c r="P97" t="s">
+        <v>749</v>
+      </c>
+      <c r="Q97">
+        <v>0</v>
+      </c>
+      <c r="T97" t="s">
+        <v>750</v>
+      </c>
+      <c r="U97">
+        <v>1</v>
+      </c>
+      <c r="V97">
+        <v>1</v>
+      </c>
+      <c r="W97">
+        <v>1</v>
+      </c>
+      <c r="X97" t="s">
+        <v>751</v>
+      </c>
+      <c r="Y97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>752</v>
+      </c>
+      <c r="B98" t="s">
+        <v>753</v>
+      </c>
+      <c r="C98" t="s">
+        <v>29</v>
+      </c>
+      <c r="D98" t="s">
+        <v>754</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+      <c r="H98" t="s">
+        <v>755</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="L98" t="s">
+        <v>756</v>
+      </c>
+      <c r="M98">
+        <v>1</v>
+      </c>
+      <c r="N98">
+        <v>1</v>
+      </c>
+      <c r="O98">
+        <v>1</v>
+      </c>
+      <c r="P98" t="s">
+        <v>757</v>
+      </c>
+      <c r="Q98">
+        <v>0</v>
+      </c>
+      <c r="T98" t="s">
+        <v>758</v>
+      </c>
+      <c r="U98">
+        <v>1</v>
+      </c>
+      <c r="V98">
+        <v>1</v>
+      </c>
+      <c r="W98">
+        <v>1</v>
+      </c>
+      <c r="X98" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>760</v>
+      </c>
+      <c r="B99" t="s">
+        <v>761</v>
+      </c>
+      <c r="C99" t="s">
+        <v>29</v>
+      </c>
+      <c r="D99" t="s">
+        <v>762</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99" t="s">
+        <v>763</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="L99" t="s">
+        <v>764</v>
+      </c>
+      <c r="M99">
+        <v>0.75</v>
+      </c>
+      <c r="N99">
+        <v>0.52941176470588236</v>
+      </c>
+      <c r="O99">
+        <v>1</v>
+      </c>
+      <c r="P99" t="s">
+        <v>765</v>
+      </c>
+      <c r="Q99">
+        <v>0</v>
+      </c>
+      <c r="T99" t="s">
+        <v>766</v>
+      </c>
+      <c r="U99">
+        <v>0</v>
+      </c>
+      <c r="V99">
+        <v>1</v>
+      </c>
+      <c r="W99">
+        <v>1</v>
+      </c>
+      <c r="X99" t="s">
+        <v>767</v>
+      </c>
+      <c r="Y99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>768</v>
+      </c>
+      <c r="B100" t="s">
+        <v>769</v>
+      </c>
+      <c r="C100" t="s">
+        <v>29</v>
+      </c>
+      <c r="D100" t="s">
+        <v>770</v>
+      </c>
+      <c r="E100">
+        <v>0.75</v>
+      </c>
+      <c r="F100">
+        <v>0.5</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+      <c r="H100" t="s">
+        <v>771</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="L100" t="s">
+        <v>772</v>
+      </c>
+      <c r="M100">
+        <v>0.75</v>
+      </c>
+      <c r="N100">
+        <v>1</v>
+      </c>
+      <c r="O100">
+        <v>1</v>
+      </c>
+      <c r="P100" t="s">
+        <v>773</v>
+      </c>
+      <c r="Q100">
+        <v>0</v>
+      </c>
+      <c r="T100" t="s">
+        <v>774</v>
+      </c>
+      <c r="U100">
+        <v>1</v>
+      </c>
+      <c r="V100">
+        <v>1</v>
+      </c>
+      <c r="W100">
+        <v>1</v>
+      </c>
+      <c r="X100" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>776</v>
+      </c>
+      <c r="B101" t="s">
+        <v>777</v>
+      </c>
+      <c r="C101" t="s">
+        <v>29</v>
+      </c>
+      <c r="D101" t="s">
+        <v>778</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="H101" t="s">
+        <v>779</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="L101" t="s">
+        <v>780</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>0.9</v>
+      </c>
+      <c r="O101">
+        <v>1</v>
+      </c>
+      <c r="P101" t="s">
+        <v>781</v>
+      </c>
+      <c r="Q101">
+        <v>0.25</v>
+      </c>
+      <c r="T101" t="s">
+        <v>782</v>
+      </c>
+      <c r="U101">
+        <v>0</v>
+      </c>
+      <c r="V101">
+        <v>1</v>
+      </c>
+      <c r="W101">
+        <v>1</v>
+      </c>
+      <c r="X101" t="s">
+        <v>783</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/results/Ragas_Merged.xlsx
+++ b/artifacts/results/Ragas_Merged.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://outlookuga-my.sharepoint.com/personal/sm11926_uga_edu/Documents/evAutomationUpdated/artifacts/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{45EDF1FD-91B0-9042-BC2C-7513BB87A3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63AEDAA4-8E72-2646-9A5B-CBD29365F301}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{45EDF1FD-91B0-9042-BC2C-7513BB87A3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E86B9D1-F836-0A4E-9CEE-A951F60836A1}"/>
   <bookViews>
-    <workbookView xWindow="14560" yWindow="660" windowWidth="20000" windowHeight="21680" xr2:uid="{8EB8A2CD-A73C-6F43-92DE-B53E8E949054}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{8EB8A2CD-A73C-6F43-92DE-B53E8E949054}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -942,118 +942,7 @@
     <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 53.361014719s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '53s'}]}}</t>
   </si>
   <si>
-    <t>List all companies with Primary Facility Type = Headquarters (including North American</t>
-  </si>
-  <si>
-    <t>Based on the provided evidence, the companies with the Primary Facility Type as "Headquarters" (including "North American Headquarters") are:
-1. **TI Fluid Systems**
-   - Location: Atlanta, Fulton County
-   - Employment: 19,600
-   - Industry Group: Passenger vehicles (EV + ICE)
-   - EV Supply Chain Role: OEM corporate footprint influencing EV strategy
-2. **Tie Down Engineering**
-   - Location: Greensboro, Greene County
-   - Employment: 2,000
-   - Industry Group: Heavy-duty trucks
-   - EV Supply Chain Role: OEM corporate and engineering footprint (electrification)
-3. **Minebea AccessSolutions USA Inc.**
-   - Location: Atlanta, Fulton County
-   - Employment: 400
-   - Industry Group: Transportation Equipment
-   - EV Supply Chain Role: General Automotive
-The evidence does not provide information about other companies with the Primary Facility Type as Headquarters.</t>
-  </si>
-  <si>
-    <t>generated</t>
-  </si>
-  <si>
-    <t>### Companies with Primary Facility Type = Headquarters (including North American Headquarters)
-**OEM corporate footprint influencing EV strategy**
-- TI Fluid Systems  
-  - Location: Atlanta, Fulton County  
-  - Employment: 19600  
-**General Automotive**
-- Minebea AccessSolutions USA Inc.  
-  - Location: Atlanta, Fulton County  
-  - Employment: 400</t>
-  </si>
-  <si>
-    <t>To list all companies with a Primary Facility Type of "Headquarters" in an Excel workbook, you would typically filter or sort the data based on that specific criterion. Since no actual workbook is provided here and I don't have access to any specific dataset, I can only provide a general approach:
-1. Open your Excel workbook.
-2. Navigate to the sheet containing company information.
-3. Use the filter function (usually found under the Data tab) to select "Headquarters" in the column labeled as Primary Facility Type or similar.
-Without having the actual data, I cannot list specific companies. However, if you follow these steps with your dataset, you should be able to identify all entries where the company's primary facility is designated as a headquarters. If you need further assistance with Excel functions or formulas for this task, feel free to ask!</t>
-  </si>
-  <si>
-    <t>The following companies have a Primary Facility Type of Headquarters (including North American Headquarters):
-*   Minebea AccessSolutions USA Inc. (Atlanta, Fulton County) - EV Supply Chain Role: General Automotive, Employment: 400
-*   TI Fluid Systems (Atlanta, Fulton County) - EV Supply Chain Role: OEM corporate footprint influencing EV strategy, Employment: 19600</t>
-  </si>
-  <si>
     <t>I am sorry, but I do not have access to the workbook to answer your question.</t>
-  </si>
-  <si>
-    <t>* Minebea AccessSolutions USA Inc. (EV Supply Chain Role: General Automotive)
-* TI Fluid Systems (EV Supply Chain Role: OEM corporate footprint influencing EV strategy)
-* Tie Down Engineering (EV Supply Chain Role: OEM corporate and engineering footprint (electrification))</t>
-  </si>
-  <si>
-    <t>I cannot list all companies with "Primary Facility Type = Headquarters" (including North American) because I do not have access to the specific workbook data. To provide an accurate list, I would need to query the workbook directly.</t>
-  </si>
-  <si>
-    <t>Headquarters) and include their Location and Employment.</t>
-  </si>
-  <si>
-    <t>Based on the provided evidence, here are the companies with their headquarters location and employment numbers:
-1. **Minebea AccessSolutions USA Inc.**
-   - Location: Atlanta, Fulton County
-   - Employment: 400
-2. **Tie Down Engineering**
-   - Location: Greensboro, Greene County
-   - Employment: 2000
-3. **TI Fluid Systems**
-   - Location: Atlanta, Fulton County
-   - Employment: 19,600
-The evidence does not provide information about other companies with headquarters in Georgia. The dataset focuses on automotive OEMs and suppliers with 50 or more employees operating in Georgia, but it does not include all such companies.</t>
-  </si>
-  <si>
-    <t>**North American Headquarters**
-- **Tie Down Engineering**
-  - Location: Greensboro, Greene County
-  - Employment: 2000
-**Headquarters (Other)**
-- **Minebea AccessSolutions USA Inc.**
-  - Location: Atlanta, Fulton County
-  - Employment: 400
-- **TI Fluid Systems**
-  - Location: Atlanta, Fulton County
-  - Employment: 19600</t>
-  </si>
-  <si>
-    <t>To answer questions about headquarters locations and employment numbers, I would need specific information from an Excel workbook or other detailed data source. Without such a reference, here's a general approach to how you might find this information:
-1. **Headquarters Location**: This is typically found in the "About Us" section of a company’s website, annual reports, or press releases. It can also be listed under corporate structure details within an Excel workbook that contains organizational data.
-2. **Employment Numbers**: Employment figures for headquarters are often detailed in financial statements, annual reports, or specific sections of an Excel workbook dedicated to human resources and organizational charts.
-If you have a particular company in mind, I could provide more tailored advice on how to find this information based on general knowledge about where such details are usually published.</t>
-  </si>
-  <si>
-    <t>Here are the companies with a Headquarters location and their Employment:
-*   Minebea AccessSolutions USA Inc., Location: Atlanta, Fulton County, Employment: 400
-*   Tie Down Engineering, Location: Greensboro, Greene County, Employment: 2000
-*   TI Fluid Systems, Location: Atlanta, Fulton County, Employment: 19600</t>
-  </si>
-  <si>
-    <t>Please provide the relevant Excel workbook data so I can answer your question about headquarters locations and employment numbers. I need the data to accurately identify the headquarters and their associated details.</t>
-  </si>
-  <si>
-    <t>**OEM (Footprint)**
-* **TI Fluid Systems** - Location: Atlanta, Fulton County; Employment: 19600
-* **Tie Down Engineering** - Location: Greensboro, Greene County; Employment: 2000
-**OEM**
-* **Minebea AccessSolutions USA Inc.** - Location: Atlanta, Fulton County; Employment: 400
-* **TDK Components USA Inc.** - Location: Atlanta, Fulton County; Employment: 1000</t>
-  </si>
-  <si>
-    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 44.018684217s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '44s'}]}}</t>
   </si>
   <si>
     <t>Which companies have Primary Facility Type = R&amp;D, and what EV Supply Chain Role are they associated with?</t>
@@ -3036,86 +2925,6 @@
     <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 31.943166022s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '31s'}]}}</t>
   </si>
   <si>
-    <t>Identify companies with Employment &gt;= 10,000 and list their Category and Classification</t>
-  </si>
-  <si>
-    <t>Based on the provided evidence, there is only one company with employment greater than or equal to 10,000:
-- **Company:** Toyota Industries Group (TACG-TICA)
-  - **Category:** OEM (Footprint)
-  - **Classification Method:** Public OEM footprint / supplier listing
-All other companies listed have employment numbers below 10,000.</t>
-  </si>
-  <si>
-    <t>Company: Toyota Industries Group (TACG-TICA) | Category: OEM (Footprint) | Classification Method: Public OEM footprint / supplier listing</t>
-  </si>
-  <si>
-    <t>To identify companies with employment numbers of at least 10,000 employees and to list their categories and classifications, I would typically look for specific data in an Excel workbook or a similar structured dataset. Since no workbook evidence is provided here, I can't give exact company names, categories, or classifications.
-However, based on general knowledge, companies with such large employment numbers are often found in industries like manufacturing (e.g., automotive), technology, retail, and finance. Categories might include "Large Enterprises," "Fortune 500 Companies," etc., while classification could be more specific to the industry sector they operate within.
-For a precise answer, you would need to filter your dataset for companies with employment figures of at least 10,000 employees and then extract their corresponding categories and classifications. If you have an Excel workbook or similar data source available, applying these filters should yield the exact information you're looking for.</t>
-  </si>
-  <si>
-    <t>Toyota Industries Group (TACG-TICA) has Employment of 18100, Category: OEM (Footprint), and Classification Method: Public OEM footprint / supplier listing.</t>
-  </si>
-  <si>
-    <t>I am unable to answer this question without access to the relevant workbook data. The request requires specific information about companies, their employment numbers, categories, and classifications, which are only available within the Excel workbooks.</t>
-  </si>
-  <si>
-    <t>Toyota Industries Group (TACG-TICA) - Category: OEM (Footprint), Classification: Public OEM footprint / supplier listing</t>
-  </si>
-  <si>
-    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 31.809574998s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-2.5-flash', 'location': 'global'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '31s'}]}}</t>
-  </si>
-  <si>
-    <t>Method.</t>
-  </si>
-  <si>
-    <t>The question "Method." is too vague and does not provide enough context to determine what specific information is being requested. It could refer to various aspects such as classification methods, manufacturing methods, or other processes related to the companies listed in the evidence.
-To provide a helpful response, please clarify what you are asking about. For example:
-- Are you asking about the classification methods used for these companies?
-- Are you inquiring about the manufacturing methods or processes used by these companies?
-- Or is there another specific method you are referring to?</t>
-  </si>
-  <si>
-    <t>Classification Method: Supplier
-Companies:
-- ACM Georgia LLC
-- Adient
-- ADVICS Manufacturing Georgia LLC
-- Ajin Georgia
-- ALBAform Inc.
-- Anovion Technologies
-- DAS Corp.
-- DAEHAN Solution Georgia LLC</t>
-  </si>
-  <si>
-    <t>It seems like you might be asking about a specific method related to Excel workbooks or a particular process within them. Could you please clarify what method you're referring to? For example, are you looking for information on how to perform a certain task in Excel (like data sorting, formula creation, etc.) or are you asking about a business method that involves the use of Excel workbooks?</t>
-  </si>
-  <si>
-    <t>The Classification Method is Supplier for ACM Georgia LLC, Adient, ADVICS Manufacturing Georgia LLC, Ajin Georgia, ALBAform Inc., Anovion Technologies, DAS Corp., and DAEHAN Solution Georgia LLC.</t>
-  </si>
-  <si>
-    <t>Please provide more context. "Method" is a very broad term. To answer your question, I need to know what you're referring to. For example, are you asking about:
-*   A method in a specific process?
-*   A method in a scientific experiment?
-*   A method in a programming context?
-*   Something else entirely?
-Once you clarify what you're asking about, I can give you a helpful answer.</t>
-  </si>
-  <si>
-    <t>The classification method for the following companies is "Supplier":
-*   ACM Georgia LLC
-*   Adient
-*   ADVICS Manufacturing Georgia LLC
-*   Ajin Georgia
-*   ALBAform Inc.
-*   Anovion Technologies
-*   DAS Corp.
-*   DAEHAN Solution Georgia LLC</t>
-  </si>
-  <si>
-    <t>A method is a way or process for accomplishing something. It can refer to a specific procedure, technique, or approach used to achieve a particular goal. In various fields, methods are formalized and documented to ensure consistency, reproducibility, and effectiveness.</t>
-  </si>
-  <si>
     <t>Among OEM categories (OEM, OEM Supply Chain, OEM Footprint, OEM (Footprint)), which has the highest total Employment?</t>
   </si>
   <si>
@@ -4687,6 +4496,126 @@
   </si>
   <si>
     <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 43.292204909s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'location': 'global', 'model': 'gemini-2.5-flash'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '43s'}]}}</t>
+  </si>
+  <si>
+    <t>Identify companies with Employment &gt;= 10,000 and list their Category and Classification Method.</t>
+  </si>
+  <si>
+    <t>List all companies with Primary Facility Type = Headquarters (including North American Headquarters) and include their Location and Employment.</t>
+  </si>
+  <si>
+    <t>Headquarters / North American Headquarters [3]: Minebea AccessSolutions USA Inc. | Facility Type: Headquarters | Location: Atlanta, Fulton County | Employment: 400 TI Fluid Systems | Facility Type: North American Headquarters | Location: Atlanta, Fulton County | Employment: 19,600 Tie Down Engineering | Facility Type: North American Headquarters | Location: Greensboro, Greene County | Employment: 2,000</t>
+  </si>
+  <si>
+    <t>**Minebea AccessSolutions USA Inc.**
+- Location: Atlanta, Fulton County
+- Employment: 400
+- EV Supply Chain Role: General Automotive
+**TI Fluid Systems**
+- Location: Atlanta, Fulton County
+- Employment: 19600
+- EV Supply Chain Role: OEM corporate footprint influencing EV strategy
+**Tie Down Engineering**
+- Location: Greensboro, Greene County
+- Employment: 2000
+- EV Supply Chain Role: OEM corporate and engineering footprint (electrification)</t>
+  </si>
+  <si>
+    <t>Without specific workbook data, I can't list exact company names, locations, or employment numbers. However, generally speaking, if you're looking for companies that have a primary facility type of "Headquarters" (which could be specified as North American Headquarters or any other regional headquarters), the information typically includes:
+1. **Company Name**: The name of the corporation.
+2. **Location**: Usually the city and state/country where the headquarters is located.
+3. **Employment**: This would refer to the number of employees working at that specific location.
+To find this data, you'd usually look for a column or field in your dataset specifically labeled "Primary Facility Type" and filter it to show only entries marked as "Headquarters". Then, extract the corresponding company name, location, and employment figures from those rows. If you have access to such a workbook, you can apply these steps directly to get the precise information you need.</t>
+  </si>
+  <si>
+    <t>Here are the companies with a Primary Facility Type of Headquarters (including North American Headquarters), their Location, and Employment:
+*   **Minebea AccessSolutions USA Inc.**, Location: Atlanta, Fulton County, Employment: 400
+*   **TI Fluid Systems**, Location: Atlanta, Fulton County, Employment: 19600
+*   **Tie Down Engineering**, Location: Greensboro, Greene County, Employment: 2000</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the Excel workbook. The request requires specific data points (Company, Primary Facility Type, Location, and Employment) that are contained within the workbook. Without the data, I cannot provide a list of companies meeting the criteria.</t>
+  </si>
+  <si>
+    <t>* Minebea AccessSolutions USA Inc. - Location: Atlanta, Fulton County, Employment: 400
+* Tie Down Engineering - Location: Greensboro, Greene County, Employment: 2000
+* TI Fluid Systems - Location: Atlanta, Fulton County, Employment: 19600</t>
+  </si>
+  <si>
+    <t>I cannot provide a list of companies with "Primary Facility Type = Headquarters" (including North American Headquarters) along with their Location and Employment without access to the specific workbook data. This information is unique to the dataset within the workbook.</t>
+  </si>
+  <si>
+    <t>Within Tier 1 suppliers, identify companies in 'Electronic and Other Electrical Equipment and Components' and list their Product / Service.</t>
+  </si>
+  <si>
+    <t>None. There are no Tier 1 suppliers in the dataset with Industry Group = Electronic and Other Electrical Equipment and Components.</t>
+  </si>
+  <si>
+    <t>No companies within Tier 1 suppliers are listed under the 'Electronic and Other Electrical Equipment and Components' industry group based on the provided evidence.</t>
+  </si>
+  <si>
+    <t>To answer this question accurately, I would need specific information from the Excel workbook you mentioned, which includes details about Tier 1 suppliers and their product/service categories. Since no workbook evidence is provided here, I can't give an exact list of companies or their products/services.
+However, generally speaking, if you have a list of Tier 1 suppliers categorized under 'Electronic and Other Electrical Equipment and Components,' the process would involve filtering that list to identify companies within this specific category and then listing out what each company provides in terms of product/service. If you could share more details or provide the workbook data, I'd be able to give a more precise answer.</t>
+  </si>
+  <si>
+    <t>The workbook evidence indicates that Hyundai MOBIS (Georgia) is in 'Electronic and Other Electrical Equipment and Components' and has the Product / Service of Capacitors, electronic automotive components.</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question. I do not have access to the Excel workbook containing the Tier 1 supplier information, including their industry classification and product/service details.</t>
+  </si>
+  <si>
+    <t>The provided workbook evidence does not contain any companies classified as 'Tier 1' within the 'Electronic and Other Electrical Equipment and Components' industry group. However, Hyundai MOBIS (Georgia) is listed as 'Tier 1/2' and is in the 'Electronic and Other Electrical Equipment and Components' industry group. Their Product / Service is Capacitors, electronic automotive components.</t>
+  </si>
+  <si>
+    <t>I cannot provide a list of specific companies and their products/services within 'Electronic and Other Electrical Equipment and Components' for Tier 1 suppliers without access to the workbook. This information is highly specific to the dataset you are referencing.
+To answer your question, I would need to see the data within your workbook that categorizes suppliers by tier, industry, and lists their products/services.</t>
+  </si>
+  <si>
+    <t>According to the Methodology sheet, how are supply chain tiers assigned (what approach is described)?</t>
+  </si>
+  <si>
+    <t>Supply chain tiers are assigned using a structured heuristic approach that reflects functional roles across OEM, Tier 1, Tier 2, and Tier 3.</t>
+  </si>
+  <si>
+    <t>Supply chain tiers reflect functional roles and are assigned using a structured heuristic approach. Companies are classified as OEM, Tier 1, Tier 2, or Tier 3 based on their supply chain role within the automotive industry.</t>
+  </si>
+  <si>
+    <t>According to common practices in supply chain analysis, tiers are typically assigned based on the level of removal from the end customer. The first tier includes direct suppliers, the second tier includes suppliers to those direct suppliers, and so forth. Without specific details from the Methodology sheet you mentioned, I can't provide exact steps or criteria used in your workbook, but generally this hierarchical approach is widely adopted for categorizing supply chain tiers.</t>
+  </si>
+  <si>
+    <t>Supply chain tiers (OEM, Tier 1, Tier 2, and Tier 3) are assigned using a structured heuristic approach.</t>
+  </si>
+  <si>
+    <t>The Methodology sheet describes a tiered supplier approach based on the amount of spend with a given supplier. Suppliers are categorized into tiers based on the total value of purchases from them.</t>
+  </si>
+  <si>
+    <t>Supply chain tiers reflect functional roles (OEM, Tier 1, Tier 2, and Tier 3) and are assigned using a structured heuristic approach.</t>
+  </si>
+  <si>
+    <t>ERROR: 429 RESOURCE_EXHAUSTED. {'error': {'code': 429, 'message': 'You exceeded your current quota, please check your plan and billing details. For more information on this error, head to: https://ai.google.dev/gemini-api/docs/rate-limits. To monitor your current usage, head to: https://ai.dev/rate-limit. \n* Quota exceeded for metric: generativelanguage.googleapis.com/generate_content_free_tier_requests, limit: 5, model: gemini-2.5-flash\nPlease retry in 12.771557018s.', 'status': 'RESOURCE_EXHAUSTED', 'details': [{'@type': 'type.googleapis.com/google.rpc.Help', 'links': [{'description': 'Learn more about Gemini API quotas', 'url': 'https://ai.google.dev/gemini-api/docs/rate-limits'}]}, {'@type': 'type.googleapis.com/google.rpc.QuotaFailure', 'violations': [{'quotaMetric': 'generativelanguage.googleapis.com/generate_content_free_tier_requests', 'quotaId': 'GenerateRequestsPerMinutePerProjectPerModel-FreeTier', 'quotaDimensions': {'model': 'gemini-2.5-flash', 'location': 'global'}, 'quotaValue': '5'}]}, {'@type': 'type.googleapis.com/google.rpc.RetryInfo', 'retryDelay': '12s'}]}}</t>
+  </si>
+  <si>
+    <t>Companies with Employment &gt;= 10,000 [10 distinct companies]: WIKA USA | Employment: 250,000 | Category: OEM Supply Chain | Classification Method: Public OEM footprint / supplier listing Yazaki North America | Employment: 230,000 | Category: OEM Footprint | Classification Method: Public OEM footprint / supplier listing YKK USA Inc. | Employment: 190,159 | Category: OEM Footprint | Classification Method: Public OEM footprint / supplier listing Yamaha Motor Manufacturing Corp. | Employment: 190,000 | Category: OEM Supply Chain | Classification Method: Public OEM footprint / supplier listing Yachiyo Manufacturing of America LLC | Employment: 173,700 | Category: OEM Supply Chain | Classification Method: Public OEM footprint / supplier listing ZF Gainesville LLC | Employment: 170,000, 106,100, 17,500 | Category: OEM Footprint, OEM Supply Chain | Classification Method: Public OEM footprint / supplier listing Woory Industrial Co. | Employment: 87,000 | Category: OEM Supply Chain | Classification Method: Public OEM footprint / supplier listing TI Fluid Systems | Employment: 19,600 | Category: OEM (Footprint) | Classification Method: Public OEM footprint / supplier listing TN Americas Holding Inc. | Employment: 19,600 | Category: OEM (Footprint) | Classification Method: Public OEM footprint / supplier listing Toyota Industries Group (TACG-TICA) | Employment: 18,100 | Category: OEM (Footprint) | Classification Method: Public OEM footprint / supplier listing</t>
+  </si>
+  <si>
+    <t>The provided evidence does not contain any companies with Employment &gt;= 10,000. The highest employment figure given is 582 for Arising Industries Inc. located in Macon, Bibb County. Therefore, there are no matches for the specified criteria.</t>
+  </si>
+  <si>
+    <t>To identify companies with employment numbers of at least 10,000 employees and to list their categories and classification methods, I would typically look for specific data in an Excel workbook or a similar structured dataset. Since no workbook evidence is provided here, I can't provide exact values from any particular source.
+However, based on general knowledge, companies with such large employment numbers are often categorized under sectors like technology, finance, manufacturing, retail, and healthcare. The classification method could vary but commonly includes industry standards (e.g., SIC codes or NAICS codes) or company self-reporting as part of public disclosures or financial filings.
+For a precise answer, you would need to specify the workbook details or provide the exact data set you are referring to.</t>
+  </si>
+  <si>
+    <t>The provided evidence does not contain any companies with Employment &gt;= 10,000. The largest employment number listed is 582 for Arising Industries Inc.</t>
+  </si>
+  <si>
+    <t>I am unable to answer this question without access to the relevant workbook data. The question requires specific information about companies, their employment numbers, categories, and classification methods, which are only available within the Excel workbooks.</t>
+  </si>
+  <si>
+    <t>No companies with employment of 10,000 or greater were found in the provided evidence.</t>
+  </si>
+  <si>
+    <t>I cannot identify companies with Employment &gt;= 10,000 and list their Category and Classification Method without access to the specific workbook data. This information is contained within the workbook and is not something I can retrieve from general knowledge.</t>
   </si>
 </sst>
 </file>
@@ -6128,16 +6057,16 @@
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>784</v>
+        <v>752</v>
       </c>
       <c r="B17" t="s">
-        <v>785</v>
+        <v>753</v>
       </c>
       <c r="C17" t="s">
         <v>29</v>
       </c>
       <c r="D17" t="s">
-        <v>786</v>
+        <v>754</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -6149,13 +6078,13 @@
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>787</v>
+        <v>755</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="L17" t="s">
-        <v>788</v>
+        <v>756</v>
       </c>
       <c r="M17">
         <v>1</v>
@@ -6167,13 +6096,13 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>789</v>
+        <v>757</v>
       </c>
       <c r="Q17">
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>790</v>
+        <v>758</v>
       </c>
       <c r="U17">
         <v>1</v>
@@ -6185,7 +6114,7 @@
         <v>1</v>
       </c>
       <c r="X17" t="s">
-        <v>791</v>
+        <v>759</v>
       </c>
       <c r="Y17">
         <v>0</v>
@@ -6193,16 +6122,16 @@
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>792</v>
+        <v>760</v>
       </c>
       <c r="B18" t="s">
-        <v>793</v>
+        <v>761</v>
       </c>
       <c r="C18" t="s">
         <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>794</v>
+        <v>762</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6214,13 +6143,13 @@
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>795</v>
+        <v>763</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="L18" t="s">
-        <v>796</v>
+        <v>764</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -6232,13 +6161,13 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>797</v>
+        <v>765</v>
       </c>
       <c r="Q18">
         <v>0</v>
       </c>
       <c r="T18" t="s">
-        <v>798</v>
+        <v>766</v>
       </c>
       <c r="U18">
         <v>0</v>
@@ -6250,21 +6179,21 @@
         <v>1</v>
       </c>
       <c r="X18" t="s">
-        <v>799</v>
+        <v>767</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>800</v>
+        <v>768</v>
       </c>
       <c r="B19" t="s">
-        <v>801</v>
+        <v>769</v>
       </c>
       <c r="C19" t="s">
         <v>29</v>
       </c>
       <c r="D19" t="s">
-        <v>802</v>
+        <v>770</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6276,13 +6205,13 @@
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>803</v>
+        <v>771</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="L19" t="s">
-        <v>804</v>
+        <v>772</v>
       </c>
       <c r="M19">
         <v>0.5</v>
@@ -6294,13 +6223,13 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>805</v>
+        <v>773</v>
       </c>
       <c r="Q19">
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>806</v>
+        <v>774</v>
       </c>
       <c r="U19">
         <v>0.25</v>
@@ -6312,7 +6241,7 @@
         <v>1</v>
       </c>
       <c r="X19" t="s">
-        <v>807</v>
+        <v>775</v>
       </c>
       <c r="Y19">
         <v>0</v>
@@ -6320,16 +6249,16 @@
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>808</v>
+        <v>776</v>
       </c>
       <c r="B20" t="s">
-        <v>809</v>
+        <v>777</v>
       </c>
       <c r="C20" t="s">
         <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>810</v>
+        <v>778</v>
       </c>
       <c r="E20">
         <v>0.25</v>
@@ -6341,13 +6270,13 @@
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>811</v>
+        <v>779</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="L20" t="s">
-        <v>812</v>
+        <v>780</v>
       </c>
       <c r="M20">
         <v>0.25</v>
@@ -6359,13 +6288,13 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>813</v>
+        <v>781</v>
       </c>
       <c r="Q20">
         <v>0</v>
       </c>
       <c r="T20" t="s">
-        <v>814</v>
+        <v>782</v>
       </c>
       <c r="U20">
         <v>0.25</v>
@@ -6377,7 +6306,7 @@
         <v>1</v>
       </c>
       <c r="X20" t="s">
-        <v>815</v>
+        <v>783</v>
       </c>
       <c r="Y20">
         <v>0</v>
@@ -6385,16 +6314,16 @@
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>816</v>
+        <v>784</v>
       </c>
       <c r="B21" t="s">
-        <v>817</v>
+        <v>785</v>
       </c>
       <c r="C21" t="s">
         <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>818</v>
+        <v>786</v>
       </c>
       <c r="E21">
         <v>0.25</v>
@@ -6406,13 +6335,13 @@
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>819</v>
+        <v>787</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="L21" t="s">
-        <v>820</v>
+        <v>788</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -6424,13 +6353,13 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>821</v>
+        <v>789</v>
       </c>
       <c r="Q21">
         <v>0</v>
       </c>
       <c r="T21" t="s">
-        <v>822</v>
+        <v>790</v>
       </c>
       <c r="U21">
         <v>0.25</v>
@@ -6442,24 +6371,24 @@
         <v>1</v>
       </c>
       <c r="X21" t="s">
-        <v>823</v>
+        <v>791</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>147</v>
+        <v>793</v>
       </c>
       <c r="B22" t="s">
-        <v>148</v>
+        <v>794</v>
       </c>
       <c r="C22" t="s">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s">
-        <v>150</v>
+        <v>795</v>
       </c>
       <c r="E22">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -6468,43 +6397,43 @@
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>151</v>
+        <v>796</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="L22" t="s">
-        <v>152</v>
+        <v>797</v>
       </c>
       <c r="M22">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="N22">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="O22">
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>153</v>
+        <v>798</v>
       </c>
       <c r="Q22">
         <v>0</v>
       </c>
       <c r="T22" t="s">
-        <v>154</v>
+        <v>799</v>
       </c>
       <c r="U22">
         <v>1</v>
       </c>
       <c r="V22">
-        <v>0.66666666666666663</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="W22">
         <v>1</v>
       </c>
       <c r="X22" t="s">
-        <v>155</v>
+        <v>800</v>
       </c>
       <c r="Y22">
         <v>0</v>
@@ -6512,16 +6441,16 @@
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B23" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C23" t="s">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="D23" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -6533,13 +6462,13 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="L23" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="M23">
         <v>1</v>
@@ -6551,16 +6480,16 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="Q23">
         <v>0</v>
       </c>
       <c r="T23" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="U23">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="V23">
         <v>1</v>
@@ -6569,24 +6498,24 @@
         <v>1</v>
       </c>
       <c r="X23" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B24" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -6595,16 +6524,16 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="L24" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="M24">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="N24">
         <v>1</v>
@@ -6613,16 +6542,16 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="Q24">
         <v>0</v>
       </c>
       <c r="T24" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="U24">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="V24">
         <v>1</v>
@@ -6631,61 +6560,64 @@
         <v>1</v>
       </c>
       <c r="X24" t="s">
-        <v>171</v>
+        <v>163</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B25" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C25" t="s">
         <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25" t="s">
+        <v>167</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="L25" t="s">
+        <v>168</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <v>1</v>
+      </c>
+      <c r="P25" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="T25" t="s">
+        <v>170</v>
+      </c>
+      <c r="U25">
         <v>0.5</v>
       </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25" t="s">
-        <v>175</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="L25" t="s">
-        <v>176</v>
-      </c>
-      <c r="M25">
-        <v>0.25</v>
-      </c>
-      <c r="N25">
-        <v>1</v>
-      </c>
-      <c r="O25">
-        <v>1</v>
-      </c>
-      <c r="P25" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="T25" t="s">
-        <v>178</v>
-      </c>
-      <c r="U25">
-        <v>0.25</v>
-      </c>
       <c r="V25">
         <v>1</v>
       </c>
@@ -6693,7 +6625,7 @@
         <v>1</v>
       </c>
       <c r="X25" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="Y25">
         <v>0</v>
@@ -6701,19 +6633,19 @@
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B26" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C26" t="s">
         <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -6722,16 +6654,16 @@
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="L26" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="M26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26">
         <v>1</v>
@@ -6740,25 +6672,25 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="Q26">
         <v>0</v>
       </c>
       <c r="T26" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="U26">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26">
         <v>1</v>
       </c>
       <c r="X26" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="Y26">
         <v>0</v>
@@ -6766,34 +6698,34 @@
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B27" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C27" t="s">
         <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>0.58823529411764708</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="L27" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -6805,184 +6737,181 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="Q27">
         <v>0</v>
       </c>
       <c r="T27" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="U27">
         <v>0</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27">
         <v>1</v>
       </c>
       <c r="X27" t="s">
-        <v>195</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B28" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C28" t="s">
         <v>29</v>
       </c>
       <c r="D28" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28">
-        <v>0.58823529411764708</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="L28" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="N28">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="O28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="Q28">
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="U28">
         <v>0</v>
       </c>
       <c r="V28">
-        <v>1</v>
+        <v>0.94444444444444442</v>
       </c>
       <c r="W28">
         <v>1</v>
       </c>
       <c r="X28" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B29" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C29" t="s">
         <v>29</v>
       </c>
       <c r="D29" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F29">
-        <v>0.88888888888888884</v>
+        <v>0.8</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
       <c r="L29" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="M29">
+        <v>0.75</v>
+      </c>
+      <c r="N29">
+        <v>1</v>
+      </c>
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="P29" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="T29" t="s">
+        <v>202</v>
+      </c>
+      <c r="U29">
         <v>0.25</v>
       </c>
-      <c r="N29">
-        <v>0.875</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="T29" t="s">
-        <v>210</v>
-      </c>
-      <c r="U29">
-        <v>0</v>
-      </c>
       <c r="V29">
-        <v>0.94444444444444442</v>
+        <v>1</v>
       </c>
       <c r="W29">
         <v>1</v>
       </c>
       <c r="X29" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B30" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C30" t="s">
         <v>29</v>
       </c>
       <c r="D30" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E30">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="F30">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
       <c r="L30" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="M30">
         <v>0.75</v>
@@ -6994,16 +6923,16 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="Q30">
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="U30">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="V30">
         <v>1</v>
@@ -7012,42 +6941,42 @@
         <v>1</v>
       </c>
       <c r="X30" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B31" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C31" t="s">
         <v>29</v>
       </c>
       <c r="D31" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="E31">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
       <c r="L31" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="M31">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -7056,16 +6985,16 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="Q31">
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="U31">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="V31">
         <v>1</v>
@@ -7074,151 +7003,151 @@
         <v>1</v>
       </c>
       <c r="X31" t="s">
-        <v>227</v>
+        <v>219</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B32" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C32" t="s">
         <v>29</v>
       </c>
       <c r="D32" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I32">
         <v>0</v>
       </c>
       <c r="L32" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="M32">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="N32">
-        <v>1</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="O32">
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="Q32">
         <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="U32">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>1</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="W32">
         <v>1</v>
       </c>
       <c r="X32" t="s">
-        <v>235</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B33" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C33" t="s">
         <v>29</v>
       </c>
       <c r="D33" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F33">
-        <v>0.5714285714285714</v>
+        <v>1</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="L33" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="N33">
-        <v>0.77777777777777779</v>
+        <v>1</v>
       </c>
       <c r="O33">
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="Q33">
         <v>0</v>
       </c>
       <c r="T33" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="V33">
-        <v>0.81818181818181823</v>
+        <v>1</v>
       </c>
       <c r="W33">
         <v>1</v>
       </c>
       <c r="X33" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="B34" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C34" t="s">
         <v>29</v>
       </c>
       <c r="D34" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="E34">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -7227,16 +7156,16 @@
         <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="L34" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="M34">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="N34">
         <v>1</v>
@@ -7245,16 +7174,16 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="Q34">
         <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="U34">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="V34">
         <v>1</v>
@@ -7263,24 +7192,24 @@
         <v>1</v>
       </c>
       <c r="X34" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="B35" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="C35" t="s">
         <v>29</v>
       </c>
       <c r="D35" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -7289,60 +7218,60 @@
         <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="L35" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="M35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35">
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="Q35">
         <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="U35">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="V35">
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W35">
         <v>1</v>
       </c>
       <c r="X35" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B36" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="C36" t="s">
         <v>29</v>
       </c>
       <c r="D36" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="E36">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -7351,60 +7280,60 @@
         <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
       <c r="L36" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36">
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="Q36">
         <v>0</v>
       </c>
       <c r="T36" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="U36">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="V36">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="W36">
         <v>1</v>
       </c>
       <c r="X36" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B37" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C37" t="s">
         <v>29</v>
       </c>
       <c r="D37" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -7413,34 +7342,34 @@
         <v>1</v>
       </c>
       <c r="H37" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="I37">
         <v>0</v>
       </c>
       <c r="L37" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="M37">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>0.95833333333333337</v>
       </c>
       <c r="O37">
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="Q37">
         <v>0</v>
       </c>
       <c r="T37" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="U37">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="V37">
         <v>1</v>
@@ -7449,69 +7378,72 @@
         <v>1</v>
       </c>
       <c r="X37" t="s">
-        <v>275</v>
+        <v>267</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B38" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C38" t="s">
         <v>29</v>
       </c>
       <c r="D38" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E38">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="G38">
         <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="I38">
         <v>0</v>
       </c>
       <c r="L38" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="M38">
         <v>0.25</v>
       </c>
       <c r="N38">
-        <v>0.95833333333333337</v>
+        <v>0.94117647058823528</v>
       </c>
       <c r="O38">
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="Q38">
         <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="U38">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V38">
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="W38">
         <v>1</v>
       </c>
       <c r="X38" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="Y38">
         <v>0</v>
@@ -7519,253 +7451,253 @@
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="B39" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C39" t="s">
         <v>29</v>
       </c>
       <c r="D39" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="E39">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>0.875</v>
+        <v>0.76470588235294112</v>
       </c>
       <c r="G39">
         <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="I39">
         <v>0</v>
       </c>
       <c r="L39" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="M39">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="N39">
-        <v>0.94117647058823528</v>
+        <v>1</v>
       </c>
       <c r="O39">
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="Q39">
         <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="U39">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="W39">
         <v>1</v>
       </c>
       <c r="X39" t="s">
-        <v>291</v>
-      </c>
-      <c r="Y39">
-        <v>0</v>
+        <v>283</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="B40" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C40" t="s">
         <v>29</v>
       </c>
       <c r="D40" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40">
-        <v>0.76470588235294112</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="G40">
         <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L40" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N40">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="O40">
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="Q40">
         <v>0</v>
       </c>
       <c r="T40" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="U40">
         <v>0</v>
       </c>
       <c r="V40">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="W40">
         <v>1</v>
       </c>
       <c r="X40" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="B41" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C41" t="s">
         <v>29</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41" t="s">
+        <v>295</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="L41" t="s">
+        <v>296</v>
+      </c>
+      <c r="M41">
+        <v>1</v>
+      </c>
+      <c r="N41">
         <v>0.83333333333333337</v>
       </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-      <c r="H41" t="s">
-        <v>303</v>
-      </c>
-      <c r="I41">
-        <v>0.5</v>
-      </c>
-      <c r="L41" t="s">
-        <v>304</v>
-      </c>
-      <c r="M41">
-        <v>0.5</v>
-      </c>
-      <c r="N41">
+      <c r="O41">
+        <v>1</v>
+      </c>
+      <c r="P41" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="T41" t="s">
+        <v>298</v>
+      </c>
+      <c r="U41">
+        <v>1</v>
+      </c>
+      <c r="V41">
         <v>0.75</v>
       </c>
-      <c r="O41">
-        <v>1</v>
-      </c>
-      <c r="P41" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q41">
-        <v>0</v>
-      </c>
-      <c r="T41" t="s">
-        <v>306</v>
-      </c>
-      <c r="U41">
-        <v>0</v>
-      </c>
-      <c r="V41">
-        <v>0.875</v>
-      </c>
       <c r="W41">
         <v>1</v>
       </c>
       <c r="X41" t="s">
-        <v>307</v>
+        <v>299</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="B42" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C42" t="s">
         <v>29</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
       <c r="F42">
-        <v>0.77777777777777779</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="G42">
         <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L42" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="M42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="O42">
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="Q42">
         <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="U42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="W42">
         <v>1</v>
       </c>
       <c r="X42" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="Y42">
         <v>0</v>
@@ -7773,208 +7705,205 @@
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="B43" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="C43" t="s">
         <v>29</v>
       </c>
       <c r="D43" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="G43">
         <v>1</v>
       </c>
       <c r="H43" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="I43">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L43" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43">
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="O43">
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="Q43">
         <v>0</v>
       </c>
       <c r="T43" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="V43">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="W43">
         <v>1</v>
       </c>
       <c r="X43" t="s">
-        <v>323</v>
-      </c>
-      <c r="Y43">
-        <v>0</v>
+        <v>315</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B44" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="C44" t="s">
         <v>29</v>
       </c>
       <c r="D44" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="E44">
         <v>1</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
       <c r="H44" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="L44" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="M44">
         <v>1</v>
       </c>
       <c r="N44">
-        <v>0.83333333333333337</v>
+        <v>0.9</v>
       </c>
       <c r="O44">
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="Q44">
         <v>0</v>
       </c>
       <c r="T44" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="U44">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="V44">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="W44">
         <v>1</v>
       </c>
       <c r="X44" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="B45" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="C45" t="s">
         <v>29</v>
       </c>
       <c r="D45" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F45">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="G45">
         <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I45">
         <v>0</v>
       </c>
       <c r="L45" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="M45">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="N45">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="O45">
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="Q45">
         <v>0</v>
       </c>
       <c r="T45" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="U45">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="V45">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="W45">
         <v>1</v>
       </c>
       <c r="X45" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B46" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="C46" t="s">
         <v>29</v>
       </c>
       <c r="D46" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="E46">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -7983,105 +7912,108 @@
         <v>1</v>
       </c>
       <c r="H46" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="L46" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="M46">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="N46">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="O46">
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="Q46">
         <v>0</v>
       </c>
       <c r="T46" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="U46">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="V46">
-        <v>1</v>
+        <v>0.76470588235294112</v>
       </c>
       <c r="W46">
         <v>1</v>
       </c>
       <c r="X46" t="s">
-        <v>347</v>
+        <v>335</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="B47" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="C47" t="s">
         <v>29</v>
       </c>
       <c r="D47" t="s">
-        <v>368</v>
+        <v>338</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G47">
         <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>369</v>
+        <v>339</v>
       </c>
       <c r="I47">
         <v>0</v>
       </c>
       <c r="L47" t="s">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="N47">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O47">
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="T47" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="V47">
-        <v>0.76470588235294112</v>
+        <v>1</v>
       </c>
       <c r="W47">
         <v>1</v>
       </c>
       <c r="X47" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="Y47">
         <v>0</v>
@@ -8089,211 +8021,208 @@
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="B48" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C48" t="s">
         <v>29</v>
       </c>
       <c r="D48" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48" t="s">
+        <v>360</v>
+      </c>
+      <c r="I48">
+        <v>0.25</v>
+      </c>
+      <c r="L48" t="s">
+        <v>361</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="O48">
         <v>0.5</v>
       </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
-      <c r="H48" t="s">
-        <v>355</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="L48" t="s">
-        <v>356</v>
-      </c>
-      <c r="M48">
-        <v>0.25</v>
-      </c>
-      <c r="N48">
-        <v>0.8</v>
-      </c>
-      <c r="O48">
-        <v>1</v>
-      </c>
       <c r="P48" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="Q48">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="T48" t="s">
-        <v>373</v>
+        <v>344</v>
       </c>
       <c r="U48">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="V48">
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="W48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X48" t="s">
-        <v>357</v>
-      </c>
-      <c r="Y48">
-        <v>0</v>
+        <v>345</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="B49" t="s">
-        <v>374</v>
+        <v>347</v>
       </c>
       <c r="C49" t="s">
         <v>29</v>
       </c>
       <c r="D49" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="F49">
-        <v>0.83333333333333337</v>
+        <v>0.72413793103448276</v>
       </c>
       <c r="G49">
         <v>1</v>
       </c>
       <c r="H49" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="I49">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L49" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="M49">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="N49">
-        <v>0.83333333333333337</v>
+        <v>0.875</v>
       </c>
       <c r="O49">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="Q49">
         <v>0</v>
       </c>
       <c r="T49" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49">
-        <v>0.66666666666666663</v>
+        <v>0.8</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X49" t="s">
-        <v>361</v>
+        <v>367</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="B50" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="C50" t="s">
         <v>29</v>
       </c>
       <c r="D50" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="E50">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="F50">
-        <v>0.72413793103448276</v>
+        <v>1</v>
       </c>
       <c r="G50">
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="L50" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="M50">
         <v>0.75</v>
       </c>
       <c r="N50">
-        <v>0.875</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="O50">
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>381</v>
+        <v>350</v>
       </c>
       <c r="Q50">
         <v>0</v>
       </c>
       <c r="T50" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="U50">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V50">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="W50">
         <v>1</v>
       </c>
       <c r="X50" t="s">
-        <v>383</v>
-      </c>
-      <c r="Y50">
-        <v>0</v>
+        <v>351</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B51" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C51" t="s">
         <v>29</v>
       </c>
       <c r="D51" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="E51">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -8302,105 +8231,108 @@
         <v>1</v>
       </c>
       <c r="H51" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="I51">
         <v>0</v>
       </c>
       <c r="L51" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="M51">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="N51">
-        <v>0.77777777777777779</v>
+        <v>0.5</v>
       </c>
       <c r="O51">
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="Q51">
         <v>0</v>
       </c>
       <c r="T51" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="U51">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V51">
-        <v>1</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="W51">
         <v>1</v>
       </c>
       <c r="X51" t="s">
-        <v>367</v>
+        <v>379</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="B52" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="C52" t="s">
         <v>29</v>
       </c>
       <c r="D52" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+      <c r="H52" t="s">
+        <v>383</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="L52" t="s">
+        <v>384</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0.75</v>
+      </c>
+      <c r="O52">
         <v>0.5</v>
       </c>
-      <c r="F52">
-        <v>1</v>
-      </c>
-      <c r="G52">
-        <v>1</v>
-      </c>
-      <c r="H52" t="s">
-        <v>391</v>
-      </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="L52" t="s">
-        <v>392</v>
-      </c>
-      <c r="M52">
-        <v>0</v>
-      </c>
-      <c r="N52">
-        <v>0.5</v>
-      </c>
-      <c r="O52">
-        <v>1</v>
-      </c>
       <c r="P52" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="Q52">
         <v>0</v>
       </c>
       <c r="T52" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="U52">
         <v>0</v>
       </c>
       <c r="V52">
-        <v>0.46666666666666667</v>
+        <v>1</v>
       </c>
       <c r="W52">
         <v>1</v>
       </c>
       <c r="X52" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="Y52">
         <v>0</v>
@@ -8408,81 +8340,78 @@
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="B53" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C53" t="s">
         <v>29</v>
       </c>
       <c r="D53" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="E53">
         <v>0</v>
       </c>
       <c r="F53">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="G53">
         <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="I53">
         <v>0</v>
       </c>
       <c r="L53" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="M53">
         <v>0</v>
       </c>
       <c r="N53">
-        <v>0.75</v>
+        <v>0.1</v>
       </c>
       <c r="O53">
         <v>0.5</v>
       </c>
       <c r="P53" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="Q53">
         <v>0</v>
       </c>
       <c r="T53" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="U53">
         <v>0</v>
       </c>
       <c r="V53">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="W53">
         <v>1</v>
       </c>
       <c r="X53" t="s">
-        <v>403</v>
-      </c>
-      <c r="Y53">
-        <v>0</v>
+        <v>395</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="B54" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C54" t="s">
         <v>29</v>
       </c>
       <c r="D54" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -8494,232 +8423,235 @@
         <v>1</v>
       </c>
       <c r="H54" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="I54">
         <v>0</v>
       </c>
       <c r="L54" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="M54">
         <v>0</v>
       </c>
       <c r="N54">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="O54">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="Q54">
         <v>0</v>
       </c>
       <c r="T54" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="U54">
         <v>0</v>
       </c>
       <c r="V54">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="W54">
         <v>1</v>
       </c>
       <c r="X54" t="s">
-        <v>411</v>
+        <v>403</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="B55" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C55" t="s">
         <v>29</v>
       </c>
       <c r="D55" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>0.84615384615384615</v>
       </c>
       <c r="G55">
         <v>1</v>
       </c>
       <c r="H55" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L55" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="M55">
         <v>0</v>
       </c>
       <c r="N55">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O55">
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="Q55">
         <v>0</v>
       </c>
       <c r="T55" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="U55">
         <v>0</v>
       </c>
       <c r="V55">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="W55">
         <v>1</v>
       </c>
       <c r="X55" t="s">
-        <v>419</v>
-      </c>
-      <c r="Y55">
-        <v>0</v>
+        <v>411</v>
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="B56" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="C56" t="s">
         <v>29</v>
       </c>
       <c r="D56" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
       <c r="F56">
-        <v>0.84615384615384615</v>
+        <v>0.5</v>
       </c>
       <c r="G56">
         <v>1</v>
       </c>
       <c r="H56" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="I56">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L56" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="M56">
         <v>0</v>
       </c>
       <c r="N56">
-        <v>1</v>
+        <v>0.84210526315789469</v>
       </c>
       <c r="O56">
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="Q56">
         <v>0</v>
       </c>
       <c r="T56" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="U56">
         <v>0</v>
       </c>
       <c r="V56">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="W56">
         <v>1</v>
       </c>
       <c r="X56" t="s">
-        <v>427</v>
+        <v>419</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="B57" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="C57" t="s">
         <v>29</v>
       </c>
       <c r="D57" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="E57">
         <v>0</v>
       </c>
       <c r="F57">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G57">
         <v>1</v>
       </c>
       <c r="H57" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="I57">
         <v>0</v>
       </c>
       <c r="L57" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="M57">
         <v>0</v>
       </c>
       <c r="N57">
-        <v>0.84210526315789469</v>
+        <v>1</v>
       </c>
       <c r="O57">
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="Q57">
         <v>0</v>
       </c>
       <c r="T57" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="U57">
         <v>0</v>
       </c>
       <c r="V57">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="W57">
         <v>1</v>
       </c>
       <c r="X57" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="Y57">
         <v>0</v>
@@ -8727,34 +8659,34 @@
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="B58" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C58" t="s">
         <v>29</v>
       </c>
       <c r="D58" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E58">
         <v>0</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G58">
         <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="I58">
         <v>0</v>
       </c>
       <c r="L58" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="M58">
         <v>0</v>
@@ -8766,107 +8698,104 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="Q58">
         <v>0</v>
       </c>
       <c r="T58" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="U58">
         <v>0</v>
       </c>
       <c r="V58">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="W58">
         <v>1</v>
       </c>
       <c r="X58" t="s">
-        <v>443</v>
-      </c>
-      <c r="Y58">
-        <v>0</v>
+        <v>435</v>
       </c>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="B59" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="C59" t="s">
         <v>29</v>
       </c>
       <c r="D59" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="E59">
         <v>0</v>
       </c>
       <c r="F59">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G59">
         <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="I59">
         <v>0</v>
       </c>
       <c r="L59" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="M59">
         <v>0</v>
       </c>
       <c r="N59">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O59">
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="Q59">
         <v>0</v>
       </c>
       <c r="T59" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="U59">
         <v>0</v>
       </c>
       <c r="V59">
-        <v>0.8</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W59">
         <v>1</v>
       </c>
       <c r="X59" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="B60" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="C60" t="s">
         <v>29</v>
       </c>
       <c r="D60" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60">
         <v>1</v>
@@ -8875,347 +8804,347 @@
         <v>1</v>
       </c>
       <c r="H60" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="I60">
         <v>0</v>
       </c>
       <c r="L60" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="M60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O60">
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="Q60">
         <v>0</v>
       </c>
       <c r="T60" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V60">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="W60">
         <v>1</v>
       </c>
       <c r="X60" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="B61" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C61" t="s">
         <v>29</v>
       </c>
       <c r="D61" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="E61">
         <v>1</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="H61" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="I61">
         <v>0</v>
       </c>
       <c r="L61" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="M61">
         <v>1</v>
       </c>
       <c r="N61">
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="O61">
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="Q61">
         <v>0</v>
       </c>
       <c r="T61" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="U61">
         <v>1</v>
       </c>
       <c r="V61">
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="W61">
         <v>1</v>
       </c>
       <c r="X61" t="s">
-        <v>467</v>
+        <v>459</v>
+      </c>
+      <c r="Y61">
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="B62" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C62" t="s">
         <v>29</v>
       </c>
       <c r="D62" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
         <v>0.75</v>
       </c>
-      <c r="G62">
-        <v>1</v>
-      </c>
       <c r="H62" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="I62">
         <v>0</v>
       </c>
       <c r="L62" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="M62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="O62">
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="Q62">
         <v>0</v>
       </c>
       <c r="T62" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="U62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V62">
-        <v>0.66666666666666663</v>
+        <v>0.6</v>
       </c>
       <c r="W62">
         <v>1</v>
       </c>
       <c r="X62" t="s">
-        <v>475</v>
-      </c>
-      <c r="Y62">
-        <v>0</v>
+        <v>467</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B63" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C63" t="s">
         <v>29</v>
       </c>
       <c r="D63" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="E63">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H63" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="I63">
         <v>0</v>
       </c>
       <c r="L63" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="M63">
         <v>0</v>
       </c>
       <c r="N63">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O63">
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="Q63">
         <v>0</v>
       </c>
       <c r="T63" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="U63">
         <v>0</v>
       </c>
       <c r="V63">
-        <v>0.6</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="W63">
         <v>1</v>
       </c>
       <c r="X63" t="s">
-        <v>483</v>
+        <v>475</v>
+      </c>
+      <c r="Y63">
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="B64" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="C64" t="s">
         <v>29</v>
       </c>
       <c r="D64" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="E64">
         <v>0</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="G64">
         <v>1</v>
       </c>
       <c r="H64" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="I64">
         <v>0</v>
       </c>
       <c r="L64" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="M64">
         <v>0</v>
       </c>
       <c r="N64">
-        <v>0.8</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="O64">
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="Q64">
         <v>0</v>
       </c>
       <c r="T64" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="U64">
         <v>0</v>
       </c>
       <c r="V64">
-        <v>0.90909090909090906</v>
+        <v>1</v>
       </c>
       <c r="W64">
         <v>1</v>
       </c>
       <c r="X64" t="s">
-        <v>491</v>
-      </c>
-      <c r="Y64">
-        <v>0</v>
+        <v>483</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>492</v>
+        <v>792</v>
       </c>
       <c r="B65" t="s">
-        <v>493</v>
+        <v>817</v>
       </c>
       <c r="C65" t="s">
         <v>29</v>
       </c>
       <c r="D65" t="s">
-        <v>494</v>
+        <v>818</v>
       </c>
       <c r="E65">
         <v>0</v>
       </c>
       <c r="F65">
-        <v>0.83333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="G65">
         <v>1</v>
       </c>
       <c r="H65" t="s">
-        <v>495</v>
+        <v>819</v>
       </c>
       <c r="I65">
         <v>0</v>
       </c>
       <c r="L65" t="s">
-        <v>496</v>
+        <v>820</v>
       </c>
       <c r="M65">
         <v>0</v>
       </c>
       <c r="N65">
-        <v>0.88888888888888884</v>
+        <v>1</v>
       </c>
       <c r="O65">
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>497</v>
+        <v>821</v>
       </c>
       <c r="Q65">
         <v>0</v>
       </c>
       <c r="T65" t="s">
-        <v>498</v>
+        <v>822</v>
       </c>
       <c r="U65">
         <v>0</v>
@@ -9227,60 +9156,63 @@
         <v>1</v>
       </c>
       <c r="X65" t="s">
-        <v>499</v>
+        <v>823</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="B66" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="C66" t="s">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="D66" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="G66">
         <v>1</v>
       </c>
       <c r="H66" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="I66">
         <v>0</v>
       </c>
       <c r="L66" t="s">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="M66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N66">
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="O66">
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="Q66">
         <v>0</v>
       </c>
       <c r="T66" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="U66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V66">
         <v>1</v>
@@ -9289,122 +9221,119 @@
         <v>1</v>
       </c>
       <c r="X66" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="B67" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="C67" t="s">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="D67" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="E67">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="I67">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L67" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
         <v>0.5</v>
       </c>
-      <c r="N67">
-        <v>1</v>
-      </c>
       <c r="O67">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P67" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="T67" t="s">
+        <v>498</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
         <v>0.5</v>
       </c>
-      <c r="T67" t="s">
-        <v>514</v>
-      </c>
-      <c r="U67">
-        <v>0.25</v>
-      </c>
-      <c r="V67">
-        <v>1</v>
-      </c>
       <c r="W67">
         <v>1</v>
       </c>
       <c r="X67" t="s">
-        <v>515</v>
-      </c>
-      <c r="Y67">
-        <v>0.25</v>
+        <v>499</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="B68" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="C68" t="s">
         <v>29</v>
       </c>
       <c r="D68" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="E68">
         <v>0</v>
       </c>
       <c r="F68">
-        <v>0.8666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="G68">
         <v>1</v>
       </c>
       <c r="H68" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="I68">
         <v>0</v>
       </c>
       <c r="L68" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="M68">
         <v>0</v>
       </c>
       <c r="N68">
-        <v>0.83333333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="O68">
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="Q68">
         <v>0</v>
       </c>
       <c r="T68" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="U68">
         <v>0</v>
@@ -9416,119 +9345,119 @@
         <v>1</v>
       </c>
       <c r="X68" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="B69" t="s">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="C69" t="s">
         <v>29</v>
       </c>
       <c r="D69" t="s">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="E69">
         <v>0</v>
       </c>
       <c r="F69">
-        <v>0.875</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="G69">
         <v>1</v>
       </c>
       <c r="H69" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="I69">
         <v>0</v>
       </c>
       <c r="L69" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="M69">
         <v>0</v>
       </c>
       <c r="N69">
-        <v>0.5</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="O69">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="Q69">
         <v>0</v>
       </c>
       <c r="T69" t="s">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="U69">
         <v>0</v>
       </c>
       <c r="V69">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W69">
         <v>1</v>
       </c>
       <c r="X69" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="B70" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="C70" t="s">
         <v>29</v>
       </c>
       <c r="D70" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="E70">
         <v>0</v>
       </c>
       <c r="F70">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70" t="s">
+        <v>519</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="L70" t="s">
+        <v>520</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
         <v>0.5</v>
       </c>
-      <c r="G70">
-        <v>1</v>
-      </c>
-      <c r="H70" t="s">
-        <v>535</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="L70" t="s">
-        <v>536</v>
-      </c>
-      <c r="M70">
-        <v>0</v>
-      </c>
-      <c r="N70">
-        <v>0.66666666666666663</v>
-      </c>
       <c r="O70">
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>537</v>
+        <v>147</v>
       </c>
       <c r="Q70">
         <v>0</v>
       </c>
       <c r="T70" t="s">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="U70">
         <v>0</v>
@@ -9540,57 +9469,60 @@
         <v>1</v>
       </c>
       <c r="X70" t="s">
-        <v>539</v>
+        <v>522</v>
+      </c>
+      <c r="Y70">
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>540</v>
+        <v>523</v>
       </c>
       <c r="B71" t="s">
-        <v>541</v>
+        <v>524</v>
       </c>
       <c r="C71" t="s">
         <v>29</v>
       </c>
       <c r="D71" t="s">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="E71">
         <v>0</v>
       </c>
       <c r="F71">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="G71">
         <v>1</v>
       </c>
       <c r="H71" t="s">
-        <v>543</v>
+        <v>526</v>
       </c>
       <c r="I71">
         <v>0</v>
       </c>
       <c r="L71" t="s">
-        <v>544</v>
+        <v>527</v>
       </c>
       <c r="M71">
         <v>0</v>
       </c>
       <c r="N71">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="O71">
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>545</v>
+        <v>528</v>
       </c>
       <c r="Q71">
         <v>0</v>
       </c>
       <c r="T71" t="s">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="U71">
         <v>0</v>
@@ -9602,60 +9534,63 @@
         <v>1</v>
       </c>
       <c r="X71" t="s">
-        <v>547</v>
+        <v>530</v>
+      </c>
+      <c r="Y71">
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="B72" t="s">
-        <v>549</v>
+        <v>532</v>
       </c>
       <c r="C72" t="s">
         <v>29</v>
       </c>
       <c r="D72" t="s">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="G72">
         <v>1</v>
       </c>
       <c r="H72" t="s">
-        <v>551</v>
+        <v>534</v>
       </c>
       <c r="I72">
         <v>0</v>
       </c>
       <c r="L72" t="s">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="M72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N72">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O72">
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>153</v>
+        <v>536</v>
       </c>
       <c r="Q72">
         <v>0</v>
       </c>
       <c r="T72" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="V72">
         <v>1</v>
@@ -9664,7 +9599,7 @@
         <v>1</v>
       </c>
       <c r="X72" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="Y72">
         <v>0</v>
@@ -9672,16 +9607,16 @@
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="B73" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="C73" t="s">
         <v>29</v>
       </c>
       <c r="D73" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -9693,16 +9628,16 @@
         <v>1</v>
       </c>
       <c r="H73" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="I73">
         <v>0</v>
       </c>
       <c r="L73" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="M73">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="N73">
         <v>1</v>
@@ -9711,16 +9646,16 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>560</v>
+        <v>544</v>
       </c>
       <c r="Q73">
         <v>0</v>
       </c>
       <c r="T73" t="s">
-        <v>561</v>
+        <v>545</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="V73">
         <v>1</v>
@@ -9729,24 +9664,21 @@
         <v>1</v>
       </c>
       <c r="X73" t="s">
-        <v>562</v>
-      </c>
-      <c r="Y73">
-        <v>0</v>
+        <v>546</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="B74" t="s">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="C74" t="s">
         <v>29</v>
       </c>
       <c r="D74" t="s">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="E74">
         <v>1</v>
@@ -9758,13 +9690,13 @@
         <v>1</v>
       </c>
       <c r="H74" t="s">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="I74">
         <v>0</v>
       </c>
       <c r="L74" t="s">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="M74">
         <v>1</v>
@@ -9776,16 +9708,16 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="Q74">
         <v>0</v>
       </c>
       <c r="T74" t="s">
-        <v>569</v>
+        <v>553</v>
       </c>
       <c r="U74">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="V74">
         <v>1</v>
@@ -9794,187 +9726,187 @@
         <v>1</v>
       </c>
       <c r="X74" t="s">
-        <v>570</v>
-      </c>
-      <c r="Y74">
-        <v>0</v>
+        <v>554</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="B75" t="s">
-        <v>572</v>
+        <v>556</v>
       </c>
       <c r="C75" t="s">
         <v>29</v>
       </c>
       <c r="D75" t="s">
-        <v>573</v>
+        <v>557</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G75">
         <v>1</v>
       </c>
       <c r="H75" t="s">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="I75">
         <v>0</v>
       </c>
       <c r="L75" t="s">
-        <v>575</v>
+        <v>559</v>
       </c>
       <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>1</v>
+      </c>
+      <c r="P75" t="s">
+        <v>560</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="T75" t="s">
+        <v>561</v>
+      </c>
+      <c r="U75">
+        <v>0.5</v>
+      </c>
+      <c r="V75">
+        <v>1</v>
+      </c>
+      <c r="W75">
+        <v>1</v>
+      </c>
+      <c r="X75" t="s">
+        <v>562</v>
+      </c>
+      <c r="Y75">
         <v>0.25</v>
-      </c>
-      <c r="N75">
-        <v>1</v>
-      </c>
-      <c r="O75">
-        <v>1</v>
-      </c>
-      <c r="P75" t="s">
-        <v>576</v>
-      </c>
-      <c r="Q75">
-        <v>0</v>
-      </c>
-      <c r="T75" t="s">
-        <v>577</v>
-      </c>
-      <c r="U75">
-        <v>0.25</v>
-      </c>
-      <c r="V75">
-        <v>1</v>
-      </c>
-      <c r="W75">
-        <v>1</v>
-      </c>
-      <c r="X75" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>579</v>
+        <v>563</v>
       </c>
       <c r="B76" t="s">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="C76" t="s">
         <v>29</v>
       </c>
       <c r="D76" t="s">
-        <v>581</v>
+        <v>565</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G76">
         <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="I76">
         <v>0</v>
       </c>
       <c r="L76" t="s">
-        <v>583</v>
+        <v>567</v>
       </c>
       <c r="M76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N76">
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="O76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P76" t="s">
-        <v>584</v>
+        <v>568</v>
       </c>
       <c r="Q76">
         <v>0</v>
       </c>
       <c r="T76" t="s">
-        <v>585</v>
+        <v>569</v>
       </c>
       <c r="U76">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="V76">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="W76">
         <v>1</v>
       </c>
       <c r="X76" t="s">
-        <v>586</v>
+        <v>570</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="B77" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
       <c r="C77" t="s">
         <v>29</v>
       </c>
       <c r="D77" t="s">
-        <v>589</v>
+        <v>573</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F77">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G77">
         <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>590</v>
+        <v>574</v>
       </c>
       <c r="I77">
         <v>0</v>
       </c>
       <c r="L77" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="M77">
         <v>1</v>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>0.92307692307692313</v>
       </c>
       <c r="O77">
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>592</v>
+        <v>147</v>
       </c>
       <c r="Q77">
         <v>0</v>
       </c>
       <c r="T77" t="s">
-        <v>593</v>
+        <v>576</v>
       </c>
       <c r="U77">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="V77">
         <v>1</v>
@@ -9983,125 +9915,125 @@
         <v>1</v>
       </c>
       <c r="X77" t="s">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="Y77">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>595</v>
+        <v>578</v>
       </c>
       <c r="B78" t="s">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="C78" t="s">
         <v>29</v>
       </c>
       <c r="D78" t="s">
-        <v>597</v>
+        <v>580</v>
       </c>
       <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78" t="s">
+        <v>581</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="L78" t="s">
+        <v>582</v>
+      </c>
+      <c r="M78">
         <v>0.25</v>
       </c>
-      <c r="F78">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="G78">
-        <v>1</v>
-      </c>
-      <c r="H78" t="s">
-        <v>598</v>
-      </c>
-      <c r="I78">
-        <v>0</v>
-      </c>
-      <c r="L78" t="s">
-        <v>599</v>
-      </c>
-      <c r="M78">
-        <v>0</v>
-      </c>
       <c r="N78">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>600</v>
+        <v>583</v>
       </c>
       <c r="Q78">
         <v>0</v>
       </c>
       <c r="T78" t="s">
-        <v>601</v>
+        <v>584</v>
       </c>
       <c r="U78">
         <v>0.25</v>
       </c>
       <c r="V78">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
       <c r="W78">
         <v>1</v>
       </c>
       <c r="X78" t="s">
-        <v>602</v>
+        <v>585</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="B79" t="s">
-        <v>604</v>
+        <v>587</v>
       </c>
       <c r="C79" t="s">
         <v>29</v>
       </c>
       <c r="D79" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="E79">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="G79">
         <v>1</v>
       </c>
       <c r="H79" t="s">
-        <v>606</v>
+        <v>589</v>
       </c>
       <c r="I79">
         <v>0</v>
       </c>
       <c r="L79" t="s">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="M79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N79">
-        <v>0.92307692307692313</v>
+        <v>1</v>
       </c>
       <c r="O79">
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>153</v>
+        <v>591</v>
       </c>
       <c r="Q79">
         <v>0</v>
       </c>
       <c r="T79" t="s">
-        <v>608</v>
+        <v>592</v>
       </c>
       <c r="U79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V79">
         <v>1</v>
@@ -10110,7 +10042,7 @@
         <v>1</v>
       </c>
       <c r="X79" t="s">
-        <v>609</v>
+        <v>593</v>
       </c>
       <c r="Y79">
         <v>0</v>
@@ -10118,143 +10050,140 @@
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="B80" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="C80" t="s">
         <v>29</v>
       </c>
       <c r="D80" t="s">
-        <v>612</v>
+        <v>596</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="F80">
-        <v>0.90909090909090906</v>
+        <v>1</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80" t="s">
-        <v>613</v>
+        <v>597</v>
       </c>
       <c r="I80">
         <v>0</v>
       </c>
       <c r="L80" t="s">
-        <v>614</v>
+        <v>598</v>
       </c>
       <c r="M80">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="N80">
-        <v>1</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="O80">
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="Q80">
         <v>0</v>
       </c>
       <c r="T80" t="s">
-        <v>616</v>
+        <v>600</v>
       </c>
       <c r="U80">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="V80">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="W80">
         <v>1</v>
       </c>
       <c r="X80" t="s">
-        <v>617</v>
+        <v>601</v>
       </c>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>618</v>
+        <v>602</v>
       </c>
       <c r="B81" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="C81" t="s">
         <v>29</v>
       </c>
       <c r="D81" t="s">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="E81">
         <v>0</v>
       </c>
       <c r="F81">
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="G81">
         <v>1</v>
       </c>
       <c r="H81" t="s">
-        <v>621</v>
+        <v>605</v>
       </c>
       <c r="I81">
         <v>0</v>
       </c>
       <c r="L81" t="s">
-        <v>622</v>
+        <v>606</v>
       </c>
       <c r="M81">
         <v>0</v>
       </c>
       <c r="N81">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O81">
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>623</v>
+        <v>607</v>
       </c>
       <c r="Q81">
         <v>0</v>
       </c>
       <c r="T81" t="s">
-        <v>624</v>
+        <v>608</v>
       </c>
       <c r="U81">
         <v>0</v>
       </c>
       <c r="V81">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="W81">
         <v>1</v>
       </c>
       <c r="X81" t="s">
-        <v>625</v>
-      </c>
-      <c r="Y81">
-        <v>0</v>
+        <v>609</v>
       </c>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>626</v>
+        <v>610</v>
       </c>
       <c r="B82" t="s">
-        <v>627</v>
+        <v>611</v>
       </c>
       <c r="C82" t="s">
         <v>29</v>
       </c>
       <c r="D82" t="s">
-        <v>628</v>
+        <v>612</v>
       </c>
       <c r="E82">
         <v>0.75</v>
@@ -10266,34 +10195,34 @@
         <v>1</v>
       </c>
       <c r="H82" t="s">
-        <v>629</v>
+        <v>613</v>
       </c>
       <c r="I82">
         <v>0</v>
       </c>
       <c r="L82" t="s">
-        <v>630</v>
+        <v>614</v>
       </c>
       <c r="M82">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="N82">
-        <v>0.88888888888888884</v>
+        <v>1</v>
       </c>
       <c r="O82">
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="Q82">
         <v>0</v>
       </c>
       <c r="T82" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="U82">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="V82">
         <v>1</v>
@@ -10302,86 +10231,86 @@
         <v>1</v>
       </c>
       <c r="X82" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="B83" t="s">
-        <v>635</v>
+        <v>619</v>
       </c>
       <c r="C83" t="s">
         <v>29</v>
       </c>
       <c r="D83" t="s">
-        <v>636</v>
+        <v>620</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+      <c r="H83" t="s">
+        <v>621</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="L83" t="s">
+        <v>622</v>
+      </c>
+      <c r="M83">
         <v>0.5</v>
       </c>
-      <c r="G83">
-        <v>1</v>
-      </c>
-      <c r="H83" t="s">
-        <v>637</v>
-      </c>
-      <c r="I83">
-        <v>0</v>
-      </c>
-      <c r="L83" t="s">
-        <v>638</v>
-      </c>
-      <c r="M83">
-        <v>0</v>
-      </c>
       <c r="N83">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O83">
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>639</v>
+        <v>147</v>
       </c>
       <c r="Q83">
         <v>0</v>
       </c>
       <c r="T83" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="V83">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W83">
         <v>1</v>
       </c>
       <c r="X83" t="s">
-        <v>641</v>
+        <v>624</v>
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>642</v>
+        <v>625</v>
       </c>
       <c r="B84" t="s">
-        <v>643</v>
+        <v>626</v>
       </c>
       <c r="C84" t="s">
         <v>29</v>
       </c>
       <c r="D84" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="E84">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F84">
         <v>1</v>
@@ -10390,57 +10319,57 @@
         <v>1</v>
       </c>
       <c r="H84" t="s">
-        <v>645</v>
+        <v>628</v>
       </c>
       <c r="I84">
         <v>0</v>
       </c>
       <c r="L84" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O84">
+        <v>1</v>
+      </c>
+      <c r="P84" t="s">
+        <v>630</v>
+      </c>
+      <c r="Q84">
+        <v>0</v>
+      </c>
+      <c r="T84" t="s">
+        <v>631</v>
+      </c>
+      <c r="U84">
+        <v>0</v>
+      </c>
+      <c r="V84">
         <v>0.5</v>
       </c>
-      <c r="N84">
-        <v>1</v>
-      </c>
-      <c r="O84">
-        <v>1</v>
-      </c>
-      <c r="P84" t="s">
-        <v>647</v>
-      </c>
-      <c r="Q84">
-        <v>0</v>
-      </c>
-      <c r="T84" t="s">
-        <v>648</v>
-      </c>
-      <c r="U84">
-        <v>1</v>
-      </c>
-      <c r="V84">
-        <v>1</v>
-      </c>
       <c r="W84">
         <v>1</v>
       </c>
       <c r="X84" t="s">
-        <v>649</v>
+        <v>632</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>650</v>
+        <v>633</v>
       </c>
       <c r="B85" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="C85" t="s">
         <v>29</v>
       </c>
       <c r="D85" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="E85">
         <v>1</v>
@@ -10452,16 +10381,16 @@
         <v>1</v>
       </c>
       <c r="H85" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="I85">
         <v>0</v>
       </c>
       <c r="L85" t="s">
-        <v>654</v>
+        <v>637</v>
       </c>
       <c r="M85">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N85">
         <v>1</v>
@@ -10470,16 +10399,16 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>153</v>
+        <v>638</v>
       </c>
       <c r="Q85">
         <v>0</v>
       </c>
       <c r="T85" t="s">
-        <v>655</v>
+        <v>639</v>
       </c>
       <c r="U85">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="V85">
         <v>1</v>
@@ -10488,101 +10417,104 @@
         <v>1</v>
       </c>
       <c r="X85" t="s">
-        <v>656</v>
+        <v>640</v>
+      </c>
+      <c r="Y85">
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
       <c r="B86" t="s">
-        <v>658</v>
+        <v>642</v>
       </c>
       <c r="C86" t="s">
         <v>29</v>
       </c>
       <c r="D86" t="s">
-        <v>659</v>
+        <v>643</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="G86">
         <v>1</v>
       </c>
       <c r="H86" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="I86">
         <v>0</v>
       </c>
       <c r="L86" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
       <c r="M86">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="N86">
-        <v>0.33333333333333331</v>
+        <v>0.875</v>
       </c>
       <c r="O86">
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>662</v>
+        <v>646</v>
       </c>
       <c r="Q86">
         <v>0</v>
       </c>
       <c r="T86" t="s">
-        <v>663</v>
+        <v>647</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V86">
-        <v>0.5</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W86">
         <v>1</v>
       </c>
       <c r="X86" t="s">
-        <v>664</v>
+        <v>648</v>
       </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>665</v>
+        <v>649</v>
       </c>
       <c r="B87" t="s">
-        <v>666</v>
+        <v>650</v>
       </c>
       <c r="C87" t="s">
         <v>29</v>
       </c>
       <c r="D87" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
       <c r="E87">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="G87">
         <v>1</v>
       </c>
       <c r="H87" t="s">
-        <v>668</v>
+        <v>652</v>
       </c>
       <c r="I87">
         <v>0</v>
       </c>
       <c r="L87" t="s">
-        <v>669</v>
+        <v>653</v>
       </c>
       <c r="M87">
         <v>1</v>
@@ -10594,206 +10526,203 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>670</v>
+        <v>654</v>
       </c>
       <c r="Q87">
         <v>0</v>
       </c>
       <c r="T87" t="s">
-        <v>671</v>
+        <v>655</v>
       </c>
       <c r="U87">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="V87">
-        <v>1</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="W87">
         <v>1</v>
       </c>
       <c r="X87" t="s">
-        <v>672</v>
-      </c>
-      <c r="Y87">
-        <v>0</v>
+        <v>656</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>673</v>
+        <v>657</v>
       </c>
       <c r="B88" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="C88" t="s">
         <v>29</v>
       </c>
       <c r="D88" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="E88">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F88">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="G88">
         <v>1</v>
       </c>
       <c r="H88" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="I88">
         <v>0</v>
       </c>
       <c r="L88" t="s">
-        <v>677</v>
+        <v>661</v>
       </c>
       <c r="M88">
         <v>0.25</v>
       </c>
       <c r="N88">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="O88">
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="Q88">
         <v>0</v>
       </c>
       <c r="T88" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="U88">
         <v>0.5</v>
       </c>
       <c r="V88">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="W88">
         <v>1</v>
       </c>
       <c r="X88" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>681</v>
+        <v>665</v>
       </c>
       <c r="B89" t="s">
-        <v>682</v>
+        <v>666</v>
       </c>
       <c r="C89" t="s">
         <v>29</v>
       </c>
       <c r="D89" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="E89">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F89">
-        <v>0.83333333333333337</v>
+        <v>0.8</v>
       </c>
       <c r="G89">
         <v>1</v>
       </c>
       <c r="H89" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="I89">
         <v>0</v>
       </c>
       <c r="L89" t="s">
-        <v>685</v>
+        <v>669</v>
       </c>
       <c r="M89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N89">
-        <v>1</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="O89">
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>686</v>
+        <v>670</v>
       </c>
       <c r="Q89">
         <v>0</v>
       </c>
       <c r="T89" t="s">
-        <v>687</v>
+        <v>671</v>
       </c>
       <c r="U89">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="V89">
-        <v>0.77777777777777779</v>
+        <v>1</v>
       </c>
       <c r="W89">
         <v>1</v>
       </c>
       <c r="X89" t="s">
-        <v>688</v>
+        <v>672</v>
       </c>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>689</v>
+        <v>673</v>
       </c>
       <c r="B90" t="s">
-        <v>690</v>
+        <v>674</v>
       </c>
       <c r="C90" t="s">
         <v>29</v>
       </c>
       <c r="D90" t="s">
-        <v>691</v>
+        <v>675</v>
       </c>
       <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+      <c r="H90" t="s">
+        <v>676</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="L90" t="s">
+        <v>677</v>
+      </c>
+      <c r="M90">
+        <v>0.5</v>
+      </c>
+      <c r="N90">
+        <v>1</v>
+      </c>
+      <c r="O90">
+        <v>1</v>
+      </c>
+      <c r="P90" t="s">
+        <v>678</v>
+      </c>
+      <c r="Q90">
+        <v>0</v>
+      </c>
+      <c r="T90" t="s">
+        <v>679</v>
+      </c>
+      <c r="U90">
         <v>0.25</v>
       </c>
-      <c r="F90">
-        <v>1</v>
-      </c>
-      <c r="G90">
-        <v>1</v>
-      </c>
-      <c r="H90" t="s">
-        <v>692</v>
-      </c>
-      <c r="I90">
-        <v>0</v>
-      </c>
-      <c r="L90" t="s">
-        <v>693</v>
-      </c>
-      <c r="M90">
-        <v>0.25</v>
-      </c>
-      <c r="N90">
-        <v>1</v>
-      </c>
-      <c r="O90">
-        <v>1</v>
-      </c>
-      <c r="P90" t="s">
-        <v>694</v>
-      </c>
-      <c r="Q90">
-        <v>0</v>
-      </c>
-      <c r="T90" t="s">
-        <v>695</v>
-      </c>
-      <c r="U90">
-        <v>0.5</v>
-      </c>
       <c r="V90">
         <v>1</v>
       </c>
@@ -10801,60 +10730,63 @@
         <v>1</v>
       </c>
       <c r="X90" t="s">
-        <v>696</v>
+        <v>680</v>
+      </c>
+      <c r="Y90">
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>697</v>
+        <v>681</v>
       </c>
       <c r="B91" t="s">
-        <v>698</v>
+        <v>682</v>
       </c>
       <c r="C91" t="s">
         <v>29</v>
       </c>
       <c r="D91" t="s">
-        <v>699</v>
+        <v>683</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F91">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G91">
         <v>1</v>
       </c>
       <c r="H91" t="s">
-        <v>700</v>
+        <v>684</v>
       </c>
       <c r="I91">
         <v>0</v>
       </c>
       <c r="L91" t="s">
-        <v>701</v>
+        <v>685</v>
       </c>
       <c r="M91">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="N91">
-        <v>0.61538461538461542</v>
+        <v>1</v>
       </c>
       <c r="O91">
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>702</v>
+        <v>686</v>
       </c>
       <c r="Q91">
         <v>0</v>
       </c>
       <c r="T91" t="s">
-        <v>703</v>
+        <v>687</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V91">
         <v>1</v>
@@ -10863,24 +10795,24 @@
         <v>1</v>
       </c>
       <c r="X91" t="s">
-        <v>704</v>
+        <v>688</v>
       </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>705</v>
+        <v>689</v>
       </c>
       <c r="B92" t="s">
-        <v>706</v>
+        <v>690</v>
       </c>
       <c r="C92" t="s">
         <v>29</v>
       </c>
       <c r="D92" t="s">
-        <v>707</v>
+        <v>691</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F92">
         <v>1</v>
@@ -10889,35 +10821,35 @@
         <v>1</v>
       </c>
       <c r="H92" t="s">
-        <v>708</v>
+        <v>692</v>
       </c>
       <c r="I92">
         <v>0</v>
       </c>
       <c r="L92" t="s">
-        <v>709</v>
+        <v>693</v>
       </c>
       <c r="M92">
+        <v>1</v>
+      </c>
+      <c r="N92">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="O92">
+        <v>1</v>
+      </c>
+      <c r="P92" t="s">
+        <v>694</v>
+      </c>
+      <c r="Q92">
+        <v>0</v>
+      </c>
+      <c r="T92" t="s">
+        <v>695</v>
+      </c>
+      <c r="U92">
         <v>0.5</v>
       </c>
-      <c r="N92">
-        <v>1</v>
-      </c>
-      <c r="O92">
-        <v>1</v>
-      </c>
-      <c r="P92" t="s">
-        <v>710</v>
-      </c>
-      <c r="Q92">
-        <v>0</v>
-      </c>
-      <c r="T92" t="s">
-        <v>711</v>
-      </c>
-      <c r="U92">
-        <v>0.25</v>
-      </c>
       <c r="V92">
         <v>1</v>
       </c>
@@ -10925,125 +10857,122 @@
         <v>1</v>
       </c>
       <c r="X92" t="s">
-        <v>712</v>
-      </c>
-      <c r="Y92">
-        <v>0</v>
+        <v>696</v>
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="B93" t="s">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="C93" t="s">
         <v>29</v>
       </c>
       <c r="D93" t="s">
-        <v>715</v>
+        <v>699</v>
       </c>
       <c r="E93">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F93">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G93">
         <v>1</v>
       </c>
       <c r="H93" t="s">
-        <v>716</v>
+        <v>700</v>
       </c>
       <c r="I93">
         <v>0</v>
       </c>
       <c r="L93" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="M93">
-        <v>0.75</v>
-      </c>
-      <c r="N93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O93">
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>718</v>
+        <v>702</v>
       </c>
       <c r="Q93">
         <v>0</v>
       </c>
       <c r="T93" t="s">
-        <v>719</v>
+        <v>703</v>
       </c>
       <c r="U93">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="V93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W93">
         <v>1</v>
       </c>
       <c r="X93" t="s">
-        <v>720</v>
+        <v>704</v>
+      </c>
+      <c r="Y93">
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>721</v>
+        <v>705</v>
       </c>
       <c r="B94" t="s">
-        <v>722</v>
+        <v>706</v>
       </c>
       <c r="C94" t="s">
         <v>29</v>
       </c>
       <c r="D94" t="s">
-        <v>723</v>
+        <v>707</v>
       </c>
       <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="F94">
         <v>0.5</v>
       </c>
-      <c r="F94">
-        <v>1</v>
-      </c>
       <c r="G94">
         <v>1</v>
       </c>
       <c r="H94" t="s">
-        <v>724</v>
+        <v>708</v>
       </c>
       <c r="I94">
         <v>0</v>
       </c>
       <c r="L94" t="s">
-        <v>725</v>
+        <v>707</v>
       </c>
       <c r="M94">
         <v>1</v>
       </c>
       <c r="N94">
-        <v>0.83333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="O94">
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>726</v>
+        <v>709</v>
       </c>
       <c r="Q94">
         <v>0</v>
       </c>
       <c r="T94" t="s">
-        <v>727</v>
+        <v>710</v>
       </c>
       <c r="U94">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="V94">
         <v>1</v>
@@ -11052,66 +10981,69 @@
         <v>1</v>
       </c>
       <c r="X94" t="s">
-        <v>728</v>
+        <v>711</v>
       </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>729</v>
+        <v>712</v>
       </c>
       <c r="B95" t="s">
-        <v>730</v>
+        <v>713</v>
       </c>
       <c r="C95" t="s">
         <v>29</v>
       </c>
       <c r="D95" t="s">
-        <v>731</v>
+        <v>714</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="F95">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G95">
         <v>1</v>
       </c>
       <c r="H95" t="s">
-        <v>732</v>
+        <v>715</v>
       </c>
       <c r="I95">
         <v>0</v>
       </c>
       <c r="L95" t="s">
-        <v>733</v>
+        <v>716</v>
       </c>
       <c r="M95">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N95">
+        <v>1</v>
       </c>
       <c r="O95">
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>734</v>
+        <v>717</v>
       </c>
       <c r="Q95">
         <v>0</v>
       </c>
       <c r="T95" t="s">
-        <v>735</v>
+        <v>718</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W95">
         <v>1</v>
       </c>
       <c r="X95" t="s">
-        <v>736</v>
+        <v>719</v>
       </c>
       <c r="Y95">
         <v>0</v>
@@ -11119,52 +11051,52 @@
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>737</v>
+        <v>720</v>
       </c>
       <c r="B96" t="s">
-        <v>738</v>
+        <v>721</v>
       </c>
       <c r="C96" t="s">
         <v>29</v>
       </c>
       <c r="D96" t="s">
-        <v>739</v>
+        <v>722</v>
       </c>
       <c r="E96">
         <v>1</v>
       </c>
       <c r="F96">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G96">
         <v>1</v>
       </c>
       <c r="H96" t="s">
-        <v>740</v>
+        <v>723</v>
       </c>
       <c r="I96">
         <v>0</v>
       </c>
       <c r="L96" t="s">
-        <v>739</v>
+        <v>724</v>
       </c>
       <c r="M96">
         <v>1</v>
       </c>
       <c r="N96">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O96">
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>741</v>
+        <v>725</v>
       </c>
       <c r="Q96">
         <v>0</v>
       </c>
       <c r="T96" t="s">
-        <v>742</v>
+        <v>726</v>
       </c>
       <c r="U96">
         <v>1</v>
@@ -11176,60 +11108,60 @@
         <v>1</v>
       </c>
       <c r="X96" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>744</v>
+        <v>728</v>
       </c>
       <c r="B97" t="s">
-        <v>745</v>
+        <v>729</v>
       </c>
       <c r="C97" t="s">
         <v>29</v>
       </c>
       <c r="D97" t="s">
-        <v>746</v>
+        <v>730</v>
       </c>
       <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+      <c r="H97" t="s">
+        <v>731</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="L97" t="s">
+        <v>732</v>
+      </c>
+      <c r="M97">
         <v>0.75</v>
       </c>
-      <c r="F97">
-        <v>1</v>
-      </c>
-      <c r="G97">
-        <v>1</v>
-      </c>
-      <c r="H97" t="s">
-        <v>747</v>
-      </c>
-      <c r="I97">
-        <v>0</v>
-      </c>
-      <c r="L97" t="s">
-        <v>748</v>
-      </c>
-      <c r="M97">
-        <v>1</v>
-      </c>
       <c r="N97">
-        <v>1</v>
+        <v>0.52941176470588236</v>
       </c>
       <c r="O97">
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>749</v>
+        <v>733</v>
       </c>
       <c r="Q97">
         <v>0</v>
       </c>
       <c r="T97" t="s">
-        <v>750</v>
+        <v>734</v>
       </c>
       <c r="U97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V97">
         <v>1</v>
@@ -11238,7 +11170,7 @@
         <v>1</v>
       </c>
       <c r="X97" t="s">
-        <v>751</v>
+        <v>735</v>
       </c>
       <c r="Y97">
         <v>0</v>
@@ -11246,37 +11178,37 @@
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>752</v>
+        <v>736</v>
       </c>
       <c r="B98" t="s">
-        <v>753</v>
+        <v>737</v>
       </c>
       <c r="C98" t="s">
         <v>29</v>
       </c>
       <c r="D98" t="s">
-        <v>754</v>
+        <v>738</v>
       </c>
       <c r="E98">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F98">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G98">
         <v>1</v>
       </c>
       <c r="H98" t="s">
-        <v>755</v>
+        <v>739</v>
       </c>
       <c r="I98">
         <v>0</v>
       </c>
       <c r="L98" t="s">
-        <v>756</v>
+        <v>740</v>
       </c>
       <c r="M98">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="N98">
         <v>1</v>
@@ -11285,13 +11217,13 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>757</v>
+        <v>741</v>
       </c>
       <c r="Q98">
         <v>0</v>
       </c>
       <c r="T98" t="s">
-        <v>758</v>
+        <v>742</v>
       </c>
       <c r="U98">
         <v>1</v>
@@ -11303,21 +11235,21 @@
         <v>1</v>
       </c>
       <c r="X98" t="s">
-        <v>759</v>
+        <v>743</v>
       </c>
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>760</v>
+        <v>744</v>
       </c>
       <c r="B99" t="s">
-        <v>761</v>
+        <v>745</v>
       </c>
       <c r="C99" t="s">
         <v>29</v>
       </c>
       <c r="D99" t="s">
-        <v>762</v>
+        <v>746</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -11329,31 +11261,31 @@
         <v>1</v>
       </c>
       <c r="H99" t="s">
-        <v>763</v>
+        <v>747</v>
       </c>
       <c r="I99">
         <v>0</v>
       </c>
       <c r="L99" t="s">
-        <v>764</v>
+        <v>748</v>
       </c>
       <c r="M99">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="N99">
-        <v>0.52941176470588236</v>
+        <v>0.9</v>
       </c>
       <c r="O99">
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="T99" t="s">
-        <v>766</v>
+        <v>750</v>
       </c>
       <c r="U99">
         <v>0</v>
@@ -11365,89 +11297,89 @@
         <v>1</v>
       </c>
       <c r="X99" t="s">
-        <v>767</v>
-      </c>
-      <c r="Y99">
-        <v>0</v>
+        <v>751</v>
       </c>
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>768</v>
+        <v>801</v>
       </c>
       <c r="B100" t="s">
-        <v>769</v>
+        <v>802</v>
       </c>
       <c r="C100" t="s">
         <v>29</v>
       </c>
       <c r="D100" t="s">
-        <v>770</v>
+        <v>803</v>
       </c>
       <c r="E100">
+        <v>1</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>0.5</v>
+      </c>
+      <c r="H100" t="s">
+        <v>804</v>
+      </c>
+      <c r="I100">
+        <v>0.5</v>
+      </c>
+      <c r="L100" t="s">
+        <v>805</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>1</v>
+      </c>
+      <c r="O100">
+        <v>1</v>
+      </c>
+      <c r="P100" t="s">
+        <v>806</v>
+      </c>
+      <c r="Q100">
+        <v>0.5</v>
+      </c>
+      <c r="T100" t="s">
+        <v>807</v>
+      </c>
+      <c r="U100">
         <v>0.75</v>
       </c>
-      <c r="F100">
-        <v>0.5</v>
-      </c>
-      <c r="G100">
-        <v>1</v>
-      </c>
-      <c r="H100" t="s">
-        <v>771</v>
-      </c>
-      <c r="I100">
-        <v>0</v>
-      </c>
-      <c r="L100" t="s">
-        <v>772</v>
-      </c>
-      <c r="M100">
-        <v>0.75</v>
-      </c>
-      <c r="N100">
-        <v>1</v>
-      </c>
-      <c r="O100">
-        <v>1</v>
-      </c>
-      <c r="P100" t="s">
-        <v>773</v>
-      </c>
-      <c r="Q100">
-        <v>0</v>
-      </c>
-      <c r="T100" t="s">
-        <v>774</v>
-      </c>
-      <c r="U100">
-        <v>1</v>
-      </c>
       <c r="V100">
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="W100">
         <v>1</v>
       </c>
       <c r="X100" t="s">
-        <v>775</v>
+        <v>808</v>
+      </c>
+      <c r="Y100">
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>776</v>
+        <v>809</v>
       </c>
       <c r="B101" t="s">
-        <v>777</v>
+        <v>810</v>
       </c>
       <c r="C101" t="s">
         <v>29</v>
       </c>
       <c r="D101" t="s">
-        <v>778</v>
+        <v>811</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101">
         <v>1</v>
@@ -11456,34 +11388,34 @@
         <v>1</v>
       </c>
       <c r="H101" t="s">
-        <v>779</v>
+        <v>812</v>
       </c>
       <c r="I101">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L101" t="s">
-        <v>780</v>
+        <v>813</v>
       </c>
       <c r="M101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N101">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O101">
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>781</v>
+        <v>814</v>
       </c>
       <c r="Q101">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="T101" t="s">
-        <v>782</v>
+        <v>815</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V101">
         <v>1</v>
@@ -11492,7 +11424,7 @@
         <v>1</v>
       </c>
       <c r="X101" t="s">
-        <v>783</v>
+        <v>816</v>
       </c>
     </row>
   </sheetData>
